--- a/test-data/hk212_hala/outputs/sequential_list/hk212_sequential_list.xlsx
+++ b/test-data/hk212_hala/outputs/sequential_list/hk212_sequential_list.xlsx
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I208"/>
+  <dimension ref="A1:J208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -528,10 +528,11 @@
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="70" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="55" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -577,6 +578,11 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>Vzorec / Zdroj výměry</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Pozn.</t>
         </is>
       </c>
@@ -626,7 +632,12 @@
       <c r="H4" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="I4" s="5" t="inlineStr"/>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>paušál (Rožmitál URS 00511 R)</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -659,7 +670,12 @@
       <c r="H5" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="I5" s="8" t="inlineStr"/>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>placeholder ~200 bm trasování sítí na pozemku</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -699,7 +715,12 @@
       <c r="H7" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="I7" s="8" t="inlineStr"/>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>1 kpl pro všech 8-12 správců sítí (per RE-RUN §6)  [výkres:C3]</t>
+        </is>
+      </c>
+      <c r="J7" s="9" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -739,7 +760,12 @@
       <c r="H9" s="4" t="n">
         <v>150</v>
       </c>
-      <c r="I9" s="5" t="inlineStr"/>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>placeholder ~150 bm (perimetr staveniště + pomocné plochy)</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -779,7 +805,12 @@
       <c r="H11" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="I11" s="5" t="inlineStr"/>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>4 měsíců × 1 ks</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="10" t="n">
@@ -812,7 +843,12 @@
       <c r="H12" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="I12" s="11" t="inlineStr"/>
+      <c r="I12" s="12" t="inlineStr">
+        <is>
+          <t>4 měsíců × 1 ks</t>
+        </is>
+      </c>
+      <c r="J12" s="12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -845,7 +881,12 @@
       <c r="H13" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="I13" s="5" t="inlineStr"/>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>4 měsíců × 1 ks</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -885,7 +926,12 @@
       <c r="H15" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="I15" s="8" t="inlineStr"/>
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t>2 ks × 4 měsíců</t>
+        </is>
+      </c>
+      <c r="J15" s="9" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -925,7 +971,12 @@
       <c r="H17" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="I17" s="5" t="inlineStr"/>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>paušál</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -958,7 +1009,12 @@
       <c r="H18" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="I18" s="8" t="inlineStr"/>
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>paušál</t>
+        </is>
+      </c>
+      <c r="J18" s="9" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -998,7 +1054,12 @@
       <c r="H20" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="I20" s="5" t="inlineStr"/>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>paušál</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -1031,7 +1092,12 @@
       <c r="H21" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="I21" s="8" t="inlineStr"/>
+      <c r="I21" s="9" t="inlineStr">
+        <is>
+          <t>4 měsíců</t>
+        </is>
+      </c>
+      <c r="J21" s="9" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
@@ -1071,7 +1137,12 @@
       <c r="H23" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="I23" s="5" t="inlineStr"/>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>paušál</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -1111,7 +1182,12 @@
       <c r="H25" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="I25" s="8" t="inlineStr"/>
+      <c r="I25" s="9" t="inlineStr">
+        <is>
+          <t>2 ks (TZ B m.7.b)  [výkres:C3, TZ:chapter]</t>
+        </is>
+      </c>
+      <c r="J25" s="9" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
@@ -1144,7 +1220,12 @@
       <c r="H26" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="I26" s="8" t="inlineStr"/>
+      <c r="I26" s="9" t="inlineStr">
+        <is>
+          <t>placeholder 5 ks (TZ B m.7.b)  [výkres:C3, TZ:B]</t>
+        </is>
+      </c>
+      <c r="J26" s="9" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
@@ -1177,7 +1258,12 @@
       <c r="H27" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="I27" s="5" t="inlineStr"/>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>2 vzrostlé + 5 drobné = 7 pařezů</t>
+        </is>
+      </c>
+      <c r="J27" s="6" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
@@ -1210,7 +1296,12 @@
       <c r="H28" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="I28" s="8" t="inlineStr"/>
+      <c r="I28" s="9" t="inlineStr">
+        <is>
+          <t>placeholder ~6 m³ dřevní hmoty</t>
+        </is>
+      </c>
+      <c r="J28" s="9" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
@@ -1250,7 +1341,12 @@
       <c r="H30" s="7" t="n">
         <v>540</v>
       </c>
-      <c r="I30" s="8" t="inlineStr">
+      <c r="I30" s="9" t="inlineStr">
+        <is>
+          <t>placeholder ~540 m² (z C3 situace + plocha pod halou)  [výkres:C3, phase:Phase 0b RE-RUN §3.10]</t>
+        </is>
+      </c>
+      <c r="J30" s="9" t="inlineStr">
         <is>
           <t>ABMV:ABMV_17</t>
         </is>
@@ -1287,7 +1383,12 @@
       <c r="H31" s="10" t="n">
         <v>80</v>
       </c>
-      <c r="I31" s="11" t="inlineStr">
+      <c r="I31" s="12" t="inlineStr">
+        <is>
+          <t>placeholder 540 m² × 0.25 m × 2 t/m³ × 30% = ~80 t</t>
+        </is>
+      </c>
+      <c r="J31" s="12" t="inlineStr">
         <is>
           <t>ABMV:ABMV_17</t>
         </is>
@@ -1324,7 +1425,11 @@
       <c r="H32" s="4" t="n">
         <v>80</v>
       </c>
-      <c r="I32" s="5" t="inlineStr">
+      <c r="I32" s="6">
+        <f> nakládání suti</f>
+        <v/>
+      </c>
+      <c r="J32" s="6" t="inlineStr">
         <is>
           <t>ABMV:ABMV_17</t>
         </is>
@@ -1375,7 +1480,12 @@
       <c r="H35" s="4" t="n">
         <v>210</v>
       </c>
-      <c r="I35" s="5" t="inlineStr"/>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>Zone-by-zone: 100 + 24 + 54 + 7 + 25 = 210 m³ (main_floor + perimeter_pas + patky_pits + kanalizace + svahy_rezerva)  [výkres:A102, TZ:10.g, phase:Phase 0b RE-RUN §3.10]  · was TBD: DXF layer scan A106/A201 for exact po…</t>
+        </is>
+      </c>
+      <c r="J35" s="6" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
@@ -1415,7 +1525,12 @@
       <c r="H37" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="I37" s="8" t="inlineStr">
+      <c r="I37" s="9" t="inlineStr">
+        <is>
+          <t>2 křížení × 5 m délka × 1.5 m š × 2.0 m h  [výkres:A201, TZ:10.g]</t>
+        </is>
+      </c>
+      <c r="J37" s="9" t="inlineStr">
         <is>
           <t>ABMV:ABMV_17</t>
         </is>
@@ -1452,7 +1567,11 @@
       <c r="H38" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="I38" s="8" t="inlineStr">
+      <c r="I38" s="9">
+        <f> ruční výkop u sítí (m³)</f>
+        <v/>
+      </c>
+      <c r="J38" s="9" t="inlineStr">
         <is>
           <t>ABMV:ABMV_17</t>
         </is>
@@ -1496,7 +1615,12 @@
       <c r="H40" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="I40" s="5" t="inlineStr">
+      <c r="I40" s="6" t="inlineStr">
+        <is>
+          <t>placeholder ~5 m³ (úsek 5 m × tlouš. 0.3 m × š. 0.8 m + ofset)  [výkres:A201, TZ:10.g]</t>
+        </is>
+      </c>
+      <c r="J40" s="6" t="inlineStr">
         <is>
           <t>ABMV:ABMV_17</t>
         </is>
@@ -1533,7 +1657,12 @@
       <c r="H41" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="I41" s="11" t="inlineStr">
+      <c r="I41" s="12" t="inlineStr">
+        <is>
+          <t>placeholder ~5 m³ (úsek 5 m × 0.3 × 0.8 + ofset)  [výkres:A201, TZ:10.g]</t>
+        </is>
+      </c>
+      <c r="J41" s="12" t="inlineStr">
         <is>
           <t>ABMV:ABMV_17</t>
         </is>
@@ -1577,7 +1706,12 @@
       <c r="H43" s="7" t="n">
         <v>31.5</v>
       </c>
-      <c r="I43" s="8" t="inlineStr">
+      <c r="I43" s="9" t="inlineStr">
+        <is>
+          <t>14 ks × 1.5 m × 1.5 m × 1.0 m (od úr. figury -0.45 do -1.45/-1.90)  [výkres:A105]</t>
+        </is>
+      </c>
+      <c r="J43" s="9" t="inlineStr">
         <is>
           <t>ABMV:ABMV_17</t>
         </is>
@@ -1614,7 +1748,12 @@
       <c r="H44" s="7" t="n">
         <v>1.28</v>
       </c>
-      <c r="I44" s="8" t="inlineStr">
+      <c r="I44" s="9" t="inlineStr">
+        <is>
+          <t>8 ks × 0.8 × 0.8 × 0.25 m (od figury -0.45 do -0.70)  [výkres:A105]</t>
+        </is>
+      </c>
+      <c r="J44" s="9" t="inlineStr">
         <is>
           <t>ABMV:ABMV_17</t>
         </is>
@@ -1651,7 +1790,12 @@
       <c r="H45" s="7" t="n">
         <v>7.2</v>
       </c>
-      <c r="I45" s="8" t="inlineStr">
+      <c r="I45" s="9" t="inlineStr">
+        <is>
+          <t>~30 bm × 0.4 m × 0.6 m (krátké propojovací pasy)  [výkres:A105, phase:Phase 0b RE-RUN §3.10]</t>
+        </is>
+      </c>
+      <c r="J45" s="9" t="inlineStr">
         <is>
           <t>ABMV:ABMV_17</t>
         </is>
@@ -1695,7 +1839,12 @@
       <c r="H47" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="I47" s="8" t="inlineStr">
+      <c r="I47" s="9" t="inlineStr">
+        <is>
+          <t>placeholder 12 m³ (vrt + zaplnění; variantní řešení per A105 mtext)  [výkres:A105]</t>
+        </is>
+      </c>
+      <c r="J47" s="9" t="inlineStr">
         <is>
           <t>ABMV:ABMV_11,ABMV_17</t>
         </is>
@@ -1732,7 +1881,12 @@
       <c r="H48" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="I48" s="8" t="inlineStr">
+      <c r="I48" s="9" t="inlineStr">
+        <is>
+          <t>placeholder 20 m² (perimetr atypického základu × hloubka)  [csn, phase:Phase 0b RE-RUN §3.10]</t>
+        </is>
+      </c>
+      <c r="J48" s="9" t="inlineStr">
         <is>
           <t>ABMV:ABMV_11,ABMV_17</t>
         </is>
@@ -1776,7 +1930,12 @@
       <c r="H50" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="I50" s="8" t="inlineStr">
+      <c r="I50" s="9" t="inlineStr">
+        <is>
+          <t>cca 16 m × 0.5 m š × 1.0 m h (TZ B m.10.g + RE-RUN §6)</t>
+        </is>
+      </c>
+      <c r="J50" s="9" t="inlineStr">
         <is>
           <t>ABMV:ABMV_17</t>
         </is>
@@ -1813,7 +1972,12 @@
       <c r="H51" s="7" t="n">
         <v>49.2</v>
       </c>
-      <c r="I51" s="8" t="inlineStr">
+      <c r="I51" s="9" t="inlineStr">
+        <is>
+          <t>82 m gravitační × 0.5 m š × 1.2 m h</t>
+        </is>
+      </c>
+      <c r="J51" s="9" t="inlineStr">
         <is>
           <t>ABMV:ABMV_17</t>
         </is>
@@ -1857,7 +2021,11 @@
       <c r="H53" s="7" t="n">
         <v>350</v>
       </c>
-      <c r="I53" s="8" t="inlineStr">
+      <c r="I53" s="9">
+        <f> celkový objem výkopu 350 m³ (Phase 0b baseline)  [phase:Phase 0b RE-RUN §3.10]</f>
+        <v/>
+      </c>
+      <c r="J53" s="9" t="inlineStr">
         <is>
           <t>ABMV:ABMV_17</t>
         </is>
@@ -1894,7 +2062,11 @@
       <c r="H54" s="7" t="n">
         <v>350</v>
       </c>
-      <c r="I54" s="8" t="inlineStr">
+      <c r="I54" s="9">
+        <f> 350 m³ × 1 (default 5 km deponie)</f>
+        <v/>
+      </c>
+      <c r="J54" s="9" t="inlineStr">
         <is>
           <t>ABMV:ABMV_17</t>
         </is>
@@ -1931,7 +2103,11 @@
       <c r="H55" s="7" t="n">
         <v>350</v>
       </c>
-      <c r="I55" s="8" t="inlineStr">
+      <c r="I55" s="9">
+        <f> 350 m³</f>
+        <v/>
+      </c>
+      <c r="J55" s="9" t="inlineStr">
         <is>
           <t>ABMV:ABMV_17</t>
         </is>
@@ -1968,7 +2144,12 @@
       <c r="H56" s="7" t="n">
         <v>630</v>
       </c>
-      <c r="I56" s="8" t="inlineStr">
+      <c r="I56" s="9" t="inlineStr">
+        <is>
+          <t>350 m³ × 1.8 t/m³ (zhutněná zemina)</t>
+        </is>
+      </c>
+      <c r="J56" s="9" t="inlineStr">
         <is>
           <t>ABMV:ABMV_17</t>
         </is>
@@ -2019,7 +2200,12 @@
       <c r="H59" s="4" t="n">
         <v>265.61</v>
       </c>
-      <c r="I59" s="5" t="inlineStr"/>
+      <c r="I59" s="6" t="inlineStr">
+        <is>
+          <t>531.22 m² × 0.5 m = 265.61 m³ × 2 operace  [igp_section:4.4, igp_document:inputs/dokumentace/IGP_ALTAGEO_526026.md, Step3]</t>
+        </is>
+      </c>
+      <c r="J59" s="6" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
@@ -2059,7 +2245,12 @@
       <c r="H61" s="7" t="n">
         <v>123.75</v>
       </c>
-      <c r="I61" s="8" t="inlineStr">
+      <c r="I61" s="9" t="inlineStr">
+        <is>
+          <t>495 m² × 0.25 m  [TZ:B]</t>
+        </is>
+      </c>
+      <c r="J61" s="9" t="inlineStr">
         <is>
           <t>ABMV:ABMV_17</t>
         </is>
@@ -2096,7 +2287,11 @@
       <c r="H62" s="7" t="n">
         <v>495</v>
       </c>
-      <c r="I62" s="8" t="inlineStr">
+      <c r="I62" s="9">
+        <f> plocha desky  [TZ:B]</f>
+        <v/>
+      </c>
+      <c r="J62" s="9" t="inlineStr">
         <is>
           <t>ABMV:ABMV_17</t>
         </is>
@@ -2140,7 +2335,11 @@
       <c r="H64" s="4" t="n">
         <v>495</v>
       </c>
-      <c r="I64" s="5" t="inlineStr"/>
+      <c r="I64" s="6">
+        <f> plocha desky  [TZ:B]</f>
+        <v/>
+      </c>
+      <c r="J64" s="6" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
@@ -2180,7 +2379,12 @@
       <c r="H66" s="7" t="n">
         <v>600</v>
       </c>
-      <c r="I66" s="8" t="inlineStr"/>
+      <c r="I66" s="9" t="inlineStr">
+        <is>
+          <t>placeholder 600 kg per RE-RUN §3.4 statika dimensioning</t>
+        </is>
+      </c>
+      <c r="J66" s="9" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
@@ -2220,7 +2424,12 @@
       <c r="H68" s="7" t="n">
         <v>66</v>
       </c>
-      <c r="I68" s="8" t="inlineStr"/>
+      <c r="I68" s="9" t="inlineStr">
+        <is>
+          <t>10 × (3.6 + 3.0) = 66.0 m²  [výkres:A105, TZ:D.1.2 (statika) — Návrh opláštění, měřeno:A105]</t>
+        </is>
+      </c>
+      <c r="J68" s="9" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="10" t="n">
@@ -2253,7 +2462,12 @@
       <c r="H69" s="10" t="n">
         <v>22.875</v>
       </c>
-      <c r="I69" s="11" t="inlineStr"/>
+      <c r="I69" s="12" t="inlineStr">
+        <is>
+          <t>10 × (1.5²×0.6 + 1.25²×0.6) = 10 × (1.35 + 0.9375) = 22.875 m³  [výkres:A105, TZ:D.1.1 p3, statika:D.1.2 p29-30]</t>
+        </is>
+      </c>
+      <c r="J69" s="12" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
@@ -2286,7 +2500,11 @@
       <c r="H70" s="7" t="n">
         <v>66</v>
       </c>
-      <c r="I70" s="8" t="inlineStr"/>
+      <c r="I70" s="9">
+        <f> HSV-2-002 = 66.0 m²  [TZ:D.1.2 (statika) — Návrh opláštění, měřeno:A105]</f>
+        <v/>
+      </c>
+      <c r="J70" s="9" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
@@ -2326,7 +2544,12 @@
       <c r="H72" s="7" t="n">
         <v>30.72</v>
       </c>
-      <c r="I72" s="8" t="inlineStr"/>
+      <c r="I72" s="9" t="inlineStr">
+        <is>
+          <t>8 × 4 × 0.8 × 1.2 = 30.72 m²  [výkres:A105, tz_typo_resolution]</t>
+        </is>
+      </c>
+      <c r="J72" s="9" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="7" t="n">
@@ -2359,7 +2582,12 @@
       <c r="H73" s="7" t="n">
         <v>6.144</v>
       </c>
-      <c r="I73" s="8" t="inlineStr"/>
+      <c r="I73" s="9" t="inlineStr">
+        <is>
+          <t>8 ks × 0.8 × 0.8 × 1.2 m = 6.144 m³  [výkres:A105, tz_typo_resolution]</t>
+        </is>
+      </c>
+      <c r="J73" s="9" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="7" t="n">
@@ -2392,7 +2620,11 @@
       <c r="H74" s="7" t="n">
         <v>30.72</v>
       </c>
-      <c r="I74" s="8" t="inlineStr"/>
+      <c r="I74" s="9">
+        <f> HSV-2-005 = 30.72 m²  [tz_typo_resolution]</f>
+        <v/>
+      </c>
+      <c r="J74" s="9" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
@@ -2432,7 +2664,12 @@
       <c r="H76" s="7" t="n">
         <v>36</v>
       </c>
-      <c r="I76" s="8" t="inlineStr"/>
+      <c r="I76" s="9" t="inlineStr">
+        <is>
+          <t>~30 bm × 2 × 0.6 m boční plocha = 36 m²  [výkres:A105]</t>
+        </is>
+      </c>
+      <c r="J76" s="9" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="7" t="n">
@@ -2465,7 +2702,12 @@
       <c r="H77" s="7" t="n">
         <v>7.2</v>
       </c>
-      <c r="I77" s="8" t="inlineStr"/>
+      <c r="I77" s="9" t="inlineStr">
+        <is>
+          <t>~30 bm × 0.4 × 0.6 m = 7.2 m³  [výkres:A105]</t>
+        </is>
+      </c>
+      <c r="J77" s="9" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
@@ -2505,7 +2747,12 @@
       <c r="H79" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="I79" s="5" t="inlineStr">
+      <c r="I79" s="6" t="inlineStr">
+        <is>
+          <t>placeholder ~30 m³ (zásypy okolo patek + nad obetonovanými sítěmi)  [phase:Phase 0b RE-RUN §3.10]</t>
+        </is>
+      </c>
+      <c r="J79" s="6" t="inlineStr">
         <is>
           <t>ABMV:ABMV_17</t>
         </is>
@@ -2549,7 +2796,12 @@
       <c r="H81" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="I81" s="8" t="inlineStr"/>
+      <c r="I81" s="9" t="inlineStr">
+        <is>
+          <t>1 ks pilota Ø800 × 8 m délka  [výkres:A105, igp_section:4.3]</t>
+        </is>
+      </c>
+      <c r="J81" s="9" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="7" t="n">
@@ -2582,7 +2834,12 @@
       <c r="H82" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="I82" s="8" t="inlineStr"/>
+      <c r="I82" s="9" t="inlineStr">
+        <is>
+          <t>1 ks × 8 m délka  [výkres:A105, igp_section:4.3]</t>
+        </is>
+      </c>
+      <c r="J82" s="9" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="7" t="n">
@@ -2615,7 +2872,12 @@
       <c r="H83" s="7" t="n">
         <v>380</v>
       </c>
-      <c r="I83" s="8" t="inlineStr"/>
+      <c r="I83" s="9" t="inlineStr">
+        <is>
+          <t>8 ks × 3.86 kg/m × 8 m + třmínky placeholder  [výkres:A105, igp_section:4.3]</t>
+        </is>
+      </c>
+      <c r="J83" s="9" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
@@ -2655,7 +2917,12 @@
       <c r="H85" s="7" t="n">
         <v>95</v>
       </c>
-      <c r="I85" s="8" t="inlineStr"/>
+      <c r="I85" s="9" t="inlineStr">
+        <is>
+          <t>obvod desky ~95 bm  [výkres:A101]</t>
+        </is>
+      </c>
+      <c r="J85" s="9" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="7" t="n">
@@ -2688,7 +2955,11 @@
       <c r="H86" s="7" t="n">
         <v>2098.3</v>
       </c>
-      <c r="I86" s="8" t="inlineStr"/>
+      <c r="I86" s="9">
+        <f> HSV-2-015 = 2098.3 kg  [měřeno:A105]</f>
+        <v/>
+      </c>
+      <c r="J86" s="9" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="4" t="n">
@@ -2721,7 +2992,12 @@
       <c r="H87" s="4" t="n">
         <v>2475</v>
       </c>
-      <c r="I87" s="5" t="inlineStr"/>
+      <c r="I87" s="6" t="inlineStr">
+        <is>
+          <t>495 m² × 5 ks/m² (typická hustota)</t>
+        </is>
+      </c>
+      <c r="J87" s="6" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="7" t="n">
@@ -2754,7 +3030,12 @@
       <c r="H88" s="7" t="n">
         <v>2098.3</v>
       </c>
-      <c r="I88" s="8" t="inlineStr"/>
+      <c r="I88" s="9" t="inlineStr">
+        <is>
+          <t>531.22 × 3.95 = 2098.3 kg  [měřeno:A105]</t>
+        </is>
+      </c>
+      <c r="J88" s="9" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="13" t="n">
@@ -2787,7 +3068,12 @@
       <c r="H89" s="13" t="n">
         <v>106.24</v>
       </c>
-      <c r="I89" s="14" t="inlineStr">
+      <c r="I89" s="15" t="inlineStr">
+        <is>
+          <t>531.22 × 0.20 = 106.24 m³  [TZ:B, měřeno:A105, ABMV]</t>
+        </is>
+      </c>
+      <c r="J89" s="15" t="inlineStr">
         <is>
           <t>rev:beton-class</t>
         </is>
@@ -2838,7 +3124,12 @@
       <c r="H92" s="4" t="n">
         <v>1400</v>
       </c>
-      <c r="I92" s="5" t="inlineStr"/>
+      <c r="I92" s="6" t="inlineStr">
+        <is>
+          <t>28 t × 50 km</t>
+        </is>
+      </c>
+      <c r="J92" s="6" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
@@ -2878,7 +3169,12 @@
       <c r="H94" s="7" t="n">
         <v>176</v>
       </c>
-      <c r="I94" s="8" t="inlineStr"/>
+      <c r="I94" s="9" t="inlineStr">
+        <is>
+          <t>(36 + 8) sloupů × 4 kotvy/sloup = 176 ks  [výkres:A105]</t>
+        </is>
+      </c>
+      <c r="J94" s="9" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
@@ -2918,7 +3214,12 @@
       <c r="H96" s="4" t="n">
         <v>200</v>
       </c>
-      <c r="I96" s="5" t="inlineStr"/>
+      <c r="I96" s="6" t="inlineStr">
+        <is>
+          <t>placeholder ~200 m³ prostorové lešení pro halu 28×19×6 m</t>
+        </is>
+      </c>
+      <c r="J96" s="6" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
@@ -2958,7 +3259,12 @@
       <c r="H98" s="4" t="n">
         <v>10263.24</v>
       </c>
-      <c r="I98" s="5" t="inlineStr"/>
+      <c r="I98" s="6" t="inlineStr">
+        <is>
+          <t>36 ks × 4.3 m × 66.3 kg/m = 10 263 kg  [výkres:A101]</t>
+        </is>
+      </c>
+      <c r="J98" s="6" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="7" t="n">
@@ -2991,7 +3297,12 @@
       <c r="H99" s="7" t="n">
         <v>1455.12</v>
       </c>
-      <c r="I99" s="8" t="inlineStr"/>
+      <c r="I99" s="9" t="inlineStr">
+        <is>
+          <t>8 ks × 4.3 m × 42.3 kg/m = 1 455 kg  [výkres:A101]</t>
+        </is>
+      </c>
+      <c r="J99" s="9" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="7" t="n">
@@ -3024,7 +3335,12 @@
       <c r="H100" s="7" t="n">
         <v>9474.959999999999</v>
       </c>
-      <c r="I100" s="8" t="inlineStr"/>
+      <c r="I100" s="9" t="inlineStr">
+        <is>
+          <t>6 rámů × 18.5 m × 77.6 kg/m × 1.1 (náběh) = 9 478 kg</t>
+        </is>
+      </c>
+      <c r="J100" s="9" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="7" t="n">
@@ -3057,7 +3373,12 @@
       <c r="H101" s="7" t="n">
         <v>5195.04</v>
       </c>
-      <c r="I101" s="8" t="inlineStr"/>
+      <c r="I101" s="9" t="inlineStr">
+        <is>
+          <t>12 řad × 27.4 m × 15.8 kg/m = 5 195 kg  [TZ:D.1.2 (statika) — vaznice rozteč]</t>
+        </is>
+      </c>
+      <c r="J101" s="9" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="7" t="n">
@@ -3090,7 +3411,12 @@
       <c r="H102" s="7" t="n">
         <v>1030.24</v>
       </c>
-      <c r="I102" s="8" t="inlineStr">
+      <c r="I102" s="9" t="inlineStr">
+        <is>
+          <t>2 ks × 27.4 m × 18.8 kg/m = 1 030 kg</t>
+        </is>
+      </c>
+      <c r="J102" s="9" t="inlineStr">
         <is>
           <t>ABMV:ABMV_15</t>
         </is>
@@ -3127,7 +3453,12 @@
       <c r="H103" s="7" t="n">
         <v>327.68</v>
       </c>
-      <c r="I103" s="8" t="inlineStr"/>
+      <c r="I103" s="9" t="inlineStr">
+        <is>
+          <t>8 ks × 6.4 m × 6.4 kg/m = 328 kg</t>
+        </is>
+      </c>
+      <c r="J103" s="9" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="7" t="n">
@@ -3160,7 +3491,12 @@
       <c r="H104" s="7" t="n">
         <v>237.12</v>
       </c>
-      <c r="I104" s="8" t="inlineStr"/>
+      <c r="I104" s="9" t="inlineStr">
+        <is>
+          <t>8 ks × 12 m × 2.47 kg/m = 237 kg  [výkres:A101]</t>
+        </is>
+      </c>
+      <c r="J104" s="9" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
@@ -3200,7 +3536,12 @@
       <c r="H106" s="7" t="n">
         <v>1450</v>
       </c>
-      <c r="I106" s="8" t="inlineStr"/>
+      <c r="I106" s="9" t="inlineStr">
+        <is>
+          <t>~6% × součet OK 27 985 kg ≈ 1 450 kg  [csn]</t>
+        </is>
+      </c>
+      <c r="J106" s="9" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
@@ -3240,7 +3581,12 @@
       <c r="H108" s="7" t="n">
         <v>28</v>
       </c>
-      <c r="I108" s="8" t="inlineStr"/>
+      <c r="I108" s="9" t="inlineStr">
+        <is>
+          <t>součet OK profilů + kotev = ~28 t</t>
+        </is>
+      </c>
+      <c r="J108" s="9" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
@@ -3280,7 +3626,11 @@
       <c r="H110" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="I110" s="8" t="inlineStr"/>
+      <c r="I110" s="9">
+        <f> pomocné lešení</f>
+        <v/>
+      </c>
+      <c r="J110" s="9" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
@@ -3320,7 +3670,12 @@
       <c r="H112" s="7" t="n">
         <v>850</v>
       </c>
-      <c r="I112" s="8" t="inlineStr"/>
+      <c r="I112" s="9" t="inlineStr">
+        <is>
+          <t>celk. povrch profilů ~30 m²/t × 28 t = 850 m²  [výkres:C2]</t>
+        </is>
+      </c>
+      <c r="J112" s="9" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="7" t="n">
@@ -3353,7 +3708,11 @@
       <c r="H113" s="7" t="n">
         <v>850</v>
       </c>
-      <c r="I113" s="8" t="inlineStr"/>
+      <c r="I113" s="9">
+        <f> antikor plocha (interiérové prvky stejně)</f>
+        <v/>
+      </c>
+      <c r="J113" s="9" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
@@ -3393,7 +3752,12 @@
       <c r="H115" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="I115" s="8" t="inlineStr"/>
+      <c r="I115" s="9" t="inlineStr">
+        <is>
+          <t>paušál  [csn]</t>
+        </is>
+      </c>
+      <c r="J115" s="9" t="inlineStr"/>
     </row>
     <row r="116" ht="22" customHeight="1">
       <c r="A116" s="2" t="inlineStr">
@@ -3440,7 +3804,12 @@
       <c r="H118" s="7" t="n">
         <v>120</v>
       </c>
-      <c r="I118" s="8" t="inlineStr"/>
+      <c r="I118" s="9" t="inlineStr">
+        <is>
+          <t>placeholder ~120 m³ pojízdné lešení pro obvodový plášť</t>
+        </is>
+      </c>
+      <c r="J118" s="9" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
@@ -3480,7 +3849,12 @@
       <c r="H120" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="I120" s="5" t="inlineStr"/>
+      <c r="I120" s="6" t="inlineStr">
+        <is>
+          <t>paušál  [TZ:D.1.1]</t>
+        </is>
+      </c>
+      <c r="J120" s="6" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
@@ -3520,7 +3894,12 @@
       <c r="H122" s="4" t="n">
         <v>528.5</v>
       </c>
-      <c r="I122" s="5" t="inlineStr">
+      <c r="I122" s="6" t="inlineStr">
+        <is>
+          <t>fasáda netto Step3 v2: 623.3 m² brutto − 94.82 m² otvory (vrata 3.5×4.0 per TZ ARS) = 528.5 m²  [TZ:D.1.1, Step3, ABMV]</t>
+        </is>
+      </c>
+      <c r="J122" s="6" t="inlineStr">
         <is>
           <t>ABMV:ABMV_13</t>
         </is>
@@ -3557,7 +3936,12 @@
       <c r="H123" s="10" t="n">
         <v>528.5</v>
       </c>
-      <c r="I123" s="11" t="inlineStr"/>
+      <c r="I123" s="12" t="inlineStr">
+        <is>
+          <t>fasáda netto Step3 v2: 623.3 m² brutto − 94.82 m² otvory (vrata 3.5×4.0 per TZ ARS) = 528.5 m²  [TZ:D.1.1, ABMV, TZ:D.1.2 (statika) — Návrh opláštění]</t>
+        </is>
+      </c>
+      <c r="J123" s="12" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
@@ -3597,7 +3981,12 @@
       <c r="H125" s="4" t="n">
         <v>558.8</v>
       </c>
-      <c r="I125" s="5" t="inlineStr">
+      <c r="I125" s="6" t="inlineStr">
+        <is>
+          <t>střecha netto Step3: brutto 556.5 m² / cos(5.25°) = 558.8 m²  [TZ:D.1.1, DXF, Step3]</t>
+        </is>
+      </c>
+      <c r="J125" s="6" t="inlineStr">
         <is>
           <t>ABMV:ABMV_13</t>
         </is>
@@ -3634,7 +4023,12 @@
       <c r="H126" s="10" t="n">
         <v>558.8</v>
       </c>
-      <c r="I126" s="11" t="inlineStr"/>
+      <c r="I126" s="12" t="inlineStr">
+        <is>
+          <t>střecha netto Step3 = 558.8 m²  [TZ:D.1.1, TZ:D.1.2 (statika) — Návrh opláštění]</t>
+        </is>
+      </c>
+      <c r="J126" s="12" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
@@ -3674,7 +4068,12 @@
       <c r="H128" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="I128" s="5" t="inlineStr"/>
+      <c r="I128" s="6" t="inlineStr">
+        <is>
+          <t>paušál  [TZ:D.1.1]</t>
+        </is>
+      </c>
+      <c r="J128" s="6" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
@@ -3714,7 +4113,12 @@
       <c r="H130" s="13" t="n">
         <v>207</v>
       </c>
-      <c r="I130" s="14" t="inlineStr">
+      <c r="I130" s="15" t="inlineStr">
+        <is>
+          <t>2 × obvod budovy 103.5 m = 207.0 bm (hrubý odhad atika + parapety)  [TZ:D.1.1, Step3]</t>
+        </is>
+      </c>
+      <c r="J130" s="15" t="inlineStr">
         <is>
           <t>rev:qty</t>
         </is>
@@ -3758,7 +4162,12 @@
       <c r="H132" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="I132" s="5" t="inlineStr"/>
+      <c r="I132" s="6" t="inlineStr">
+        <is>
+          <t>paušál  [TZ:D.1.1]</t>
+        </is>
+      </c>
+      <c r="J132" s="6" t="inlineStr"/>
     </row>
     <row r="133" ht="22" customHeight="1">
       <c r="A133" s="2" t="inlineStr">
@@ -3805,7 +4214,12 @@
       <c r="H135" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="I135" s="5" t="inlineStr"/>
+      <c r="I135" s="6" t="inlineStr">
+        <is>
+          <t>paušál</t>
+        </is>
+      </c>
+      <c r="J135" s="6" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
@@ -3845,7 +4259,12 @@
       <c r="H137" s="7" t="n">
         <v>95</v>
       </c>
-      <c r="I137" s="8" t="inlineStr"/>
+      <c r="I137" s="9" t="inlineStr">
+        <is>
+          <t>obvod střechy 95.0 bm  [TZ:B]</t>
+        </is>
+      </c>
+      <c r="J137" s="9" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="7" t="n">
@@ -3878,7 +4297,12 @@
       <c r="H138" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="I138" s="8" t="inlineStr"/>
+      <c r="I138" s="9" t="inlineStr">
+        <is>
+          <t>placeholder ~15 bm (úžlabí pultové střechy 5.25°)</t>
+        </is>
+      </c>
+      <c r="J138" s="9" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="7" t="n">
@@ -3911,7 +4335,12 @@
       <c r="H139" s="7" t="n">
         <v>25.2</v>
       </c>
-      <c r="I139" s="8" t="inlineStr"/>
+      <c r="I139" s="9" t="inlineStr">
+        <is>
+          <t>4 nároží × 6.3 m výška</t>
+        </is>
+      </c>
+      <c r="J139" s="9" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
@@ -3951,7 +4380,12 @@
       <c r="H141" s="7" t="n">
         <v>120</v>
       </c>
-      <c r="I141" s="8" t="inlineStr"/>
+      <c r="I141" s="9" t="inlineStr">
+        <is>
+          <t>placeholder ~120 bm (spáry mezi všemi klempířskými prvky)</t>
+        </is>
+      </c>
+      <c r="J141" s="9" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
@@ -3991,7 +4425,12 @@
       <c r="H143" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="I143" s="5" t="inlineStr">
+      <c r="I143" s="6" t="inlineStr">
+        <is>
+          <t>4 ks (A104 DXF count working, ABMV_20: A101=3 vs A104=4)  [výkres:A104]</t>
+        </is>
+      </c>
+      <c r="J143" s="6" t="inlineStr">
         <is>
           <t>ABMV:ABMV_20</t>
         </is>
@@ -4028,7 +4467,12 @@
       <c r="H144" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="I144" s="8" t="inlineStr">
+      <c r="I144" s="9" t="inlineStr">
+        <is>
+          <t>4 kpl (jeden na každý svod)</t>
+        </is>
+      </c>
+      <c r="J144" s="9" t="inlineStr">
         <is>
           <t>ABMV:ABMV_20</t>
         </is>
@@ -4072,7 +4516,12 @@
       <c r="H146" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="I146" s="8" t="inlineStr"/>
+      <c r="I146" s="9" t="inlineStr">
+        <is>
+          <t>3 ks (A101 INSERT Wavin × 3 dle DXF parse)  [výkres:A101]</t>
+        </is>
+      </c>
+      <c r="J146" s="9" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="7" t="n">
@@ -4105,7 +4554,11 @@
       <c r="H147" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="I147" s="8" t="inlineStr"/>
+      <c r="I147" s="9">
+        <f> dodávka</f>
+        <v/>
+      </c>
+      <c r="J147" s="9" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="3" t="inlineStr">
@@ -4145,7 +4598,12 @@
       <c r="H149" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="I149" s="8" t="inlineStr"/>
+      <c r="I149" s="9" t="inlineStr">
+        <is>
+          <t>~30.0 bm podél JZ + SZ fasády (RE-RUN §3.7)  [výkres:A105]</t>
+        </is>
+      </c>
+      <c r="J149" s="9" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="7" t="n">
@@ -4178,7 +4636,11 @@
       <c r="H150" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="I150" s="8" t="inlineStr"/>
+      <c r="I150" s="9">
+        <f> liniový žlab</f>
+        <v/>
+      </c>
+      <c r="J150" s="9" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
@@ -4218,7 +4680,12 @@
       <c r="H152" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="I152" s="5" t="inlineStr"/>
+      <c r="I152" s="6" t="inlineStr">
+        <is>
+          <t>placeholder ~25 bm (vpusti + prostupy)</t>
+        </is>
+      </c>
+      <c r="J152" s="6" t="inlineStr"/>
     </row>
     <row r="153" ht="22" customHeight="1">
       <c r="A153" s="2" t="inlineStr">
@@ -4265,7 +4732,12 @@
       <c r="H155" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="I155" s="5" t="inlineStr"/>
+      <c r="I155" s="6" t="inlineStr">
+        <is>
+          <t>21 ks (V1..V21 z DXF A101 INSERT OKNO_1k)  [výkres:A101]</t>
+        </is>
+      </c>
+      <c r="J155" s="6" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="10" t="n">
@@ -4298,7 +4770,11 @@
       <c r="H156" s="10" t="n">
         <v>21</v>
       </c>
-      <c r="I156" s="11" t="inlineStr"/>
+      <c r="I156" s="12">
+        <f> dodávka okna</f>
+        <v/>
+      </c>
+      <c r="J156" s="12" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="4" t="n">
@@ -4331,7 +4807,12 @@
       <c r="H157" s="4" t="n">
         <v>22.05</v>
       </c>
-      <c r="I157" s="5" t="inlineStr"/>
+      <c r="I157" s="6" t="inlineStr">
+        <is>
+          <t>21 ks × 1.05 m (šířka okna + přesah)</t>
+        </is>
+      </c>
+      <c r="J157" s="6" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="7" t="n">
@@ -4364,7 +4845,12 @@
       <c r="H158" s="7" t="n">
         <v>63</v>
       </c>
-      <c r="I158" s="8" t="inlineStr"/>
+      <c r="I158" s="9" t="inlineStr">
+        <is>
+          <t>21 ks × 3 bm (perimetr 3 stran, parapet samostatně)</t>
+        </is>
+      </c>
+      <c r="J158" s="9" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="3" t="inlineStr">
@@ -4404,7 +4890,12 @@
       <c r="H160" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="I160" s="5" t="inlineStr"/>
+      <c r="I160" s="6" t="inlineStr">
+        <is>
+          <t>4 ks (DXF A101 INSERT 'Vrata sekční' = 4)  [výkres:A101, TZ:3.2]</t>
+        </is>
+      </c>
+      <c r="J160" s="6" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="7" t="n">
@@ -4437,7 +4928,12 @@
       <c r="H161" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="I161" s="8" t="inlineStr"/>
+      <c r="I161" s="9" t="inlineStr">
+        <is>
+          <t>4 ks pohon (jeden na každá vrata)</t>
+        </is>
+      </c>
+      <c r="J161" s="9" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="7" t="n">
@@ -4470,7 +4966,12 @@
       <c r="H162" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="I162" s="8" t="inlineStr"/>
+      <c r="I162" s="9" t="inlineStr">
+        <is>
+          <t>4 ks ruční odblok</t>
+        </is>
+      </c>
+      <c r="J162" s="9" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="7" t="n">
@@ -4503,7 +5004,11 @@
       <c r="H163" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="I163" s="8" t="inlineStr"/>
+      <c r="I163" s="9">
+        <f> dodávka vrat</f>
+        <v/>
+      </c>
+      <c r="J163" s="9" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="3" t="inlineStr">
@@ -4543,7 +5048,12 @@
       <c r="H165" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="I165" s="8" t="inlineStr"/>
+      <c r="I165" s="9" t="inlineStr">
+        <is>
+          <t>2 ks (DXF A101 INSERT 'Vnější dveře dvoukřídlé')  [výkres:A101]</t>
+        </is>
+      </c>
+      <c r="J165" s="9" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="7" t="n">
@@ -4576,7 +5086,11 @@
       <c r="H166" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="I166" s="8" t="inlineStr"/>
+      <c r="I166" s="9">
+        <f> dodávka dveří</f>
+        <v/>
+      </c>
+      <c r="J166" s="9" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="7" t="n">
@@ -4609,7 +5123,12 @@
       <c r="H167" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="I167" s="8" t="inlineStr"/>
+      <c r="I167" s="9" t="inlineStr">
+        <is>
+          <t>2 kpl</t>
+        </is>
+      </c>
+      <c r="J167" s="9" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="10" t="n">
@@ -4642,7 +5161,12 @@
       <c r="H168" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="I168" s="11" t="inlineStr"/>
+      <c r="I168" s="12" t="inlineStr">
+        <is>
+          <t>2 kpl</t>
+        </is>
+      </c>
+      <c r="J168" s="12" t="inlineStr"/>
     </row>
     <row r="169" ht="22" customHeight="1">
       <c r="A169" s="2" t="inlineStr">
@@ -4689,7 +5213,12 @@
       <c r="H171" s="4" t="n">
         <v>28.5</v>
       </c>
-      <c r="I171" s="5" t="inlineStr"/>
+      <c r="I171" s="6" t="inlineStr">
+        <is>
+          <t>95.0 bm × 0.3 m = 28.5 m²</t>
+        </is>
+      </c>
+      <c r="J171" s="6" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="3" t="inlineStr">
@@ -4729,7 +5258,12 @@
       <c r="H173" s="4" t="n">
         <v>28.5</v>
       </c>
-      <c r="I173" s="5" t="inlineStr"/>
+      <c r="I173" s="6" t="inlineStr">
+        <is>
+          <t>95.0 bm × 0.3 m = 28.5 m²  [TZ:B]</t>
+        </is>
+      </c>
+      <c r="J173" s="6" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="3" t="inlineStr">
@@ -4769,7 +5303,12 @@
       <c r="H175" s="7" t="n">
         <v>95</v>
       </c>
-      <c r="I175" s="8" t="inlineStr"/>
+      <c r="I175" s="9" t="inlineStr">
+        <is>
+          <t>obvod 95.0 bm</t>
+        </is>
+      </c>
+      <c r="J175" s="9" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="3" t="inlineStr">
@@ -4809,7 +5348,12 @@
       <c r="H177" s="7" t="n">
         <v>47.5</v>
       </c>
-      <c r="I177" s="8" t="inlineStr"/>
+      <c r="I177" s="9" t="inlineStr">
+        <is>
+          <t>95.0 bm × 0.5 m</t>
+        </is>
+      </c>
+      <c r="J177" s="9" t="inlineStr"/>
     </row>
     <row r="178" ht="22" customHeight="1">
       <c r="A178" s="2" t="inlineStr">
@@ -4856,7 +5400,12 @@
       <c r="H180" s="4" t="n">
         <v>495</v>
       </c>
-      <c r="I180" s="5" t="inlineStr"/>
+      <c r="I180" s="6" t="inlineStr">
+        <is>
+          <t>495.0 m² (celá plocha podlahy)</t>
+        </is>
+      </c>
+      <c r="J180" s="6" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="3" t="inlineStr">
@@ -4896,7 +5445,12 @@
       <c r="H182" s="7" t="n">
         <v>495</v>
       </c>
-      <c r="I182" s="8" t="inlineStr">
+      <c r="I182" s="9" t="inlineStr">
+        <is>
+          <t>495.0 m²  [TZ:podlaha]</t>
+        </is>
+      </c>
+      <c r="J182" s="9" t="inlineStr">
         <is>
           <t>ABMV:ABMV_10</t>
         </is>
@@ -4940,7 +5494,12 @@
       <c r="H184" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="I184" s="5" t="inlineStr">
+      <c r="I184" s="6" t="inlineStr">
+        <is>
+          <t>placeholder ~30 m² (3 stroje × ~10 m² každé anchorage zóna)  [výkres:A107]</t>
+        </is>
+      </c>
+      <c r="J184" s="6" t="inlineStr">
         <is>
           <t>ABMV:ABMV_3,ABMV_16</t>
         </is>
@@ -4984,7 +5543,12 @@
       <c r="H186" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="I186" s="8" t="inlineStr"/>
+      <c r="I186" s="9" t="inlineStr">
+        <is>
+          <t>placeholder ~60 bm (pole dilatace á 6 m na 495 m² ploše)</t>
+        </is>
+      </c>
+      <c r="J186" s="9" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="7" t="n">
@@ -5017,7 +5581,12 @@
       <c r="H187" s="7" t="n">
         <v>95</v>
       </c>
-      <c r="I187" s="8" t="inlineStr"/>
+      <c r="I187" s="9" t="inlineStr">
+        <is>
+          <t>obvod desky 95 bm</t>
+        </is>
+      </c>
+      <c r="J187" s="9" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="7" t="n">
@@ -5050,7 +5619,12 @@
       <c r="H188" s="7" t="n">
         <v>495</v>
       </c>
-      <c r="I188" s="8" t="inlineStr">
+      <c r="I188" s="9" t="inlineStr">
+        <is>
+          <t>495.0 m² (pokud zvolena PU varianta)</t>
+        </is>
+      </c>
+      <c r="J188" s="9" t="inlineStr">
         <is>
           <t>ABMV:ABMV_10</t>
         </is>
@@ -5101,7 +5675,12 @@
       <c r="H191" s="4" t="n">
         <v>200</v>
       </c>
-      <c r="I191" s="5" t="inlineStr"/>
+      <c r="I191" s="6" t="inlineStr">
+        <is>
+          <t>placeholder 200 t·km (in-site přesuny, default)</t>
+        </is>
+      </c>
+      <c r="J191" s="6" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="3" t="inlineStr">
@@ -5141,7 +5720,12 @@
       <c r="H193" s="4" t="n">
         <v>1500</v>
       </c>
-      <c r="I193" s="5" t="inlineStr"/>
+      <c r="I193" s="6" t="inlineStr">
+        <is>
+          <t>placeholder ~1500 t·km (30 t materiálů × 50 km)</t>
+        </is>
+      </c>
+      <c r="J193" s="6" t="inlineStr"/>
     </row>
     <row r="194" ht="22" customHeight="1">
       <c r="A194" s="2" t="inlineStr">
@@ -5188,7 +5772,12 @@
       <c r="H196" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="I196" s="8" t="inlineStr"/>
+      <c r="I196" s="9" t="inlineStr">
+        <is>
+          <t>paušál (Rožmitál 00523 R precedent)  [csn]</t>
+        </is>
+      </c>
+      <c r="J196" s="9" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" s="7" t="n">
@@ -5221,7 +5810,12 @@
       <c r="H197" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="I197" s="8" t="inlineStr"/>
+      <c r="I197" s="9" t="inlineStr">
+        <is>
+          <t>paušál  [csn]</t>
+        </is>
+      </c>
+      <c r="J197" s="9" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" s="7" t="n">
@@ -5254,7 +5848,12 @@
       <c r="H198" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="I198" s="8" t="inlineStr"/>
+      <c r="I198" s="9" t="inlineStr">
+        <is>
+          <t>paušál  [csn]</t>
+        </is>
+      </c>
+      <c r="J198" s="9" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="3" t="inlineStr">
@@ -5294,7 +5893,12 @@
       <c r="H200" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="I200" s="5" t="inlineStr"/>
+      <c r="I200" s="6" t="inlineStr">
+        <is>
+          <t>placeholder ~30 m³ stavebního odpadu kat. O</t>
+        </is>
+      </c>
+      <c r="J200" s="6" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" s="7" t="n">
@@ -5327,7 +5931,12 @@
       <c r="H201" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="I201" s="8" t="inlineStr"/>
+      <c r="I201" s="9" t="inlineStr">
+        <is>
+          <t>placeholder ~2 m³ kat. N</t>
+        </is>
+      </c>
+      <c r="J201" s="9" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" s="3" t="inlineStr">
@@ -5367,7 +5976,12 @@
       <c r="H203" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="I203" s="5" t="inlineStr"/>
+      <c r="I203" s="6" t="inlineStr">
+        <is>
+          <t>paušál</t>
+        </is>
+      </c>
+      <c r="J203" s="6" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="3" t="inlineStr">
@@ -5407,7 +6021,12 @@
       <c r="H205" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="I205" s="8" t="inlineStr"/>
+      <c r="I205" s="9" t="inlineStr">
+        <is>
+          <t>paušál</t>
+        </is>
+      </c>
+      <c r="J205" s="9" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" s="7" t="n">
@@ -5440,7 +6059,12 @@
       <c r="H206" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="I206" s="8" t="inlineStr"/>
+      <c r="I206" s="9" t="inlineStr">
+        <is>
+          <t>paušál</t>
+        </is>
+      </c>
+      <c r="J206" s="9" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="3" t="inlineStr">
@@ -5480,89 +6104,94 @@
       <c r="H208" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="I208" s="5" t="inlineStr"/>
+      <c r="I208" s="6" t="inlineStr">
+        <is>
+          <t>2 ks (per TZ B m.7.b náhradní výsadba)  [TZ:7.b]</t>
+        </is>
+      </c>
+      <c r="J208" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="79">
-    <mergeCell ref="A90:I90"/>
-    <mergeCell ref="A172:I172"/>
-    <mergeCell ref="A164:I164"/>
-    <mergeCell ref="A154:I154"/>
-    <mergeCell ref="A195:I195"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A33:I33"/>
-    <mergeCell ref="A204:I204"/>
-    <mergeCell ref="A42:I42"/>
-    <mergeCell ref="A140:I140"/>
-    <mergeCell ref="A22:I22"/>
-    <mergeCell ref="A109:I109"/>
-    <mergeCell ref="A19:I19"/>
-    <mergeCell ref="A190:I190"/>
-    <mergeCell ref="A117:I117"/>
-    <mergeCell ref="A111:I111"/>
-    <mergeCell ref="A39:I39"/>
-    <mergeCell ref="A142:I142"/>
-    <mergeCell ref="A169:I169"/>
-    <mergeCell ref="A153:I153"/>
-    <mergeCell ref="A46:I46"/>
-    <mergeCell ref="A136:I136"/>
-    <mergeCell ref="A192:I192"/>
-    <mergeCell ref="A105:I105"/>
-    <mergeCell ref="A145:I145"/>
-    <mergeCell ref="A179:I179"/>
-    <mergeCell ref="A71:I71"/>
-    <mergeCell ref="A129:I129"/>
-    <mergeCell ref="A194:I194"/>
-    <mergeCell ref="A116:I116"/>
-    <mergeCell ref="A181:I181"/>
-    <mergeCell ref="A8:I8"/>
-    <mergeCell ref="A91:I91"/>
-    <mergeCell ref="A131:I131"/>
-    <mergeCell ref="A52:I52"/>
-    <mergeCell ref="A63:I63"/>
-    <mergeCell ref="A10:I10"/>
-    <mergeCell ref="A93:I93"/>
-    <mergeCell ref="A34:I34"/>
-    <mergeCell ref="A49:I49"/>
-    <mergeCell ref="A36:I36"/>
-    <mergeCell ref="A207:I207"/>
-    <mergeCell ref="A78:I78"/>
-    <mergeCell ref="A183:I183"/>
-    <mergeCell ref="A65:I65"/>
-    <mergeCell ref="A75:I75"/>
-    <mergeCell ref="A133:I133"/>
-    <mergeCell ref="A80:I80"/>
-    <mergeCell ref="A3:I3"/>
-    <mergeCell ref="A57:I57"/>
-    <mergeCell ref="A14:I14"/>
-    <mergeCell ref="A185:I185"/>
-    <mergeCell ref="A170:I170"/>
-    <mergeCell ref="A202:I202"/>
-    <mergeCell ref="A67:I67"/>
-    <mergeCell ref="A24:I24"/>
-    <mergeCell ref="A148:I148"/>
-    <mergeCell ref="A124:I124"/>
-    <mergeCell ref="A6:I6"/>
-    <mergeCell ref="A119:I119"/>
-    <mergeCell ref="A16:I16"/>
-    <mergeCell ref="A174:I174"/>
-    <mergeCell ref="A84:I84"/>
-    <mergeCell ref="A189:I189"/>
-    <mergeCell ref="A95:I95"/>
-    <mergeCell ref="A151:I151"/>
-    <mergeCell ref="A159:I159"/>
-    <mergeCell ref="A97:I97"/>
-    <mergeCell ref="A29:I29"/>
-    <mergeCell ref="A134:I134"/>
-    <mergeCell ref="A199:I199"/>
-    <mergeCell ref="A121:I121"/>
-    <mergeCell ref="A127:I127"/>
-    <mergeCell ref="A176:I176"/>
-    <mergeCell ref="A58:I58"/>
-    <mergeCell ref="A114:I114"/>
-    <mergeCell ref="A107:I107"/>
-    <mergeCell ref="A178:I178"/>
-    <mergeCell ref="A60:I60"/>
+    <mergeCell ref="A194:J194"/>
+    <mergeCell ref="A181:J181"/>
+    <mergeCell ref="A91:J91"/>
+    <mergeCell ref="A52:J52"/>
+    <mergeCell ref="A63:J63"/>
+    <mergeCell ref="A93:J93"/>
+    <mergeCell ref="A34:J34"/>
+    <mergeCell ref="A148:J148"/>
+    <mergeCell ref="A49:J49"/>
+    <mergeCell ref="A36:J36"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A119:J119"/>
+    <mergeCell ref="A174:J174"/>
+    <mergeCell ref="A183:J183"/>
+    <mergeCell ref="A75:J75"/>
+    <mergeCell ref="A133:J133"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A95:J95"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A159:J159"/>
+    <mergeCell ref="A97:J97"/>
+    <mergeCell ref="A29:J29"/>
+    <mergeCell ref="A121:J121"/>
+    <mergeCell ref="A170:J170"/>
+    <mergeCell ref="A202:J202"/>
+    <mergeCell ref="A58:J58"/>
+    <mergeCell ref="A67:J67"/>
+    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="A60:J60"/>
+    <mergeCell ref="A124:J124"/>
+    <mergeCell ref="A172:J172"/>
+    <mergeCell ref="A16:J16"/>
+    <mergeCell ref="A84:J84"/>
+    <mergeCell ref="A71:J71"/>
+    <mergeCell ref="A189:J189"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A204:J204"/>
+    <mergeCell ref="A42:J42"/>
+    <mergeCell ref="A151:J151"/>
+    <mergeCell ref="A22:J22"/>
+    <mergeCell ref="A190:J190"/>
+    <mergeCell ref="A134:J134"/>
+    <mergeCell ref="A199:J199"/>
+    <mergeCell ref="A127:J127"/>
+    <mergeCell ref="A176:J176"/>
+    <mergeCell ref="A114:J114"/>
+    <mergeCell ref="A169:J169"/>
+    <mergeCell ref="A107:J107"/>
+    <mergeCell ref="A178:J178"/>
+    <mergeCell ref="A153:J153"/>
+    <mergeCell ref="A90:J90"/>
+    <mergeCell ref="A164:J164"/>
+    <mergeCell ref="A145:J145"/>
+    <mergeCell ref="A154:J154"/>
+    <mergeCell ref="A195:J195"/>
+    <mergeCell ref="A33:J33"/>
+    <mergeCell ref="A116:J116"/>
+    <mergeCell ref="A8:J8"/>
+    <mergeCell ref="A131:J131"/>
+    <mergeCell ref="A140:J140"/>
+    <mergeCell ref="A109:J109"/>
+    <mergeCell ref="A10:J10"/>
+    <mergeCell ref="A19:J19"/>
+    <mergeCell ref="A117:J117"/>
+    <mergeCell ref="A111:J111"/>
+    <mergeCell ref="A39:J39"/>
+    <mergeCell ref="A142:J142"/>
+    <mergeCell ref="A207:J207"/>
+    <mergeCell ref="A78:J78"/>
+    <mergeCell ref="A65:J65"/>
+    <mergeCell ref="A80:J80"/>
+    <mergeCell ref="A46:J46"/>
+    <mergeCell ref="A136:J136"/>
+    <mergeCell ref="A192:J192"/>
+    <mergeCell ref="A105:J105"/>
+    <mergeCell ref="A57:J57"/>
+    <mergeCell ref="A179:J179"/>
+    <mergeCell ref="A129:J129"/>
+    <mergeCell ref="A185:J185"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/test-data/hk212_hala/outputs/sequential_list/hk212_sequential_list.xlsx
+++ b/test-data/hk212_hala/outputs/sequential_list/hk212_sequential_list.xlsx
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J208"/>
+  <dimension ref="A1:J215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3859,7 +3859,7 @@
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>→ Stěnové panely KS NF 200 mm — dodávka + montáž</t>
+          <t>→ Stěnové panely KS 1000 NF 120 mm — dodávka + montáž</t>
         </is>
       </c>
     </row>
@@ -3883,7 +3883,7 @@
       </c>
       <c r="F122" s="6" t="inlineStr">
         <is>
-          <t>Kingspan KS NF 200 mm, jádro minerální vata (MW) per TZ ARS p4 + PBR §3 + ABMV_13 closure, plech vnější/vnitřní 0.6/0.4 mm, profilace M (Micro)/Q (Minibox), S280GD/S280GD, dle EN 14509:2013, výrobní závod Hradec Králové (Kingspan ČR), barva bílá + modrá (RAL standard)</t>
+          <t>Kingspan KS 1000 NF 120 mm, jádro minerální vata (MW), per Úprava dveří + TZ ARS DPZ D.1.1 — alternativně k orig. 200 mm</t>
         </is>
       </c>
       <c r="G122" s="4" t="inlineStr">
@@ -3892,11 +3892,11 @@
         </is>
       </c>
       <c r="H122" s="4" t="n">
-        <v>528.5</v>
+        <v>510.81</v>
       </c>
       <c r="I122" s="6" t="inlineStr">
         <is>
-          <t>fasáda netto Step3 v2: 623.3 m² brutto − 94.82 m² otvory (vrata 3.5×4.0 per TZ ARS) = 528.5 m²  [TZ:D.1.1, Step3, ABMV]</t>
+          <t>fasáda brutto Úprava dveří: 94.57 m obvod × 6.085 m okap + 17.58 m² štíty = 593.06 m² brutto − 82.25 m² FR zóny (rohy s dveřmi) = 510.81 m² (bez vyřezání otvorů — sendvič ordered celý)  [TZ:D.1.1, Step3, ABMV]</t>
         </is>
       </c>
       <c r="J122" s="6" t="inlineStr">
@@ -3925,7 +3925,7 @@
       </c>
       <c r="F123" s="12" t="inlineStr">
         <is>
-          <t>Montáž obvodového opláštění Kingspan KS NF 200 mm — kotvení samořeznými šrouby + EPDM těsnicí podložkou k ocelové konstrukci (rozteč rámů 6,1 m per statika), per TZ ARS D.1.1 p4 montážní předpis výrobce</t>
+          <t>Montáž obvodového opláštění Kingspan KS 1000 NF 120 mm — kotvení samořeznými šrouby + EPDM těsnicí podložkou k ocelové konstrukci (rozteč rámů 6.1 m)</t>
         </is>
       </c>
       <c r="G123" s="10" t="inlineStr">
@@ -3934,19 +3934,18 @@
         </is>
       </c>
       <c r="H123" s="10" t="n">
-        <v>528.5</v>
-      </c>
-      <c r="I123" s="12" t="inlineStr">
-        <is>
-          <t>fasáda netto Step3 v2: 623.3 m² brutto − 94.82 m² otvory (vrata 3.5×4.0 per TZ ARS) = 528.5 m²  [TZ:D.1.1, ABMV, TZ:D.1.2 (statika) — Návrh opláštění]</t>
-        </is>
+        <v>510.81</v>
+      </c>
+      <c r="I123" s="12">
+        <f> dodávka PSV-OPL-001 = 510.81 m²  [TZ:D.1.1, ABMV, TZ:D.1.2 (statika) — Návrh opláštění]</f>
+        <v/>
       </c>
       <c r="J123" s="12" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
         <is>
-          <t>→ Střešní panely KS FF-ROC 200 mm — dodávka + montáž</t>
+          <t>→ Stěnové panely KS 1000 FR 150 mm (rohové zóny) — dodávka + montáž</t>
         </is>
       </c>
     </row>
@@ -3965,12 +3964,12 @@
       </c>
       <c r="E125" s="5" t="inlineStr">
         <is>
-          <t>PSV-OPL-003</t>
+          <t>PSV-OPL-009</t>
         </is>
       </c>
       <c r="F125" s="6" t="inlineStr">
         <is>
-          <t>Kingspan KS FF-ROC tl. 200 mm, jádro ROC (Rockwool — minerální vata), pro šikmé střechy sklon 5.25°, plech vnější/vnitřní 0.6/0.5 mm, profilace trapéz 34 mm/Q (minibox), S280GD/S280GD, dle EN 14509:2013, výrobní závod Lipsko (Kingspan Polská republika), vaznice rozteč max 1.5 m per statika</t>
+          <t>Kingspan KS 1000 FR 150 mm, jádro PIR (fire-resistant), 2 rohové zóny u vstupních dveří (45.69 + 36.56 m²) — Úprava dveří</t>
         </is>
       </c>
       <c r="G125" s="4" t="inlineStr">
@@ -3979,18 +3978,14 @@
         </is>
       </c>
       <c r="H125" s="4" t="n">
-        <v>558.8</v>
+        <v>82.25</v>
       </c>
       <c r="I125" s="6" t="inlineStr">
         <is>
-          <t>střecha netto Step3: brutto 556.5 m² / cos(5.25°) = 558.8 m²  [TZ:D.1.1, DXF, Step3]</t>
-        </is>
-      </c>
-      <c r="J125" s="6" t="inlineStr">
-        <is>
-          <t>ABMV:ABMV_13</t>
-        </is>
-      </c>
+          <t>45.69 m² + 36.56 m² = 82.25 m² (2 šrafované rohové zóny v POHLED F a POHLED 01 — user manual měření)  [výkres:Hala HK_Úprava dveří, TZ:B p.8]  · was 82.25: Úprava dveří revision — first appearance</t>
+        </is>
+      </c>
+      <c r="J125" s="6" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="10" t="n">
@@ -4007,12 +4002,12 @@
       </c>
       <c r="E126" s="11" t="inlineStr">
         <is>
-          <t>PSV-OPL-004</t>
+          <t>PSV-OPL-010</t>
         </is>
       </c>
       <c r="F126" s="12" t="inlineStr">
         <is>
-          <t>Montáž střešního opláštění Kingspan KS FF-ROC 200 mm — kotvení k ocelové konstrukci samořeznými šrouby + těsnění přesahů, uložení prosté/spojité (2-3 polí) na vaznicích rozteč max 1.5 m per statika TZ D.1.2</t>
+          <t>Montáž Kingspan KS 1000 FR 150 mm — 2 rohové zóny (45.69 + 36.56 m²), kotvení samořeznými šrouby + EPDM podložka</t>
         </is>
       </c>
       <c r="G126" s="10" t="inlineStr">
@@ -4021,19 +4016,18 @@
         </is>
       </c>
       <c r="H126" s="10" t="n">
-        <v>558.8</v>
-      </c>
-      <c r="I126" s="12" t="inlineStr">
-        <is>
-          <t>střecha netto Step3 = 558.8 m²  [TZ:D.1.1, TZ:D.1.2 (statika) — Návrh opláštění]</t>
-        </is>
+        <v>82.25</v>
+      </c>
+      <c r="I126" s="12">
+        <f> dodávka PSV-OPL-009 = 82.25 m²  [výkres:Hala HK_Úprava dveří]  · was 82.25: Úprava dveří revision — first appearance</f>
+        <v/>
       </c>
       <c r="J126" s="12" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>→ Spojovací materiál + EPDM těsnění Kingspan</t>
+          <t>→ Střešní panely KS 1000 RW 160 mm (hlavní střecha) — dodávka + montáž</t>
         </is>
       </c>
     </row>
@@ -4052,389 +4046,387 @@
       </c>
       <c r="E128" s="5" t="inlineStr">
         <is>
+          <t>PSV-OPL-003</t>
+        </is>
+      </c>
+      <c r="F128" s="6" t="inlineStr">
+        <is>
+          <t>Kingspan KS 1000 RW 160 mm, jádro PIR, pro šikmé střechy sklon 5.25°, hlavní střecha (mimo zónu FF 175)</t>
+        </is>
+      </c>
+      <c r="G128" s="4" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="H128" s="4" t="n">
+        <v>500.6</v>
+      </c>
+      <c r="I128" s="6" t="inlineStr">
+        <is>
+          <t>střecha total 558.8 m² − FF 175 zóna 58.20 m² (57.95 m² projection / cos 5.25°) = 500.6 m² — Úprava dveří section view  [TZ:D.1.1, DXF, Step3]</t>
+        </is>
+      </c>
+      <c r="J128" s="6" t="inlineStr">
+        <is>
+          <t>ABMV:ABMV_13</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="10" t="n">
+        <v>82</v>
+      </c>
+      <c r="B129" s="11" t="inlineStr"/>
+      <c r="C129" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="D129" s="11" t="inlineStr">
+        <is>
+          <t>PSV-OPL</t>
+        </is>
+      </c>
+      <c r="E129" s="11" t="inlineStr">
+        <is>
+          <t>PSV-OPL-004</t>
+        </is>
+      </c>
+      <c r="F129" s="12" t="inlineStr">
+        <is>
+          <t>Montáž střešního opláštění Kingspan KS 1000 RW 160 mm — kotvení k ocelové konstrukci samořeznými šrouby + těsnění přesahů</t>
+        </is>
+      </c>
+      <c r="G129" s="10" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="H129" s="10" t="n">
+        <v>500.6</v>
+      </c>
+      <c r="I129" s="12">
+        <f> dodávka PSV-OPL-003 = 500.6 m²  [TZ:D.1.1, TZ:D.1.2 (statika) — Návrh opláštění, výkres:Hala HK_Úprava dveří]</f>
+        <v/>
+      </c>
+      <c r="J129" s="12" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="3" t="inlineStr">
+        <is>
+          <t>→ Střešní panely KS 1000 FF 175 mm (zóna) — dodávka + montáž</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="4" t="n">
+        <v>83</v>
+      </c>
+      <c r="B131" s="5" t="inlineStr"/>
+      <c r="C131" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D131" s="5" t="inlineStr">
+        <is>
+          <t>PSV-OPL</t>
+        </is>
+      </c>
+      <c r="E131" s="5" t="inlineStr">
+        <is>
+          <t>PSV-OPL-011</t>
+        </is>
+      </c>
+      <c r="F131" s="6" t="inlineStr">
+        <is>
+          <t>Kingspan KS 1000 FF 175 mm, jádro FF (Rockwool), zóna ve střeše — Úprava dveří section view</t>
+        </is>
+      </c>
+      <c r="G131" s="4" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="H131" s="4" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="I131" s="6" t="inlineStr">
+        <is>
+          <t>57.95 m² projection (user měřeno) / cos(5.25°) = 58.20 m² (slope-corrected)  [výkres:Hala HK_Úprava dveří]  · was 58.2: Úprava dveří revision — first appearance</t>
+        </is>
+      </c>
+      <c r="J131" s="6" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="10" t="n">
+        <v>84</v>
+      </c>
+      <c r="B132" s="11" t="inlineStr"/>
+      <c r="C132" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="D132" s="11" t="inlineStr">
+        <is>
+          <t>PSV-OPL</t>
+        </is>
+      </c>
+      <c r="E132" s="11" t="inlineStr">
+        <is>
+          <t>PSV-OPL-012</t>
+        </is>
+      </c>
+      <c r="F132" s="12" t="inlineStr">
+        <is>
+          <t>Montáž Kingspan KS 1000 FF 175 mm — zóna 58.20 m² ve střeše</t>
+        </is>
+      </c>
+      <c r="G132" s="10" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="H132" s="10" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="I132" s="12">
+        <f> dodávka PSV-OPL-011 = 58.20 m²  [výkres:Hala HK_Úprava dveří]  · was 58.2: Úprava dveří revision — first appearance</f>
+        <v/>
+      </c>
+      <c r="J132" s="12" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="3" t="inlineStr">
+        <is>
+          <t>→ Spojovací materiál + EPDM těsnění Kingspan</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="4" t="n">
+        <v>85</v>
+      </c>
+      <c r="B134" s="5" t="inlineStr"/>
+      <c r="C134" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D134" s="5" t="inlineStr">
+        <is>
+          <t>PSV-OPL</t>
+        </is>
+      </c>
+      <c r="E134" s="5" t="inlineStr">
+        <is>
           <t>PSV-OPL-006</t>
         </is>
       </c>
-      <c r="F128" s="6" t="inlineStr">
+      <c r="F134" s="6" t="inlineStr">
         <is>
           <t>Spojovací materiál + těsnění + EPDM podložky Kingspan systém — paušál pro celý objem opláštění</t>
         </is>
       </c>
-      <c r="G128" s="4" t="inlineStr">
+      <c r="G134" s="4" t="inlineStr">
         <is>
           <t>kpl</t>
         </is>
       </c>
-      <c r="H128" s="4" t="n">
+      <c r="H134" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="I128" s="6" t="inlineStr">
+      <c r="I134" s="6" t="inlineStr">
         <is>
           <t>paušál  [TZ:D.1.1]</t>
         </is>
       </c>
-      <c r="J128" s="6" t="inlineStr"/>
-    </row>
-    <row r="129">
-      <c r="A129" s="3" t="inlineStr">
+      <c r="J134" s="6" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="3" t="inlineStr">
         <is>
           <t>→ Klempířské lemy přechody střecha–fasáda</t>
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="13" t="n">
-        <v>82</v>
-      </c>
-      <c r="B130" s="14" t="inlineStr"/>
-      <c r="C130" s="13" t="n">
+    <row r="136">
+      <c r="A136" s="13" t="n">
+        <v>86</v>
+      </c>
+      <c r="B136" s="14" t="inlineStr"/>
+      <c r="C136" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="D130" s="14" t="inlineStr">
+      <c r="D136" s="14" t="inlineStr">
         <is>
           <t>PSV-OPL</t>
         </is>
       </c>
-      <c r="E130" s="14" t="inlineStr">
+      <c r="E136" s="14" t="inlineStr">
         <is>
           <t>PSV-OPL-005</t>
         </is>
       </c>
-      <c r="F130" s="15" t="inlineStr">
+      <c r="F136" s="15" t="inlineStr">
         <is>
           <t>Klempířské lemy + přechody střecha–fasáda, pozinkovaný plech — atika, úžlabí, nároží, parapety, krycí lišty — dle TZ ARS DPZ D.1.1</t>
         </is>
       </c>
-      <c r="G130" s="13" t="inlineStr">
+      <c r="G136" s="13" t="inlineStr">
         <is>
           <t>bm</t>
         </is>
       </c>
-      <c r="H130" s="13" t="n">
-        <v>207</v>
-      </c>
-      <c r="I130" s="15" t="inlineStr">
-        <is>
-          <t>2 × obvod budovy 103.5 m = 207.0 bm (hrubý odhad atika + parapety)  [TZ:D.1.1, Step3]</t>
-        </is>
-      </c>
-      <c r="J130" s="15" t="inlineStr">
+      <c r="H136" s="13" t="n">
+        <v>189.14</v>
+      </c>
+      <c r="I136" s="15" t="inlineStr">
+        <is>
+          <t>2 × obvod budovy 94.57 m (Úprava dveří) = 189.14 bm (hrubý odhad atika + parapety)  [TZ:D.1.1, Step3, výkres:Hala HK_Úprava dveří]</t>
+        </is>
+      </c>
+      <c r="J136" s="15" t="inlineStr">
         <is>
           <t>rev:qty</t>
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="3" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="3" t="inlineStr">
         <is>
           <t>→ Statické posouzení uchycení Kingspan</t>
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="4" t="n">
-        <v>83</v>
-      </c>
-      <c r="B132" s="5" t="inlineStr"/>
-      <c r="C132" s="4" t="n">
+    <row r="138">
+      <c r="A138" s="4" t="n">
+        <v>87</v>
+      </c>
+      <c r="B138" s="5" t="inlineStr"/>
+      <c r="C138" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="D132" s="5" t="inlineStr">
+      <c r="D138" s="5" t="inlineStr">
         <is>
           <t>PSV-OPL</t>
         </is>
       </c>
-      <c r="E132" s="5" t="inlineStr">
+      <c r="E138" s="5" t="inlineStr">
         <is>
           <t>PSV-OPL-008</t>
         </is>
       </c>
-      <c r="F132" s="6" t="inlineStr">
+      <c r="F138" s="6" t="inlineStr">
         <is>
           <t>Statické posouzení uchycení Kingspan k ocelové konstrukci + revizní zpráva — paušál</t>
         </is>
       </c>
-      <c r="G132" s="4" t="inlineStr">
+      <c r="G138" s="4" t="inlineStr">
         <is>
           <t>paušál</t>
         </is>
       </c>
-      <c r="H132" s="4" t="n">
+      <c r="H138" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="I132" s="6" t="inlineStr">
+      <c r="I138" s="6" t="inlineStr">
         <is>
           <t>paušál  [TZ:D.1.1]</t>
         </is>
       </c>
-      <c r="J132" s="6" t="inlineStr"/>
-    </row>
-    <row r="133" ht="22" customHeight="1">
-      <c r="A133" s="2" t="inlineStr">
+      <c r="J138" s="6" t="inlineStr"/>
+    </row>
+    <row r="139" ht="22" customHeight="1">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>═══ FÁZE 6: KLEMPÍŘSKÉ + ODVODNĚNÍ STŘECHY ═══</t>
         </is>
       </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="3" t="inlineStr">
-        <is>
-          <t>→ Doprava klempířiny na stavbu</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="4" t="n">
-        <v>84</v>
-      </c>
-      <c r="B135" s="5" t="inlineStr"/>
-      <c r="C135" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="D135" s="5" t="inlineStr">
-        <is>
-          <t>PSV-78x</t>
-        </is>
-      </c>
-      <c r="E135" s="5" t="inlineStr">
-        <is>
-          <t>PSV-78x-012</t>
-        </is>
-      </c>
-      <c r="F135" s="6" t="inlineStr">
-        <is>
-          <t>Doprava klempířiny + materiálu na stavbu — paušál</t>
-        </is>
-      </c>
-      <c r="G135" s="4" t="inlineStr">
-        <is>
-          <t>paušál</t>
-        </is>
-      </c>
-      <c r="H135" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I135" s="6" t="inlineStr">
-        <is>
-          <t>paušál</t>
-        </is>
-      </c>
-      <c r="J135" s="6" t="inlineStr"/>
-    </row>
-    <row r="136">
-      <c r="A136" s="3" t="inlineStr">
-        <is>
-          <t>→ Atikové oplechování + úžlabí + nároží</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="7" t="n">
-        <v>85</v>
-      </c>
-      <c r="B137" s="8" t="inlineStr"/>
-      <c r="C137" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="D137" s="8" t="inlineStr">
-        <is>
-          <t>PSV-78x</t>
-        </is>
-      </c>
-      <c r="E137" s="8" t="inlineStr">
-        <is>
-          <t>PSV-78x-007</t>
-        </is>
-      </c>
-      <c r="F137" s="9" t="inlineStr">
-        <is>
-          <t>Atikové oplechování titanzinek tl. 0.7 mm, rš 500 mm — po obvodu střechy</t>
-        </is>
-      </c>
-      <c r="G137" s="7" t="inlineStr">
-        <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="H137" s="7" t="n">
-        <v>95</v>
-      </c>
-      <c r="I137" s="9" t="inlineStr">
-        <is>
-          <t>obvod střechy 95.0 bm  [TZ:B]</t>
-        </is>
-      </c>
-      <c r="J137" s="9" t="inlineStr"/>
-    </row>
-    <row r="138">
-      <c r="A138" s="7" t="n">
-        <v>86</v>
-      </c>
-      <c r="B138" s="8" t="inlineStr"/>
-      <c r="C138" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="D138" s="8" t="inlineStr">
-        <is>
-          <t>PSV-78x</t>
-        </is>
-      </c>
-      <c r="E138" s="8" t="inlineStr">
-        <is>
-          <t>PSV-78x-008</t>
-        </is>
-      </c>
-      <c r="F138" s="9" t="inlineStr">
-        <is>
-          <t>Lemování úžlabí střechy titanzinek — diagonální linie</t>
-        </is>
-      </c>
-      <c r="G138" s="7" t="inlineStr">
-        <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="H138" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="I138" s="9" t="inlineStr">
-        <is>
-          <t>placeholder ~15 bm (úžlabí pultové střechy 5.25°)</t>
-        </is>
-      </c>
-      <c r="J138" s="9" t="inlineStr"/>
-    </row>
-    <row r="139">
-      <c r="A139" s="7" t="n">
-        <v>87</v>
-      </c>
-      <c r="B139" s="8" t="inlineStr"/>
-      <c r="C139" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="D139" s="8" t="inlineStr">
-        <is>
-          <t>PSV-78x</t>
-        </is>
-      </c>
-      <c r="E139" s="8" t="inlineStr">
-        <is>
-          <t>PSV-78x-009</t>
-        </is>
-      </c>
-      <c r="F139" s="9" t="inlineStr">
-        <is>
-          <t>Lemování nároží titanzinek — vertikální rohy fasády</t>
-        </is>
-      </c>
-      <c r="G139" s="7" t="inlineStr">
-        <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="H139" s="7" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="I139" s="9" t="inlineStr">
-        <is>
-          <t>4 nároží × 6.3 m výška</t>
-        </is>
-      </c>
-      <c r="J139" s="9" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
         <is>
-          <t>→ Tmelení spár klempířských konstrukcí</t>
+          <t>→ Doprava klempířiny na stavbu</t>
         </is>
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="7" t="n">
+      <c r="A141" s="4" t="n">
         <v>88</v>
       </c>
-      <c r="B141" s="8" t="inlineStr"/>
-      <c r="C141" s="7" t="n">
+      <c r="B141" s="5" t="inlineStr"/>
+      <c r="C141" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="D141" s="8" t="inlineStr">
+      <c r="D141" s="5" t="inlineStr">
         <is>
           <t>PSV-78x</t>
         </is>
       </c>
-      <c r="E141" s="8" t="inlineStr">
-        <is>
-          <t>PSV-78x-010</t>
-        </is>
-      </c>
-      <c r="F141" s="9" t="inlineStr">
-        <is>
-          <t>Krytí spár klempířských konstrukcí — silikonový tmel</t>
-        </is>
-      </c>
-      <c r="G141" s="7" t="inlineStr">
-        <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="H141" s="7" t="n">
-        <v>120</v>
-      </c>
-      <c r="I141" s="9" t="inlineStr">
-        <is>
-          <t>placeholder ~120 bm (spáry mezi všemi klempířskými prvky)</t>
-        </is>
-      </c>
-      <c r="J141" s="9" t="inlineStr"/>
+      <c r="E141" s="5" t="inlineStr">
+        <is>
+          <t>PSV-78x-012</t>
+        </is>
+      </c>
+      <c r="F141" s="6" t="inlineStr">
+        <is>
+          <t>Doprava klempířiny + materiálu na stavbu — paušál</t>
+        </is>
+      </c>
+      <c r="G141" s="4" t="inlineStr">
+        <is>
+          <t>paušál</t>
+        </is>
+      </c>
+      <c r="H141" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I141" s="6" t="inlineStr">
+        <is>
+          <t>paušál</t>
+        </is>
+      </c>
+      <c r="J141" s="6" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
         <is>
-          <t>→ Lindab svody — dodávka + montáž</t>
+          <t>→ Atikové oplechování + úžlabí + nároží</t>
         </is>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="4" t="n">
+      <c r="A143" s="7" t="n">
         <v>89</v>
       </c>
-      <c r="B143" s="5" t="inlineStr"/>
-      <c r="C143" s="4" t="n">
+      <c r="B143" s="8" t="inlineStr"/>
+      <c r="C143" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="D143" s="5" t="inlineStr">
+      <c r="D143" s="8" t="inlineStr">
         <is>
           <t>PSV-78x</t>
         </is>
       </c>
-      <c r="E143" s="5" t="inlineStr">
-        <is>
-          <t>PSV-78x-001</t>
-        </is>
-      </c>
-      <c r="F143" s="6" t="inlineStr">
-        <is>
-          <t>Dodávka Lindab Round Downpipe 150/100 Antique White, vč. kolen a spojek</t>
-        </is>
-      </c>
-      <c r="G143" s="4" t="inlineStr">
-        <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="H143" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="I143" s="6" t="inlineStr">
-        <is>
-          <t>4 ks (A104 DXF count working, ABMV_20: A101=3 vs A104=4)  [výkres:A104]</t>
-        </is>
-      </c>
-      <c r="J143" s="6" t="inlineStr">
-        <is>
-          <t>ABMV:ABMV_20</t>
-        </is>
-      </c>
+      <c r="E143" s="8" t="inlineStr">
+        <is>
+          <t>PSV-78x-007</t>
+        </is>
+      </c>
+      <c r="F143" s="9" t="inlineStr">
+        <is>
+          <t>Atikové oplechování titanzinek tl. 0.7 mm, rš 500 mm — po obvodu střechy</t>
+        </is>
+      </c>
+      <c r="G143" s="7" t="inlineStr">
+        <is>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="H143" s="7" t="n">
+        <v>95</v>
+      </c>
+      <c r="I143" s="9" t="inlineStr">
+        <is>
+          <t>obvod střechy 95.0 bm  [TZ:B]</t>
+        </is>
+      </c>
+      <c r="J143" s="9" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="7" t="n">
@@ -4451,77 +4443,73 @@
       </c>
       <c r="E144" s="8" t="inlineStr">
         <is>
-          <t>PSV-78x-002</t>
+          <t>PSV-78x-008</t>
         </is>
       </c>
       <c r="F144" s="9" t="inlineStr">
         <is>
-          <t>Montáž svodů Lindab — příchytky, kotvení do fasády</t>
+          <t>Lemování úžlabí střechy titanzinek — diagonální linie</t>
         </is>
       </c>
       <c r="G144" s="7" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="H144" s="7" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="I144" s="9" t="inlineStr">
         <is>
-          <t>4 kpl (jeden na každý svod)</t>
-        </is>
-      </c>
-      <c r="J144" s="9" t="inlineStr">
-        <is>
-          <t>ABMV:ABMV_20</t>
-        </is>
-      </c>
+          <t>placeholder ~15 bm (úžlabí pultové střechy 5.25°)</t>
+        </is>
+      </c>
+      <c r="J144" s="9" t="inlineStr"/>
     </row>
     <row r="145">
-      <c r="A145" s="3" t="inlineStr">
-        <is>
-          <t>→ Wavin Tegra střešní vpusti — dodávka + montáž</t>
-        </is>
-      </c>
+      <c r="A145" s="7" t="n">
+        <v>91</v>
+      </c>
+      <c r="B145" s="8" t="inlineStr"/>
+      <c r="C145" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="D145" s="8" t="inlineStr">
+        <is>
+          <t>PSV-78x</t>
+        </is>
+      </c>
+      <c r="E145" s="8" t="inlineStr">
+        <is>
+          <t>PSV-78x-009</t>
+        </is>
+      </c>
+      <c r="F145" s="9" t="inlineStr">
+        <is>
+          <t>Lemování nároží titanzinek — vertikální rohy fasády</t>
+        </is>
+      </c>
+      <c r="G145" s="7" t="inlineStr">
+        <is>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="H145" s="7" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="I145" s="9" t="inlineStr">
+        <is>
+          <t>4 nároží × 6.3 m výška</t>
+        </is>
+      </c>
+      <c r="J145" s="9" t="inlineStr"/>
     </row>
     <row r="146">
-      <c r="A146" s="7" t="n">
-        <v>91</v>
-      </c>
-      <c r="B146" s="8" t="inlineStr"/>
-      <c r="C146" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="D146" s="8" t="inlineStr">
-        <is>
-          <t>PSV-78x</t>
-        </is>
-      </c>
-      <c r="E146" s="8" t="inlineStr">
-        <is>
-          <t>PSV-78x-003</t>
-        </is>
-      </c>
-      <c r="F146" s="9" t="inlineStr">
-        <is>
-          <t>Wavin Tegra střešní vpust Round Iron Cover + Concrete Ring DN300</t>
-        </is>
-      </c>
-      <c r="G146" s="7" t="inlineStr">
-        <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="H146" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="I146" s="9" t="inlineStr">
-        <is>
-          <t>3 ks (A101 INSERT Wavin × 3 dle DXF parse)  [výkres:A101]</t>
-        </is>
-      </c>
-      <c r="J146" s="9" t="inlineStr"/>
+      <c r="A146" s="3" t="inlineStr">
+        <is>
+          <t>→ Tmelení spár klempířských konstrukcí</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="7" t="n">
@@ -4538,72 +4526,77 @@
       </c>
       <c r="E147" s="8" t="inlineStr">
         <is>
-          <t>PSV-78x-004</t>
+          <t>PSV-78x-010</t>
         </is>
       </c>
       <c r="F147" s="9" t="inlineStr">
         <is>
-          <t>Montáž střešních vpustí Wavin Tegra — osazení, napojení na svody</t>
+          <t>Krytí spár klempířských konstrukcí — silikonový tmel</t>
         </is>
       </c>
       <c r="G147" s="7" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="H147" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="I147" s="9">
-        <f> dodávka</f>
-        <v/>
+        <v>120</v>
+      </c>
+      <c r="I147" s="9" t="inlineStr">
+        <is>
+          <t>placeholder ~120 bm (spáry mezi všemi klempířskými prvky)</t>
+        </is>
       </c>
       <c r="J147" s="9" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="3" t="inlineStr">
         <is>
-          <t>→ MEA Mearin liniový žlab + mřížka</t>
+          <t>→ Lindab svody — dodávka + montáž</t>
         </is>
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="7" t="n">
+      <c r="A149" s="4" t="n">
         <v>93</v>
       </c>
-      <c r="B149" s="8" t="inlineStr"/>
-      <c r="C149" s="7" t="n">
+      <c r="B149" s="5" t="inlineStr"/>
+      <c r="C149" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="D149" s="8" t="inlineStr">
+      <c r="D149" s="5" t="inlineStr">
         <is>
           <t>PSV-78x</t>
         </is>
       </c>
-      <c r="E149" s="8" t="inlineStr">
-        <is>
-          <t>PSV-78x-005</t>
-        </is>
-      </c>
-      <c r="F149" s="9" t="inlineStr">
-        <is>
-          <t>MEA Mearin Plus 3000 NW300 liniový žlab — podél JZ a SZ fasády</t>
-        </is>
-      </c>
-      <c r="G149" s="7" t="inlineStr">
-        <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="H149" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="I149" s="9" t="inlineStr">
-        <is>
-          <t>~30.0 bm podél JZ + SZ fasády (RE-RUN §3.7)  [výkres:A105]</t>
-        </is>
-      </c>
-      <c r="J149" s="9" t="inlineStr"/>
+      <c r="E149" s="5" t="inlineStr">
+        <is>
+          <t>PSV-78x-001</t>
+        </is>
+      </c>
+      <c r="F149" s="6" t="inlineStr">
+        <is>
+          <t>Dodávka Lindab Round Downpipe 150/100 Antique White, vč. kolen a spojek</t>
+        </is>
+      </c>
+      <c r="G149" s="4" t="inlineStr">
+        <is>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="H149" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I149" s="6" t="inlineStr">
+        <is>
+          <t>4 ks (A104 DXF count working, ABMV_20: A101=3 vs A104=4)  [výkres:A104]</t>
+        </is>
+      </c>
+      <c r="J149" s="6" t="inlineStr">
+        <is>
+          <t>ABMV:ABMV_20</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="7" t="n">
@@ -4620,402 +4613,407 @@
       </c>
       <c r="E150" s="8" t="inlineStr">
         <is>
+          <t>PSV-78x-002</t>
+        </is>
+      </c>
+      <c r="F150" s="9" t="inlineStr">
+        <is>
+          <t>Montáž svodů Lindab — příchytky, kotvení do fasády</t>
+        </is>
+      </c>
+      <c r="G150" s="7" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="H150" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="I150" s="9" t="inlineStr">
+        <is>
+          <t>4 kpl (jeden na každý svod)</t>
+        </is>
+      </c>
+      <c r="J150" s="9" t="inlineStr">
+        <is>
+          <t>ABMV:ABMV_20</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="3" t="inlineStr">
+        <is>
+          <t>→ Wavin Tegra střešní vpusti — dodávka + montáž</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="7" t="n">
+        <v>95</v>
+      </c>
+      <c r="B152" s="8" t="inlineStr"/>
+      <c r="C152" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="D152" s="8" t="inlineStr">
+        <is>
+          <t>PSV-78x</t>
+        </is>
+      </c>
+      <c r="E152" s="8" t="inlineStr">
+        <is>
+          <t>PSV-78x-003</t>
+        </is>
+      </c>
+      <c r="F152" s="9" t="inlineStr">
+        <is>
+          <t>Wavin Tegra střešní vpust Round Iron Cover + Concrete Ring DN300</t>
+        </is>
+      </c>
+      <c r="G152" s="7" t="inlineStr">
+        <is>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="H152" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I152" s="9" t="inlineStr">
+        <is>
+          <t>3 ks (A101 INSERT Wavin × 3 dle DXF parse)  [výkres:A101]</t>
+        </is>
+      </c>
+      <c r="J152" s="9" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="7" t="n">
+        <v>96</v>
+      </c>
+      <c r="B153" s="8" t="inlineStr"/>
+      <c r="C153" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="D153" s="8" t="inlineStr">
+        <is>
+          <t>PSV-78x</t>
+        </is>
+      </c>
+      <c r="E153" s="8" t="inlineStr">
+        <is>
+          <t>PSV-78x-004</t>
+        </is>
+      </c>
+      <c r="F153" s="9" t="inlineStr">
+        <is>
+          <t>Montáž střešních vpustí Wavin Tegra — osazení, napojení na svody</t>
+        </is>
+      </c>
+      <c r="G153" s="7" t="inlineStr">
+        <is>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="H153" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I153" s="9">
+        <f> dodávka</f>
+        <v/>
+      </c>
+      <c r="J153" s="9" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="3" t="inlineStr">
+        <is>
+          <t>→ MEA Mearin liniový žlab + mřížka</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="7" t="n">
+        <v>97</v>
+      </c>
+      <c r="B155" s="8" t="inlineStr"/>
+      <c r="C155" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="D155" s="8" t="inlineStr">
+        <is>
+          <t>PSV-78x</t>
+        </is>
+      </c>
+      <c r="E155" s="8" t="inlineStr">
+        <is>
+          <t>PSV-78x-005</t>
+        </is>
+      </c>
+      <c r="F155" s="9" t="inlineStr">
+        <is>
+          <t>MEA Mearin Plus 3000 NW300 liniový žlab — podél JZ a SZ fasády</t>
+        </is>
+      </c>
+      <c r="G155" s="7" t="inlineStr">
+        <is>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="H155" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="I155" s="9" t="inlineStr">
+        <is>
+          <t>~30.0 bm podél JZ + SZ fasády (RE-RUN §3.7)  [výkres:A105]</t>
+        </is>
+      </c>
+      <c r="J155" s="9" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="7" t="n">
+        <v>98</v>
+      </c>
+      <c r="B156" s="8" t="inlineStr"/>
+      <c r="C156" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="D156" s="8" t="inlineStr">
+        <is>
+          <t>PSV-78x</t>
+        </is>
+      </c>
+      <c r="E156" s="8" t="inlineStr">
+        <is>
           <t>PSV-78x-006</t>
         </is>
       </c>
-      <c r="F150" s="9" t="inlineStr">
+      <c r="F156" s="9" t="inlineStr">
         <is>
           <t>Mřížka MEA Mearin Plus 3000 + osazovací rám — pochozí provedení</t>
         </is>
       </c>
-      <c r="G150" s="7" t="inlineStr">
+      <c r="G156" s="7" t="inlineStr">
         <is>
           <t>bm</t>
         </is>
       </c>
-      <c r="H150" s="7" t="n">
+      <c r="H156" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="I150" s="9">
+      <c r="I156" s="9">
         <f> liniový žlab</f>
         <v/>
       </c>
-      <c r="J150" s="9" t="inlineStr"/>
-    </row>
-    <row r="151">
-      <c r="A151" s="3" t="inlineStr">
+      <c r="J156" s="9" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="3" t="inlineStr">
         <is>
           <t>→ Ostatní oplechování (parapety, lemy)</t>
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="4" t="n">
-        <v>95</v>
-      </c>
-      <c r="B152" s="5" t="inlineStr"/>
-      <c r="C152" s="4" t="n">
+    <row r="158">
+      <c r="A158" s="4" t="n">
+        <v>99</v>
+      </c>
+      <c r="B158" s="5" t="inlineStr"/>
+      <c r="C158" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="D152" s="5" t="inlineStr">
+      <c r="D158" s="5" t="inlineStr">
         <is>
           <t>PSV-78x</t>
         </is>
       </c>
-      <c r="E152" s="5" t="inlineStr">
+      <c r="E158" s="5" t="inlineStr">
         <is>
           <t>PSV-78x-011</t>
         </is>
       </c>
-      <c r="F152" s="6" t="inlineStr">
+      <c r="F158" s="6" t="inlineStr">
         <is>
           <t>Ostatní oplechování — parapety střešních vpustí, lemy prostupů</t>
         </is>
       </c>
-      <c r="G152" s="4" t="inlineStr">
+      <c r="G158" s="4" t="inlineStr">
         <is>
           <t>bm</t>
         </is>
       </c>
-      <c r="H152" s="4" t="n">
+      <c r="H158" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="I152" s="6" t="inlineStr">
+      <c r="I158" s="6" t="inlineStr">
         <is>
           <t>placeholder ~25 bm (vpusti + prostupy)</t>
         </is>
       </c>
-      <c r="J152" s="6" t="inlineStr"/>
-    </row>
-    <row r="153" ht="22" customHeight="1">
-      <c r="A153" s="2" t="inlineStr">
+      <c r="J158" s="6" t="inlineStr"/>
+    </row>
+    <row r="159" ht="22" customHeight="1">
+      <c r="A159" s="2" t="inlineStr">
         <is>
           <t>═══ FÁZE 7: VÝPLNĚ OTVORŮ ═══</t>
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="3" t="inlineStr">
-        <is>
-          <t>→ Okna plastová — dodávka + montáž + parapet + lemy</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="4" t="n">
-        <v>96</v>
-      </c>
-      <c r="B155" s="5" t="inlineStr"/>
-      <c r="C155" s="4" t="n">
+    <row r="160">
+      <c r="A160" s="3" t="inlineStr">
+        <is>
+          <t>→ Okna plastová — dodávka (fixní + otvíravé) + montáž + parapet + lemy</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B161" s="5" t="inlineStr"/>
+      <c r="C161" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="D155" s="5" t="inlineStr">
+      <c r="D161" s="5" t="inlineStr">
         <is>
           <t>PSV-76x</t>
         </is>
       </c>
-      <c r="E155" s="5" t="inlineStr">
+      <c r="E161" s="5" t="inlineStr">
         <is>
           <t>PSV-76x-001</t>
         </is>
       </c>
-      <c r="F155" s="6" t="inlineStr">
-        <is>
-          <t>Dodávka okno plastové 1000 × 1000 mm, izol. dvojsklo Ug ≤ 1.1, barva šedá</t>
-        </is>
-      </c>
-      <c r="G155" s="4" t="inlineStr">
+      <c r="F161" s="6" t="inlineStr">
+        <is>
+          <t>Dodávka okno plastové fixní 1000 × 1000 mm, izol. dvojsklo Ug ≤ 1.1, barva šedá</t>
+        </is>
+      </c>
+      <c r="G161" s="4" t="inlineStr">
         <is>
           <t>ks</t>
         </is>
       </c>
-      <c r="H155" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="I155" s="6" t="inlineStr">
-        <is>
-          <t>21 ks (V1..V21 z DXF A101 INSERT OKNO_1k)  [výkres:A101]</t>
-        </is>
-      </c>
-      <c r="J155" s="6" t="inlineStr"/>
-    </row>
-    <row r="156">
-      <c r="A156" s="10" t="n">
-        <v>97</v>
-      </c>
-      <c r="B156" s="11" t="inlineStr"/>
-      <c r="C156" s="10" t="n">
+      <c r="H161" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="I161" s="6" t="inlineStr">
+        <is>
+          <t>29 ks fixních (z 34 oken celkem; 5 otvíravých v PSV-76x-013) — Úprava dveří POHLED OSA A/F/06/01  [výkres:A101, výkres:Hala HK_Úprava dveří]</t>
+        </is>
+      </c>
+      <c r="J161" s="6" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="10" t="n">
+        <v>101</v>
+      </c>
+      <c r="B162" s="11" t="inlineStr"/>
+      <c r="C162" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="D156" s="11" t="inlineStr">
+      <c r="D162" s="11" t="inlineStr">
         <is>
           <t>PSV-76x</t>
         </is>
       </c>
-      <c r="E156" s="11" t="inlineStr">
+      <c r="E162" s="11" t="inlineStr">
+        <is>
+          <t>PSV-76x-013</t>
+        </is>
+      </c>
+      <c r="F162" s="12" t="inlineStr">
+        <is>
+          <t>Dodávka okno plastové otvíravé 1000 × 1000 mm, izol. dvojsklo Ug ≤ 1.1, barva šedá, kování pro mikroventilaci</t>
+        </is>
+      </c>
+      <c r="G162" s="10" t="inlineStr">
+        <is>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="H162" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="I162" s="12" t="inlineStr">
+        <is>
+          <t>5 ks otvíravých z 34 oken celkem — Úprava dveří POHLED OSA A/F/06/01 user-confirmed split  [výkres:Hala HK_Úprava dveří]  · was 5.0: Úprava dveří revision — first appearance</t>
+        </is>
+      </c>
+      <c r="J162" s="12" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="4" t="n">
+        <v>102</v>
+      </c>
+      <c r="B163" s="5" t="inlineStr"/>
+      <c r="C163" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D163" s="5" t="inlineStr">
+        <is>
+          <t>PSV-76x</t>
+        </is>
+      </c>
+      <c r="E163" s="5" t="inlineStr">
         <is>
           <t>PSV-76x-002</t>
         </is>
       </c>
-      <c r="F156" s="12" t="inlineStr">
-        <is>
-          <t>Montáž okna plastového do osazovacího otvoru, vč. kotvení a pěny</t>
-        </is>
-      </c>
-      <c r="G156" s="10" t="inlineStr">
+      <c r="F163" s="6" t="inlineStr">
+        <is>
+          <t>Montáž okna plastového 1000 × 1000 mm (fixní i otvíravé) do osazovacího otvoru, vč. kotvení a pěny</t>
+        </is>
+      </c>
+      <c r="G163" s="4" t="inlineStr">
         <is>
           <t>ks</t>
         </is>
       </c>
-      <c r="H156" s="10" t="n">
-        <v>21</v>
-      </c>
-      <c r="I156" s="12">
-        <f> dodávka okna</f>
-        <v/>
-      </c>
-      <c r="J156" s="12" t="inlineStr"/>
-    </row>
-    <row r="157">
-      <c r="A157" s="4" t="n">
-        <v>98</v>
-      </c>
-      <c r="B157" s="5" t="inlineStr"/>
-      <c r="C157" s="4" t="n">
+      <c r="H163" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="I163" s="6" t="inlineStr">
+        <is>
+          <t>34 ks celkem (29 fixní + 5 otvíravé) — Úprava dveří POHLED OSA A/F/06/01  [výkres:Hala HK_Úprava dveří]</t>
+        </is>
+      </c>
+      <c r="J163" s="6" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="10" t="n">
+        <v>103</v>
+      </c>
+      <c r="B164" s="11" t="inlineStr"/>
+      <c r="C164" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="D157" s="5" t="inlineStr">
+      <c r="D164" s="11" t="inlineStr">
         <is>
           <t>PSV-76x</t>
         </is>
       </c>
-      <c r="E157" s="5" t="inlineStr">
+      <c r="E164" s="11" t="inlineStr">
         <is>
           <t>PSV-76x-003</t>
         </is>
       </c>
-      <c r="F157" s="6" t="inlineStr">
+      <c r="F164" s="12" t="inlineStr">
         <is>
           <t>Vnější parapet pozinkovaný plech, š. 200 mm, s krytkami</t>
         </is>
       </c>
-      <c r="G157" s="4" t="inlineStr">
+      <c r="G164" s="10" t="inlineStr">
         <is>
           <t>bm</t>
         </is>
       </c>
-      <c r="H157" s="4" t="n">
-        <v>22.05</v>
-      </c>
-      <c r="I157" s="6" t="inlineStr">
-        <is>
-          <t>21 ks × 1.05 m (šířka okna + přesah)</t>
-        </is>
-      </c>
-      <c r="J157" s="6" t="inlineStr"/>
-    </row>
-    <row r="158">
-      <c r="A158" s="7" t="n">
-        <v>99</v>
-      </c>
-      <c r="B158" s="8" t="inlineStr"/>
-      <c r="C158" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="D158" s="8" t="inlineStr">
-        <is>
-          <t>PSV-76x</t>
-        </is>
-      </c>
-      <c r="E158" s="8" t="inlineStr">
-        <is>
-          <t>PSV-76x-004</t>
-        </is>
-      </c>
-      <c r="F158" s="9" t="inlineStr">
-        <is>
-          <t>Vnější okenní lemy plastové — rohové + nadokenní</t>
-        </is>
-      </c>
-      <c r="G158" s="7" t="inlineStr">
-        <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="H158" s="7" t="n">
-        <v>63</v>
-      </c>
-      <c r="I158" s="9" t="inlineStr">
-        <is>
-          <t>21 ks × 3 bm (perimetr 3 stran, parapet samostatně)</t>
-        </is>
-      </c>
-      <c r="J158" s="9" t="inlineStr"/>
-    </row>
-    <row r="159">
-      <c r="A159" s="3" t="inlineStr">
-        <is>
-          <t>→ Sekční vrata 3500×4000 — dodávka + pohon + montáž</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="B160" s="5" t="inlineStr"/>
-      <c r="C160" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="D160" s="5" t="inlineStr">
-        <is>
-          <t>PSV-76x</t>
-        </is>
-      </c>
-      <c r="E160" s="5" t="inlineStr">
-        <is>
-          <t>PSV-76x-005</t>
-        </is>
-      </c>
-      <c r="F160" s="6" t="inlineStr">
-        <is>
-          <t>Dodávka sekční vrata 3500 × 4000 mm (š × v) s tepelněizolační výplní, motorická</t>
-        </is>
-      </c>
-      <c r="G160" s="4" t="inlineStr">
-        <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="H160" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="I160" s="6" t="inlineStr">
-        <is>
-          <t>4 ks (DXF A101 INSERT 'Vrata sekční' = 4)  [výkres:A101, TZ:3.2]</t>
-        </is>
-      </c>
-      <c r="J160" s="6" t="inlineStr"/>
-    </row>
-    <row r="161">
-      <c r="A161" s="7" t="n">
-        <v>101</v>
-      </c>
-      <c r="B161" s="8" t="inlineStr"/>
-      <c r="C161" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="D161" s="8" t="inlineStr">
-        <is>
-          <t>PSV-76x</t>
-        </is>
-      </c>
-      <c r="E161" s="8" t="inlineStr">
-        <is>
-          <t>PSV-76x-006</t>
-        </is>
-      </c>
-      <c r="F161" s="9" t="inlineStr">
-        <is>
-          <t>Elektrický pohon vrat sekčních s dálkovým ovládáním + nouzové odblokování</t>
-        </is>
-      </c>
-      <c r="G161" s="7" t="inlineStr">
-        <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="H161" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="I161" s="9" t="inlineStr">
-        <is>
-          <t>4 ks pohon (jeden na každá vrata)</t>
-        </is>
-      </c>
-      <c r="J161" s="9" t="inlineStr"/>
-    </row>
-    <row r="162">
-      <c r="A162" s="7" t="n">
-        <v>102</v>
-      </c>
-      <c r="B162" s="8" t="inlineStr"/>
-      <c r="C162" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="D162" s="8" t="inlineStr">
-        <is>
-          <t>PSV-76x</t>
-        </is>
-      </c>
-      <c r="E162" s="8" t="inlineStr">
-        <is>
-          <t>PSV-76x-007</t>
-        </is>
-      </c>
-      <c r="F162" s="9" t="inlineStr">
-        <is>
-          <t>Nouzové ruční odblokování vrat sekčních — pro výpadek el.</t>
-        </is>
-      </c>
-      <c r="G162" s="7" t="inlineStr">
-        <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="H162" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="I162" s="9" t="inlineStr">
-        <is>
-          <t>4 ks ruční odblok</t>
-        </is>
-      </c>
-      <c r="J162" s="9" t="inlineStr"/>
-    </row>
-    <row r="163">
-      <c r="A163" s="7" t="n">
-        <v>103</v>
-      </c>
-      <c r="B163" s="8" t="inlineStr"/>
-      <c r="C163" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="D163" s="8" t="inlineStr">
-        <is>
-          <t>PSV-76x</t>
-        </is>
-      </c>
-      <c r="E163" s="8" t="inlineStr">
-        <is>
-          <t>PSV-76x-008</t>
-        </is>
-      </c>
-      <c r="F163" s="9" t="inlineStr">
-        <is>
-          <t>Montáž sekčních vrat — osazení do otvoru, ukotvení, nastavení</t>
-        </is>
-      </c>
-      <c r="G163" s="7" t="inlineStr">
-        <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="H163" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="I163" s="9">
-        <f> dodávka vrat</f>
-        <v/>
-      </c>
-      <c r="J163" s="9" t="inlineStr"/>
-    </row>
-    <row r="164">
-      <c r="A164" s="3" t="inlineStr">
-        <is>
-          <t>→ Vnější 2-křídlé dveře — dodávka + montáž + zámek + práh</t>
-        </is>
-      </c>
+      <c r="H164" s="10" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="I164" s="12" t="inlineStr">
+        <is>
+          <t>34 ks × 1.05 m (šířka okna + přesah) = 35.7 bm — Úprava dveří 34 oken  [výkres:Hala HK_Úprava dveří]</t>
+        </is>
+      </c>
+      <c r="J164" s="12" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="7" t="n">
@@ -5032,364 +5030,425 @@
       </c>
       <c r="E165" s="8" t="inlineStr">
         <is>
+          <t>PSV-76x-004</t>
+        </is>
+      </c>
+      <c r="F165" s="9" t="inlineStr">
+        <is>
+          <t>Vnější okenní lemy plastové — rohové + nadokenní</t>
+        </is>
+      </c>
+      <c r="G165" s="7" t="inlineStr">
+        <is>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="H165" s="7" t="n">
+        <v>102</v>
+      </c>
+      <c r="I165" s="9" t="inlineStr">
+        <is>
+          <t>34 ks × 3 bm (perimetr 3 stran, parapet samostatně) = 102 bm — Úprava dveří 34 oken  [výkres:Hala HK_Úprava dveří]</t>
+        </is>
+      </c>
+      <c r="J165" s="9" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="3" t="inlineStr">
+        <is>
+          <t>→ Sekční vrata 3500×4000 — dodávka + pohon + montáž</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="4" t="n">
+        <v>105</v>
+      </c>
+      <c r="B167" s="5" t="inlineStr"/>
+      <c r="C167" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D167" s="5" t="inlineStr">
+        <is>
+          <t>PSV-76x</t>
+        </is>
+      </c>
+      <c r="E167" s="5" t="inlineStr">
+        <is>
+          <t>PSV-76x-005</t>
+        </is>
+      </c>
+      <c r="F167" s="6" t="inlineStr">
+        <is>
+          <t>Dodávka sekční vrata 3500 × 4000 mm (š × v) s tepelněizolační výplní, motorická</t>
+        </is>
+      </c>
+      <c r="G167" s="4" t="inlineStr">
+        <is>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="H167" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I167" s="6" t="inlineStr">
+        <is>
+          <t>4 ks (DXF A101 INSERT 'Vrata sekční' = 4)  [výkres:A101, TZ:3.2]</t>
+        </is>
+      </c>
+      <c r="J167" s="6" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="7" t="n">
+        <v>106</v>
+      </c>
+      <c r="B168" s="8" t="inlineStr"/>
+      <c r="C168" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="D168" s="8" t="inlineStr">
+        <is>
+          <t>PSV-76x</t>
+        </is>
+      </c>
+      <c r="E168" s="8" t="inlineStr">
+        <is>
+          <t>PSV-76x-006</t>
+        </is>
+      </c>
+      <c r="F168" s="9" t="inlineStr">
+        <is>
+          <t>Elektrický pohon vrat sekčních s dálkovým ovládáním + nouzové odblokování</t>
+        </is>
+      </c>
+      <c r="G168" s="7" t="inlineStr">
+        <is>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="H168" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="I168" s="9" t="inlineStr">
+        <is>
+          <t>4 ks pohon (jeden na každá vrata)</t>
+        </is>
+      </c>
+      <c r="J168" s="9" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="7" t="n">
+        <v>107</v>
+      </c>
+      <c r="B169" s="8" t="inlineStr"/>
+      <c r="C169" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="D169" s="8" t="inlineStr">
+        <is>
+          <t>PSV-76x</t>
+        </is>
+      </c>
+      <c r="E169" s="8" t="inlineStr">
+        <is>
+          <t>PSV-76x-007</t>
+        </is>
+      </c>
+      <c r="F169" s="9" t="inlineStr">
+        <is>
+          <t>Nouzové ruční odblokování vrat sekčních — pro výpadek el.</t>
+        </is>
+      </c>
+      <c r="G169" s="7" t="inlineStr">
+        <is>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="H169" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="I169" s="9" t="inlineStr">
+        <is>
+          <t>4 ks ruční odblok</t>
+        </is>
+      </c>
+      <c r="J169" s="9" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="7" t="n">
+        <v>108</v>
+      </c>
+      <c r="B170" s="8" t="inlineStr"/>
+      <c r="C170" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="D170" s="8" t="inlineStr">
+        <is>
+          <t>PSV-76x</t>
+        </is>
+      </c>
+      <c r="E170" s="8" t="inlineStr">
+        <is>
+          <t>PSV-76x-008</t>
+        </is>
+      </c>
+      <c r="F170" s="9" t="inlineStr">
+        <is>
+          <t>Montáž sekčních vrat — osazení do otvoru, ukotvení, nastavení</t>
+        </is>
+      </c>
+      <c r="G170" s="7" t="inlineStr">
+        <is>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="H170" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="I170" s="9">
+        <f> dodávka vrat</f>
+        <v/>
+      </c>
+      <c r="J170" s="9" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="3" t="inlineStr">
+        <is>
+          <t>→ Vnější 2-křídlé dveře — dodávka + montáž + zámek + práh</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="7" t="n">
+        <v>109</v>
+      </c>
+      <c r="B172" s="8" t="inlineStr"/>
+      <c r="C172" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="D172" s="8" t="inlineStr">
+        <is>
+          <t>PSV-76x</t>
+        </is>
+      </c>
+      <c r="E172" s="8" t="inlineStr">
+        <is>
           <t>PSV-76x-009</t>
         </is>
       </c>
-      <c r="F165" s="9" t="inlineStr">
-        <is>
-          <t>Dodávka vnější dvoukřídlé dveře 1050 × 2100 mm, izol. plnostěnné, klika a zámek</t>
-        </is>
-      </c>
-      <c r="G165" s="7" t="inlineStr">
+      <c r="F172" s="9" t="inlineStr">
+        <is>
+          <t>Dodávka vnější dvoukřídlé dveře plastové 1050 × 2100 mm, izol. plnostěnné, klika a zámek</t>
+        </is>
+      </c>
+      <c r="G172" s="7" t="inlineStr">
         <is>
           <t>ks</t>
         </is>
       </c>
-      <c r="H165" s="7" t="n">
+      <c r="H172" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="I165" s="9" t="inlineStr">
-        <is>
-          <t>2 ks (DXF A101 INSERT 'Vnější dveře dvoukřídlé')  [výkres:A101]</t>
-        </is>
-      </c>
-      <c r="J165" s="9" t="inlineStr"/>
-    </row>
-    <row r="166">
-      <c r="A166" s="7" t="n">
-        <v>105</v>
-      </c>
-      <c r="B166" s="8" t="inlineStr"/>
-      <c r="C166" s="7" t="n">
+      <c r="I172" s="9" t="inlineStr">
+        <is>
+          <t>2 ks (Úprava dveří potvrzeno) — materiál plastové dle user expectation, čeká finální potvrzení projektantem  [výkres:A101, výkres:Hala HK_Úprava dveří]</t>
+        </is>
+      </c>
+      <c r="J172" s="9" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="7" t="n">
+        <v>110</v>
+      </c>
+      <c r="B173" s="8" t="inlineStr"/>
+      <c r="C173" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="D166" s="8" t="inlineStr">
+      <c r="D173" s="8" t="inlineStr">
         <is>
           <t>PSV-76x</t>
         </is>
       </c>
-      <c r="E166" s="8" t="inlineStr">
+      <c r="E173" s="8" t="inlineStr">
         <is>
           <t>PSV-76x-010</t>
         </is>
       </c>
-      <c r="F166" s="9" t="inlineStr">
+      <c r="F173" s="9" t="inlineStr">
         <is>
           <t>Montáž vnějších 2-křídlých dveří — osazení, kotvení, pěna</t>
         </is>
       </c>
-      <c r="G166" s="7" t="inlineStr">
+      <c r="G173" s="7" t="inlineStr">
         <is>
           <t>ks</t>
         </is>
       </c>
-      <c r="H166" s="7" t="n">
+      <c r="H173" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="I166" s="9">
+      <c r="I173" s="9">
         <f> dodávka dveří</f>
         <v/>
       </c>
-      <c r="J166" s="9" t="inlineStr"/>
-    </row>
-    <row r="167">
-      <c r="A167" s="7" t="n">
-        <v>106</v>
-      </c>
-      <c r="B167" s="8" t="inlineStr"/>
-      <c r="C167" s="7" t="n">
+      <c r="J173" s="9" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="7" t="n">
+        <v>111</v>
+      </c>
+      <c r="B174" s="8" t="inlineStr"/>
+      <c r="C174" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="D167" s="8" t="inlineStr">
+      <c r="D174" s="8" t="inlineStr">
         <is>
           <t>PSV-76x</t>
         </is>
       </c>
-      <c r="E167" s="8" t="inlineStr">
+      <c r="E174" s="8" t="inlineStr">
         <is>
           <t>PSV-76x-011</t>
         </is>
       </c>
-      <c r="F167" s="9" t="inlineStr">
+      <c r="F174" s="9" t="inlineStr">
         <is>
           <t>Kompletní zámkový systém + klika pro vnější 2-křídlé dveře</t>
         </is>
       </c>
-      <c r="G167" s="7" t="inlineStr">
+      <c r="G174" s="7" t="inlineStr">
         <is>
           <t>kpl</t>
         </is>
       </c>
-      <c r="H167" s="7" t="n">
+      <c r="H174" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="I167" s="9" t="inlineStr">
+      <c r="I174" s="9" t="inlineStr">
         <is>
           <t>2 kpl</t>
         </is>
       </c>
-      <c r="J167" s="9" t="inlineStr"/>
-    </row>
-    <row r="168">
-      <c r="A168" s="10" t="n">
-        <v>107</v>
-      </c>
-      <c r="B168" s="11" t="inlineStr"/>
-      <c r="C168" s="10" t="n">
+      <c r="J174" s="9" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="10" t="n">
+        <v>112</v>
+      </c>
+      <c r="B175" s="11" t="inlineStr"/>
+      <c r="C175" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="D168" s="11" t="inlineStr">
+      <c r="D175" s="11" t="inlineStr">
         <is>
           <t>PSV-76x</t>
         </is>
       </c>
-      <c r="E168" s="11" t="inlineStr">
+      <c r="E175" s="11" t="inlineStr">
         <is>
           <t>PSV-76x-012</t>
         </is>
       </c>
-      <c r="F168" s="12" t="inlineStr">
+      <c r="F175" s="12" t="inlineStr">
         <is>
           <t>Práh + lemování ostění vnějších dveří — pozink plech</t>
         </is>
       </c>
-      <c r="G168" s="10" t="inlineStr">
+      <c r="G175" s="10" t="inlineStr">
         <is>
           <t>kpl</t>
         </is>
       </c>
-      <c r="H168" s="10" t="n">
+      <c r="H175" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="I168" s="12" t="inlineStr">
+      <c r="I175" s="12" t="inlineStr">
         <is>
           <t>2 kpl</t>
         </is>
       </c>
-      <c r="J168" s="12" t="inlineStr"/>
-    </row>
-    <row r="169" ht="22" customHeight="1">
-      <c r="A169" s="2" t="inlineStr">
+      <c r="J175" s="12" t="inlineStr"/>
+    </row>
+    <row r="176" ht="22" customHeight="1">
+      <c r="A176" s="2" t="inlineStr">
         <is>
           <t>═══ FÁZE 8: IZOLACE + SOKL ═══</t>
         </is>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" s="3" t="inlineStr">
+    <row r="177">
+      <c r="A177" s="3" t="inlineStr">
         <is>
           <t>→ Penetrace soklu</t>
         </is>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" s="4" t="n">
-        <v>108</v>
-      </c>
-      <c r="B171" s="5" t="inlineStr"/>
-      <c r="C171" s="4" t="n">
+    <row r="178">
+      <c r="A178" s="4" t="n">
+        <v>113</v>
+      </c>
+      <c r="B178" s="5" t="inlineStr"/>
+      <c r="C178" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="D171" s="5" t="inlineStr">
+      <c r="D178" s="5" t="inlineStr">
         <is>
           <t>PSV-71x</t>
         </is>
       </c>
-      <c r="E171" s="5" t="inlineStr">
+      <c r="E178" s="5" t="inlineStr">
         <is>
           <t>PSV-71x-001</t>
         </is>
       </c>
-      <c r="F171" s="6" t="inlineStr">
+      <c r="F178" s="6" t="inlineStr">
         <is>
           <t>Penetrace soklu — penetrační nátěr pod hydroizolaci</t>
         </is>
       </c>
-      <c r="G171" s="4" t="inlineStr">
+      <c r="G178" s="4" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="H171" s="4" t="n">
+      <c r="H178" s="4" t="n">
         <v>28.5</v>
       </c>
-      <c r="I171" s="6" t="inlineStr">
+      <c r="I178" s="6" t="inlineStr">
         <is>
           <t>95.0 bm × 0.3 m = 28.5 m²</t>
         </is>
       </c>
-      <c r="J171" s="6" t="inlineStr"/>
-    </row>
-    <row r="172">
-      <c r="A172" s="3" t="inlineStr">
-        <is>
-          <t>→ Hydroizolace svislá soklu — SBS pás</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" s="4" t="n">
-        <v>109</v>
-      </c>
-      <c r="B173" s="5" t="inlineStr"/>
-      <c r="C173" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="D173" s="5" t="inlineStr">
-        <is>
-          <t>PSV-71x</t>
-        </is>
-      </c>
-      <c r="E173" s="5" t="inlineStr">
-        <is>
-          <t>PSV-71x-002</t>
-        </is>
-      </c>
-      <c r="F173" s="6" t="inlineStr">
-        <is>
-          <t>Hydroizolace svislá soklu — SBS modifikovaný asfaltový pás, natavený</t>
-        </is>
-      </c>
-      <c r="G173" s="4" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="H173" s="4" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="I173" s="6" t="inlineStr">
-        <is>
-          <t>95.0 bm × 0.3 m = 28.5 m²  [TZ:B]</t>
-        </is>
-      </c>
-      <c r="J173" s="6" t="inlineStr"/>
-    </row>
-    <row r="174">
-      <c r="A174" s="3" t="inlineStr">
-        <is>
-          <t>→ Hydroizolační lišty rohové + napojení</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" s="7" t="n">
-        <v>110</v>
-      </c>
-      <c r="B175" s="8" t="inlineStr"/>
-      <c r="C175" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="D175" s="8" t="inlineStr">
-        <is>
-          <t>PSV-71x</t>
-        </is>
-      </c>
-      <c r="E175" s="8" t="inlineStr">
-        <is>
-          <t>PSV-71x-003</t>
-        </is>
-      </c>
-      <c r="F175" s="9" t="inlineStr">
-        <is>
-          <t>Hydroizolační lišty rohové + napojení svislé na vodorovnou pásku</t>
-        </is>
-      </c>
-      <c r="G175" s="7" t="inlineStr">
-        <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="H175" s="7" t="n">
-        <v>95</v>
-      </c>
-      <c r="I175" s="9" t="inlineStr">
-        <is>
-          <t>obvod 95.0 bm</t>
-        </is>
-      </c>
-      <c r="J175" s="9" t="inlineStr"/>
-    </row>
-    <row r="176">
-      <c r="A176" s="3" t="inlineStr">
-        <is>
-          <t>→ Ochranná vrstva — nopová folie HDPE</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" s="7" t="n">
-        <v>111</v>
-      </c>
-      <c r="B177" s="8" t="inlineStr"/>
-      <c r="C177" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="D177" s="8" t="inlineStr">
-        <is>
-          <t>PSV-71x</t>
-        </is>
-      </c>
-      <c r="E177" s="8" t="inlineStr">
-        <is>
-          <t>PSV-71x-004</t>
-        </is>
-      </c>
-      <c r="F177" s="9" t="inlineStr">
-        <is>
-          <t>Ochranná vrstva hydroizolace — nopová folie HDPE, š. 0.5 m</t>
-        </is>
-      </c>
-      <c r="G177" s="7" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="H177" s="7" t="n">
-        <v>47.5</v>
-      </c>
-      <c r="I177" s="9" t="inlineStr">
-        <is>
-          <t>95.0 bm × 0.5 m</t>
-        </is>
-      </c>
-      <c r="J177" s="9" t="inlineStr"/>
-    </row>
-    <row r="178" ht="22" customHeight="1">
-      <c r="A178" s="2" t="inlineStr">
-        <is>
-          <t>═══ FÁZE 9: PODLAHA PRŮMYSLOVÁ ═══</t>
-        </is>
-      </c>
+      <c r="J178" s="6" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" s="3" t="inlineStr">
         <is>
-          <t>→ Penetrace + primer pod stěrku</t>
+          <t>→ Hydroizolace svislá soklu — SBS pás</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="4" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B180" s="5" t="inlineStr"/>
       <c r="C180" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D180" s="5" t="inlineStr">
         <is>
-          <t>PSV-77x</t>
+          <t>PSV-71x</t>
         </is>
       </c>
       <c r="E180" s="5" t="inlineStr">
         <is>
-          <t>PSV-77x-001</t>
+          <t>PSV-71x-002</t>
         </is>
       </c>
       <c r="F180" s="6" t="inlineStr">
         <is>
-          <t>Penetrace + primer pod průmyslovou stěrku podlahy</t>
+          <t>Hydroizolace svislá soklu — SBS modifikovaný asfaltový pás, natavený</t>
         </is>
       </c>
       <c r="G180" s="4" t="inlineStr">
@@ -5398,11 +5457,11 @@
         </is>
       </c>
       <c r="H180" s="4" t="n">
-        <v>495</v>
+        <v>28.5</v>
       </c>
       <c r="I180" s="6" t="inlineStr">
         <is>
-          <t>495.0 m² (celá plocha podlahy)</t>
+          <t>95.0 bm × 0.3 m = 28.5 m²  [TZ:B]</t>
         </is>
       </c>
       <c r="J180" s="6" t="inlineStr"/>
@@ -5410,465 +5469,434 @@
     <row r="181">
       <c r="A181" s="3" t="inlineStr">
         <is>
-          <t>→ Epoxidová / PU stěrka 4–5 mm</t>
+          <t>→ Hydroizolační lišty rohové + napojení</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="7" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B182" s="8" t="inlineStr"/>
       <c r="C182" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D182" s="8" t="inlineStr">
         <is>
-          <t>PSV-77x</t>
+          <t>PSV-71x</t>
         </is>
       </c>
       <c r="E182" s="8" t="inlineStr">
         <is>
-          <t>PSV-77x-002</t>
+          <t>PSV-71x-003</t>
         </is>
       </c>
       <c r="F182" s="9" t="inlineStr">
         <is>
-          <t>Průmyslová epoxidová / PU stěrka podlahy tl. 4-5 mm, zatížení 1600 kg/m²</t>
+          <t>Hydroizolační lišty rohové + napojení svislé na vodorovnou pásku</t>
         </is>
       </c>
       <c r="G182" s="7" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="H182" s="7" t="n">
-        <v>495</v>
+        <v>95</v>
       </c>
       <c r="I182" s="9" t="inlineStr">
         <is>
-          <t>495.0 m²  [TZ:podlaha]</t>
-        </is>
-      </c>
-      <c r="J182" s="9" t="inlineStr">
-        <is>
-          <t>ABMV:ABMV_10</t>
-        </is>
-      </c>
+          <t>obvod 95.0 bm</t>
+        </is>
+      </c>
+      <c r="J182" s="9" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="3" t="inlineStr">
         <is>
-          <t>→ Lokální zesílení anchorage zón strojů</t>
+          <t>→ Ochranná vrstva — nopová folie HDPE</t>
         </is>
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="4" t="n">
-        <v>114</v>
-      </c>
-      <c r="B184" s="5" t="inlineStr"/>
-      <c r="C184" s="4" t="n">
+      <c r="A184" s="7" t="n">
+        <v>116</v>
+      </c>
+      <c r="B184" s="8" t="inlineStr"/>
+      <c r="C184" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="D184" s="8" t="inlineStr">
+        <is>
+          <t>PSV-71x</t>
+        </is>
+      </c>
+      <c r="E184" s="8" t="inlineStr">
+        <is>
+          <t>PSV-71x-004</t>
+        </is>
+      </c>
+      <c r="F184" s="9" t="inlineStr">
+        <is>
+          <t>Ochranná vrstva hydroizolace — nopová folie HDPE, š. 0.5 m</t>
+        </is>
+      </c>
+      <c r="G184" s="7" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="H184" s="7" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="I184" s="9" t="inlineStr">
+        <is>
+          <t>95.0 bm × 0.5 m</t>
+        </is>
+      </c>
+      <c r="J184" s="9" t="inlineStr"/>
+    </row>
+    <row r="185" ht="22" customHeight="1">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>═══ FÁZE 9: PODLAHA PRŮMYSLOVÁ ═══</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="3" t="inlineStr">
+        <is>
+          <t>→ Penetrace + primer pod stěrku</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="4" t="n">
+        <v>117</v>
+      </c>
+      <c r="B187" s="5" t="inlineStr"/>
+      <c r="C187" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="D184" s="5" t="inlineStr">
+      <c r="D187" s="5" t="inlineStr">
         <is>
           <t>PSV-77x</t>
         </is>
       </c>
-      <c r="E184" s="5" t="inlineStr">
-        <is>
-          <t>PSV-77x-003</t>
-        </is>
-      </c>
-      <c r="F184" s="6" t="inlineStr">
-        <is>
-          <t>Lokální zesílení podlahy v anchorage zónách strojů — vyšší tl. stěrky 8 mm</t>
-        </is>
-      </c>
-      <c r="G184" s="4" t="inlineStr">
+      <c r="E187" s="5" t="inlineStr">
+        <is>
+          <t>PSV-77x-001</t>
+        </is>
+      </c>
+      <c r="F187" s="6" t="inlineStr">
+        <is>
+          <t>Penetrace + primer pod průmyslovou stěrku podlahy</t>
+        </is>
+      </c>
+      <c r="G187" s="4" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="H184" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="I184" s="6" t="inlineStr">
-        <is>
-          <t>placeholder ~30 m² (3 stroje × ~10 m² každé anchorage zóna)  [výkres:A107]</t>
-        </is>
-      </c>
-      <c r="J184" s="6" t="inlineStr">
-        <is>
-          <t>ABMV:ABMV_3,ABMV_16</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" s="3" t="inlineStr">
-        <is>
-          <t>→ Dilatace + lemy + protiskluz</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" s="7" t="n">
-        <v>115</v>
-      </c>
-      <c r="B186" s="8" t="inlineStr"/>
-      <c r="C186" s="7" t="n">
+      <c r="H187" s="4" t="n">
+        <v>495</v>
+      </c>
+      <c r="I187" s="6" t="inlineStr">
+        <is>
+          <t>495.0 m² (celá plocha podlahy)</t>
+        </is>
+      </c>
+      <c r="J187" s="6" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="3" t="inlineStr">
+        <is>
+          <t>→ Epoxidová / PU stěrka 4–5 mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="7" t="n">
+        <v>118</v>
+      </c>
+      <c r="B189" s="8" t="inlineStr"/>
+      <c r="C189" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="D186" s="8" t="inlineStr">
+      <c r="D189" s="8" t="inlineStr">
         <is>
           <t>PSV-77x</t>
         </is>
       </c>
-      <c r="E186" s="8" t="inlineStr">
-        <is>
-          <t>PSV-77x-004</t>
-        </is>
-      </c>
-      <c r="F186" s="9" t="inlineStr">
-        <is>
-          <t>Dilatační lišty podlahy — kovové, řezané spáry á 6 m</t>
-        </is>
-      </c>
-      <c r="G186" s="7" t="inlineStr">
-        <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="H186" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="I186" s="9" t="inlineStr">
-        <is>
-          <t>placeholder ~60 bm (pole dilatace á 6 m na 495 m² ploše)</t>
-        </is>
-      </c>
-      <c r="J186" s="9" t="inlineStr"/>
-    </row>
-    <row r="187">
-      <c r="A187" s="7" t="n">
-        <v>116</v>
-      </c>
-      <c r="B187" s="8" t="inlineStr"/>
-      <c r="C187" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="D187" s="8" t="inlineStr">
-        <is>
-          <t>PSV-77x</t>
-        </is>
-      </c>
-      <c r="E187" s="8" t="inlineStr">
-        <is>
-          <t>PSV-77x-005</t>
-        </is>
-      </c>
-      <c r="F187" s="9" t="inlineStr">
-        <is>
-          <t>Lemovací úhelníky podlahy — pozink po obvodu stěrky</t>
-        </is>
-      </c>
-      <c r="G187" s="7" t="inlineStr">
-        <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="H187" s="7" t="n">
-        <v>95</v>
-      </c>
-      <c r="I187" s="9" t="inlineStr">
-        <is>
-          <t>obvod desky 95 bm</t>
-        </is>
-      </c>
-      <c r="J187" s="9" t="inlineStr"/>
-    </row>
-    <row r="188">
-      <c r="A188" s="7" t="n">
-        <v>117</v>
-      </c>
-      <c r="B188" s="8" t="inlineStr"/>
-      <c r="C188" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="D188" s="8" t="inlineStr">
-        <is>
-          <t>PSV-77x</t>
-        </is>
-      </c>
-      <c r="E188" s="8" t="inlineStr">
-        <is>
-          <t>PSV-77x-006</t>
-        </is>
-      </c>
-      <c r="F188" s="9" t="inlineStr">
-        <is>
-          <t>Protiskluzový posyp křemičitým pískem — pro PU variantu</t>
-        </is>
-      </c>
-      <c r="G188" s="7" t="inlineStr">
+      <c r="E189" s="8" t="inlineStr">
+        <is>
+          <t>PSV-77x-002</t>
+        </is>
+      </c>
+      <c r="F189" s="9" t="inlineStr">
+        <is>
+          <t>Průmyslová epoxidová / PU stěrka podlahy tl. 4-5 mm, zatížení 1600 kg/m²</t>
+        </is>
+      </c>
+      <c r="G189" s="7" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="H188" s="7" t="n">
+      <c r="H189" s="7" t="n">
         <v>495</v>
       </c>
-      <c r="I188" s="9" t="inlineStr">
-        <is>
-          <t>495.0 m² (pokud zvolena PU varianta)</t>
-        </is>
-      </c>
-      <c r="J188" s="9" t="inlineStr">
+      <c r="I189" s="9" t="inlineStr">
+        <is>
+          <t>495.0 m²  [TZ:podlaha]</t>
+        </is>
+      </c>
+      <c r="J189" s="9" t="inlineStr">
         <is>
           <t>ABMV:ABMV_10</t>
-        </is>
-      </c>
-    </row>
-    <row r="189" ht="22" customHeight="1">
-      <c r="A189" s="2" t="inlineStr">
-        <is>
-          <t>═══ FÁZE 10: OSTATNÍ + PŘESUN HMOT ═══</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="3" t="inlineStr">
         <is>
-          <t>→ Přesun hmot HSV vodorovně</t>
+          <t>→ Lokální zesílení anchorage zón strojů</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="4" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B191" s="5" t="inlineStr"/>
       <c r="C191" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D191" s="5" t="inlineStr">
         <is>
-          <t>HSV-9</t>
+          <t>PSV-77x</t>
         </is>
       </c>
       <c r="E191" s="5" t="inlineStr">
         <is>
-          <t>HSV-9-001</t>
+          <t>PSV-77x-003</t>
         </is>
       </c>
       <c r="F191" s="6" t="inlineStr">
         <is>
-          <t>Přesun hmot HSV vodorovně — beton, výztuž, ocel, klempířina</t>
+          <t>Lokální zesílení podlahy v anchorage zónách strojů — vyšší tl. stěrky 8 mm</t>
         </is>
       </c>
       <c r="G191" s="4" t="inlineStr">
         <is>
-          <t>t·km</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="H191" s="4" t="n">
-        <v>200</v>
+        <v>30</v>
       </c>
       <c r="I191" s="6" t="inlineStr">
         <is>
-          <t>placeholder 200 t·km (in-site přesuny, default)</t>
-        </is>
-      </c>
-      <c r="J191" s="6" t="inlineStr"/>
+          <t>placeholder ~30 m² (3 stroje × ~10 m² každé anchorage zóna)  [výkres:A107]</t>
+        </is>
+      </c>
+      <c r="J191" s="6" t="inlineStr">
+        <is>
+          <t>ABMV:ABMV_3,ABMV_16</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="3" t="inlineStr">
         <is>
-          <t>→ Doprava materiálu na stavbu — paušál</t>
+          <t>→ Dilatace + lemy + protiskluz</t>
         </is>
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="4" t="n">
-        <v>119</v>
-      </c>
-      <c r="B193" s="5" t="inlineStr"/>
-      <c r="C193" s="4" t="n">
+      <c r="A193" s="7" t="n">
+        <v>120</v>
+      </c>
+      <c r="B193" s="8" t="inlineStr"/>
+      <c r="C193" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="D193" s="8" t="inlineStr">
+        <is>
+          <t>PSV-77x</t>
+        </is>
+      </c>
+      <c r="E193" s="8" t="inlineStr">
+        <is>
+          <t>PSV-77x-004</t>
+        </is>
+      </c>
+      <c r="F193" s="9" t="inlineStr">
+        <is>
+          <t>Dilatační lišty podlahy — kovové, řezané spáry á 6 m</t>
+        </is>
+      </c>
+      <c r="G193" s="7" t="inlineStr">
+        <is>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="H193" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="I193" s="9" t="inlineStr">
+        <is>
+          <t>placeholder ~60 bm (pole dilatace á 6 m na 495 m² ploše)</t>
+        </is>
+      </c>
+      <c r="J193" s="9" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="7" t="n">
+        <v>121</v>
+      </c>
+      <c r="B194" s="8" t="inlineStr"/>
+      <c r="C194" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="D194" s="8" t="inlineStr">
+        <is>
+          <t>PSV-77x</t>
+        </is>
+      </c>
+      <c r="E194" s="8" t="inlineStr">
+        <is>
+          <t>PSV-77x-005</t>
+        </is>
+      </c>
+      <c r="F194" s="9" t="inlineStr">
+        <is>
+          <t>Lemovací úhelníky podlahy — pozink po obvodu stěrky</t>
+        </is>
+      </c>
+      <c r="G194" s="7" t="inlineStr">
+        <is>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="H194" s="7" t="n">
+        <v>95</v>
+      </c>
+      <c r="I194" s="9" t="inlineStr">
+        <is>
+          <t>obvod desky 95 bm</t>
+        </is>
+      </c>
+      <c r="J194" s="9" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="7" t="n">
+        <v>122</v>
+      </c>
+      <c r="B195" s="8" t="inlineStr"/>
+      <c r="C195" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="D195" s="8" t="inlineStr">
+        <is>
+          <t>PSV-77x</t>
+        </is>
+      </c>
+      <c r="E195" s="8" t="inlineStr">
+        <is>
+          <t>PSV-77x-006</t>
+        </is>
+      </c>
+      <c r="F195" s="9" t="inlineStr">
+        <is>
+          <t>Protiskluzový posyp křemičitým pískem — pro PU variantu</t>
+        </is>
+      </c>
+      <c r="G195" s="7" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="H195" s="7" t="n">
+        <v>495</v>
+      </c>
+      <c r="I195" s="9" t="inlineStr">
+        <is>
+          <t>495.0 m² (pokud zvolena PU varianta)</t>
+        </is>
+      </c>
+      <c r="J195" s="9" t="inlineStr">
+        <is>
+          <t>ABMV:ABMV_10</t>
+        </is>
+      </c>
+    </row>
+    <row r="196" ht="22" customHeight="1">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>═══ FÁZE 10: OSTATNÍ + PŘESUN HMOT ═══</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="3" t="inlineStr">
+        <is>
+          <t>→ Přesun hmot HSV vodorovně</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="4" t="n">
+        <v>123</v>
+      </c>
+      <c r="B198" s="5" t="inlineStr"/>
+      <c r="C198" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="D193" s="5" t="inlineStr">
-        <is>
-          <t>VRN</t>
-        </is>
-      </c>
-      <c r="E193" s="5" t="inlineStr">
-        <is>
-          <t>VRN-013</t>
-        </is>
-      </c>
-      <c r="F193" s="6" t="inlineStr">
-        <is>
-          <t>Doprava materiálu na stavbu vodorovně — paušál pro veškerou montáž</t>
-        </is>
-      </c>
-      <c r="G193" s="4" t="inlineStr">
+      <c r="D198" s="5" t="inlineStr">
+        <is>
+          <t>HSV-9</t>
+        </is>
+      </c>
+      <c r="E198" s="5" t="inlineStr">
+        <is>
+          <t>HSV-9-001</t>
+        </is>
+      </c>
+      <c r="F198" s="6" t="inlineStr">
+        <is>
+          <t>Přesun hmot HSV vodorovně — beton, výztuž, ocel, klempířina</t>
+        </is>
+      </c>
+      <c r="G198" s="4" t="inlineStr">
         <is>
           <t>t·km</t>
         </is>
       </c>
-      <c r="H193" s="4" t="n">
-        <v>1500</v>
-      </c>
-      <c r="I193" s="6" t="inlineStr">
-        <is>
-          <t>placeholder ~1500 t·km (30 t materiálů × 50 km)</t>
-        </is>
-      </c>
-      <c r="J193" s="6" t="inlineStr"/>
-    </row>
-    <row r="194" ht="22" customHeight="1">
-      <c r="A194" s="2" t="inlineStr">
-        <is>
-          <t>═══ FÁZE 11: DOKONČENÍ + REVIZE + ODEVZDÁNÍ ═══</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" s="3" t="inlineStr">
-        <is>
-          <t>→ Revize TZB (elektro, hydrant, hromosvod)</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" s="7" t="n">
-        <v>120</v>
-      </c>
-      <c r="B196" s="8" t="inlineStr"/>
-      <c r="C196" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="D196" s="8" t="inlineStr">
-        <is>
-          <t>VRN</t>
-        </is>
-      </c>
-      <c r="E196" s="8" t="inlineStr">
-        <is>
-          <t>VRN-020</t>
-        </is>
-      </c>
-      <c r="F196" s="9" t="inlineStr">
-        <is>
-          <t>Revize elektroinstalace + protokol</t>
-        </is>
-      </c>
-      <c r="G196" s="7" t="inlineStr">
-        <is>
-          <t>paušál</t>
-        </is>
-      </c>
-      <c r="H196" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I196" s="9" t="inlineStr">
-        <is>
-          <t>paušál (Rožmitál 00523 R precedent)  [csn]</t>
-        </is>
-      </c>
-      <c r="J196" s="9" t="inlineStr"/>
-    </row>
-    <row r="197">
-      <c r="A197" s="7" t="n">
-        <v>121</v>
-      </c>
-      <c r="B197" s="8" t="inlineStr"/>
-      <c r="C197" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="D197" s="8" t="inlineStr">
-        <is>
-          <t>VRN</t>
-        </is>
-      </c>
-      <c r="E197" s="8" t="inlineStr">
-        <is>
-          <t>VRN-021</t>
-        </is>
-      </c>
-      <c r="F197" s="9" t="inlineStr">
-        <is>
-          <t>Revize hydrantového systému + tlaková zkouška</t>
-        </is>
-      </c>
-      <c r="G197" s="7" t="inlineStr">
-        <is>
-          <t>paušál</t>
-        </is>
-      </c>
-      <c r="H197" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I197" s="9" t="inlineStr">
-        <is>
-          <t>paušál  [csn]</t>
-        </is>
-      </c>
-      <c r="J197" s="9" t="inlineStr"/>
-    </row>
-    <row r="198">
-      <c r="A198" s="7" t="n">
-        <v>122</v>
-      </c>
-      <c r="B198" s="8" t="inlineStr"/>
-      <c r="C198" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="D198" s="8" t="inlineStr">
-        <is>
-          <t>VRN</t>
-        </is>
-      </c>
-      <c r="E198" s="8" t="inlineStr">
-        <is>
-          <t>VRN-022</t>
-        </is>
-      </c>
-      <c r="F198" s="9" t="inlineStr">
-        <is>
-          <t>Revize hromosvodu / LPS — měření ekvipotenciality, zemniče, svody</t>
-        </is>
-      </c>
-      <c r="G198" s="7" t="inlineStr">
-        <is>
-          <t>paušál</t>
-        </is>
-      </c>
-      <c r="H198" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I198" s="9" t="inlineStr">
-        <is>
-          <t>paušál  [csn]</t>
-        </is>
-      </c>
-      <c r="J198" s="9" t="inlineStr"/>
+      <c r="H198" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="I198" s="6" t="inlineStr">
+        <is>
+          <t>placeholder 200 t·km (in-site přesuny, default)</t>
+        </is>
+      </c>
+      <c r="J198" s="6" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="3" t="inlineStr">
         <is>
-          <t>→ Likvidace odpadů O + N</t>
+          <t>→ Doprava materiálu na stavbu — paušál</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="4" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B200" s="5" t="inlineStr"/>
       <c r="C200" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D200" s="5" t="inlineStr">
         <is>
@@ -5877,122 +5905,122 @@
       </c>
       <c r="E200" s="5" t="inlineStr">
         <is>
-          <t>VRN-011</t>
+          <t>VRN-013</t>
         </is>
       </c>
       <c r="F200" s="6" t="inlineStr">
         <is>
-          <t>Likvidace odpadů kategorie O (běžný) — kontejner + odvoz + skládkovné</t>
+          <t>Doprava materiálu na stavbu vodorovně — paušál pro veškerou montáž</t>
         </is>
       </c>
       <c r="G200" s="4" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>t·km</t>
         </is>
       </c>
       <c r="H200" s="4" t="n">
-        <v>30</v>
+        <v>1500</v>
       </c>
       <c r="I200" s="6" t="inlineStr">
         <is>
-          <t>placeholder ~30 m³ stavebního odpadu kat. O</t>
+          <t>placeholder ~1500 t·km (30 t materiálů × 50 km)</t>
         </is>
       </c>
       <c r="J200" s="6" t="inlineStr"/>
     </row>
-    <row r="201">
-      <c r="A201" s="7" t="n">
-        <v>124</v>
-      </c>
-      <c r="B201" s="8" t="inlineStr"/>
-      <c r="C201" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="D201" s="8" t="inlineStr">
-        <is>
-          <t>VRN</t>
-        </is>
-      </c>
-      <c r="E201" s="8" t="inlineStr">
-        <is>
-          <t>VRN-012</t>
-        </is>
-      </c>
-      <c r="F201" s="9" t="inlineStr">
-        <is>
-          <t>Likvidace odpadů kategorie N (nebezpečné — barvy, oleje, tmely)</t>
-        </is>
-      </c>
-      <c r="G201" s="7" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="H201" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I201" s="9" t="inlineStr">
-        <is>
-          <t>placeholder ~2 m³ kat. N</t>
-        </is>
-      </c>
-      <c r="J201" s="9" t="inlineStr"/>
+    <row r="201" ht="22" customHeight="1">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>═══ FÁZE 11: DOKONČENÍ + REVIZE + ODEVZDÁNÍ ═══</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="3" t="inlineStr">
         <is>
-          <t>→ Geodetické zaměření DSPS</t>
+          <t>→ Revize TZB (elektro, hydrant, hromosvod)</t>
         </is>
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="4" t="n">
+      <c r="A203" s="7" t="n">
         <v>125</v>
       </c>
-      <c r="B203" s="5" t="inlineStr"/>
-      <c r="C203" s="4" t="n">
+      <c r="B203" s="8" t="inlineStr"/>
+      <c r="C203" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="D203" s="5" t="inlineStr">
+      <c r="D203" s="8" t="inlineStr">
         <is>
           <t>VRN</t>
         </is>
       </c>
-      <c r="E203" s="5" t="inlineStr">
-        <is>
-          <t>VRN-015</t>
-        </is>
-      </c>
-      <c r="F203" s="6" t="inlineStr">
-        <is>
-          <t>Geodetické zaměření skutečného provedení (DSPS) — po dokončení stavby</t>
-        </is>
-      </c>
-      <c r="G203" s="4" t="inlineStr">
+      <c r="E203" s="8" t="inlineStr">
+        <is>
+          <t>VRN-020</t>
+        </is>
+      </c>
+      <c r="F203" s="9" t="inlineStr">
+        <is>
+          <t>Revize elektroinstalace + protokol</t>
+        </is>
+      </c>
+      <c r="G203" s="7" t="inlineStr">
         <is>
           <t>paušál</t>
         </is>
       </c>
-      <c r="H203" s="4" t="n">
+      <c r="H203" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="I203" s="6" t="inlineStr">
+      <c r="I203" s="9" t="inlineStr">
+        <is>
+          <t>paušál (Rožmitál 00523 R precedent)  [csn]</t>
+        </is>
+      </c>
+      <c r="J203" s="9" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="7" t="n">
+        <v>126</v>
+      </c>
+      <c r="B204" s="8" t="inlineStr"/>
+      <c r="C204" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="D204" s="8" t="inlineStr">
+        <is>
+          <t>VRN</t>
+        </is>
+      </c>
+      <c r="E204" s="8" t="inlineStr">
+        <is>
+          <t>VRN-021</t>
+        </is>
+      </c>
+      <c r="F204" s="9" t="inlineStr">
+        <is>
+          <t>Revize hydrantového systému + tlaková zkouška</t>
+        </is>
+      </c>
+      <c r="G204" s="7" t="inlineStr">
         <is>
           <t>paušál</t>
         </is>
       </c>
-      <c r="J203" s="6" t="inlineStr"/>
-    </row>
-    <row r="204">
-      <c r="A204" s="3" t="inlineStr">
-        <is>
-          <t>→ Předávací protokoly + kolaudace</t>
-        </is>
-      </c>
+      <c r="H204" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I204" s="9" t="inlineStr">
+        <is>
+          <t>paušál  [csn]</t>
+        </is>
+      </c>
+      <c r="J204" s="9" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" s="7" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B205" s="8" t="inlineStr"/>
       <c r="C205" s="7" t="n">
@@ -6005,12 +6033,12 @@
       </c>
       <c r="E205" s="8" t="inlineStr">
         <is>
-          <t>VRN-018</t>
+          <t>VRN-022</t>
         </is>
       </c>
       <c r="F205" s="9" t="inlineStr">
         <is>
-          <t>Předávací protokoly + dokumentace skutečného provedení (DSPS)</t>
+          <t>Revize hromosvodu / LPS — měření ekvipotenciality, zemniče, svody</t>
         </is>
       </c>
       <c r="G205" s="7" t="inlineStr">
@@ -6023,109 +6051,284 @@
       </c>
       <c r="I205" s="9" t="inlineStr">
         <is>
+          <t>paušál  [csn]</t>
+        </is>
+      </c>
+      <c r="J205" s="9" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="3" t="inlineStr">
+        <is>
+          <t>→ Likvidace odpadů O + N</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="4" t="n">
+        <v>128</v>
+      </c>
+      <c r="B207" s="5" t="inlineStr"/>
+      <c r="C207" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="D207" s="5" t="inlineStr">
+        <is>
+          <t>VRN</t>
+        </is>
+      </c>
+      <c r="E207" s="5" t="inlineStr">
+        <is>
+          <t>VRN-011</t>
+        </is>
+      </c>
+      <c r="F207" s="6" t="inlineStr">
+        <is>
+          <t>Likvidace odpadů kategorie O (běžný) — kontejner + odvoz + skládkovné</t>
+        </is>
+      </c>
+      <c r="G207" s="4" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="H207" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="I207" s="6" t="inlineStr">
+        <is>
+          <t>placeholder ~30 m³ stavebního odpadu kat. O</t>
+        </is>
+      </c>
+      <c r="J207" s="6" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="7" t="n">
+        <v>129</v>
+      </c>
+      <c r="B208" s="8" t="inlineStr"/>
+      <c r="C208" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="D208" s="8" t="inlineStr">
+        <is>
+          <t>VRN</t>
+        </is>
+      </c>
+      <c r="E208" s="8" t="inlineStr">
+        <is>
+          <t>VRN-012</t>
+        </is>
+      </c>
+      <c r="F208" s="9" t="inlineStr">
+        <is>
+          <t>Likvidace odpadů kategorie N (nebezpečné — barvy, oleje, tmely)</t>
+        </is>
+      </c>
+      <c r="G208" s="7" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="H208" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I208" s="9" t="inlineStr">
+        <is>
+          <t>placeholder ~2 m³ kat. N</t>
+        </is>
+      </c>
+      <c r="J208" s="9" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="3" t="inlineStr">
+        <is>
+          <t>→ Geodetické zaměření DSPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="4" t="n">
+        <v>130</v>
+      </c>
+      <c r="B210" s="5" t="inlineStr"/>
+      <c r="C210" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="D210" s="5" t="inlineStr">
+        <is>
+          <t>VRN</t>
+        </is>
+      </c>
+      <c r="E210" s="5" t="inlineStr">
+        <is>
+          <t>VRN-015</t>
+        </is>
+      </c>
+      <c r="F210" s="6" t="inlineStr">
+        <is>
+          <t>Geodetické zaměření skutečného provedení (DSPS) — po dokončení stavby</t>
+        </is>
+      </c>
+      <c r="G210" s="4" t="inlineStr">
+        <is>
           <t>paušál</t>
         </is>
       </c>
-      <c r="J205" s="9" t="inlineStr"/>
-    </row>
-    <row r="206">
-      <c r="A206" s="7" t="n">
-        <v>127</v>
-      </c>
-      <c r="B206" s="8" t="inlineStr"/>
-      <c r="C206" s="7" t="n">
+      <c r="H210" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I210" s="6" t="inlineStr">
+        <is>
+          <t>paušál</t>
+        </is>
+      </c>
+      <c r="J210" s="6" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="3" t="inlineStr">
+        <is>
+          <t>→ Předávací protokoly + kolaudace</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="7" t="n">
+        <v>131</v>
+      </c>
+      <c r="B212" s="8" t="inlineStr"/>
+      <c r="C212" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="D206" s="8" t="inlineStr">
+      <c r="D212" s="8" t="inlineStr">
         <is>
           <t>VRN</t>
         </is>
       </c>
-      <c r="E206" s="8" t="inlineStr">
+      <c r="E212" s="8" t="inlineStr">
+        <is>
+          <t>VRN-018</t>
+        </is>
+      </c>
+      <c r="F212" s="9" t="inlineStr">
+        <is>
+          <t>Předávací protokoly + dokumentace skutečného provedení (DSPS)</t>
+        </is>
+      </c>
+      <c r="G212" s="7" t="inlineStr">
+        <is>
+          <t>paušál</t>
+        </is>
+      </c>
+      <c r="H212" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I212" s="9" t="inlineStr">
+        <is>
+          <t>paušál</t>
+        </is>
+      </c>
+      <c r="J212" s="9" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="7" t="n">
+        <v>132</v>
+      </c>
+      <c r="B213" s="8" t="inlineStr"/>
+      <c r="C213" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="D213" s="8" t="inlineStr">
+        <is>
+          <t>VRN</t>
+        </is>
+      </c>
+      <c r="E213" s="8" t="inlineStr">
         <is>
           <t>VRN-019</t>
         </is>
       </c>
-      <c r="F206" s="9" t="inlineStr">
+      <c r="F213" s="9" t="inlineStr">
         <is>
           <t>Kolaudační řízení — příprava + účast na jednání + revize dokumentace</t>
         </is>
       </c>
-      <c r="G206" s="7" t="inlineStr">
+      <c r="G213" s="7" t="inlineStr">
         <is>
           <t>paušál</t>
         </is>
       </c>
-      <c r="H206" s="7" t="n">
+      <c r="H213" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="I206" s="9" t="inlineStr">
+      <c r="I213" s="9" t="inlineStr">
         <is>
           <t>paušál</t>
         </is>
       </c>
-      <c r="J206" s="9" t="inlineStr"/>
-    </row>
-    <row r="207">
-      <c r="A207" s="3" t="inlineStr">
+      <c r="J213" s="9" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="3" t="inlineStr">
         <is>
           <t>→ Náhradní výsadba dřevin (po dokončení)</t>
         </is>
       </c>
     </row>
-    <row r="208">
-      <c r="A208" s="4" t="n">
-        <v>128</v>
-      </c>
-      <c r="B208" s="5" t="inlineStr"/>
-      <c r="C208" s="4" t="n">
+    <row r="215">
+      <c r="A215" s="4" t="n">
+        <v>133</v>
+      </c>
+      <c r="B215" s="5" t="inlineStr"/>
+      <c r="C215" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="D208" s="5" t="inlineStr">
+      <c r="D215" s="5" t="inlineStr">
         <is>
           <t>HSV-1</t>
         </is>
       </c>
-      <c r="E208" s="5" t="inlineStr">
+      <c r="E215" s="5" t="inlineStr">
         <is>
           <t>HSV-1-024</t>
         </is>
       </c>
-      <c r="F208" s="6" t="inlineStr">
+      <c r="F215" s="6" t="inlineStr">
         <is>
           <t>Náhradní výsadba dřevin per rozhodnutí orgánu životního prostředí</t>
         </is>
       </c>
-      <c r="G208" s="4" t="inlineStr">
+      <c r="G215" s="4" t="inlineStr">
         <is>
           <t>ks</t>
         </is>
       </c>
-      <c r="H208" s="4" t="n">
+      <c r="H215" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="I208" s="6" t="inlineStr">
+      <c r="I215" s="6" t="inlineStr">
         <is>
           <t>2 ks (per TZ B m.7.b náhradní výsadba)  [TZ:7.b]</t>
         </is>
       </c>
-      <c r="J208" s="6" t="inlineStr"/>
+      <c r="J215" s="6" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="79">
-    <mergeCell ref="A194:J194"/>
+  <mergeCells count="81">
     <mergeCell ref="A181:J181"/>
     <mergeCell ref="A91:J91"/>
+    <mergeCell ref="A171:J171"/>
     <mergeCell ref="A52:J52"/>
     <mergeCell ref="A63:J63"/>
     <mergeCell ref="A93:J93"/>
+    <mergeCell ref="A130:J130"/>
     <mergeCell ref="A34:J34"/>
     <mergeCell ref="A148:J148"/>
+    <mergeCell ref="A157:J157"/>
     <mergeCell ref="A49:J49"/>
     <mergeCell ref="A36:J36"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="A119:J119"/>
-    <mergeCell ref="A174:J174"/>
+    <mergeCell ref="A196:J196"/>
     <mergeCell ref="A183:J183"/>
     <mergeCell ref="A75:J75"/>
     <mergeCell ref="A133:J133"/>
@@ -6135,43 +6338,44 @@
     <mergeCell ref="A159:J159"/>
     <mergeCell ref="A97:J97"/>
     <mergeCell ref="A29:J29"/>
+    <mergeCell ref="A209:J209"/>
     <mergeCell ref="A121:J121"/>
-    <mergeCell ref="A170:J170"/>
     <mergeCell ref="A202:J202"/>
     <mergeCell ref="A58:J58"/>
+    <mergeCell ref="A211:J211"/>
     <mergeCell ref="A67:J67"/>
+    <mergeCell ref="A186:J186"/>
     <mergeCell ref="A24:J24"/>
+    <mergeCell ref="A201:J201"/>
     <mergeCell ref="A60:J60"/>
+    <mergeCell ref="A197:J197"/>
+    <mergeCell ref="A146:J146"/>
     <mergeCell ref="A124:J124"/>
-    <mergeCell ref="A172:J172"/>
     <mergeCell ref="A16:J16"/>
     <mergeCell ref="A84:J84"/>
-    <mergeCell ref="A71:J71"/>
-    <mergeCell ref="A189:J189"/>
+    <mergeCell ref="A214:J214"/>
     <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A204:J204"/>
     <mergeCell ref="A42:J42"/>
     <mergeCell ref="A151:J151"/>
+    <mergeCell ref="A160:J160"/>
     <mergeCell ref="A22:J22"/>
+    <mergeCell ref="A135:J135"/>
+    <mergeCell ref="A206:J206"/>
     <mergeCell ref="A190:J190"/>
-    <mergeCell ref="A134:J134"/>
     <mergeCell ref="A199:J199"/>
     <mergeCell ref="A127:J127"/>
     <mergeCell ref="A176:J176"/>
     <mergeCell ref="A114:J114"/>
-    <mergeCell ref="A169:J169"/>
     <mergeCell ref="A107:J107"/>
-    <mergeCell ref="A178:J178"/>
-    <mergeCell ref="A153:J153"/>
+    <mergeCell ref="A137:J137"/>
+    <mergeCell ref="A177:J177"/>
     <mergeCell ref="A90:J90"/>
-    <mergeCell ref="A164:J164"/>
-    <mergeCell ref="A145:J145"/>
+    <mergeCell ref="A139:J139"/>
     <mergeCell ref="A154:J154"/>
-    <mergeCell ref="A195:J195"/>
     <mergeCell ref="A33:J33"/>
     <mergeCell ref="A116:J116"/>
     <mergeCell ref="A8:J8"/>
-    <mergeCell ref="A131:J131"/>
+    <mergeCell ref="A188:J188"/>
     <mergeCell ref="A140:J140"/>
     <mergeCell ref="A109:J109"/>
     <mergeCell ref="A10:J10"/>
@@ -6179,18 +6383,17 @@
     <mergeCell ref="A117:J117"/>
     <mergeCell ref="A111:J111"/>
     <mergeCell ref="A39:J39"/>
+    <mergeCell ref="A166:J166"/>
     <mergeCell ref="A142:J142"/>
-    <mergeCell ref="A207:J207"/>
     <mergeCell ref="A78:J78"/>
     <mergeCell ref="A65:J65"/>
     <mergeCell ref="A80:J80"/>
     <mergeCell ref="A46:J46"/>
-    <mergeCell ref="A136:J136"/>
     <mergeCell ref="A192:J192"/>
     <mergeCell ref="A105:J105"/>
     <mergeCell ref="A57:J57"/>
     <mergeCell ref="A179:J179"/>
-    <mergeCell ref="A129:J129"/>
+    <mergeCell ref="A71:J71"/>
     <mergeCell ref="A185:J185"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/test-data/hk212_hala/outputs/sequential_list/hk212_sequential_list.xlsx
+++ b/test-data/hk212_hala/outputs/sequential_list/hk212_sequential_list.xlsx
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J215"/>
+  <dimension ref="A1:J220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2165,7 +2165,7 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>→ Výměna aktivní zóny pláně</t>
+          <t>→ Výměna aktivní zóny — odstr. navážek → odvoz → dovoz štěrku → hutnění → Edef2 → geodet</t>
         </is>
       </c>
     </row>
@@ -2184,12 +2184,12 @@
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>HSV-1-028</t>
+          <t>HSV-1-028a</t>
         </is>
       </c>
       <c r="F59" s="6" t="inlineStr">
         <is>
-          <t>Výměna aktivní zóny pláně — odstranění navážek GT1 + nahrazení hutněným štěrkem tl. 0.5 m, Edef2 ≥ 45 MPa (Edef2/Edef1 &lt; 2.2)</t>
+          <t>Odstranění navážek GT1 z aktivní zóny — výkop + naložení na dopravní prostředek</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr">
@@ -2202,155 +2202,207 @@
       </c>
       <c r="I59" s="6" t="inlineStr">
         <is>
-          <t>531.22 m² × 0.5 m = 265.61 m³ × 2 operace  [igp_section:4.4, igp_document:inputs/dokumentace/IGP_ALTAGEO_526026.md, Step3]</t>
+          <t>531.22 m² (A105 deska) × 0.5 m (mocnost výměny per IGP §4.4) = 265.61 m³  [igp_section:4.4, igp_document:inputs/dokumentace/IGP_ALTAGEO_526026.md, Step3]  · was 265.61: Sub-item 1) výkop navážek — first appearance</t>
         </is>
       </c>
       <c r="J59" s="6" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="inlineStr">
-        <is>
-          <t>→ Štěrkové lože + zhutnění podloží</t>
-        </is>
-      </c>
+      <c r="A60" s="10" t="n">
+        <v>38</v>
+      </c>
+      <c r="B60" s="11" t="inlineStr"/>
+      <c r="C60" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D60" s="11" t="inlineStr">
+        <is>
+          <t>HSV-1</t>
+        </is>
+      </c>
+      <c r="E60" s="11" t="inlineStr">
+        <is>
+          <t>HSV-1-028b</t>
+        </is>
+      </c>
+      <c r="F60" s="12" t="inlineStr">
+        <is>
+          <t>Odvoz vytěžených navážek GT1 na skládku (vč. poplatku skládkovné)</t>
+        </is>
+      </c>
+      <c r="G60" s="10" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="H60" s="10" t="n">
+        <v>265.61</v>
+      </c>
+      <c r="I60" s="12">
+        <f> HSV-1-028a vytěžený objem = 265.61 m³ (1 : 1 odvoz vykopaného materiálu)  [igp_section:4.4, igp_document:inputs/dokumentace/IGP_ALTAGEO_526026.md, Step3]  · was 265.61: Sub-item 2) odvoz na skládku — first appearance</f>
+        <v/>
+      </c>
+      <c r="J60" s="12" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="7" t="n">
-        <v>38</v>
-      </c>
-      <c r="B61" s="8" t="inlineStr"/>
-      <c r="C61" s="7" t="n">
+      <c r="A61" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="B61" s="5" t="inlineStr"/>
+      <c r="C61" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D61" s="8" t="inlineStr">
+      <c r="D61" s="5" t="inlineStr">
         <is>
           <t>HSV-1</t>
         </is>
       </c>
-      <c r="E61" s="8" t="inlineStr">
-        <is>
-          <t>HSV-1-013</t>
-        </is>
-      </c>
-      <c r="F61" s="9" t="inlineStr">
-        <is>
-          <t>Štěrkové lože pod základovou deskou, tl. 250 mm, frakce 0/63</t>
-        </is>
-      </c>
-      <c r="G61" s="7" t="inlineStr">
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>HSV-1-028c</t>
+        </is>
+      </c>
+      <c r="F61" s="6" t="inlineStr">
+        <is>
+          <t>Dovoz hutného štěrku frakce 0/63 (alt. 0/125) na staveniště</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="H61" s="7" t="n">
-        <v>123.75</v>
-      </c>
-      <c r="I61" s="9" t="inlineStr">
-        <is>
-          <t>495 m² × 0.25 m  [TZ:B]</t>
-        </is>
-      </c>
-      <c r="J61" s="9" t="inlineStr">
-        <is>
-          <t>ABMV:ABMV_17</t>
-        </is>
-      </c>
+      <c r="H61" s="4" t="n">
+        <v>265.61</v>
+      </c>
+      <c r="I61" s="6">
+        <f> objem výměny 265.61 m³ (nahrazení 1 : 1 ekvivalent odstraněného)  [igp_section:4.4, igp_document:inputs/dokumentace/IGP_ALTAGEO_526026.md, Step3]  · was 265.61: Sub-item 3) dovoz hutného štěrku — first appearance</f>
+        <v/>
+      </c>
+      <c r="J61" s="6" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="7" t="n">
-        <v>39</v>
-      </c>
-      <c r="B62" s="8" t="inlineStr"/>
-      <c r="C62" s="7" t="n">
+      <c r="A62" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="B62" s="11" t="inlineStr"/>
+      <c r="C62" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="D62" s="8" t="inlineStr">
+      <c r="D62" s="11" t="inlineStr">
         <is>
           <t>HSV-1</t>
         </is>
       </c>
-      <c r="E62" s="8" t="inlineStr">
-        <is>
-          <t>HSV-1-014</t>
-        </is>
-      </c>
-      <c r="F62" s="9" t="inlineStr">
-        <is>
-          <t>Zhutnění podloží Edef,2 ≥ 45 MPa, Edef2/Ede &lt; 1.75</t>
-        </is>
-      </c>
-      <c r="G62" s="7" t="inlineStr">
+      <c r="E62" s="11" t="inlineStr">
+        <is>
+          <t>HSV-1-028d</t>
+        </is>
+      </c>
+      <c r="F62" s="12" t="inlineStr">
+        <is>
+          <t>Rozprostření štěrku po vrstvách max 300 mm + hutnění vibračním válcem / pěchem (ČSN 72 1006)</t>
+        </is>
+      </c>
+      <c r="G62" s="10" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="H62" s="10" t="n">
+        <v>265.61</v>
+      </c>
+      <c r="I62" s="12">
+        <f> 265.61 m³ rozprostřeno v ≥ 2 vrstvách po max 0.3 m (ČSN 72 1006 §6.3 míra zhutnění)  [igp_section:4.4, igp_document:inputs/dokumentace/IGP_ALTAGEO_526026.md, Step3]  · was 265.61: Sub-item 4) rozprostření + hutnění —…</f>
+        <v/>
+      </c>
+      <c r="J62" s="12" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="B63" s="5" t="inlineStr"/>
+      <c r="C63" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>HSV-1</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>HSV-1-028e</t>
+        </is>
+      </c>
+      <c r="F63" s="6" t="inlineStr">
+        <is>
+          <t>Statická zatěžovací zkouška Edef2 ≥ 45 MPa (Edef2/Edef1 &lt; 2.2), min 3 měřená místa</t>
+        </is>
+      </c>
+      <c r="G63" s="4" t="inlineStr">
+        <is>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="H63" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I63" s="6" t="inlineStr">
+        <is>
+          <t>3 ks (ČSN 72 1006 minimum pro plochu &lt; 1000 m²; deska 531.22 m² → 3 měřená místa)  [igp_section:4.4, igp_document:inputs/dokumentace/IGP_ALTAGEO_526026.md, Step3]  · was 3.0: Sub-item 5) Edef2 kontrolní zkouška — first…</t>
+        </is>
+      </c>
+      <c r="J63" s="6" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B64" s="11" t="inlineStr"/>
+      <c r="C64" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D64" s="11" t="inlineStr">
+        <is>
+          <t>HSV-1</t>
+        </is>
+      </c>
+      <c r="E64" s="11" t="inlineStr">
+        <is>
+          <t>HSV-1-028f</t>
+        </is>
+      </c>
+      <c r="F64" s="12" t="inlineStr">
+        <is>
+          <t>Geodetická kontrola roviny aktivní zóny po hutnění</t>
+        </is>
+      </c>
+      <c r="G64" s="10" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="H62" s="7" t="n">
-        <v>495</v>
-      </c>
-      <c r="I62" s="9">
-        <f> plocha desky  [TZ:B]</f>
+      <c r="H64" s="10" t="n">
+        <v>531.22</v>
+      </c>
+      <c r="I64" s="12">
+        <f> A105 deska 19.04 × 27.90 = 531.22 m² (celá plocha aktivní zóny)  [igp_section:4.4, igp_document:inputs/dokumentace/IGP_ALTAGEO_526026.md, Step3]  · was 531.22: Sub-item 6) geodetická kontrola roviny — first appearance</f>
         <v/>
       </c>
-      <c r="J62" s="9" t="inlineStr">
-        <is>
-          <t>ABMV:ABMV_17</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="3" t="inlineStr">
-        <is>
-          <t>→ Hydroizolace plošná pod desku</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="B64" s="5" t="inlineStr"/>
-      <c r="C64" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D64" s="5" t="inlineStr">
-        <is>
-          <t>HSV-2</t>
-        </is>
-      </c>
-      <c r="E64" s="5" t="inlineStr">
-        <is>
-          <t>HSV-2-018</t>
-        </is>
-      </c>
-      <c r="F64" s="6" t="inlineStr">
-        <is>
-          <t>Hydroizolace plošná pod podlahovou desku — 1× SBS modifikovaný asfaltový pás</t>
-        </is>
-      </c>
-      <c r="G64" s="4" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="H64" s="4" t="n">
-        <v>495</v>
-      </c>
-      <c r="I64" s="6">
-        <f> plocha desky  [TZ:B]</f>
-        <v/>
-      </c>
-      <c r="J64" s="6" t="inlineStr"/>
+      <c r="J64" s="12" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>→ Výztuž patek a pasů</t>
+          <t>→ Štěrkové lože + zhutnění podloží</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B66" s="8" t="inlineStr"/>
       <c r="C66" s="7" t="n">
@@ -2358,202 +2410,178 @@
       </c>
       <c r="D66" s="8" t="inlineStr">
         <is>
+          <t>HSV-1</t>
+        </is>
+      </c>
+      <c r="E66" s="8" t="inlineStr">
+        <is>
+          <t>HSV-1-013</t>
+        </is>
+      </c>
+      <c r="F66" s="9" t="inlineStr">
+        <is>
+          <t>Štěrkové lože pod základovou deskou, tl. 250 mm, frakce 0/63</t>
+        </is>
+      </c>
+      <c r="G66" s="7" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="H66" s="7" t="n">
+        <v>123.75</v>
+      </c>
+      <c r="I66" s="9" t="inlineStr">
+        <is>
+          <t>495 m² × 0.25 m  [TZ:B]</t>
+        </is>
+      </c>
+      <c r="J66" s="9" t="inlineStr">
+        <is>
+          <t>ABMV:ABMV_17</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="7" t="n">
+        <v>44</v>
+      </c>
+      <c r="B67" s="8" t="inlineStr"/>
+      <c r="C67" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D67" s="8" t="inlineStr">
+        <is>
+          <t>HSV-1</t>
+        </is>
+      </c>
+      <c r="E67" s="8" t="inlineStr">
+        <is>
+          <t>HSV-1-014</t>
+        </is>
+      </c>
+      <c r="F67" s="9" t="inlineStr">
+        <is>
+          <t>Zhutnění podloží Edef,2 ≥ 45 MPa, Edef2/Ede &lt; 1.75</t>
+        </is>
+      </c>
+      <c r="G67" s="7" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="H67" s="7" t="n">
+        <v>495</v>
+      </c>
+      <c r="I67" s="9">
+        <f> plocha desky  [TZ:B]</f>
+        <v/>
+      </c>
+      <c r="J67" s="9" t="inlineStr">
+        <is>
+          <t>ABMV:ABMV_17</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>→ Hydroizolace plošná pod desku</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="B69" s="5" t="inlineStr"/>
+      <c r="C69" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
           <t>HSV-2</t>
         </is>
       </c>
-      <c r="E66" s="8" t="inlineStr">
+      <c r="E69" s="5" t="inlineStr">
+        <is>
+          <t>HSV-2-018</t>
+        </is>
+      </c>
+      <c r="F69" s="6" t="inlineStr">
+        <is>
+          <t>Hydroizolace plošná pod podlahovou desku — 1× SBS modifikovaný asfaltový pás</t>
+        </is>
+      </c>
+      <c r="G69" s="4" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="H69" s="4" t="n">
+        <v>495</v>
+      </c>
+      <c r="I69" s="6">
+        <f> plocha desky  [TZ:B]</f>
+        <v/>
+      </c>
+      <c r="J69" s="6" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>→ Výztuž patek a pasů</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="7" t="n">
+        <v>46</v>
+      </c>
+      <c r="B71" s="8" t="inlineStr"/>
+      <c r="C71" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D71" s="8" t="inlineStr">
+        <is>
+          <t>HSV-2</t>
+        </is>
+      </c>
+      <c r="E71" s="8" t="inlineStr">
         <is>
           <t>HSV-2-009</t>
         </is>
       </c>
-      <c r="F66" s="9" t="inlineStr">
+      <c r="F71" s="9" t="inlineStr">
         <is>
           <t>Výztuž patek a pasů ze svařovaných sítí + vázaná B500B</t>
         </is>
       </c>
-      <c r="G66" s="7" t="inlineStr">
+      <c r="G71" s="7" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="H66" s="7" t="n">
+      <c r="H71" s="7" t="n">
         <v>600</v>
       </c>
-      <c r="I66" s="9" t="inlineStr">
+      <c r="I71" s="9" t="inlineStr">
         <is>
           <t>placeholder 600 kg per RE-RUN §3.4 statika dimensioning</t>
         </is>
       </c>
-      <c r="J66" s="9" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="3" t="inlineStr">
+      <c r="J71" s="9" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
         <is>
           <t>→ Patky rámové — bednění + beton + odbednění</t>
         </is>
       </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="7" t="n">
-        <v>42</v>
-      </c>
-      <c r="B68" s="8" t="inlineStr"/>
-      <c r="C68" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="D68" s="8" t="inlineStr">
-        <is>
-          <t>HSV-2</t>
-        </is>
-      </c>
-      <c r="E68" s="8" t="inlineStr">
-        <is>
-          <t>HSV-2-002</t>
-        </is>
-      </c>
-      <c r="F68" s="9" t="inlineStr">
-        <is>
-          <t>Bednění patek rámových dvoustupňových — zřízení</t>
-        </is>
-      </c>
-      <c r="G68" s="7" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="H68" s="7" t="n">
-        <v>66</v>
-      </c>
-      <c r="I68" s="9" t="inlineStr">
-        <is>
-          <t>10 × (3.6 + 3.0) = 66.0 m²  [výkres:A105, TZ:D.1.2 (statika) — Návrh opláštění, měřeno:A105]</t>
-        </is>
-      </c>
-      <c r="J68" s="9" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="10" t="n">
-        <v>43</v>
-      </c>
-      <c r="B69" s="11" t="inlineStr"/>
-      <c r="C69" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="D69" s="11" t="inlineStr">
-        <is>
-          <t>HSV-2</t>
-        </is>
-      </c>
-      <c r="E69" s="11" t="inlineStr">
-        <is>
-          <t>HSV-2-001</t>
-        </is>
-      </c>
-      <c r="F69" s="12" t="inlineStr">
-        <is>
-          <t>Beton patek rámových C16/20 XC0 prostý, dvoustupňové</t>
-        </is>
-      </c>
-      <c r="G69" s="10" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="H69" s="10" t="n">
-        <v>22.875</v>
-      </c>
-      <c r="I69" s="12" t="inlineStr">
-        <is>
-          <t>10 × (1.5²×0.6 + 1.25²×0.6) = 10 × (1.35 + 0.9375) = 22.875 m³  [výkres:A105, TZ:D.1.1 p3, statika:D.1.2 p29-30]</t>
-        </is>
-      </c>
-      <c r="J69" s="12" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="7" t="n">
-        <v>44</v>
-      </c>
-      <c r="B70" s="8" t="inlineStr"/>
-      <c r="C70" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="D70" s="8" t="inlineStr">
-        <is>
-          <t>HSV-2</t>
-        </is>
-      </c>
-      <c r="E70" s="8" t="inlineStr">
-        <is>
-          <t>HSV-2-003</t>
-        </is>
-      </c>
-      <c r="F70" s="9" t="inlineStr">
-        <is>
-          <t>Bednění patek rámových dvoustupňových — odstranění</t>
-        </is>
-      </c>
-      <c r="G70" s="7" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="H70" s="7" t="n">
-        <v>66</v>
-      </c>
-      <c r="I70" s="9">
-        <f> HSV-2-002 = 66.0 m²  [TZ:D.1.2 (statika) — Návrh opláštění, měřeno:A105]</f>
-        <v/>
-      </c>
-      <c r="J70" s="9" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="3" t="inlineStr">
-        <is>
-          <t>→ Patky štítové — bednění + beton + odbednění</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="7" t="n">
-        <v>45</v>
-      </c>
-      <c r="B72" s="8" t="inlineStr"/>
-      <c r="C72" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="D72" s="8" t="inlineStr">
-        <is>
-          <t>HSV-2</t>
-        </is>
-      </c>
-      <c r="E72" s="8" t="inlineStr">
-        <is>
-          <t>HSV-2-005</t>
-        </is>
-      </c>
-      <c r="F72" s="9" t="inlineStr">
-        <is>
-          <t>Bednění patek štítových — zřízení</t>
-        </is>
-      </c>
-      <c r="G72" s="7" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="H72" s="7" t="n">
-        <v>30.72</v>
-      </c>
-      <c r="I72" s="9" t="inlineStr">
-        <is>
-          <t>8 × 4 × 0.8 × 1.2 = 30.72 m²  [výkres:A105, tz_typo_resolution]</t>
-        </is>
-      </c>
-      <c r="J72" s="9" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="7" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B73" s="8" t="inlineStr"/>
       <c r="C73" s="7" t="n">
@@ -2566,114 +2594,114 @@
       </c>
       <c r="E73" s="8" t="inlineStr">
         <is>
-          <t>HSV-2-004</t>
+          <t>HSV-2-002</t>
         </is>
       </c>
       <c r="F73" s="9" t="inlineStr">
         <is>
-          <t>Beton patek štítových C16/20 XC0 prostý, dvoustupňové</t>
+          <t>Bednění patek rámových dvoustupňových — zřízení</t>
         </is>
       </c>
       <c r="G73" s="7" t="inlineStr">
         <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="H73" s="7" t="n">
+        <v>66</v>
+      </c>
+      <c r="I73" s="9" t="inlineStr">
+        <is>
+          <t>10 × (3.6 + 3.0) = 66.0 m²  [výkres:A105, TZ:D.1.2 (statika) — Návrh opláštění, měřeno:A105]</t>
+        </is>
+      </c>
+      <c r="J73" s="9" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B74" s="11" t="inlineStr"/>
+      <c r="C74" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D74" s="11" t="inlineStr">
+        <is>
+          <t>HSV-2</t>
+        </is>
+      </c>
+      <c r="E74" s="11" t="inlineStr">
+        <is>
+          <t>HSV-2-001</t>
+        </is>
+      </c>
+      <c r="F74" s="12" t="inlineStr">
+        <is>
+          <t>Beton patek rámových C16/20 XC0 prostý, dvoustupňové</t>
+        </is>
+      </c>
+      <c r="G74" s="10" t="inlineStr">
+        <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="H73" s="7" t="n">
-        <v>6.144</v>
-      </c>
-      <c r="I73" s="9" t="inlineStr">
-        <is>
-          <t>8 ks × 0.8 × 0.8 × 1.2 m = 6.144 m³  [výkres:A105, tz_typo_resolution]</t>
-        </is>
-      </c>
-      <c r="J73" s="9" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="7" t="n">
-        <v>47</v>
-      </c>
-      <c r="B74" s="8" t="inlineStr"/>
-      <c r="C74" s="7" t="n">
+      <c r="H74" s="10" t="n">
+        <v>22.875</v>
+      </c>
+      <c r="I74" s="12" t="inlineStr">
+        <is>
+          <t>10 × (1.5²×0.6 + 1.25²×0.6) = 10 × (1.35 + 0.9375) = 22.875 m³  [výkres:A105, TZ:D.1.1 p3, statika:D.1.2 p29-30]</t>
+        </is>
+      </c>
+      <c r="J74" s="12" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="7" t="n">
+        <v>49</v>
+      </c>
+      <c r="B75" s="8" t="inlineStr"/>
+      <c r="C75" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="D74" s="8" t="inlineStr">
+      <c r="D75" s="8" t="inlineStr">
         <is>
           <t>HSV-2</t>
         </is>
       </c>
-      <c r="E74" s="8" t="inlineStr">
-        <is>
-          <t>HSV-2-006</t>
-        </is>
-      </c>
-      <c r="F74" s="9" t="inlineStr">
-        <is>
-          <t>Bednění patek štítových — odstranění</t>
-        </is>
-      </c>
-      <c r="G74" s="7" t="inlineStr">
+      <c r="E75" s="8" t="inlineStr">
+        <is>
+          <t>HSV-2-003</t>
+        </is>
+      </c>
+      <c r="F75" s="9" t="inlineStr">
+        <is>
+          <t>Bednění patek rámových dvoustupňových — odstranění</t>
+        </is>
+      </c>
+      <c r="G75" s="7" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="H74" s="7" t="n">
-        <v>30.72</v>
-      </c>
-      <c r="I74" s="9">
-        <f> HSV-2-005 = 30.72 m²  [tz_typo_resolution]</f>
+      <c r="H75" s="7" t="n">
+        <v>66</v>
+      </c>
+      <c r="I75" s="9">
+        <f> HSV-2-002 = 66.0 m²  [TZ:D.1.2 (statika) — Návrh opláštění, měřeno:A105]</f>
         <v/>
       </c>
-      <c r="J74" s="9" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="3" t="inlineStr">
-        <is>
-          <t>→ Pasy ŽB — bednění + beton</t>
-        </is>
-      </c>
+      <c r="J75" s="9" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="7" t="n">
-        <v>48</v>
-      </c>
-      <c r="B76" s="8" t="inlineStr"/>
-      <c r="C76" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="D76" s="8" t="inlineStr">
-        <is>
-          <t>HSV-2</t>
-        </is>
-      </c>
-      <c r="E76" s="8" t="inlineStr">
-        <is>
-          <t>HSV-2-008</t>
-        </is>
-      </c>
-      <c r="F76" s="9" t="inlineStr">
-        <is>
-          <t>Bednění pasů — zřízení</t>
-        </is>
-      </c>
-      <c r="G76" s="7" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="H76" s="7" t="n">
-        <v>36</v>
-      </c>
-      <c r="I76" s="9" t="inlineStr">
-        <is>
-          <t>~30 bm × 2 × 0.6 m boční plocha = 36 m²  [výkres:A105]</t>
-        </is>
-      </c>
-      <c r="J76" s="9" t="inlineStr"/>
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>→ Patky štítové — bednění + beton + odbednění</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="7" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B77" s="8" t="inlineStr"/>
       <c r="C77" s="7" t="n">
@@ -2686,88 +2714,114 @@
       </c>
       <c r="E77" s="8" t="inlineStr">
         <is>
-          <t>HSV-2-007</t>
+          <t>HSV-2-005</t>
         </is>
       </c>
       <c r="F77" s="9" t="inlineStr">
         <is>
-          <t>Beton krátkých pasů v rozích a propojení mezi patkami C16/20 XC0</t>
+          <t>Bednění patek štítových — zřízení</t>
         </is>
       </c>
       <c r="G77" s="7" t="inlineStr">
         <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="H77" s="7" t="n">
+        <v>30.72</v>
+      </c>
+      <c r="I77" s="9" t="inlineStr">
+        <is>
+          <t>8 × 4 × 0.8 × 1.2 = 30.72 m²  [výkres:A105, tz_typo_resolution]</t>
+        </is>
+      </c>
+      <c r="J77" s="9" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="7" t="n">
+        <v>51</v>
+      </c>
+      <c r="B78" s="8" t="inlineStr"/>
+      <c r="C78" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D78" s="8" t="inlineStr">
+        <is>
+          <t>HSV-2</t>
+        </is>
+      </c>
+      <c r="E78" s="8" t="inlineStr">
+        <is>
+          <t>HSV-2-004</t>
+        </is>
+      </c>
+      <c r="F78" s="9" t="inlineStr">
+        <is>
+          <t>Beton patek štítových C16/20 XC0 prostý, dvoustupňové</t>
+        </is>
+      </c>
+      <c r="G78" s="7" t="inlineStr">
+        <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="H77" s="7" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="I77" s="9" t="inlineStr">
-        <is>
-          <t>~30 bm × 0.4 × 0.6 m = 7.2 m³  [výkres:A105]</t>
-        </is>
-      </c>
-      <c r="J77" s="9" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="3" t="inlineStr">
-        <is>
-          <t>→ Zásyp výkopů kolem patek</t>
-        </is>
-      </c>
+      <c r="H78" s="7" t="n">
+        <v>6.144</v>
+      </c>
+      <c r="I78" s="9" t="inlineStr">
+        <is>
+          <t>8 ks × 0.8 × 0.8 × 1.2 m = 6.144 m³  [výkres:A105, tz_typo_resolution]</t>
+        </is>
+      </c>
+      <c r="J78" s="9" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="B79" s="5" t="inlineStr"/>
-      <c r="C79" s="4" t="n">
+      <c r="A79" s="7" t="n">
+        <v>52</v>
+      </c>
+      <c r="B79" s="8" t="inlineStr"/>
+      <c r="C79" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="D79" s="5" t="inlineStr">
-        <is>
-          <t>HSV-1</t>
-        </is>
-      </c>
-      <c r="E79" s="5" t="inlineStr">
-        <is>
-          <t>HSV-1-015</t>
-        </is>
-      </c>
-      <c r="F79" s="6" t="inlineStr">
-        <is>
-          <t>Zásyp výkopů kolem patek + okolo obetonovaných sítí, zhutněný</t>
-        </is>
-      </c>
-      <c r="G79" s="4" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="H79" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="I79" s="6" t="inlineStr">
-        <is>
-          <t>placeholder ~30 m³ (zásypy okolo patek + nad obetonovanými sítěmi)  [phase:Phase 0b RE-RUN §3.10]</t>
-        </is>
-      </c>
-      <c r="J79" s="6" t="inlineStr">
-        <is>
-          <t>ABMV:ABMV_17</t>
-        </is>
-      </c>
+      <c r="D79" s="8" t="inlineStr">
+        <is>
+          <t>HSV-2</t>
+        </is>
+      </c>
+      <c r="E79" s="8" t="inlineStr">
+        <is>
+          <t>HSV-2-006</t>
+        </is>
+      </c>
+      <c r="F79" s="9" t="inlineStr">
+        <is>
+          <t>Bednění patek štítových — odstranění</t>
+        </is>
+      </c>
+      <c r="G79" s="7" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="H79" s="7" t="n">
+        <v>30.72</v>
+      </c>
+      <c r="I79" s="9">
+        <f> HSV-2-005 = 30.72 m²  [tz_typo_resolution]</f>
+        <v/>
+      </c>
+      <c r="J79" s="9" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>→ VARIANTA — pilota Ø800 / L=8 m (alternativa)</t>
+          <t>→ Pasy ŽB — bednění + beton</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="7" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B81" s="8" t="inlineStr"/>
       <c r="C81" s="7" t="n">
@@ -2780,32 +2834,32 @@
       </c>
       <c r="E81" s="8" t="inlineStr">
         <is>
-          <t>HSV-2-010</t>
+          <t>HSV-2-008</t>
         </is>
       </c>
       <c r="F81" s="9" t="inlineStr">
         <is>
-          <t>VARIANTA — pilota Ø800 / L=8 m C25/30 XC4 vrtná</t>
+          <t>Bednění pasů — zřízení</t>
         </is>
       </c>
       <c r="G81" s="7" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="H81" s="7" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="I81" s="9" t="inlineStr">
         <is>
-          <t>1 ks pilota Ø800 × 8 m délka  [výkres:A105, igp_section:4.3]</t>
+          <t>~30 bm × 2 × 0.6 m boční plocha = 36 m²  [výkres:A105]</t>
         </is>
       </c>
       <c r="J81" s="9" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="7" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B82" s="8" t="inlineStr"/>
       <c r="C82" s="7" t="n">
@@ -2818,115 +2872,88 @@
       </c>
       <c r="E82" s="8" t="inlineStr">
         <is>
-          <t>HSV-2-011</t>
+          <t>HSV-2-007</t>
         </is>
       </c>
       <c r="F82" s="9" t="inlineStr">
         <is>
-          <t>VARIANTA — vrtání piloty Ø800 do hor. tř. 3-4</t>
+          <t>Beton krátkých pasů v rozích a propojení mezi patkami C16/20 XC0</t>
         </is>
       </c>
       <c r="G82" s="7" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="H82" s="7" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="I82" s="9" t="inlineStr">
         <is>
-          <t>1 ks × 8 m délka  [výkres:A105, igp_section:4.3]</t>
+          <t>~30 bm × 0.4 × 0.6 m = 7.2 m³  [výkres:A105]</t>
         </is>
       </c>
       <c r="J82" s="9" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="7" t="n">
-        <v>53</v>
-      </c>
-      <c r="B83" s="8" t="inlineStr"/>
-      <c r="C83" s="7" t="n">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>→ Zásyp výkopů kolem patek</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="B84" s="5" t="inlineStr"/>
+      <c r="C84" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D83" s="8" t="inlineStr">
-        <is>
-          <t>HSV-2</t>
-        </is>
-      </c>
-      <c r="E83" s="8" t="inlineStr">
-        <is>
-          <t>HSV-2-012</t>
-        </is>
-      </c>
-      <c r="F83" s="9" t="inlineStr">
-        <is>
-          <t>VARIANTA — výztuž piloty 8× R25 podélná + třmínky Ø10 á 200 B500B</t>
-        </is>
-      </c>
-      <c r="G83" s="7" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="H83" s="7" t="n">
-        <v>380</v>
-      </c>
-      <c r="I83" s="9" t="inlineStr">
-        <is>
-          <t>8 ks × 3.86 kg/m × 8 m + třmínky placeholder  [výkres:A105, igp_section:4.3]</t>
-        </is>
-      </c>
-      <c r="J83" s="9" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="3" t="inlineStr">
-        <is>
-          <t>→ Podlahová deska — bednění + výztuž + distance + beton</t>
+      <c r="D84" s="5" t="inlineStr">
+        <is>
+          <t>HSV-1</t>
+        </is>
+      </c>
+      <c r="E84" s="5" t="inlineStr">
+        <is>
+          <t>HSV-1-015</t>
+        </is>
+      </c>
+      <c r="F84" s="6" t="inlineStr">
+        <is>
+          <t>Zásyp výkopů kolem patek + okolo obetonovaných sítí, zhutněný</t>
+        </is>
+      </c>
+      <c r="G84" s="4" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="H84" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="I84" s="6" t="inlineStr">
+        <is>
+          <t>placeholder ~30 m³ (zásypy okolo patek + nad obetonovanými sítěmi)  [phase:Phase 0b RE-RUN §3.10]</t>
+        </is>
+      </c>
+      <c r="J84" s="6" t="inlineStr">
+        <is>
+          <t>ABMV:ABMV_17</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="7" t="n">
-        <v>54</v>
-      </c>
-      <c r="B85" s="8" t="inlineStr"/>
-      <c r="C85" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="D85" s="8" t="inlineStr">
-        <is>
-          <t>HSV-2</t>
-        </is>
-      </c>
-      <c r="E85" s="8" t="inlineStr">
-        <is>
-          <t>HSV-2-014</t>
-        </is>
-      </c>
-      <c r="F85" s="9" t="inlineStr">
-        <is>
-          <t>Bednění obvodové desky — zřízení</t>
-        </is>
-      </c>
-      <c r="G85" s="7" t="inlineStr">
-        <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="H85" s="7" t="n">
-        <v>95</v>
-      </c>
-      <c r="I85" s="9" t="inlineStr">
-        <is>
-          <t>obvod desky ~95 bm  [výkres:A101]</t>
-        </is>
-      </c>
-      <c r="J85" s="9" t="inlineStr"/>
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>→ VARIANTA — pilota Ø800 / L=8 m (alternativa)</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B86" s="8" t="inlineStr"/>
       <c r="C86" s="7" t="n">
@@ -2939,69 +2966,70 @@
       </c>
       <c r="E86" s="8" t="inlineStr">
         <is>
-          <t>HSV-2-016</t>
+          <t>HSV-2-010</t>
         </is>
       </c>
       <c r="F86" s="9" t="inlineStr">
         <is>
-          <t>Výztuž desky KARI síť Ø8 oka 100×100 mm B500B — dolní vrstva</t>
+          <t>VARIANTA — pilota Ø800 / L=8 m C25/30 XC4 vrtná</t>
         </is>
       </c>
       <c r="G86" s="7" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="H86" s="7" t="n">
-        <v>2098.3</v>
-      </c>
-      <c r="I86" s="9">
-        <f> HSV-2-015 = 2098.3 kg  [měřeno:A105]</f>
-        <v/>
+        <v>1</v>
+      </c>
+      <c r="I86" s="9" t="inlineStr">
+        <is>
+          <t>1 ks pilota Ø800 × 8 m délka  [výkres:A105, igp_section:4.3]</t>
+        </is>
       </c>
       <c r="J86" s="9" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="4" t="n">
-        <v>56</v>
-      </c>
-      <c r="B87" s="5" t="inlineStr"/>
-      <c r="C87" s="4" t="n">
+      <c r="A87" s="7" t="n">
+        <v>57</v>
+      </c>
+      <c r="B87" s="8" t="inlineStr"/>
+      <c r="C87" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="D87" s="5" t="inlineStr">
+      <c r="D87" s="8" t="inlineStr">
         <is>
           <t>HSV-2</t>
         </is>
       </c>
-      <c r="E87" s="5" t="inlineStr">
-        <is>
-          <t>HSV-2-017</t>
-        </is>
-      </c>
-      <c r="F87" s="6" t="inlineStr">
-        <is>
-          <t>Distanční podložky výztuže desky — plast / beton, krytí 30 mm</t>
-        </is>
-      </c>
-      <c r="G87" s="4" t="inlineStr">
-        <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="H87" s="4" t="n">
-        <v>2475</v>
-      </c>
-      <c r="I87" s="6" t="inlineStr">
-        <is>
-          <t>495 m² × 5 ks/m² (typická hustota)</t>
-        </is>
-      </c>
-      <c r="J87" s="6" t="inlineStr"/>
+      <c r="E87" s="8" t="inlineStr">
+        <is>
+          <t>HSV-2-011</t>
+        </is>
+      </c>
+      <c r="F87" s="9" t="inlineStr">
+        <is>
+          <t>VARIANTA — vrtání piloty Ø800 do hor. tř. 3-4</t>
+        </is>
+      </c>
+      <c r="G87" s="7" t="inlineStr">
+        <is>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="H87" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="I87" s="9" t="inlineStr">
+        <is>
+          <t>1 ks × 8 m délka  [výkres:A105, igp_section:4.3]</t>
+        </is>
+      </c>
+      <c r="J87" s="9" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="7" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B88" s="8" t="inlineStr"/>
       <c r="C88" s="7" t="n">
@@ -3014,12 +3042,12 @@
       </c>
       <c r="E88" s="8" t="inlineStr">
         <is>
-          <t>HSV-2-015</t>
+          <t>HSV-2-012</t>
         </is>
       </c>
       <c r="F88" s="9" t="inlineStr">
         <is>
-          <t>Výztuž desky KARI síť Ø8 oka 100×100 mm B500B — horní vrstva</t>
+          <t>VARIANTA — výztuž piloty 8× R25 podélná + třmínky Ø10 á 200 B500B</t>
         </is>
       </c>
       <c r="G88" s="7" t="inlineStr">
@@ -3028,247 +3056,277 @@
         </is>
       </c>
       <c r="H88" s="7" t="n">
+        <v>380</v>
+      </c>
+      <c r="I88" s="9" t="inlineStr">
+        <is>
+          <t>8 ks × 3.86 kg/m × 8 m + třmínky placeholder  [výkres:A105, igp_section:4.3]</t>
+        </is>
+      </c>
+      <c r="J88" s="9" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>→ Podlahová deska — bednění + výztuž + distance + beton</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="7" t="n">
+        <v>59</v>
+      </c>
+      <c r="B90" s="8" t="inlineStr"/>
+      <c r="C90" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D90" s="8" t="inlineStr">
+        <is>
+          <t>HSV-2</t>
+        </is>
+      </c>
+      <c r="E90" s="8" t="inlineStr">
+        <is>
+          <t>HSV-2-014</t>
+        </is>
+      </c>
+      <c r="F90" s="9" t="inlineStr">
+        <is>
+          <t>Bednění obvodové desky — zřízení</t>
+        </is>
+      </c>
+      <c r="G90" s="7" t="inlineStr">
+        <is>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="H90" s="7" t="n">
+        <v>95</v>
+      </c>
+      <c r="I90" s="9" t="inlineStr">
+        <is>
+          <t>obvod desky ~95 bm  [výkres:A101]</t>
+        </is>
+      </c>
+      <c r="J90" s="9" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="B91" s="8" t="inlineStr"/>
+      <c r="C91" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D91" s="8" t="inlineStr">
+        <is>
+          <t>HSV-2</t>
+        </is>
+      </c>
+      <c r="E91" s="8" t="inlineStr">
+        <is>
+          <t>HSV-2-016</t>
+        </is>
+      </c>
+      <c r="F91" s="9" t="inlineStr">
+        <is>
+          <t>Výztuž desky KARI síť Ø8 oka 100×100 mm B500B — dolní vrstva</t>
+        </is>
+      </c>
+      <c r="G91" s="7" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="H91" s="7" t="n">
         <v>2098.3</v>
       </c>
-      <c r="I88" s="9" t="inlineStr">
-        <is>
-          <t>531.22 × 3.95 = 2098.3 kg  [měřeno:A105]</t>
-        </is>
-      </c>
-      <c r="J88" s="9" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="13" t="n">
-        <v>58</v>
-      </c>
-      <c r="B89" s="14" t="inlineStr"/>
-      <c r="C89" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="D89" s="14" t="inlineStr">
-        <is>
-          <t>HSV-2</t>
-        </is>
-      </c>
-      <c r="E89" s="14" t="inlineStr">
-        <is>
-          <t>HSV-2-013</t>
-        </is>
-      </c>
-      <c r="F89" s="15" t="inlineStr">
-        <is>
-          <t>Beton podlahové desky C25/30 XC4, tl. 200 mm — strojně rovnaný povrch</t>
-        </is>
-      </c>
-      <c r="G89" s="13" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="H89" s="13" t="n">
-        <v>106.24</v>
-      </c>
-      <c r="I89" s="15" t="inlineStr">
-        <is>
-          <t>531.22 × 0.20 = 106.24 m³  [TZ:B, měřeno:A105, ABMV]</t>
-        </is>
-      </c>
-      <c r="J89" s="15" t="inlineStr">
-        <is>
-          <t>rev:beton-class</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="22" customHeight="1">
-      <c r="A90" s="2" t="inlineStr">
-        <is>
-          <t>═══ FÁZE 4: NOSNÁ OCELOVÁ KONSTRUKCE ═══</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="3" t="inlineStr">
-        <is>
-          <t>→ Doprava OK na stavbu</t>
-        </is>
-      </c>
+      <c r="I91" s="9">
+        <f> HSV-2-015 = 2098.3 kg  [měřeno:A105]</f>
+        <v/>
+      </c>
+      <c r="J91" s="9" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="4" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B92" s="5" t="inlineStr"/>
       <c r="C92" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D92" s="5" t="inlineStr">
+        <is>
+          <t>HSV-2</t>
+        </is>
+      </c>
+      <c r="E92" s="5" t="inlineStr">
+        <is>
+          <t>HSV-2-017</t>
+        </is>
+      </c>
+      <c r="F92" s="6" t="inlineStr">
+        <is>
+          <t>Distanční podložky výztuže desky — plast / beton, krytí 30 mm</t>
+        </is>
+      </c>
+      <c r="G92" s="4" t="inlineStr">
+        <is>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="H92" s="4" t="n">
+        <v>2475</v>
+      </c>
+      <c r="I92" s="6" t="inlineStr">
+        <is>
+          <t>495 m² × 5 ks/m² (typická hustota)</t>
+        </is>
+      </c>
+      <c r="J92" s="6" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="7" t="n">
+        <v>62</v>
+      </c>
+      <c r="B93" s="8" t="inlineStr"/>
+      <c r="C93" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D93" s="8" t="inlineStr">
+        <is>
+          <t>HSV-2</t>
+        </is>
+      </c>
+      <c r="E93" s="8" t="inlineStr">
+        <is>
+          <t>HSV-2-015</t>
+        </is>
+      </c>
+      <c r="F93" s="9" t="inlineStr">
+        <is>
+          <t>Výztuž desky KARI síť Ø8 oka 100×100 mm B500B — horní vrstva</t>
+        </is>
+      </c>
+      <c r="G93" s="7" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="H93" s="7" t="n">
+        <v>2098.3</v>
+      </c>
+      <c r="I93" s="9" t="inlineStr">
+        <is>
+          <t>531.22 × 3.95 = 2098.3 kg  [měřeno:A105]</t>
+        </is>
+      </c>
+      <c r="J93" s="9" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="13" t="n">
+        <v>63</v>
+      </c>
+      <c r="B94" s="14" t="inlineStr"/>
+      <c r="C94" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D94" s="14" t="inlineStr">
+        <is>
+          <t>HSV-2</t>
+        </is>
+      </c>
+      <c r="E94" s="14" t="inlineStr">
+        <is>
+          <t>HSV-2-013</t>
+        </is>
+      </c>
+      <c r="F94" s="15" t="inlineStr">
+        <is>
+          <t>Beton podlahové desky C25/30 XC4, tl. 200 mm — strojně rovnaný povrch</t>
+        </is>
+      </c>
+      <c r="G94" s="13" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="H94" s="13" t="n">
+        <v>106.24</v>
+      </c>
+      <c r="I94" s="15" t="inlineStr">
+        <is>
+          <t>531.22 × 0.20 = 106.24 m³  [TZ:B, měřeno:A105, ABMV]</t>
+        </is>
+      </c>
+      <c r="J94" s="15" t="inlineStr">
+        <is>
+          <t>rev:beton-class</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="22" customHeight="1">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>═══ FÁZE 4: NOSNÁ OCELOVÁ KONSTRUKCE ═══</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>→ Doprava OK na stavbu</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="n">
+        <v>64</v>
+      </c>
+      <c r="B97" s="5" t="inlineStr"/>
+      <c r="C97" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="D92" s="5" t="inlineStr">
+      <c r="D97" s="5" t="inlineStr">
         <is>
           <t>HSV-3</t>
         </is>
       </c>
-      <c r="E92" s="5" t="inlineStr">
+      <c r="E97" s="5" t="inlineStr">
         <is>
           <t>HSV-3-011</t>
         </is>
       </c>
-      <c r="F92" s="6" t="inlineStr">
+      <c r="F97" s="6" t="inlineStr">
         <is>
           <t>Doprava ocelové konstrukce na stavbu (default 50 km)</t>
         </is>
       </c>
-      <c r="G92" s="4" t="inlineStr">
+      <c r="G97" s="4" t="inlineStr">
         <is>
           <t>t·km</t>
         </is>
       </c>
-      <c r="H92" s="4" t="n">
+      <c r="H97" s="4" t="n">
         <v>1400</v>
       </c>
-      <c r="I92" s="6" t="inlineStr">
+      <c r="I97" s="6" t="inlineStr">
         <is>
           <t>28 t × 50 km</t>
         </is>
       </c>
-      <c r="J92" s="6" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="3" t="inlineStr">
+      <c r="J97" s="6" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="inlineStr">
         <is>
           <t>→ Kotvení sloupů ke patkám</t>
         </is>
       </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="B94" s="8" t="inlineStr"/>
-      <c r="C94" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="D94" s="8" t="inlineStr">
-        <is>
-          <t>HSV-3</t>
-        </is>
-      </c>
-      <c r="E94" s="8" t="inlineStr">
-        <is>
-          <t>HSV-3-009</t>
-        </is>
-      </c>
-      <c r="F94" s="9" t="inlineStr">
-        <is>
-          <t>Kotvení sloupů ke patkám — chemická kotva M20 nebo zalité šrouby, výztužná deska</t>
-        </is>
-      </c>
-      <c r="G94" s="7" t="inlineStr">
-        <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="H94" s="7" t="n">
-        <v>176</v>
-      </c>
-      <c r="I94" s="9" t="inlineStr">
-        <is>
-          <t>(36 + 8) sloupů × 4 kotvy/sloup = 176 ks  [výkres:A105]</t>
-        </is>
-      </c>
-      <c r="J94" s="9" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="3" t="inlineStr">
-        <is>
-          <t>→ Pomocné lešení OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="4" t="n">
-        <v>61</v>
-      </c>
-      <c r="B96" s="5" t="inlineStr"/>
-      <c r="C96" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="D96" s="5" t="inlineStr">
-        <is>
-          <t>HSV-9</t>
-        </is>
-      </c>
-      <c r="E96" s="5" t="inlineStr">
-        <is>
-          <t>HSV-9-002</t>
-        </is>
-      </c>
-      <c r="F96" s="6" t="inlineStr">
-        <is>
-          <t>Pomocné lešení pro montáž ocelové konstrukce, výška do 6 m</t>
-        </is>
-      </c>
-      <c r="G96" s="4" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="H96" s="4" t="n">
-        <v>200</v>
-      </c>
-      <c r="I96" s="6" t="inlineStr">
-        <is>
-          <t>placeholder ~200 m³ prostorové lešení pro halu 28×19×6 m</t>
-        </is>
-      </c>
-      <c r="J96" s="6" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="3" t="inlineStr">
-        <is>
-          <t>→ Dodávka prvků OK (sloupy, příčle, vaznice, ztužidla)</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="4" t="n">
-        <v>62</v>
-      </c>
-      <c r="B98" s="5" t="inlineStr"/>
-      <c r="C98" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="D98" s="5" t="inlineStr">
-        <is>
-          <t>HSV-3</t>
-        </is>
-      </c>
-      <c r="E98" s="5" t="inlineStr">
-        <is>
-          <t>HSV-3-001</t>
-        </is>
-      </c>
-      <c r="F98" s="6" t="inlineStr">
-        <is>
-          <t>Specifikace + dodávka sloupy IPE 400 S235 jakost J0, EXC2 dle ČSN EN 1090-2</t>
-        </is>
-      </c>
-      <c r="G98" s="4" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="H98" s="4" t="n">
-        <v>10263.24</v>
-      </c>
-      <c r="I98" s="6" t="inlineStr">
-        <is>
-          <t>36 ks × 4.3 m × 66.3 kg/m = 10 263 kg  [výkres:A101]</t>
-        </is>
-      </c>
-      <c r="J98" s="6" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="7" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B99" s="8" t="inlineStr"/>
       <c r="C99" s="7" t="n">
@@ -3281,184 +3339,118 @@
       </c>
       <c r="E99" s="8" t="inlineStr">
         <is>
-          <t>HSV-3-002</t>
+          <t>HSV-3-009</t>
         </is>
       </c>
       <c r="F99" s="9" t="inlineStr">
         <is>
-          <t>Specifikace + dodávka sloupy HEA 200 S235 jakost J0, štítové, EXC2</t>
+          <t>Kotvení sloupů ke patkám — chemická kotva M20 nebo zalité šrouby, výztužná deska</t>
         </is>
       </c>
       <c r="G99" s="7" t="inlineStr">
         <is>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="H99" s="7" t="n">
+        <v>176</v>
+      </c>
+      <c r="I99" s="9" t="inlineStr">
+        <is>
+          <t>(36 + 8) sloupů × 4 kotvy/sloup = 176 ks  [výkres:A105]</t>
+        </is>
+      </c>
+      <c r="J99" s="9" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="inlineStr">
+        <is>
+          <t>→ Pomocné lešení OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="4" t="n">
+        <v>66</v>
+      </c>
+      <c r="B101" s="5" t="inlineStr"/>
+      <c r="C101" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D101" s="5" t="inlineStr">
+        <is>
+          <t>HSV-9</t>
+        </is>
+      </c>
+      <c r="E101" s="5" t="inlineStr">
+        <is>
+          <t>HSV-9-002</t>
+        </is>
+      </c>
+      <c r="F101" s="6" t="inlineStr">
+        <is>
+          <t>Pomocné lešení pro montáž ocelové konstrukce, výška do 6 m</t>
+        </is>
+      </c>
+      <c r="G101" s="4" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="H101" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="I101" s="6" t="inlineStr">
+        <is>
+          <t>placeholder ~200 m³ prostorové lešení pro halu 28×19×6 m</t>
+        </is>
+      </c>
+      <c r="J101" s="6" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="3" t="inlineStr">
+        <is>
+          <t>→ Dodávka prvků OK (sloupy, příčle, vaznice, ztužidla)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="B103" s="5" t="inlineStr"/>
+      <c r="C103" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D103" s="5" t="inlineStr">
+        <is>
+          <t>HSV-3</t>
+        </is>
+      </c>
+      <c r="E103" s="5" t="inlineStr">
+        <is>
+          <t>HSV-3-001</t>
+        </is>
+      </c>
+      <c r="F103" s="6" t="inlineStr">
+        <is>
+          <t>Specifikace + dodávka sloupy IPE 400 S235 jakost J0, EXC2 dle ČSN EN 1090-2</t>
+        </is>
+      </c>
+      <c r="G103" s="4" t="inlineStr">
+        <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="H99" s="7" t="n">
-        <v>1455.12</v>
-      </c>
-      <c r="I99" s="9" t="inlineStr">
-        <is>
-          <t>8 ks × 4.3 m × 42.3 kg/m = 1 455 kg  [výkres:A101]</t>
-        </is>
-      </c>
-      <c r="J99" s="9" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="7" t="n">
-        <v>64</v>
-      </c>
-      <c r="B100" s="8" t="inlineStr"/>
-      <c r="C100" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="D100" s="8" t="inlineStr">
-        <is>
-          <t>HSV-3</t>
-        </is>
-      </c>
-      <c r="E100" s="8" t="inlineStr">
-        <is>
-          <t>HSV-3-003</t>
-        </is>
-      </c>
-      <c r="F100" s="9" t="inlineStr">
-        <is>
-          <t>Specifikace + dodávka příčlí IPE 450 S235 s náběhem (sklon 5.25°)</t>
-        </is>
-      </c>
-      <c r="G100" s="7" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="H100" s="7" t="n">
-        <v>9474.959999999999</v>
-      </c>
-      <c r="I100" s="9" t="inlineStr">
-        <is>
-          <t>6 rámů × 18.5 m × 77.6 kg/m × 1.1 (náběh) = 9 478 kg</t>
-        </is>
-      </c>
-      <c r="J100" s="9" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="7" t="n">
-        <v>65</v>
-      </c>
-      <c r="B101" s="8" t="inlineStr"/>
-      <c r="C101" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="D101" s="8" t="inlineStr">
-        <is>
-          <t>HSV-3</t>
-        </is>
-      </c>
-      <c r="E101" s="8" t="inlineStr">
-        <is>
-          <t>HSV-3-004</t>
-        </is>
-      </c>
-      <c r="F101" s="9" t="inlineStr">
-        <is>
-          <t>Specifikace + dodávka vaznice IPE 160 S235 jakost J0</t>
-        </is>
-      </c>
-      <c r="G101" s="7" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="H101" s="7" t="n">
-        <v>5195.04</v>
-      </c>
-      <c r="I101" s="9" t="inlineStr">
-        <is>
-          <t>12 řad × 27.4 m × 15.8 kg/m = 5 195 kg  [TZ:D.1.2 (statika) — vaznice rozteč]</t>
-        </is>
-      </c>
-      <c r="J101" s="9" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="7" t="n">
-        <v>66</v>
-      </c>
-      <c r="B102" s="8" t="inlineStr"/>
-      <c r="C102" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="D102" s="8" t="inlineStr">
-        <is>
-          <t>HSV-3</t>
-        </is>
-      </c>
-      <c r="E102" s="8" t="inlineStr">
-        <is>
-          <t>HSV-3-005</t>
-        </is>
-      </c>
-      <c r="F102" s="9" t="inlineStr">
-        <is>
-          <t>Specifikace + dodávka vaznice krajní UPE 160 S235 jakost J0</t>
-        </is>
-      </c>
-      <c r="G102" s="7" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="H102" s="7" t="n">
-        <v>1030.24</v>
-      </c>
-      <c r="I102" s="9" t="inlineStr">
-        <is>
-          <t>2 ks × 27.4 m × 18.8 kg/m = 1 030 kg</t>
-        </is>
-      </c>
-      <c r="J102" s="9" t="inlineStr">
-        <is>
-          <t>ABMV:ABMV_15</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="7" t="n">
-        <v>67</v>
-      </c>
-      <c r="B103" s="8" t="inlineStr"/>
-      <c r="C103" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="D103" s="8" t="inlineStr">
-        <is>
-          <t>HSV-3</t>
-        </is>
-      </c>
-      <c r="E103" s="8" t="inlineStr">
-        <is>
-          <t>HSV-3-006</t>
-        </is>
-      </c>
-      <c r="F103" s="9" t="inlineStr">
-        <is>
-          <t>Specifikace + dodávka ztužidla stěnová L 70/70/6 S235</t>
-        </is>
-      </c>
-      <c r="G103" s="7" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="H103" s="7" t="n">
-        <v>327.68</v>
-      </c>
-      <c r="I103" s="9" t="inlineStr">
-        <is>
-          <t>8 ks × 6.4 m × 6.4 kg/m = 328 kg</t>
-        </is>
-      </c>
-      <c r="J103" s="9" t="inlineStr"/>
+      <c r="H103" s="4" t="n">
+        <v>10263.24</v>
+      </c>
+      <c r="I103" s="6" t="inlineStr">
+        <is>
+          <t>36 ks × 4.3 m × 66.3 kg/m = 10 263 kg  [výkres:A101]</t>
+        </is>
+      </c>
+      <c r="J103" s="6" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="7" t="n">
@@ -3475,12 +3467,12 @@
       </c>
       <c r="E104" s="8" t="inlineStr">
         <is>
-          <t>HSV-3-007</t>
+          <t>HSV-3-002</t>
         </is>
       </c>
       <c r="F104" s="9" t="inlineStr">
         <is>
-          <t>Specifikace + dodávka ztužidla střešní z kruhových tyčí Ø20 S235</t>
+          <t>Specifikace + dodávka sloupy HEA 200 S235 jakost J0, štítové, EXC2</t>
         </is>
       </c>
       <c r="G104" s="7" t="inlineStr">
@@ -3489,25 +3481,56 @@
         </is>
       </c>
       <c r="H104" s="7" t="n">
-        <v>237.12</v>
+        <v>1455.12</v>
       </c>
       <c r="I104" s="9" t="inlineStr">
         <is>
-          <t>8 ks × 12 m × 2.47 kg/m = 237 kg  [výkres:A101]</t>
+          <t>8 ks × 4.3 m × 42.3 kg/m = 1 455 kg  [výkres:A101]</t>
         </is>
       </c>
       <c r="J104" s="9" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" s="3" t="inlineStr">
-        <is>
-          <t>→ Styčníkové plechy + spojovací materiál</t>
-        </is>
-      </c>
+      <c r="A105" s="7" t="n">
+        <v>69</v>
+      </c>
+      <c r="B105" s="8" t="inlineStr"/>
+      <c r="C105" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D105" s="8" t="inlineStr">
+        <is>
+          <t>HSV-3</t>
+        </is>
+      </c>
+      <c r="E105" s="8" t="inlineStr">
+        <is>
+          <t>HSV-3-003</t>
+        </is>
+      </c>
+      <c r="F105" s="9" t="inlineStr">
+        <is>
+          <t>Specifikace + dodávka příčlí IPE 450 S235 s náběhem (sklon 5.25°)</t>
+        </is>
+      </c>
+      <c r="G105" s="7" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="H105" s="7" t="n">
+        <v>9474.959999999999</v>
+      </c>
+      <c r="I105" s="9" t="inlineStr">
+        <is>
+          <t>6 rámů × 18.5 m × 77.6 kg/m × 1.1 (náběh) = 9 478 kg</t>
+        </is>
+      </c>
+      <c r="J105" s="9" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="7" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B106" s="8" t="inlineStr"/>
       <c r="C106" s="7" t="n">
@@ -3520,12 +3543,12 @@
       </c>
       <c r="E106" s="8" t="inlineStr">
         <is>
-          <t>HSV-3-008</t>
+          <t>HSV-3-004</t>
         </is>
       </c>
       <c r="F106" s="9" t="inlineStr">
         <is>
-          <t>Styčníkové plechy + spojovací materiál šroubový grade 8.8 — celk. paušál 6%</t>
+          <t>Specifikace + dodávka vaznice IPE 160 S235 jakost J0</t>
         </is>
       </c>
       <c r="G106" s="7" t="inlineStr">
@@ -3534,25 +3557,60 @@
         </is>
       </c>
       <c r="H106" s="7" t="n">
-        <v>1450</v>
+        <v>5195.04</v>
       </c>
       <c r="I106" s="9" t="inlineStr">
         <is>
-          <t>~6% × součet OK 27 985 kg ≈ 1 450 kg  [csn]</t>
+          <t>12 řad × 27.4 m × 15.8 kg/m = 5 195 kg  [TZ:D.1.2 (statika) — vaznice rozteč]</t>
         </is>
       </c>
       <c r="J106" s="9" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" s="3" t="inlineStr">
-        <is>
-          <t>→ Montáž OK — kompletace rámové haly</t>
+      <c r="A107" s="7" t="n">
+        <v>71</v>
+      </c>
+      <c r="B107" s="8" t="inlineStr"/>
+      <c r="C107" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D107" s="8" t="inlineStr">
+        <is>
+          <t>HSV-3</t>
+        </is>
+      </c>
+      <c r="E107" s="8" t="inlineStr">
+        <is>
+          <t>HSV-3-005</t>
+        </is>
+      </c>
+      <c r="F107" s="9" t="inlineStr">
+        <is>
+          <t>Specifikace + dodávka vaznice krajní UPE 160 S235 jakost J0</t>
+        </is>
+      </c>
+      <c r="G107" s="7" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="H107" s="7" t="n">
+        <v>1030.24</v>
+      </c>
+      <c r="I107" s="9" t="inlineStr">
+        <is>
+          <t>2 ks × 27.4 m × 18.8 kg/m = 1 030 kg</t>
+        </is>
+      </c>
+      <c r="J107" s="9" t="inlineStr">
+        <is>
+          <t>ABMV:ABMV_15</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="7" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B108" s="8" t="inlineStr"/>
       <c r="C108" s="7" t="n">
@@ -3565,121 +3623,122 @@
       </c>
       <c r="E108" s="8" t="inlineStr">
         <is>
-          <t>HSV-3-010</t>
+          <t>HSV-3-006</t>
         </is>
       </c>
       <c r="F108" s="9" t="inlineStr">
         <is>
-          <t>Montáž ocelové konstrukce — kompletní rámová hala, dle ČSN EN 1090-2 EXC2 tol. cl. 1</t>
+          <t>Specifikace + dodávka ztužidla stěnová L 70/70/6 S235</t>
         </is>
       </c>
       <c r="G108" s="7" t="inlineStr">
         <is>
-          <t>t</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="H108" s="7" t="n">
-        <v>28</v>
+        <v>327.68</v>
       </c>
       <c r="I108" s="9" t="inlineStr">
         <is>
-          <t>součet OK profilů + kotev = ~28 t</t>
+          <t>8 ks × 6.4 m × 6.4 kg/m = 328 kg</t>
         </is>
       </c>
       <c r="J108" s="9" t="inlineStr"/>
     </row>
     <row r="109">
-      <c r="A109" s="3" t="inlineStr">
-        <is>
-          <t>→ Demontáž pomocného lešení po montáži OK</t>
-        </is>
-      </c>
+      <c r="A109" s="7" t="n">
+        <v>73</v>
+      </c>
+      <c r="B109" s="8" t="inlineStr"/>
+      <c r="C109" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D109" s="8" t="inlineStr">
+        <is>
+          <t>HSV-3</t>
+        </is>
+      </c>
+      <c r="E109" s="8" t="inlineStr">
+        <is>
+          <t>HSV-3-007</t>
+        </is>
+      </c>
+      <c r="F109" s="9" t="inlineStr">
+        <is>
+          <t>Specifikace + dodávka ztužidla střešní z kruhových tyčí Ø20 S235</t>
+        </is>
+      </c>
+      <c r="G109" s="7" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="H109" s="7" t="n">
+        <v>237.12</v>
+      </c>
+      <c r="I109" s="9" t="inlineStr">
+        <is>
+          <t>8 ks × 12 m × 2.47 kg/m = 237 kg  [výkres:A101]</t>
+        </is>
+      </c>
+      <c r="J109" s="9" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" s="7" t="n">
-        <v>71</v>
-      </c>
-      <c r="B110" s="8" t="inlineStr"/>
-      <c r="C110" s="7" t="n">
+      <c r="A110" s="3" t="inlineStr">
+        <is>
+          <t>→ Styčníkové plechy + spojovací materiál</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="7" t="n">
+        <v>74</v>
+      </c>
+      <c r="B111" s="8" t="inlineStr"/>
+      <c r="C111" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="D110" s="8" t="inlineStr">
-        <is>
-          <t>HSV-9</t>
-        </is>
-      </c>
-      <c r="E110" s="8" t="inlineStr">
-        <is>
-          <t>HSV-9-003</t>
-        </is>
-      </c>
-      <c r="F110" s="9" t="inlineStr">
-        <is>
-          <t>Demontáž pomocného lešení po dokončení montáže</t>
-        </is>
-      </c>
-      <c r="G110" s="7" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="H110" s="7" t="n">
-        <v>200</v>
-      </c>
-      <c r="I110" s="9">
-        <f> pomocné lešení</f>
-        <v/>
-      </c>
-      <c r="J110" s="9" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="3" t="inlineStr">
-        <is>
-          <t>→ Povrchové úpravy OK (antikoroze + protipožární)</t>
-        </is>
-      </c>
+      <c r="D111" s="8" t="inlineStr">
+        <is>
+          <t>HSV-3</t>
+        </is>
+      </c>
+      <c r="E111" s="8" t="inlineStr">
+        <is>
+          <t>HSV-3-008</t>
+        </is>
+      </c>
+      <c r="F111" s="9" t="inlineStr">
+        <is>
+          <t>Styčníkové plechy + spojovací materiál šroubový grade 8.8 — celk. paušál 6%</t>
+        </is>
+      </c>
+      <c r="G111" s="7" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="H111" s="7" t="n">
+        <v>1450</v>
+      </c>
+      <c r="I111" s="9" t="inlineStr">
+        <is>
+          <t>~6% × součet OK 27 985 kg ≈ 1 450 kg  [csn]</t>
+        </is>
+      </c>
+      <c r="J111" s="9" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" s="7" t="n">
-        <v>72</v>
-      </c>
-      <c r="B112" s="8" t="inlineStr"/>
-      <c r="C112" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="D112" s="8" t="inlineStr">
-        <is>
-          <t>HSV-3</t>
-        </is>
-      </c>
-      <c r="E112" s="8" t="inlineStr">
-        <is>
-          <t>HSV-3-012</t>
-        </is>
-      </c>
-      <c r="F112" s="9" t="inlineStr">
-        <is>
-          <t>Antikorozní nátěr 2-vrstvý dle ISO 12944, korozní katego­rie C2, P1, životnost 15 let</t>
-        </is>
-      </c>
-      <c r="G112" s="7" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="H112" s="7" t="n">
-        <v>850</v>
-      </c>
-      <c r="I112" s="9" t="inlineStr">
-        <is>
-          <t>celk. povrch profilů ~30 m²/t × 28 t = 850 m²  [výkres:C2]</t>
-        </is>
-      </c>
-      <c r="J112" s="9" t="inlineStr"/>
+      <c r="A112" s="3" t="inlineStr">
+        <is>
+          <t>→ Montáž OK — kompletace rámové haly</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="7" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B113" s="8" t="inlineStr"/>
       <c r="C113" s="7" t="n">
@@ -3692,38 +3751,39 @@
       </c>
       <c r="E113" s="8" t="inlineStr">
         <is>
-          <t>HSV-3-013</t>
+          <t>HSV-3-010</t>
         </is>
       </c>
       <c r="F113" s="9" t="inlineStr">
         <is>
-          <t>Protipožární nátěr — interiérové prvky R 15 DP1</t>
+          <t>Montáž ocelové konstrukce — kompletní rámová hala, dle ČSN EN 1090-2 EXC2 tol. cl. 1</t>
         </is>
       </c>
       <c r="G113" s="7" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>t</t>
         </is>
       </c>
       <c r="H113" s="7" t="n">
-        <v>850</v>
-      </c>
-      <c r="I113" s="9">
-        <f> antikor plocha (interiérové prvky stejně)</f>
-        <v/>
+        <v>28</v>
+      </c>
+      <c r="I113" s="9" t="inlineStr">
+        <is>
+          <t>součet OK profilů + kotev = ~28 t</t>
+        </is>
       </c>
       <c r="J113" s="9" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>→ Revize OK + protokol EXC2</t>
+          <t>→ Demontáž pomocného lešení po montáži OK</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="7" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B115" s="8" t="inlineStr"/>
       <c r="C115" s="7" t="n">
@@ -3731,227 +3791,222 @@
       </c>
       <c r="D115" s="8" t="inlineStr">
         <is>
+          <t>HSV-9</t>
+        </is>
+      </c>
+      <c r="E115" s="8" t="inlineStr">
+        <is>
+          <t>HSV-9-003</t>
+        </is>
+      </c>
+      <c r="F115" s="9" t="inlineStr">
+        <is>
+          <t>Demontáž pomocného lešení po dokončení montáže</t>
+        </is>
+      </c>
+      <c r="G115" s="7" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="H115" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="I115" s="9">
+        <f> pomocné lešení</f>
+        <v/>
+      </c>
+      <c r="J115" s="9" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="3" t="inlineStr">
+        <is>
+          <t>→ Povrchové úpravy OK (antikoroze + protipožární)</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="7" t="n">
+        <v>77</v>
+      </c>
+      <c r="B117" s="8" t="inlineStr"/>
+      <c r="C117" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D117" s="8" t="inlineStr">
+        <is>
           <t>HSV-3</t>
         </is>
       </c>
-      <c r="E115" s="8" t="inlineStr">
-        <is>
-          <t>HSV-3-014</t>
-        </is>
-      </c>
-      <c r="F115" s="9" t="inlineStr">
-        <is>
-          <t>Revize ocelové konstrukce + protokol o předání, EXC2 ČSN EN 1090-2</t>
-        </is>
-      </c>
-      <c r="G115" s="7" t="inlineStr">
-        <is>
-          <t>paušál</t>
-        </is>
-      </c>
-      <c r="H115" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I115" s="9" t="inlineStr">
-        <is>
-          <t>paušál  [csn]</t>
-        </is>
-      </c>
-      <c r="J115" s="9" t="inlineStr"/>
-    </row>
-    <row r="116" ht="22" customHeight="1">
-      <c r="A116" s="2" t="inlineStr">
-        <is>
-          <t>═══ FÁZE 5: OPLÁŠTĚNÍ KINGSPAN ═══</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="3" t="inlineStr">
-        <is>
-          <t>→ Pomocné lešení pro opláštění (pojízdné)</t>
-        </is>
-      </c>
+      <c r="E117" s="8" t="inlineStr">
+        <is>
+          <t>HSV-3-012</t>
+        </is>
+      </c>
+      <c r="F117" s="9" t="inlineStr">
+        <is>
+          <t>Antikorozní nátěr 2-vrstvý dle ISO 12944, korozní katego­rie C2, P1, životnost 15 let</t>
+        </is>
+      </c>
+      <c r="G117" s="7" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="H117" s="7" t="n">
+        <v>850</v>
+      </c>
+      <c r="I117" s="9" t="inlineStr">
+        <is>
+          <t>celk. povrch profilů ~30 m²/t × 28 t = 850 m²  [výkres:C2]</t>
+        </is>
+      </c>
+      <c r="J117" s="9" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="7" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B118" s="8" t="inlineStr"/>
       <c r="C118" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D118" s="8" t="inlineStr">
         <is>
-          <t>HSV-9</t>
+          <t>HSV-3</t>
         </is>
       </c>
       <c r="E118" s="8" t="inlineStr">
         <is>
-          <t>HSV-9-004</t>
+          <t>HSV-3-013</t>
         </is>
       </c>
       <c r="F118" s="9" t="inlineStr">
         <is>
-          <t>Pomocné lešení pro montáž opláštění (Kingspan) a klempířiny — pojízdné</t>
+          <t>Protipožární nátěr — interiérové prvky R 15 DP1</t>
         </is>
       </c>
       <c r="G118" s="7" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="H118" s="7" t="n">
-        <v>120</v>
-      </c>
-      <c r="I118" s="9" t="inlineStr">
-        <is>
-          <t>placeholder ~120 m³ pojízdné lešení pro obvodový plášť</t>
-        </is>
+        <v>850</v>
+      </c>
+      <c r="I118" s="9">
+        <f> antikor plocha (interiérové prvky stejně)</f>
+        <v/>
       </c>
       <c r="J118" s="9" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>→ Doprava sendvičových panelů Kingspan</t>
+          <t>→ Revize OK + protokol EXC2</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="4" t="n">
-        <v>76</v>
-      </c>
-      <c r="B120" s="5" t="inlineStr"/>
-      <c r="C120" s="4" t="n">
+      <c r="A120" s="7" t="n">
+        <v>79</v>
+      </c>
+      <c r="B120" s="8" t="inlineStr"/>
+      <c r="C120" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D120" s="8" t="inlineStr">
+        <is>
+          <t>HSV-3</t>
+        </is>
+      </c>
+      <c r="E120" s="8" t="inlineStr">
+        <is>
+          <t>HSV-3-014</t>
+        </is>
+      </c>
+      <c r="F120" s="9" t="inlineStr">
+        <is>
+          <t>Revize ocelové konstrukce + protokol o předání, EXC2 ČSN EN 1090-2</t>
+        </is>
+      </c>
+      <c r="G120" s="7" t="inlineStr">
+        <is>
+          <t>paušál</t>
+        </is>
+      </c>
+      <c r="H120" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I120" s="9" t="inlineStr">
+        <is>
+          <t>paušál  [csn]</t>
+        </is>
+      </c>
+      <c r="J120" s="9" t="inlineStr"/>
+    </row>
+    <row r="121" ht="22" customHeight="1">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>═══ FÁZE 5: OPLÁŠTĚNÍ KINGSPAN ═══</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="3" t="inlineStr">
+        <is>
+          <t>→ Pomocné lešení pro opláštění (pojízdné)</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="7" t="n">
+        <v>80</v>
+      </c>
+      <c r="B123" s="8" t="inlineStr"/>
+      <c r="C123" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="D120" s="5" t="inlineStr">
-        <is>
-          <t>PSV-OPL</t>
-        </is>
-      </c>
-      <c r="E120" s="5" t="inlineStr">
-        <is>
-          <t>PSV-OPL-007</t>
-        </is>
-      </c>
-      <c r="F120" s="6" t="inlineStr">
-        <is>
-          <t>Doprava sendvičových panelů Kingspan na stavbu — paušál</t>
-        </is>
-      </c>
-      <c r="G120" s="4" t="inlineStr">
-        <is>
-          <t>paušál</t>
-        </is>
-      </c>
-      <c r="H120" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I120" s="6" t="inlineStr">
-        <is>
-          <t>paušál  [TZ:D.1.1]</t>
-        </is>
-      </c>
-      <c r="J120" s="6" t="inlineStr"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="3" t="inlineStr">
-        <is>
-          <t>→ Stěnové panely KS 1000 NF 120 mm — dodávka + montáž</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="4" t="n">
-        <v>77</v>
-      </c>
-      <c r="B122" s="5" t="inlineStr"/>
-      <c r="C122" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="D122" s="5" t="inlineStr">
-        <is>
-          <t>PSV-OPL</t>
-        </is>
-      </c>
-      <c r="E122" s="5" t="inlineStr">
-        <is>
-          <t>PSV-OPL-001</t>
-        </is>
-      </c>
-      <c r="F122" s="6" t="inlineStr">
-        <is>
-          <t>Kingspan KS 1000 NF 120 mm, jádro minerální vata (MW), per Úprava dveří + TZ ARS DPZ D.1.1 — alternativně k orig. 200 mm</t>
-        </is>
-      </c>
-      <c r="G122" s="4" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="H122" s="4" t="n">
-        <v>510.81</v>
-      </c>
-      <c r="I122" s="6" t="inlineStr">
-        <is>
-          <t>fasáda brutto Úprava dveří: 94.57 m obvod × 6.085 m okap + 17.58 m² štíty = 593.06 m² brutto − 82.25 m² FR zóny (rohy s dveřmi) = 510.81 m² (bez vyřezání otvorů — sendvič ordered celý)  [TZ:D.1.1, Step3, ABMV]</t>
-        </is>
-      </c>
-      <c r="J122" s="6" t="inlineStr">
-        <is>
-          <t>ABMV:ABMV_13</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="10" t="n">
-        <v>78</v>
-      </c>
-      <c r="B123" s="11" t="inlineStr"/>
-      <c r="C123" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="D123" s="11" t="inlineStr">
-        <is>
-          <t>PSV-OPL</t>
-        </is>
-      </c>
-      <c r="E123" s="11" t="inlineStr">
-        <is>
-          <t>PSV-OPL-002</t>
-        </is>
-      </c>
-      <c r="F123" s="12" t="inlineStr">
-        <is>
-          <t>Montáž obvodového opláštění Kingspan KS 1000 NF 120 mm — kotvení samořeznými šrouby + EPDM těsnicí podložkou k ocelové konstrukci (rozteč rámů 6.1 m)</t>
-        </is>
-      </c>
-      <c r="G123" s="10" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="H123" s="10" t="n">
-        <v>510.81</v>
-      </c>
-      <c r="I123" s="12">
-        <f> dodávka PSV-OPL-001 = 510.81 m²  [TZ:D.1.1, ABMV, TZ:D.1.2 (statika) — Návrh opláštění]</f>
-        <v/>
-      </c>
-      <c r="J123" s="12" t="inlineStr"/>
+      <c r="D123" s="8" t="inlineStr">
+        <is>
+          <t>HSV-9</t>
+        </is>
+      </c>
+      <c r="E123" s="8" t="inlineStr">
+        <is>
+          <t>HSV-9-004</t>
+        </is>
+      </c>
+      <c r="F123" s="9" t="inlineStr">
+        <is>
+          <t>Pomocné lešení pro montáž opláštění (Kingspan) a klempířiny — pojízdné</t>
+        </is>
+      </c>
+      <c r="G123" s="7" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="H123" s="7" t="n">
+        <v>120</v>
+      </c>
+      <c r="I123" s="9" t="inlineStr">
+        <is>
+          <t>placeholder ~120 m³ pojízdné lešení pro obvodový plášť</t>
+        </is>
+      </c>
+      <c r="J123" s="9" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
         <is>
-          <t>→ Stěnové panely KS 1000 FR 150 mm (rohové zóny) — dodávka + montáž</t>
+          <t>→ Doprava sendvičových panelů Kingspan</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="4" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B125" s="5" t="inlineStr"/>
       <c r="C125" s="4" t="n">
@@ -3964,643 +4019,642 @@
       </c>
       <c r="E125" s="5" t="inlineStr">
         <is>
+          <t>PSV-OPL-007</t>
+        </is>
+      </c>
+      <c r="F125" s="6" t="inlineStr">
+        <is>
+          <t>Doprava sendvičových panelů Kingspan na stavbu — paušál</t>
+        </is>
+      </c>
+      <c r="G125" s="4" t="inlineStr">
+        <is>
+          <t>paušál</t>
+        </is>
+      </c>
+      <c r="H125" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I125" s="6" t="inlineStr">
+        <is>
+          <t>paušál  [TZ:D.1.1]</t>
+        </is>
+      </c>
+      <c r="J125" s="6" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="3" t="inlineStr">
+        <is>
+          <t>→ Stěnové panely KS 1000 NF 120 mm — dodávka + montáž</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="4" t="n">
+        <v>82</v>
+      </c>
+      <c r="B127" s="5" t="inlineStr"/>
+      <c r="C127" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D127" s="5" t="inlineStr">
+        <is>
+          <t>PSV-OPL</t>
+        </is>
+      </c>
+      <c r="E127" s="5" t="inlineStr">
+        <is>
+          <t>PSV-OPL-001</t>
+        </is>
+      </c>
+      <c r="F127" s="6" t="inlineStr">
+        <is>
+          <t>Kingspan KS 1000 NF 120 mm, jádro minerální vata (MW), per Úprava dveří + TZ ARS DPZ D.1.1 — alternativně k orig. 200 mm</t>
+        </is>
+      </c>
+      <c r="G127" s="4" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="H127" s="4" t="n">
+        <v>510.81</v>
+      </c>
+      <c r="I127" s="6" t="inlineStr">
+        <is>
+          <t>fasáda brutto Úprava dveří: 94.57 m obvod × 6.085 m okap + 17.58 m² štíty = 593.06 m² brutto − 82.25 m² FR zóny (rohy s dveřmi) = 510.81 m² (bez vyřezání otvorů — sendvič ordered celý)  [TZ:D.1.1, Step3, ABMV]</t>
+        </is>
+      </c>
+      <c r="J127" s="6" t="inlineStr">
+        <is>
+          <t>ABMV:ABMV_13</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="10" t="n">
+        <v>83</v>
+      </c>
+      <c r="B128" s="11" t="inlineStr"/>
+      <c r="C128" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="D128" s="11" t="inlineStr">
+        <is>
+          <t>PSV-OPL</t>
+        </is>
+      </c>
+      <c r="E128" s="11" t="inlineStr">
+        <is>
+          <t>PSV-OPL-002</t>
+        </is>
+      </c>
+      <c r="F128" s="12" t="inlineStr">
+        <is>
+          <t>Montáž obvodového opláštění Kingspan KS 1000 NF 120 mm — kotvení samořeznými šrouby + EPDM těsnicí podložkou k ocelové konstrukci (rozteč rámů 6.1 m)</t>
+        </is>
+      </c>
+      <c r="G128" s="10" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="H128" s="10" t="n">
+        <v>510.81</v>
+      </c>
+      <c r="I128" s="12">
+        <f> dodávka PSV-OPL-001 = 510.81 m²  [TZ:D.1.1, ABMV, TZ:D.1.2 (statika) — Návrh opláštění]</f>
+        <v/>
+      </c>
+      <c r="J128" s="12" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="3" t="inlineStr">
+        <is>
+          <t>→ Stěnové panely KS 1000 FR 150 mm (rohové zóny) — dodávka + montáž</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="4" t="n">
+        <v>84</v>
+      </c>
+      <c r="B130" s="5" t="inlineStr"/>
+      <c r="C130" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D130" s="5" t="inlineStr">
+        <is>
+          <t>PSV-OPL</t>
+        </is>
+      </c>
+      <c r="E130" s="5" t="inlineStr">
+        <is>
           <t>PSV-OPL-009</t>
         </is>
       </c>
-      <c r="F125" s="6" t="inlineStr">
+      <c r="F130" s="6" t="inlineStr">
         <is>
           <t>Kingspan KS 1000 FR 150 mm, jádro PIR (fire-resistant), 2 rohové zóny u vstupních dveří (45.69 + 36.56 m²) — Úprava dveří</t>
         </is>
       </c>
-      <c r="G125" s="4" t="inlineStr">
+      <c r="G130" s="4" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="H125" s="4" t="n">
+      <c r="H130" s="4" t="n">
         <v>82.25</v>
       </c>
-      <c r="I125" s="6" t="inlineStr">
+      <c r="I130" s="6" t="inlineStr">
         <is>
           <t>45.69 m² + 36.56 m² = 82.25 m² (2 šrafované rohové zóny v POHLED F a POHLED 01 — user manual měření)  [výkres:Hala HK_Úprava dveří, TZ:B p.8]  · was 82.25: Úprava dveří revision — first appearance</t>
         </is>
       </c>
-      <c r="J125" s="6" t="inlineStr"/>
-    </row>
-    <row r="126">
-      <c r="A126" s="10" t="n">
-        <v>80</v>
-      </c>
-      <c r="B126" s="11" t="inlineStr"/>
-      <c r="C126" s="10" t="n">
+      <c r="J130" s="6" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="10" t="n">
+        <v>85</v>
+      </c>
+      <c r="B131" s="11" t="inlineStr"/>
+      <c r="C131" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="D126" s="11" t="inlineStr">
+      <c r="D131" s="11" t="inlineStr">
         <is>
           <t>PSV-OPL</t>
         </is>
       </c>
-      <c r="E126" s="11" t="inlineStr">
+      <c r="E131" s="11" t="inlineStr">
         <is>
           <t>PSV-OPL-010</t>
         </is>
       </c>
-      <c r="F126" s="12" t="inlineStr">
+      <c r="F131" s="12" t="inlineStr">
         <is>
           <t>Montáž Kingspan KS 1000 FR 150 mm — 2 rohové zóny (45.69 + 36.56 m²), kotvení samořeznými šrouby + EPDM podložka</t>
         </is>
       </c>
-      <c r="G126" s="10" t="inlineStr">
+      <c r="G131" s="10" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="H126" s="10" t="n">
+      <c r="H131" s="10" t="n">
         <v>82.25</v>
       </c>
-      <c r="I126" s="12">
+      <c r="I131" s="12">
         <f> dodávka PSV-OPL-009 = 82.25 m²  [výkres:Hala HK_Úprava dveří]  · was 82.25: Úprava dveří revision — first appearance</f>
         <v/>
       </c>
-      <c r="J126" s="12" t="inlineStr"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="3" t="inlineStr">
+      <c r="J131" s="12" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="3" t="inlineStr">
         <is>
           <t>→ Střešní panely KS 1000 RW 160 mm (hlavní střecha) — dodávka + montáž</t>
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="4" t="n">
-        <v>81</v>
-      </c>
-      <c r="B128" s="5" t="inlineStr"/>
-      <c r="C128" s="4" t="n">
+    <row r="133">
+      <c r="A133" s="4" t="n">
+        <v>86</v>
+      </c>
+      <c r="B133" s="5" t="inlineStr"/>
+      <c r="C133" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="D128" s="5" t="inlineStr">
+      <c r="D133" s="5" t="inlineStr">
         <is>
           <t>PSV-OPL</t>
         </is>
       </c>
-      <c r="E128" s="5" t="inlineStr">
+      <c r="E133" s="5" t="inlineStr">
         <is>
           <t>PSV-OPL-003</t>
         </is>
       </c>
-      <c r="F128" s="6" t="inlineStr">
+      <c r="F133" s="6" t="inlineStr">
         <is>
           <t>Kingspan KS 1000 RW 160 mm, jádro PIR, pro šikmé střechy sklon 5.25°, hlavní střecha (mimo zónu FF 175)</t>
         </is>
       </c>
-      <c r="G128" s="4" t="inlineStr">
+      <c r="G133" s="4" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="H128" s="4" t="n">
+      <c r="H133" s="4" t="n">
         <v>500.6</v>
       </c>
-      <c r="I128" s="6" t="inlineStr">
+      <c r="I133" s="6" t="inlineStr">
         <is>
           <t>střecha total 558.8 m² − FF 175 zóna 58.20 m² (57.95 m² projection / cos 5.25°) = 500.6 m² — Úprava dveří section view  [TZ:D.1.1, DXF, Step3]</t>
         </is>
       </c>
-      <c r="J128" s="6" t="inlineStr">
+      <c r="J133" s="6" t="inlineStr">
         <is>
           <t>ABMV:ABMV_13</t>
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="10" t="n">
-        <v>82</v>
-      </c>
-      <c r="B129" s="11" t="inlineStr"/>
-      <c r="C129" s="10" t="n">
+    <row r="134">
+      <c r="A134" s="10" t="n">
+        <v>87</v>
+      </c>
+      <c r="B134" s="11" t="inlineStr"/>
+      <c r="C134" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="D129" s="11" t="inlineStr">
+      <c r="D134" s="11" t="inlineStr">
         <is>
           <t>PSV-OPL</t>
         </is>
       </c>
-      <c r="E129" s="11" t="inlineStr">
+      <c r="E134" s="11" t="inlineStr">
         <is>
           <t>PSV-OPL-004</t>
         </is>
       </c>
-      <c r="F129" s="12" t="inlineStr">
+      <c r="F134" s="12" t="inlineStr">
         <is>
           <t>Montáž střešního opláštění Kingspan KS 1000 RW 160 mm — kotvení k ocelové konstrukci samořeznými šrouby + těsnění přesahů</t>
         </is>
       </c>
-      <c r="G129" s="10" t="inlineStr">
+      <c r="G134" s="10" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="H129" s="10" t="n">
+      <c r="H134" s="10" t="n">
         <v>500.6</v>
       </c>
-      <c r="I129" s="12">
+      <c r="I134" s="12">
         <f> dodávka PSV-OPL-003 = 500.6 m²  [TZ:D.1.1, TZ:D.1.2 (statika) — Návrh opláštění, výkres:Hala HK_Úprava dveří]</f>
         <v/>
       </c>
-      <c r="J129" s="12" t="inlineStr"/>
-    </row>
-    <row r="130">
-      <c r="A130" s="3" t="inlineStr">
+      <c r="J134" s="12" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="3" t="inlineStr">
         <is>
           <t>→ Střešní panely KS 1000 FF 175 mm (zóna) — dodávka + montáž</t>
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="4" t="n">
-        <v>83</v>
-      </c>
-      <c r="B131" s="5" t="inlineStr"/>
-      <c r="C131" s="4" t="n">
+    <row r="136">
+      <c r="A136" s="4" t="n">
+        <v>88</v>
+      </c>
+      <c r="B136" s="5" t="inlineStr"/>
+      <c r="C136" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="D131" s="5" t="inlineStr">
+      <c r="D136" s="5" t="inlineStr">
         <is>
           <t>PSV-OPL</t>
         </is>
       </c>
-      <c r="E131" s="5" t="inlineStr">
+      <c r="E136" s="5" t="inlineStr">
         <is>
           <t>PSV-OPL-011</t>
         </is>
       </c>
-      <c r="F131" s="6" t="inlineStr">
+      <c r="F136" s="6" t="inlineStr">
         <is>
           <t>Kingspan KS 1000 FF 175 mm, jádro FF (Rockwool), zóna ve střeše — Úprava dveří section view</t>
         </is>
       </c>
-      <c r="G131" s="4" t="inlineStr">
+      <c r="G136" s="4" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="H131" s="4" t="n">
+      <c r="H136" s="4" t="n">
         <v>58.2</v>
       </c>
-      <c r="I131" s="6" t="inlineStr">
+      <c r="I136" s="6" t="inlineStr">
         <is>
           <t>57.95 m² projection (user měřeno) / cos(5.25°) = 58.20 m² (slope-corrected)  [výkres:Hala HK_Úprava dveří]  · was 58.2: Úprava dveří revision — first appearance</t>
         </is>
       </c>
-      <c r="J131" s="6" t="inlineStr"/>
-    </row>
-    <row r="132">
-      <c r="A132" s="10" t="n">
-        <v>84</v>
-      </c>
-      <c r="B132" s="11" t="inlineStr"/>
-      <c r="C132" s="10" t="n">
+      <c r="J136" s="6" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="10" t="n">
+        <v>89</v>
+      </c>
+      <c r="B137" s="11" t="inlineStr"/>
+      <c r="C137" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="D132" s="11" t="inlineStr">
+      <c r="D137" s="11" t="inlineStr">
         <is>
           <t>PSV-OPL</t>
         </is>
       </c>
-      <c r="E132" s="11" t="inlineStr">
+      <c r="E137" s="11" t="inlineStr">
         <is>
           <t>PSV-OPL-012</t>
         </is>
       </c>
-      <c r="F132" s="12" t="inlineStr">
+      <c r="F137" s="12" t="inlineStr">
         <is>
           <t>Montáž Kingspan KS 1000 FF 175 mm — zóna 58.20 m² ve střeše</t>
         </is>
       </c>
-      <c r="G132" s="10" t="inlineStr">
+      <c r="G137" s="10" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="H132" s="10" t="n">
+      <c r="H137" s="10" t="n">
         <v>58.2</v>
       </c>
-      <c r="I132" s="12">
+      <c r="I137" s="12">
         <f> dodávka PSV-OPL-011 = 58.20 m²  [výkres:Hala HK_Úprava dveří]  · was 58.2: Úprava dveří revision — first appearance</f>
         <v/>
       </c>
-      <c r="J132" s="12" t="inlineStr"/>
-    </row>
-    <row r="133">
-      <c r="A133" s="3" t="inlineStr">
+      <c r="J137" s="12" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="3" t="inlineStr">
         <is>
           <t>→ Spojovací materiál + EPDM těsnění Kingspan</t>
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="4" t="n">
-        <v>85</v>
-      </c>
-      <c r="B134" s="5" t="inlineStr"/>
-      <c r="C134" s="4" t="n">
+    <row r="139">
+      <c r="A139" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="B139" s="5" t="inlineStr"/>
+      <c r="C139" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="D134" s="5" t="inlineStr">
+      <c r="D139" s="5" t="inlineStr">
         <is>
           <t>PSV-OPL</t>
         </is>
       </c>
-      <c r="E134" s="5" t="inlineStr">
+      <c r="E139" s="5" t="inlineStr">
         <is>
           <t>PSV-OPL-006</t>
         </is>
       </c>
-      <c r="F134" s="6" t="inlineStr">
+      <c r="F139" s="6" t="inlineStr">
         <is>
           <t>Spojovací materiál + těsnění + EPDM podložky Kingspan systém — paušál pro celý objem opláštění</t>
         </is>
       </c>
-      <c r="G134" s="4" t="inlineStr">
+      <c r="G139" s="4" t="inlineStr">
         <is>
           <t>kpl</t>
         </is>
       </c>
-      <c r="H134" s="4" t="n">
+      <c r="H139" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="I134" s="6" t="inlineStr">
+      <c r="I139" s="6" t="inlineStr">
         <is>
           <t>paušál  [TZ:D.1.1]</t>
         </is>
       </c>
-      <c r="J134" s="6" t="inlineStr"/>
-    </row>
-    <row r="135">
-      <c r="A135" s="3" t="inlineStr">
-        <is>
-          <t>→ Klempířské lemy přechody střecha–fasáda</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="13" t="n">
-        <v>86</v>
-      </c>
-      <c r="B136" s="14" t="inlineStr"/>
-      <c r="C136" s="13" t="n">
-        <v>5</v>
-      </c>
-      <c r="D136" s="14" t="inlineStr">
-        <is>
-          <t>PSV-OPL</t>
-        </is>
-      </c>
-      <c r="E136" s="14" t="inlineStr">
-        <is>
-          <t>PSV-OPL-005</t>
-        </is>
-      </c>
-      <c r="F136" s="15" t="inlineStr">
-        <is>
-          <t>Klempířské lemy + přechody střecha–fasáda, pozinkovaný plech — atika, úžlabí, nároží, parapety, krycí lišty — dle TZ ARS DPZ D.1.1</t>
-        </is>
-      </c>
-      <c r="G136" s="13" t="inlineStr">
-        <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="H136" s="13" t="n">
-        <v>189.14</v>
-      </c>
-      <c r="I136" s="15" t="inlineStr">
-        <is>
-          <t>2 × obvod budovy 94.57 m (Úprava dveří) = 189.14 bm (hrubý odhad atika + parapety)  [TZ:D.1.1, Step3, výkres:Hala HK_Úprava dveří]</t>
-        </is>
-      </c>
-      <c r="J136" s="15" t="inlineStr">
-        <is>
-          <t>rev:qty</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="3" t="inlineStr">
-        <is>
-          <t>→ Statické posouzení uchycení Kingspan</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="4" t="n">
-        <v>87</v>
-      </c>
-      <c r="B138" s="5" t="inlineStr"/>
-      <c r="C138" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="D138" s="5" t="inlineStr">
-        <is>
-          <t>PSV-OPL</t>
-        </is>
-      </c>
-      <c r="E138" s="5" t="inlineStr">
-        <is>
-          <t>PSV-OPL-008</t>
-        </is>
-      </c>
-      <c r="F138" s="6" t="inlineStr">
-        <is>
-          <t>Statické posouzení uchycení Kingspan k ocelové konstrukci + revizní zpráva — paušál</t>
-        </is>
-      </c>
-      <c r="G138" s="4" t="inlineStr">
-        <is>
-          <t>paušál</t>
-        </is>
-      </c>
-      <c r="H138" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I138" s="6" t="inlineStr">
-        <is>
-          <t>paušál  [TZ:D.1.1]</t>
-        </is>
-      </c>
-      <c r="J138" s="6" t="inlineStr"/>
-    </row>
-    <row r="139" ht="22" customHeight="1">
-      <c r="A139" s="2" t="inlineStr">
-        <is>
-          <t>═══ FÁZE 6: KLEMPÍŘSKÉ + ODVODNĚNÍ STŘECHY ═══</t>
-        </is>
-      </c>
+      <c r="J139" s="6" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
         <is>
-          <t>→ Doprava klempířiny na stavbu</t>
+          <t>→ Klempířské lemy přechody střecha–fasáda</t>
         </is>
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="4" t="n">
-        <v>88</v>
-      </c>
-      <c r="B141" s="5" t="inlineStr"/>
-      <c r="C141" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="D141" s="5" t="inlineStr">
-        <is>
-          <t>PSV-78x</t>
-        </is>
-      </c>
-      <c r="E141" s="5" t="inlineStr">
-        <is>
-          <t>PSV-78x-012</t>
-        </is>
-      </c>
-      <c r="F141" s="6" t="inlineStr">
-        <is>
-          <t>Doprava klempířiny + materiálu na stavbu — paušál</t>
-        </is>
-      </c>
-      <c r="G141" s="4" t="inlineStr">
-        <is>
-          <t>paušál</t>
-        </is>
-      </c>
-      <c r="H141" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I141" s="6" t="inlineStr">
-        <is>
-          <t>paušál</t>
-        </is>
-      </c>
-      <c r="J141" s="6" t="inlineStr"/>
+      <c r="A141" s="13" t="n">
+        <v>91</v>
+      </c>
+      <c r="B141" s="14" t="inlineStr"/>
+      <c r="C141" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="D141" s="14" t="inlineStr">
+        <is>
+          <t>PSV-OPL</t>
+        </is>
+      </c>
+      <c r="E141" s="14" t="inlineStr">
+        <is>
+          <t>PSV-OPL-005</t>
+        </is>
+      </c>
+      <c r="F141" s="15" t="inlineStr">
+        <is>
+          <t>Klempířské lemy + přechody střecha–fasáda, pozinkovaný plech — atika, úžlabí, nároží, parapety, krycí lišty — dle TZ ARS DPZ D.1.1</t>
+        </is>
+      </c>
+      <c r="G141" s="13" t="inlineStr">
+        <is>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="H141" s="13" t="n">
+        <v>189.14</v>
+      </c>
+      <c r="I141" s="15" t="inlineStr">
+        <is>
+          <t>2 × obvod budovy 94.57 m (Úprava dveří) = 189.14 bm (hrubý odhad atika + parapety)  [TZ:D.1.1, Step3, výkres:Hala HK_Úprava dveří]</t>
+        </is>
+      </c>
+      <c r="J141" s="15" t="inlineStr">
+        <is>
+          <t>rev:qty</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
         <is>
+          <t>→ Statické posouzení uchycení Kingspan</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="4" t="n">
+        <v>92</v>
+      </c>
+      <c r="B143" s="5" t="inlineStr"/>
+      <c r="C143" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D143" s="5" t="inlineStr">
+        <is>
+          <t>PSV-OPL</t>
+        </is>
+      </c>
+      <c r="E143" s="5" t="inlineStr">
+        <is>
+          <t>PSV-OPL-008</t>
+        </is>
+      </c>
+      <c r="F143" s="6" t="inlineStr">
+        <is>
+          <t>Statické posouzení uchycení Kingspan k ocelové konstrukci + revizní zpráva — paušál</t>
+        </is>
+      </c>
+      <c r="G143" s="4" t="inlineStr">
+        <is>
+          <t>paušál</t>
+        </is>
+      </c>
+      <c r="H143" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I143" s="6" t="inlineStr">
+        <is>
+          <t>paušál  [TZ:D.1.1]</t>
+        </is>
+      </c>
+      <c r="J143" s="6" t="inlineStr"/>
+    </row>
+    <row r="144" ht="22" customHeight="1">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>═══ FÁZE 6: KLEMPÍŘSKÉ + ODVODNĚNÍ STŘECHY ═══</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="3" t="inlineStr">
+        <is>
+          <t>→ Doprava klempířiny na stavbu</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="4" t="n">
+        <v>93</v>
+      </c>
+      <c r="B146" s="5" t="inlineStr"/>
+      <c r="C146" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D146" s="5" t="inlineStr">
+        <is>
+          <t>PSV-78x</t>
+        </is>
+      </c>
+      <c r="E146" s="5" t="inlineStr">
+        <is>
+          <t>PSV-78x-012</t>
+        </is>
+      </c>
+      <c r="F146" s="6" t="inlineStr">
+        <is>
+          <t>Doprava klempířiny + materiálu na stavbu — paušál</t>
+        </is>
+      </c>
+      <c r="G146" s="4" t="inlineStr">
+        <is>
+          <t>paušál</t>
+        </is>
+      </c>
+      <c r="H146" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I146" s="6" t="inlineStr">
+        <is>
+          <t>paušál</t>
+        </is>
+      </c>
+      <c r="J146" s="6" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="3" t="inlineStr">
+        <is>
           <t>→ Atikové oplechování + úžlabí + nároží</t>
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="7" t="n">
-        <v>89</v>
-      </c>
-      <c r="B143" s="8" t="inlineStr"/>
-      <c r="C143" s="7" t="n">
+    <row r="148">
+      <c r="A148" s="7" t="n">
+        <v>94</v>
+      </c>
+      <c r="B148" s="8" t="inlineStr"/>
+      <c r="C148" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="D143" s="8" t="inlineStr">
+      <c r="D148" s="8" t="inlineStr">
         <is>
           <t>PSV-78x</t>
         </is>
       </c>
-      <c r="E143" s="8" t="inlineStr">
+      <c r="E148" s="8" t="inlineStr">
         <is>
           <t>PSV-78x-007</t>
         </is>
       </c>
-      <c r="F143" s="9" t="inlineStr">
+      <c r="F148" s="9" t="inlineStr">
         <is>
           <t>Atikové oplechování titanzinek tl. 0.7 mm, rš 500 mm — po obvodu střechy</t>
         </is>
       </c>
-      <c r="G143" s="7" t="inlineStr">
+      <c r="G148" s="7" t="inlineStr">
         <is>
           <t>bm</t>
         </is>
       </c>
-      <c r="H143" s="7" t="n">
+      <c r="H148" s="7" t="n">
         <v>95</v>
       </c>
-      <c r="I143" s="9" t="inlineStr">
+      <c r="I148" s="9" t="inlineStr">
         <is>
           <t>obvod střechy 95.0 bm  [TZ:B]</t>
         </is>
       </c>
-      <c r="J143" s="9" t="inlineStr"/>
-    </row>
-    <row r="144">
-      <c r="A144" s="7" t="n">
-        <v>90</v>
-      </c>
-      <c r="B144" s="8" t="inlineStr"/>
-      <c r="C144" s="7" t="n">
+      <c r="J148" s="9" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="7" t="n">
+        <v>95</v>
+      </c>
+      <c r="B149" s="8" t="inlineStr"/>
+      <c r="C149" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="D144" s="8" t="inlineStr">
+      <c r="D149" s="8" t="inlineStr">
         <is>
           <t>PSV-78x</t>
         </is>
       </c>
-      <c r="E144" s="8" t="inlineStr">
+      <c r="E149" s="8" t="inlineStr">
         <is>
           <t>PSV-78x-008</t>
         </is>
       </c>
-      <c r="F144" s="9" t="inlineStr">
+      <c r="F149" s="9" t="inlineStr">
         <is>
           <t>Lemování úžlabí střechy titanzinek — diagonální linie</t>
         </is>
       </c>
-      <c r="G144" s="7" t="inlineStr">
+      <c r="G149" s="7" t="inlineStr">
         <is>
           <t>bm</t>
         </is>
       </c>
-      <c r="H144" s="7" t="n">
+      <c r="H149" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="I144" s="9" t="inlineStr">
+      <c r="I149" s="9" t="inlineStr">
         <is>
           <t>placeholder ~15 bm (úžlabí pultové střechy 5.25°)</t>
         </is>
       </c>
-      <c r="J144" s="9" t="inlineStr"/>
-    </row>
-    <row r="145">
-      <c r="A145" s="7" t="n">
-        <v>91</v>
-      </c>
-      <c r="B145" s="8" t="inlineStr"/>
-      <c r="C145" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="D145" s="8" t="inlineStr">
-        <is>
-          <t>PSV-78x</t>
-        </is>
-      </c>
-      <c r="E145" s="8" t="inlineStr">
-        <is>
-          <t>PSV-78x-009</t>
-        </is>
-      </c>
-      <c r="F145" s="9" t="inlineStr">
-        <is>
-          <t>Lemování nároží titanzinek — vertikální rohy fasády</t>
-        </is>
-      </c>
-      <c r="G145" s="7" t="inlineStr">
-        <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="H145" s="7" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="I145" s="9" t="inlineStr">
-        <is>
-          <t>4 nároží × 6.3 m výška</t>
-        </is>
-      </c>
-      <c r="J145" s="9" t="inlineStr"/>
-    </row>
-    <row r="146">
-      <c r="A146" s="3" t="inlineStr">
-        <is>
-          <t>→ Tmelení spár klempířských konstrukcí</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="7" t="n">
-        <v>92</v>
-      </c>
-      <c r="B147" s="8" t="inlineStr"/>
-      <c r="C147" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="D147" s="8" t="inlineStr">
-        <is>
-          <t>PSV-78x</t>
-        </is>
-      </c>
-      <c r="E147" s="8" t="inlineStr">
-        <is>
-          <t>PSV-78x-010</t>
-        </is>
-      </c>
-      <c r="F147" s="9" t="inlineStr">
-        <is>
-          <t>Krytí spár klempířských konstrukcí — silikonový tmel</t>
-        </is>
-      </c>
-      <c r="G147" s="7" t="inlineStr">
-        <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="H147" s="7" t="n">
-        <v>120</v>
-      </c>
-      <c r="I147" s="9" t="inlineStr">
-        <is>
-          <t>placeholder ~120 bm (spáry mezi všemi klempířskými prvky)</t>
-        </is>
-      </c>
-      <c r="J147" s="9" t="inlineStr"/>
-    </row>
-    <row r="148">
-      <c r="A148" s="3" t="inlineStr">
-        <is>
-          <t>→ Lindab svody — dodávka + montáž</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="4" t="n">
-        <v>93</v>
-      </c>
-      <c r="B149" s="5" t="inlineStr"/>
-      <c r="C149" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="D149" s="5" t="inlineStr">
-        <is>
-          <t>PSV-78x</t>
-        </is>
-      </c>
-      <c r="E149" s="5" t="inlineStr">
-        <is>
-          <t>PSV-78x-001</t>
-        </is>
-      </c>
-      <c r="F149" s="6" t="inlineStr">
-        <is>
-          <t>Dodávka Lindab Round Downpipe 150/100 Antique White, vč. kolen a spojek</t>
-        </is>
-      </c>
-      <c r="G149" s="4" t="inlineStr">
-        <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="H149" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="I149" s="6" t="inlineStr">
-        <is>
-          <t>4 ks (A104 DXF count working, ABMV_20: A101=3 vs A104=4)  [výkres:A104]</t>
-        </is>
-      </c>
-      <c r="J149" s="6" t="inlineStr">
-        <is>
-          <t>ABMV:ABMV_20</t>
-        </is>
-      </c>
+      <c r="J149" s="9" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="7" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B150" s="8" t="inlineStr"/>
       <c r="C150" s="7" t="n">
@@ -4613,43 +4667,39 @@
       </c>
       <c r="E150" s="8" t="inlineStr">
         <is>
-          <t>PSV-78x-002</t>
+          <t>PSV-78x-009</t>
         </is>
       </c>
       <c r="F150" s="9" t="inlineStr">
         <is>
-          <t>Montáž svodů Lindab — příchytky, kotvení do fasády</t>
+          <t>Lemování nároží titanzinek — vertikální rohy fasády</t>
         </is>
       </c>
       <c r="G150" s="7" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="H150" s="7" t="n">
-        <v>4</v>
+        <v>25.2</v>
       </c>
       <c r="I150" s="9" t="inlineStr">
         <is>
-          <t>4 kpl (jeden na každý svod)</t>
-        </is>
-      </c>
-      <c r="J150" s="9" t="inlineStr">
-        <is>
-          <t>ABMV:ABMV_20</t>
-        </is>
-      </c>
+          <t>4 nároží × 6.3 m výška</t>
+        </is>
+      </c>
+      <c r="J150" s="9" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
         <is>
-          <t>→ Wavin Tegra střešní vpusti — dodávka + montáž</t>
+          <t>→ Tmelení spár klempířských konstrukcí</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="7" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B152" s="8" t="inlineStr"/>
       <c r="C152" s="7" t="n">
@@ -4662,76 +4712,81 @@
       </c>
       <c r="E152" s="8" t="inlineStr">
         <is>
-          <t>PSV-78x-003</t>
+          <t>PSV-78x-010</t>
         </is>
       </c>
       <c r="F152" s="9" t="inlineStr">
         <is>
-          <t>Wavin Tegra střešní vpust Round Iron Cover + Concrete Ring DN300</t>
+          <t>Krytí spár klempířských konstrukcí — silikonový tmel</t>
         </is>
       </c>
       <c r="G152" s="7" t="inlineStr">
         <is>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="H152" s="7" t="n">
+        <v>120</v>
+      </c>
+      <c r="I152" s="9" t="inlineStr">
+        <is>
+          <t>placeholder ~120 bm (spáry mezi všemi klempířskými prvky)</t>
+        </is>
+      </c>
+      <c r="J152" s="9" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="3" t="inlineStr">
+        <is>
+          <t>→ Lindab svody — dodávka + montáž</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="4" t="n">
+        <v>98</v>
+      </c>
+      <c r="B154" s="5" t="inlineStr"/>
+      <c r="C154" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D154" s="5" t="inlineStr">
+        <is>
+          <t>PSV-78x</t>
+        </is>
+      </c>
+      <c r="E154" s="5" t="inlineStr">
+        <is>
+          <t>PSV-78x-001</t>
+        </is>
+      </c>
+      <c r="F154" s="6" t="inlineStr">
+        <is>
+          <t>Dodávka Lindab Round Downpipe 150/100 Antique White, vč. kolen a spojek</t>
+        </is>
+      </c>
+      <c r="G154" s="4" t="inlineStr">
+        <is>
           <t>ks</t>
         </is>
       </c>
-      <c r="H152" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="I152" s="9" t="inlineStr">
-        <is>
-          <t>3 ks (A101 INSERT Wavin × 3 dle DXF parse)  [výkres:A101]</t>
-        </is>
-      </c>
-      <c r="J152" s="9" t="inlineStr"/>
-    </row>
-    <row r="153">
-      <c r="A153" s="7" t="n">
-        <v>96</v>
-      </c>
-      <c r="B153" s="8" t="inlineStr"/>
-      <c r="C153" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="D153" s="8" t="inlineStr">
-        <is>
-          <t>PSV-78x</t>
-        </is>
-      </c>
-      <c r="E153" s="8" t="inlineStr">
-        <is>
-          <t>PSV-78x-004</t>
-        </is>
-      </c>
-      <c r="F153" s="9" t="inlineStr">
-        <is>
-          <t>Montáž střešních vpustí Wavin Tegra — osazení, napojení na svody</t>
-        </is>
-      </c>
-      <c r="G153" s="7" t="inlineStr">
-        <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="H153" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="I153" s="9">
-        <f> dodávka</f>
-        <v/>
-      </c>
-      <c r="J153" s="9" t="inlineStr"/>
-    </row>
-    <row r="154">
-      <c r="A154" s="3" t="inlineStr">
-        <is>
-          <t>→ MEA Mearin liniový žlab + mřížka</t>
+      <c r="H154" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I154" s="6" t="inlineStr">
+        <is>
+          <t>4 ks (A104 DXF count working, ABMV_20: A101=3 vs A104=4)  [výkres:A104]</t>
+        </is>
+      </c>
+      <c r="J154" s="6" t="inlineStr">
+        <is>
+          <t>ABMV:ABMV_20</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="7" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B155" s="8" t="inlineStr"/>
       <c r="C155" s="7" t="n">
@@ -4744,439 +4799,411 @@
       </c>
       <c r="E155" s="8" t="inlineStr">
         <is>
+          <t>PSV-78x-002</t>
+        </is>
+      </c>
+      <c r="F155" s="9" t="inlineStr">
+        <is>
+          <t>Montáž svodů Lindab — příchytky, kotvení do fasády</t>
+        </is>
+      </c>
+      <c r="G155" s="7" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="H155" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="I155" s="9" t="inlineStr">
+        <is>
+          <t>4 kpl (jeden na každý svod)</t>
+        </is>
+      </c>
+      <c r="J155" s="9" t="inlineStr">
+        <is>
+          <t>ABMV:ABMV_20</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="3" t="inlineStr">
+        <is>
+          <t>→ Wavin Tegra střešní vpusti — dodávka + montáž</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B157" s="8" t="inlineStr"/>
+      <c r="C157" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="D157" s="8" t="inlineStr">
+        <is>
+          <t>PSV-78x</t>
+        </is>
+      </c>
+      <c r="E157" s="8" t="inlineStr">
+        <is>
+          <t>PSV-78x-003</t>
+        </is>
+      </c>
+      <c r="F157" s="9" t="inlineStr">
+        <is>
+          <t>Wavin Tegra střešní vpust Round Iron Cover + Concrete Ring DN300</t>
+        </is>
+      </c>
+      <c r="G157" s="7" t="inlineStr">
+        <is>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="H157" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I157" s="9" t="inlineStr">
+        <is>
+          <t>3 ks (A101 INSERT Wavin × 3 dle DXF parse)  [výkres:A101]</t>
+        </is>
+      </c>
+      <c r="J157" s="9" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="7" t="n">
+        <v>101</v>
+      </c>
+      <c r="B158" s="8" t="inlineStr"/>
+      <c r="C158" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="D158" s="8" t="inlineStr">
+        <is>
+          <t>PSV-78x</t>
+        </is>
+      </c>
+      <c r="E158" s="8" t="inlineStr">
+        <is>
+          <t>PSV-78x-004</t>
+        </is>
+      </c>
+      <c r="F158" s="9" t="inlineStr">
+        <is>
+          <t>Montáž střešních vpustí Wavin Tegra — osazení, napojení na svody</t>
+        </is>
+      </c>
+      <c r="G158" s="7" t="inlineStr">
+        <is>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="H158" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I158" s="9">
+        <f> dodávka</f>
+        <v/>
+      </c>
+      <c r="J158" s="9" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="3" t="inlineStr">
+        <is>
+          <t>→ MEA Mearin liniový žlab + mřížka</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="7" t="n">
+        <v>102</v>
+      </c>
+      <c r="B160" s="8" t="inlineStr"/>
+      <c r="C160" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="D160" s="8" t="inlineStr">
+        <is>
+          <t>PSV-78x</t>
+        </is>
+      </c>
+      <c r="E160" s="8" t="inlineStr">
+        <is>
           <t>PSV-78x-005</t>
         </is>
       </c>
-      <c r="F155" s="9" t="inlineStr">
+      <c r="F160" s="9" t="inlineStr">
         <is>
           <t>MEA Mearin Plus 3000 NW300 liniový žlab — podél JZ a SZ fasády</t>
         </is>
       </c>
-      <c r="G155" s="7" t="inlineStr">
+      <c r="G160" s="7" t="inlineStr">
         <is>
           <t>bm</t>
         </is>
       </c>
-      <c r="H155" s="7" t="n">
+      <c r="H160" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="I155" s="9" t="inlineStr">
+      <c r="I160" s="9" t="inlineStr">
         <is>
           <t>~30.0 bm podél JZ + SZ fasády (RE-RUN §3.7)  [výkres:A105]</t>
         </is>
       </c>
-      <c r="J155" s="9" t="inlineStr"/>
-    </row>
-    <row r="156">
-      <c r="A156" s="7" t="n">
-        <v>98</v>
-      </c>
-      <c r="B156" s="8" t="inlineStr"/>
-      <c r="C156" s="7" t="n">
+      <c r="J160" s="9" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="7" t="n">
+        <v>103</v>
+      </c>
+      <c r="B161" s="8" t="inlineStr"/>
+      <c r="C161" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="D156" s="8" t="inlineStr">
+      <c r="D161" s="8" t="inlineStr">
         <is>
           <t>PSV-78x</t>
         </is>
       </c>
-      <c r="E156" s="8" t="inlineStr">
+      <c r="E161" s="8" t="inlineStr">
         <is>
           <t>PSV-78x-006</t>
         </is>
       </c>
-      <c r="F156" s="9" t="inlineStr">
+      <c r="F161" s="9" t="inlineStr">
         <is>
           <t>Mřížka MEA Mearin Plus 3000 + osazovací rám — pochozí provedení</t>
         </is>
       </c>
-      <c r="G156" s="7" t="inlineStr">
+      <c r="G161" s="7" t="inlineStr">
         <is>
           <t>bm</t>
         </is>
       </c>
-      <c r="H156" s="7" t="n">
+      <c r="H161" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="I156" s="9">
+      <c r="I161" s="9">
         <f> liniový žlab</f>
         <v/>
       </c>
-      <c r="J156" s="9" t="inlineStr"/>
-    </row>
-    <row r="157">
-      <c r="A157" s="3" t="inlineStr">
+      <c r="J161" s="9" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="3" t="inlineStr">
         <is>
           <t>→ Ostatní oplechování (parapety, lemy)</t>
         </is>
       </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="4" t="n">
-        <v>99</v>
-      </c>
-      <c r="B158" s="5" t="inlineStr"/>
-      <c r="C158" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="D158" s="5" t="inlineStr">
-        <is>
-          <t>PSV-78x</t>
-        </is>
-      </c>
-      <c r="E158" s="5" t="inlineStr">
-        <is>
-          <t>PSV-78x-011</t>
-        </is>
-      </c>
-      <c r="F158" s="6" t="inlineStr">
-        <is>
-          <t>Ostatní oplechování — parapety střešních vpustí, lemy prostupů</t>
-        </is>
-      </c>
-      <c r="G158" s="4" t="inlineStr">
-        <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="H158" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="I158" s="6" t="inlineStr">
-        <is>
-          <t>placeholder ~25 bm (vpusti + prostupy)</t>
-        </is>
-      </c>
-      <c r="J158" s="6" t="inlineStr"/>
-    </row>
-    <row r="159" ht="22" customHeight="1">
-      <c r="A159" s="2" t="inlineStr">
-        <is>
-          <t>═══ FÁZE 7: VÝPLNĚ OTVORŮ ═══</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="3" t="inlineStr">
-        <is>
-          <t>→ Okna plastová — dodávka (fixní + otvíravé) + montáž + parapet + lemy</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="B161" s="5" t="inlineStr"/>
-      <c r="C161" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="D161" s="5" t="inlineStr">
-        <is>
-          <t>PSV-76x</t>
-        </is>
-      </c>
-      <c r="E161" s="5" t="inlineStr">
-        <is>
-          <t>PSV-76x-001</t>
-        </is>
-      </c>
-      <c r="F161" s="6" t="inlineStr">
-        <is>
-          <t>Dodávka okno plastové fixní 1000 × 1000 mm, izol. dvojsklo Ug ≤ 1.1, barva šedá</t>
-        </is>
-      </c>
-      <c r="G161" s="4" t="inlineStr">
-        <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="H161" s="4" t="n">
-        <v>29</v>
-      </c>
-      <c r="I161" s="6" t="inlineStr">
-        <is>
-          <t>29 ks fixních (z 34 oken celkem; 5 otvíravých v PSV-76x-013) — Úprava dveří POHLED OSA A/F/06/01  [výkres:A101, výkres:Hala HK_Úprava dveří]</t>
-        </is>
-      </c>
-      <c r="J161" s="6" t="inlineStr"/>
-    </row>
-    <row r="162">
-      <c r="A162" s="10" t="n">
-        <v>101</v>
-      </c>
-      <c r="B162" s="11" t="inlineStr"/>
-      <c r="C162" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="D162" s="11" t="inlineStr">
-        <is>
-          <t>PSV-76x</t>
-        </is>
-      </c>
-      <c r="E162" s="11" t="inlineStr">
-        <is>
-          <t>PSV-76x-013</t>
-        </is>
-      </c>
-      <c r="F162" s="12" t="inlineStr">
-        <is>
-          <t>Dodávka okno plastové otvíravé 1000 × 1000 mm, izol. dvojsklo Ug ≤ 1.1, barva šedá, kování pro mikroventilaci</t>
-        </is>
-      </c>
-      <c r="G162" s="10" t="inlineStr">
-        <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="H162" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="I162" s="12" t="inlineStr">
-        <is>
-          <t>5 ks otvíravých z 34 oken celkem — Úprava dveří POHLED OSA A/F/06/01 user-confirmed split  [výkres:Hala HK_Úprava dveří]  · was 5.0: Úprava dveří revision — first appearance</t>
-        </is>
-      </c>
-      <c r="J162" s="12" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="4" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B163" s="5" t="inlineStr"/>
       <c r="C163" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D163" s="5" t="inlineStr">
+        <is>
+          <t>PSV-78x</t>
+        </is>
+      </c>
+      <c r="E163" s="5" t="inlineStr">
+        <is>
+          <t>PSV-78x-011</t>
+        </is>
+      </c>
+      <c r="F163" s="6" t="inlineStr">
+        <is>
+          <t>Ostatní oplechování — parapety střešních vpustí, lemy prostupů</t>
+        </is>
+      </c>
+      <c r="G163" s="4" t="inlineStr">
+        <is>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="H163" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="I163" s="6" t="inlineStr">
+        <is>
+          <t>placeholder ~25 bm (vpusti + prostupy)</t>
+        </is>
+      </c>
+      <c r="J163" s="6" t="inlineStr"/>
+    </row>
+    <row r="164" ht="22" customHeight="1">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>═══ FÁZE 7: VÝPLNĚ OTVORŮ ═══</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="3" t="inlineStr">
+        <is>
+          <t>→ Okna plastová — dodávka (fixní + otvíravé) + montáž + parapet + lemy</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="4" t="n">
+        <v>105</v>
+      </c>
+      <c r="B166" s="5" t="inlineStr"/>
+      <c r="C166" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="D163" s="5" t="inlineStr">
+      <c r="D166" s="5" t="inlineStr">
         <is>
           <t>PSV-76x</t>
         </is>
       </c>
-      <c r="E163" s="5" t="inlineStr">
+      <c r="E166" s="5" t="inlineStr">
+        <is>
+          <t>PSV-76x-001</t>
+        </is>
+      </c>
+      <c r="F166" s="6" t="inlineStr">
+        <is>
+          <t>Dodávka okno plastové fixní 1000 × 1000 mm, izol. dvojsklo Ug ≤ 1.1, barva šedá</t>
+        </is>
+      </c>
+      <c r="G166" s="4" t="inlineStr">
+        <is>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="H166" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="I166" s="6" t="inlineStr">
+        <is>
+          <t>29 ks fixních (z 34 oken celkem; 5 otvíravých v PSV-76x-013) — Úprava dveří POHLED OSA A/F/06/01  [výkres:A101, výkres:Hala HK_Úprava dveří]</t>
+        </is>
+      </c>
+      <c r="J166" s="6" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="10" t="n">
+        <v>106</v>
+      </c>
+      <c r="B167" s="11" t="inlineStr"/>
+      <c r="C167" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="D167" s="11" t="inlineStr">
+        <is>
+          <t>PSV-76x</t>
+        </is>
+      </c>
+      <c r="E167" s="11" t="inlineStr">
+        <is>
+          <t>PSV-76x-013</t>
+        </is>
+      </c>
+      <c r="F167" s="12" t="inlineStr">
+        <is>
+          <t>Dodávka okno plastové otvíravé 1000 × 1000 mm, izol. dvojsklo Ug ≤ 1.1, barva šedá, kování pro mikroventilaci</t>
+        </is>
+      </c>
+      <c r="G167" s="10" t="inlineStr">
+        <is>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="H167" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="I167" s="12" t="inlineStr">
+        <is>
+          <t>5 ks otvíravých z 34 oken celkem — Úprava dveří POHLED OSA A/F/06/01 user-confirmed split  [výkres:Hala HK_Úprava dveří]  · was 5.0: Úprava dveří revision — first appearance</t>
+        </is>
+      </c>
+      <c r="J167" s="12" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="4" t="n">
+        <v>107</v>
+      </c>
+      <c r="B168" s="5" t="inlineStr"/>
+      <c r="C168" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D168" s="5" t="inlineStr">
+        <is>
+          <t>PSV-76x</t>
+        </is>
+      </c>
+      <c r="E168" s="5" t="inlineStr">
         <is>
           <t>PSV-76x-002</t>
         </is>
       </c>
-      <c r="F163" s="6" t="inlineStr">
+      <c r="F168" s="6" t="inlineStr">
         <is>
           <t>Montáž okna plastového 1000 × 1000 mm (fixní i otvíravé) do osazovacího otvoru, vč. kotvení a pěny</t>
         </is>
       </c>
-      <c r="G163" s="4" t="inlineStr">
+      <c r="G168" s="4" t="inlineStr">
         <is>
           <t>ks</t>
         </is>
       </c>
-      <c r="H163" s="4" t="n">
+      <c r="H168" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="I163" s="6" t="inlineStr">
+      <c r="I168" s="6" t="inlineStr">
         <is>
           <t>34 ks celkem (29 fixní + 5 otvíravé) — Úprava dveří POHLED OSA A/F/06/01  [výkres:Hala HK_Úprava dveří]</t>
         </is>
       </c>
-      <c r="J163" s="6" t="inlineStr"/>
-    </row>
-    <row r="164">
-      <c r="A164" s="10" t="n">
-        <v>103</v>
-      </c>
-      <c r="B164" s="11" t="inlineStr"/>
-      <c r="C164" s="10" t="n">
+      <c r="J168" s="6" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="10" t="n">
+        <v>108</v>
+      </c>
+      <c r="B169" s="11" t="inlineStr"/>
+      <c r="C169" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="D164" s="11" t="inlineStr">
+      <c r="D169" s="11" t="inlineStr">
         <is>
           <t>PSV-76x</t>
         </is>
       </c>
-      <c r="E164" s="11" t="inlineStr">
+      <c r="E169" s="11" t="inlineStr">
         <is>
           <t>PSV-76x-003</t>
         </is>
       </c>
-      <c r="F164" s="12" t="inlineStr">
+      <c r="F169" s="12" t="inlineStr">
         <is>
           <t>Vnější parapet pozinkovaný plech, š. 200 mm, s krytkami</t>
         </is>
       </c>
-      <c r="G164" s="10" t="inlineStr">
+      <c r="G169" s="10" t="inlineStr">
         <is>
           <t>bm</t>
         </is>
       </c>
-      <c r="H164" s="10" t="n">
+      <c r="H169" s="10" t="n">
         <v>35.7</v>
       </c>
-      <c r="I164" s="12" t="inlineStr">
+      <c r="I169" s="12" t="inlineStr">
         <is>
           <t>34 ks × 1.05 m (šířka okna + přesah) = 35.7 bm — Úprava dveří 34 oken  [výkres:Hala HK_Úprava dveří]</t>
         </is>
       </c>
-      <c r="J164" s="12" t="inlineStr"/>
-    </row>
-    <row r="165">
-      <c r="A165" s="7" t="n">
-        <v>104</v>
-      </c>
-      <c r="B165" s="8" t="inlineStr"/>
-      <c r="C165" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="D165" s="8" t="inlineStr">
-        <is>
-          <t>PSV-76x</t>
-        </is>
-      </c>
-      <c r="E165" s="8" t="inlineStr">
-        <is>
-          <t>PSV-76x-004</t>
-        </is>
-      </c>
-      <c r="F165" s="9" t="inlineStr">
-        <is>
-          <t>Vnější okenní lemy plastové — rohové + nadokenní</t>
-        </is>
-      </c>
-      <c r="G165" s="7" t="inlineStr">
-        <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="H165" s="7" t="n">
-        <v>102</v>
-      </c>
-      <c r="I165" s="9" t="inlineStr">
-        <is>
-          <t>34 ks × 3 bm (perimetr 3 stran, parapet samostatně) = 102 bm — Úprava dveří 34 oken  [výkres:Hala HK_Úprava dveří]</t>
-        </is>
-      </c>
-      <c r="J165" s="9" t="inlineStr"/>
-    </row>
-    <row r="166">
-      <c r="A166" s="3" t="inlineStr">
-        <is>
-          <t>→ Sekční vrata 3500×4000 — dodávka + pohon + montáž</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="4" t="n">
-        <v>105</v>
-      </c>
-      <c r="B167" s="5" t="inlineStr"/>
-      <c r="C167" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="D167" s="5" t="inlineStr">
-        <is>
-          <t>PSV-76x</t>
-        </is>
-      </c>
-      <c r="E167" s="5" t="inlineStr">
-        <is>
-          <t>PSV-76x-005</t>
-        </is>
-      </c>
-      <c r="F167" s="6" t="inlineStr">
-        <is>
-          <t>Dodávka sekční vrata 3500 × 4000 mm (š × v) s tepelněizolační výplní, motorická</t>
-        </is>
-      </c>
-      <c r="G167" s="4" t="inlineStr">
-        <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="H167" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="I167" s="6" t="inlineStr">
-        <is>
-          <t>4 ks (DXF A101 INSERT 'Vrata sekční' = 4)  [výkres:A101, TZ:3.2]</t>
-        </is>
-      </c>
-      <c r="J167" s="6" t="inlineStr"/>
-    </row>
-    <row r="168">
-      <c r="A168" s="7" t="n">
-        <v>106</v>
-      </c>
-      <c r="B168" s="8" t="inlineStr"/>
-      <c r="C168" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="D168" s="8" t="inlineStr">
-        <is>
-          <t>PSV-76x</t>
-        </is>
-      </c>
-      <c r="E168" s="8" t="inlineStr">
-        <is>
-          <t>PSV-76x-006</t>
-        </is>
-      </c>
-      <c r="F168" s="9" t="inlineStr">
-        <is>
-          <t>Elektrický pohon vrat sekčních s dálkovým ovládáním + nouzové odblokování</t>
-        </is>
-      </c>
-      <c r="G168" s="7" t="inlineStr">
-        <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="H168" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="I168" s="9" t="inlineStr">
-        <is>
-          <t>4 ks pohon (jeden na každá vrata)</t>
-        </is>
-      </c>
-      <c r="J168" s="9" t="inlineStr"/>
-    </row>
-    <row r="169">
-      <c r="A169" s="7" t="n">
-        <v>107</v>
-      </c>
-      <c r="B169" s="8" t="inlineStr"/>
-      <c r="C169" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="D169" s="8" t="inlineStr">
-        <is>
-          <t>PSV-76x</t>
-        </is>
-      </c>
-      <c r="E169" s="8" t="inlineStr">
-        <is>
-          <t>PSV-76x-007</t>
-        </is>
-      </c>
-      <c r="F169" s="9" t="inlineStr">
-        <is>
-          <t>Nouzové ruční odblokování vrat sekčních — pro výpadek el.</t>
-        </is>
-      </c>
-      <c r="G169" s="7" t="inlineStr">
-        <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="H169" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="I169" s="9" t="inlineStr">
-        <is>
-          <t>4 ks ruční odblok</t>
-        </is>
-      </c>
-      <c r="J169" s="9" t="inlineStr"/>
+      <c r="J169" s="12" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="7" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B170" s="8" t="inlineStr"/>
       <c r="C170" s="7" t="n">
@@ -5189,76 +5216,77 @@
       </c>
       <c r="E170" s="8" t="inlineStr">
         <is>
-          <t>PSV-76x-008</t>
+          <t>PSV-76x-004</t>
         </is>
       </c>
       <c r="F170" s="9" t="inlineStr">
         <is>
-          <t>Montáž sekčních vrat — osazení do otvoru, ukotvení, nastavení</t>
+          <t>Vnější okenní lemy plastové — rohové + nadokenní</t>
         </is>
       </c>
       <c r="G170" s="7" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="H170" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="I170" s="9">
-        <f> dodávka vrat</f>
-        <v/>
+        <v>102</v>
+      </c>
+      <c r="I170" s="9" t="inlineStr">
+        <is>
+          <t>34 ks × 3 bm (perimetr 3 stran, parapet samostatně) = 102 bm — Úprava dveří 34 oken  [výkres:Hala HK_Úprava dveří]</t>
+        </is>
       </c>
       <c r="J170" s="9" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="3" t="inlineStr">
         <is>
-          <t>→ Vnější 2-křídlé dveře — dodávka + montáž + zámek + práh</t>
+          <t>→ Sekční vrata 3500×4000 — dodávka + pohon + montáž</t>
         </is>
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="7" t="n">
-        <v>109</v>
-      </c>
-      <c r="B172" s="8" t="inlineStr"/>
-      <c r="C172" s="7" t="n">
+      <c r="A172" s="4" t="n">
+        <v>110</v>
+      </c>
+      <c r="B172" s="5" t="inlineStr"/>
+      <c r="C172" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="D172" s="8" t="inlineStr">
+      <c r="D172" s="5" t="inlineStr">
         <is>
           <t>PSV-76x</t>
         </is>
       </c>
-      <c r="E172" s="8" t="inlineStr">
-        <is>
-          <t>PSV-76x-009</t>
-        </is>
-      </c>
-      <c r="F172" s="9" t="inlineStr">
-        <is>
-          <t>Dodávka vnější dvoukřídlé dveře plastové 1050 × 2100 mm, izol. plnostěnné, klika a zámek</t>
-        </is>
-      </c>
-      <c r="G172" s="7" t="inlineStr">
+      <c r="E172" s="5" t="inlineStr">
+        <is>
+          <t>PSV-76x-005</t>
+        </is>
+      </c>
+      <c r="F172" s="6" t="inlineStr">
+        <is>
+          <t>Dodávka sekční vrata 3500 × 4000 mm (š × v) s tepelněizolační výplní, motorická</t>
+        </is>
+      </c>
+      <c r="G172" s="4" t="inlineStr">
         <is>
           <t>ks</t>
         </is>
       </c>
-      <c r="H172" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I172" s="9" t="inlineStr">
-        <is>
-          <t>2 ks (Úprava dveří potvrzeno) — materiál plastové dle user expectation, čeká finální potvrzení projektantem  [výkres:A101, výkres:Hala HK_Úprava dveří]</t>
-        </is>
-      </c>
-      <c r="J172" s="9" t="inlineStr"/>
+      <c r="H172" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I172" s="6" t="inlineStr">
+        <is>
+          <t>4 ks (DXF A101 INSERT 'Vrata sekční' = 4)  [výkres:A101, TZ:3.2]</t>
+        </is>
+      </c>
+      <c r="J172" s="6" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="7" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B173" s="8" t="inlineStr"/>
       <c r="C173" s="7" t="n">
@@ -5271,12 +5299,12 @@
       </c>
       <c r="E173" s="8" t="inlineStr">
         <is>
-          <t>PSV-76x-010</t>
+          <t>PSV-76x-006</t>
         </is>
       </c>
       <c r="F173" s="9" t="inlineStr">
         <is>
-          <t>Montáž vnějších 2-křídlých dveří — osazení, kotvení, pěna</t>
+          <t>Elektrický pohon vrat sekčních s dálkovým ovládáním + nouzové odblokování</t>
         </is>
       </c>
       <c r="G173" s="7" t="inlineStr">
@@ -5285,17 +5313,18 @@
         </is>
       </c>
       <c r="H173" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I173" s="9">
-        <f> dodávka dveří</f>
-        <v/>
+        <v>4</v>
+      </c>
+      <c r="I173" s="9" t="inlineStr">
+        <is>
+          <t>4 ks pohon (jeden na každá vrata)</t>
+        </is>
       </c>
       <c r="J173" s="9" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="7" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B174" s="8" t="inlineStr"/>
       <c r="C174" s="7" t="n">
@@ -5308,452 +5337,473 @@
       </c>
       <c r="E174" s="8" t="inlineStr">
         <is>
+          <t>PSV-76x-007</t>
+        </is>
+      </c>
+      <c r="F174" s="9" t="inlineStr">
+        <is>
+          <t>Nouzové ruční odblokování vrat sekčních — pro výpadek el.</t>
+        </is>
+      </c>
+      <c r="G174" s="7" t="inlineStr">
+        <is>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="H174" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="I174" s="9" t="inlineStr">
+        <is>
+          <t>4 ks ruční odblok</t>
+        </is>
+      </c>
+      <c r="J174" s="9" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="7" t="n">
+        <v>113</v>
+      </c>
+      <c r="B175" s="8" t="inlineStr"/>
+      <c r="C175" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="D175" s="8" t="inlineStr">
+        <is>
+          <t>PSV-76x</t>
+        </is>
+      </c>
+      <c r="E175" s="8" t="inlineStr">
+        <is>
+          <t>PSV-76x-008</t>
+        </is>
+      </c>
+      <c r="F175" s="9" t="inlineStr">
+        <is>
+          <t>Montáž sekčních vrat — osazení do otvoru, ukotvení, nastavení</t>
+        </is>
+      </c>
+      <c r="G175" s="7" t="inlineStr">
+        <is>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="H175" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="I175" s="9">
+        <f> dodávka vrat</f>
+        <v/>
+      </c>
+      <c r="J175" s="9" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="3" t="inlineStr">
+        <is>
+          <t>→ Vnější 2-křídlé dveře — dodávka + montáž + zámek + práh</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="7" t="n">
+        <v>114</v>
+      </c>
+      <c r="B177" s="8" t="inlineStr"/>
+      <c r="C177" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="D177" s="8" t="inlineStr">
+        <is>
+          <t>PSV-76x</t>
+        </is>
+      </c>
+      <c r="E177" s="8" t="inlineStr">
+        <is>
+          <t>PSV-76x-009</t>
+        </is>
+      </c>
+      <c r="F177" s="9" t="inlineStr">
+        <is>
+          <t>Dodávka vnější dvoukřídlé dveře plastové 1050 × 2100 mm, izol. plnostěnné, klika a zámek</t>
+        </is>
+      </c>
+      <c r="G177" s="7" t="inlineStr">
+        <is>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="H177" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I177" s="9" t="inlineStr">
+        <is>
+          <t>2 ks (Úprava dveří potvrzeno) — materiál plastové dle user expectation, čeká finální potvrzení projektantem  [výkres:A101, výkres:Hala HK_Úprava dveří]</t>
+        </is>
+      </c>
+      <c r="J177" s="9" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="7" t="n">
+        <v>115</v>
+      </c>
+      <c r="B178" s="8" t="inlineStr"/>
+      <c r="C178" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="D178" s="8" t="inlineStr">
+        <is>
+          <t>PSV-76x</t>
+        </is>
+      </c>
+      <c r="E178" s="8" t="inlineStr">
+        <is>
+          <t>PSV-76x-010</t>
+        </is>
+      </c>
+      <c r="F178" s="9" t="inlineStr">
+        <is>
+          <t>Montáž vnějších 2-křídlých dveří — osazení, kotvení, pěna</t>
+        </is>
+      </c>
+      <c r="G178" s="7" t="inlineStr">
+        <is>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="H178" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I178" s="9">
+        <f> dodávka dveří</f>
+        <v/>
+      </c>
+      <c r="J178" s="9" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="7" t="n">
+        <v>116</v>
+      </c>
+      <c r="B179" s="8" t="inlineStr"/>
+      <c r="C179" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="D179" s="8" t="inlineStr">
+        <is>
+          <t>PSV-76x</t>
+        </is>
+      </c>
+      <c r="E179" s="8" t="inlineStr">
+        <is>
           <t>PSV-76x-011</t>
         </is>
       </c>
-      <c r="F174" s="9" t="inlineStr">
+      <c r="F179" s="9" t="inlineStr">
         <is>
           <t>Kompletní zámkový systém + klika pro vnější 2-křídlé dveře</t>
         </is>
       </c>
-      <c r="G174" s="7" t="inlineStr">
+      <c r="G179" s="7" t="inlineStr">
         <is>
           <t>kpl</t>
         </is>
       </c>
-      <c r="H174" s="7" t="n">
+      <c r="H179" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="I174" s="9" t="inlineStr">
+      <c r="I179" s="9" t="inlineStr">
         <is>
           <t>2 kpl</t>
         </is>
       </c>
-      <c r="J174" s="9" t="inlineStr"/>
-    </row>
-    <row r="175">
-      <c r="A175" s="10" t="n">
-        <v>112</v>
-      </c>
-      <c r="B175" s="11" t="inlineStr"/>
-      <c r="C175" s="10" t="n">
+      <c r="J179" s="9" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="10" t="n">
+        <v>117</v>
+      </c>
+      <c r="B180" s="11" t="inlineStr"/>
+      <c r="C180" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="D175" s="11" t="inlineStr">
+      <c r="D180" s="11" t="inlineStr">
         <is>
           <t>PSV-76x</t>
         </is>
       </c>
-      <c r="E175" s="11" t="inlineStr">
+      <c r="E180" s="11" t="inlineStr">
         <is>
           <t>PSV-76x-012</t>
         </is>
       </c>
-      <c r="F175" s="12" t="inlineStr">
+      <c r="F180" s="12" t="inlineStr">
         <is>
           <t>Práh + lemování ostění vnějších dveří — pozink plech</t>
         </is>
       </c>
-      <c r="G175" s="10" t="inlineStr">
+      <c r="G180" s="10" t="inlineStr">
         <is>
           <t>kpl</t>
         </is>
       </c>
-      <c r="H175" s="10" t="n">
+      <c r="H180" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="I175" s="12" t="inlineStr">
+      <c r="I180" s="12" t="inlineStr">
         <is>
           <t>2 kpl</t>
         </is>
       </c>
-      <c r="J175" s="12" t="inlineStr"/>
-    </row>
-    <row r="176" ht="22" customHeight="1">
-      <c r="A176" s="2" t="inlineStr">
+      <c r="J180" s="12" t="inlineStr"/>
+    </row>
+    <row r="181" ht="22" customHeight="1">
+      <c r="A181" s="2" t="inlineStr">
         <is>
           <t>═══ FÁZE 8: IZOLACE + SOKL ═══</t>
         </is>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" s="3" t="inlineStr">
+    <row r="182">
+      <c r="A182" s="3" t="inlineStr">
         <is>
           <t>→ Penetrace soklu</t>
         </is>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" s="4" t="n">
-        <v>113</v>
-      </c>
-      <c r="B178" s="5" t="inlineStr"/>
-      <c r="C178" s="4" t="n">
+    <row r="183">
+      <c r="A183" s="4" t="n">
+        <v>118</v>
+      </c>
+      <c r="B183" s="5" t="inlineStr"/>
+      <c r="C183" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="D178" s="5" t="inlineStr">
+      <c r="D183" s="5" t="inlineStr">
         <is>
           <t>PSV-71x</t>
         </is>
       </c>
-      <c r="E178" s="5" t="inlineStr">
+      <c r="E183" s="5" t="inlineStr">
         <is>
           <t>PSV-71x-001</t>
         </is>
       </c>
-      <c r="F178" s="6" t="inlineStr">
+      <c r="F183" s="6" t="inlineStr">
         <is>
           <t>Penetrace soklu — penetrační nátěr pod hydroizolaci</t>
         </is>
       </c>
-      <c r="G178" s="4" t="inlineStr">
+      <c r="G183" s="4" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="H178" s="4" t="n">
+      <c r="H183" s="4" t="n">
         <v>28.5</v>
       </c>
-      <c r="I178" s="6" t="inlineStr">
+      <c r="I183" s="6" t="inlineStr">
         <is>
           <t>95.0 bm × 0.3 m = 28.5 m²</t>
         </is>
       </c>
-      <c r="J178" s="6" t="inlineStr"/>
-    </row>
-    <row r="179">
-      <c r="A179" s="3" t="inlineStr">
+      <c r="J183" s="6" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="3" t="inlineStr">
         <is>
           <t>→ Hydroizolace svislá soklu — SBS pás</t>
         </is>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" s="4" t="n">
-        <v>114</v>
-      </c>
-      <c r="B180" s="5" t="inlineStr"/>
-      <c r="C180" s="4" t="n">
+    <row r="185">
+      <c r="A185" s="4" t="n">
+        <v>119</v>
+      </c>
+      <c r="B185" s="5" t="inlineStr"/>
+      <c r="C185" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="D180" s="5" t="inlineStr">
+      <c r="D185" s="5" t="inlineStr">
         <is>
           <t>PSV-71x</t>
         </is>
       </c>
-      <c r="E180" s="5" t="inlineStr">
+      <c r="E185" s="5" t="inlineStr">
         <is>
           <t>PSV-71x-002</t>
         </is>
       </c>
-      <c r="F180" s="6" t="inlineStr">
+      <c r="F185" s="6" t="inlineStr">
         <is>
           <t>Hydroizolace svislá soklu — SBS modifikovaný asfaltový pás, natavený</t>
         </is>
       </c>
-      <c r="G180" s="4" t="inlineStr">
+      <c r="G185" s="4" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="H180" s="4" t="n">
+      <c r="H185" s="4" t="n">
         <v>28.5</v>
       </c>
-      <c r="I180" s="6" t="inlineStr">
+      <c r="I185" s="6" t="inlineStr">
         <is>
           <t>95.0 bm × 0.3 m = 28.5 m²  [TZ:B]</t>
         </is>
       </c>
-      <c r="J180" s="6" t="inlineStr"/>
-    </row>
-    <row r="181">
-      <c r="A181" s="3" t="inlineStr">
-        <is>
-          <t>→ Hydroizolační lišty rohové + napojení</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" s="7" t="n">
-        <v>115</v>
-      </c>
-      <c r="B182" s="8" t="inlineStr"/>
-      <c r="C182" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="D182" s="8" t="inlineStr">
-        <is>
-          <t>PSV-71x</t>
-        </is>
-      </c>
-      <c r="E182" s="8" t="inlineStr">
-        <is>
-          <t>PSV-71x-003</t>
-        </is>
-      </c>
-      <c r="F182" s="9" t="inlineStr">
-        <is>
-          <t>Hydroizolační lišty rohové + napojení svislé na vodorovnou pásku</t>
-        </is>
-      </c>
-      <c r="G182" s="7" t="inlineStr">
-        <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="H182" s="7" t="n">
-        <v>95</v>
-      </c>
-      <c r="I182" s="9" t="inlineStr">
-        <is>
-          <t>obvod 95.0 bm</t>
-        </is>
-      </c>
-      <c r="J182" s="9" t="inlineStr"/>
-    </row>
-    <row r="183">
-      <c r="A183" s="3" t="inlineStr">
-        <is>
-          <t>→ Ochranná vrstva — nopová folie HDPE</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" s="7" t="n">
-        <v>116</v>
-      </c>
-      <c r="B184" s="8" t="inlineStr"/>
-      <c r="C184" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="D184" s="8" t="inlineStr">
-        <is>
-          <t>PSV-71x</t>
-        </is>
-      </c>
-      <c r="E184" s="8" t="inlineStr">
-        <is>
-          <t>PSV-71x-004</t>
-        </is>
-      </c>
-      <c r="F184" s="9" t="inlineStr">
-        <is>
-          <t>Ochranná vrstva hydroizolace — nopová folie HDPE, š. 0.5 m</t>
-        </is>
-      </c>
-      <c r="G184" s="7" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="H184" s="7" t="n">
-        <v>47.5</v>
-      </c>
-      <c r="I184" s="9" t="inlineStr">
-        <is>
-          <t>95.0 bm × 0.5 m</t>
-        </is>
-      </c>
-      <c r="J184" s="9" t="inlineStr"/>
-    </row>
-    <row r="185" ht="22" customHeight="1">
-      <c r="A185" s="2" t="inlineStr">
-        <is>
-          <t>═══ FÁZE 9: PODLAHA PRŮMYSLOVÁ ═══</t>
-        </is>
-      </c>
+      <c r="J185" s="6" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="3" t="inlineStr">
         <is>
-          <t>→ Penetrace + primer pod stěrku</t>
+          <t>→ Hydroizolační lišty rohové + napojení</t>
         </is>
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="4" t="n">
-        <v>117</v>
-      </c>
-      <c r="B187" s="5" t="inlineStr"/>
-      <c r="C187" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="D187" s="5" t="inlineStr">
-        <is>
-          <t>PSV-77x</t>
-        </is>
-      </c>
-      <c r="E187" s="5" t="inlineStr">
-        <is>
-          <t>PSV-77x-001</t>
-        </is>
-      </c>
-      <c r="F187" s="6" t="inlineStr">
-        <is>
-          <t>Penetrace + primer pod průmyslovou stěrku podlahy</t>
-        </is>
-      </c>
-      <c r="G187" s="4" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="H187" s="4" t="n">
-        <v>495</v>
-      </c>
-      <c r="I187" s="6" t="inlineStr">
-        <is>
-          <t>495.0 m² (celá plocha podlahy)</t>
-        </is>
-      </c>
-      <c r="J187" s="6" t="inlineStr"/>
+      <c r="A187" s="7" t="n">
+        <v>120</v>
+      </c>
+      <c r="B187" s="8" t="inlineStr"/>
+      <c r="C187" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="D187" s="8" t="inlineStr">
+        <is>
+          <t>PSV-71x</t>
+        </is>
+      </c>
+      <c r="E187" s="8" t="inlineStr">
+        <is>
+          <t>PSV-71x-003</t>
+        </is>
+      </c>
+      <c r="F187" s="9" t="inlineStr">
+        <is>
+          <t>Hydroizolační lišty rohové + napojení svislé na vodorovnou pásku</t>
+        </is>
+      </c>
+      <c r="G187" s="7" t="inlineStr">
+        <is>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="H187" s="7" t="n">
+        <v>95</v>
+      </c>
+      <c r="I187" s="9" t="inlineStr">
+        <is>
+          <t>obvod 95.0 bm</t>
+        </is>
+      </c>
+      <c r="J187" s="9" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="3" t="inlineStr">
         <is>
-          <t>→ Epoxidová / PU stěrka 4–5 mm</t>
+          <t>→ Ochranná vrstva — nopová folie HDPE</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="7" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B189" s="8" t="inlineStr"/>
       <c r="C189" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="D189" s="8" t="inlineStr">
+        <is>
+          <t>PSV-71x</t>
+        </is>
+      </c>
+      <c r="E189" s="8" t="inlineStr">
+        <is>
+          <t>PSV-71x-004</t>
+        </is>
+      </c>
+      <c r="F189" s="9" t="inlineStr">
+        <is>
+          <t>Ochranná vrstva hydroizolace — nopová folie HDPE, š. 0.5 m</t>
+        </is>
+      </c>
+      <c r="G189" s="7" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="H189" s="7" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="I189" s="9" t="inlineStr">
+        <is>
+          <t>95.0 bm × 0.5 m</t>
+        </is>
+      </c>
+      <c r="J189" s="9" t="inlineStr"/>
+    </row>
+    <row r="190" ht="22" customHeight="1">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>═══ FÁZE 9: PODLAHA PRŮMYSLOVÁ ═══</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="3" t="inlineStr">
+        <is>
+          <t>→ Penetrace + primer pod stěrku</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="4" t="n">
+        <v>122</v>
+      </c>
+      <c r="B192" s="5" t="inlineStr"/>
+      <c r="C192" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="D189" s="8" t="inlineStr">
+      <c r="D192" s="5" t="inlineStr">
         <is>
           <t>PSV-77x</t>
         </is>
       </c>
-      <c r="E189" s="8" t="inlineStr">
-        <is>
-          <t>PSV-77x-002</t>
-        </is>
-      </c>
-      <c r="F189" s="9" t="inlineStr">
-        <is>
-          <t>Průmyslová epoxidová / PU stěrka podlahy tl. 4-5 mm, zatížení 1600 kg/m²</t>
-        </is>
-      </c>
-      <c r="G189" s="7" t="inlineStr">
+      <c r="E192" s="5" t="inlineStr">
+        <is>
+          <t>PSV-77x-001</t>
+        </is>
+      </c>
+      <c r="F192" s="6" t="inlineStr">
+        <is>
+          <t>Penetrace + primer pod průmyslovou stěrku podlahy</t>
+        </is>
+      </c>
+      <c r="G192" s="4" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="H189" s="7" t="n">
+      <c r="H192" s="4" t="n">
         <v>495</v>
       </c>
-      <c r="I189" s="9" t="inlineStr">
-        <is>
-          <t>495.0 m²  [TZ:podlaha]</t>
-        </is>
-      </c>
-      <c r="J189" s="9" t="inlineStr">
-        <is>
-          <t>ABMV:ABMV_10</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" s="3" t="inlineStr">
-        <is>
-          <t>→ Lokální zesílení anchorage zón strojů</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" s="4" t="n">
-        <v>119</v>
-      </c>
-      <c r="B191" s="5" t="inlineStr"/>
-      <c r="C191" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="D191" s="5" t="inlineStr">
-        <is>
-          <t>PSV-77x</t>
-        </is>
-      </c>
-      <c r="E191" s="5" t="inlineStr">
-        <is>
-          <t>PSV-77x-003</t>
-        </is>
-      </c>
-      <c r="F191" s="6" t="inlineStr">
-        <is>
-          <t>Lokální zesílení podlahy v anchorage zónách strojů — vyšší tl. stěrky 8 mm</t>
-        </is>
-      </c>
-      <c r="G191" s="4" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="H191" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="I191" s="6" t="inlineStr">
-        <is>
-          <t>placeholder ~30 m² (3 stroje × ~10 m² každé anchorage zóna)  [výkres:A107]</t>
-        </is>
-      </c>
-      <c r="J191" s="6" t="inlineStr">
-        <is>
-          <t>ABMV:ABMV_3,ABMV_16</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" s="3" t="inlineStr">
-        <is>
-          <t>→ Dilatace + lemy + protiskluz</t>
-        </is>
-      </c>
+      <c r="I192" s="6" t="inlineStr">
+        <is>
+          <t>495.0 m² (celá plocha podlahy)</t>
+        </is>
+      </c>
+      <c r="J192" s="6" t="inlineStr"/>
     </row>
     <row r="193">
-      <c r="A193" s="7" t="n">
-        <v>120</v>
-      </c>
-      <c r="B193" s="8" t="inlineStr"/>
-      <c r="C193" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="D193" s="8" t="inlineStr">
-        <is>
-          <t>PSV-77x</t>
-        </is>
-      </c>
-      <c r="E193" s="8" t="inlineStr">
-        <is>
-          <t>PSV-77x-004</t>
-        </is>
-      </c>
-      <c r="F193" s="9" t="inlineStr">
-        <is>
-          <t>Dilatační lišty podlahy — kovové, řezané spáry á 6 m</t>
-        </is>
-      </c>
-      <c r="G193" s="7" t="inlineStr">
-        <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="H193" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="I193" s="9" t="inlineStr">
-        <is>
-          <t>placeholder ~60 bm (pole dilatace á 6 m na 495 m² ploše)</t>
-        </is>
-      </c>
-      <c r="J193" s="9" t="inlineStr"/>
+      <c r="A193" s="3" t="inlineStr">
+        <is>
+          <t>→ Epoxidová / PU stěrka 4–5 mm</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="7" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B194" s="8" t="inlineStr"/>
       <c r="C194" s="7" t="n">
@@ -5766,344 +5816,321 @@
       </c>
       <c r="E194" s="8" t="inlineStr">
         <is>
-          <t>PSV-77x-005</t>
+          <t>PSV-77x-002</t>
         </is>
       </c>
       <c r="F194" s="9" t="inlineStr">
         <is>
-          <t>Lemovací úhelníky podlahy — pozink po obvodu stěrky</t>
+          <t>Průmyslová epoxidová / PU stěrka podlahy tl. 4-5 mm, zatížení 1600 kg/m²</t>
         </is>
       </c>
       <c r="G194" s="7" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="H194" s="7" t="n">
-        <v>95</v>
+        <v>495</v>
       </c>
       <c r="I194" s="9" t="inlineStr">
         <is>
-          <t>obvod desky 95 bm</t>
-        </is>
-      </c>
-      <c r="J194" s="9" t="inlineStr"/>
+          <t>495.0 m²  [TZ:podlaha]</t>
+        </is>
+      </c>
+      <c r="J194" s="9" t="inlineStr">
+        <is>
+          <t>ABMV:ABMV_10</t>
+        </is>
+      </c>
     </row>
     <row r="195">
-      <c r="A195" s="7" t="n">
-        <v>122</v>
-      </c>
-      <c r="B195" s="8" t="inlineStr"/>
-      <c r="C195" s="7" t="n">
+      <c r="A195" s="3" t="inlineStr">
+        <is>
+          <t>→ Lokální zesílení anchorage zón strojů</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="4" t="n">
+        <v>124</v>
+      </c>
+      <c r="B196" s="5" t="inlineStr"/>
+      <c r="C196" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="D195" s="8" t="inlineStr">
+      <c r="D196" s="5" t="inlineStr">
         <is>
           <t>PSV-77x</t>
         </is>
       </c>
-      <c r="E195" s="8" t="inlineStr">
-        <is>
-          <t>PSV-77x-006</t>
-        </is>
-      </c>
-      <c r="F195" s="9" t="inlineStr">
-        <is>
-          <t>Protiskluzový posyp křemičitým pískem — pro PU variantu</t>
-        </is>
-      </c>
-      <c r="G195" s="7" t="inlineStr">
+      <c r="E196" s="5" t="inlineStr">
+        <is>
+          <t>PSV-77x-003</t>
+        </is>
+      </c>
+      <c r="F196" s="6" t="inlineStr">
+        <is>
+          <t>Lokální zesílení podlahy v anchorage zónách strojů — vyšší tl. stěrky 8 mm</t>
+        </is>
+      </c>
+      <c r="G196" s="4" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="H195" s="7" t="n">
-        <v>495</v>
-      </c>
-      <c r="I195" s="9" t="inlineStr">
-        <is>
-          <t>495.0 m² (pokud zvolena PU varianta)</t>
-        </is>
-      </c>
-      <c r="J195" s="9" t="inlineStr">
-        <is>
-          <t>ABMV:ABMV_10</t>
-        </is>
-      </c>
-    </row>
-    <row r="196" ht="22" customHeight="1">
-      <c r="A196" s="2" t="inlineStr">
-        <is>
-          <t>═══ FÁZE 10: OSTATNÍ + PŘESUN HMOT ═══</t>
+      <c r="H196" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="I196" s="6" t="inlineStr">
+        <is>
+          <t>placeholder ~30 m² (3 stroje × ~10 m² každé anchorage zóna)  [výkres:A107]</t>
+        </is>
+      </c>
+      <c r="J196" s="6" t="inlineStr">
+        <is>
+          <t>ABMV:ABMV_3,ABMV_16</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="3" t="inlineStr">
         <is>
-          <t>→ Přesun hmot HSV vodorovně</t>
+          <t>→ Dilatace + lemy + protiskluz</t>
         </is>
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="4" t="n">
-        <v>123</v>
-      </c>
-      <c r="B198" s="5" t="inlineStr"/>
-      <c r="C198" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D198" s="5" t="inlineStr">
-        <is>
-          <t>HSV-9</t>
-        </is>
-      </c>
-      <c r="E198" s="5" t="inlineStr">
-        <is>
-          <t>HSV-9-001</t>
-        </is>
-      </c>
-      <c r="F198" s="6" t="inlineStr">
-        <is>
-          <t>Přesun hmot HSV vodorovně — beton, výztuž, ocel, klempířina</t>
-        </is>
-      </c>
-      <c r="G198" s="4" t="inlineStr">
-        <is>
-          <t>t·km</t>
-        </is>
-      </c>
-      <c r="H198" s="4" t="n">
-        <v>200</v>
-      </c>
-      <c r="I198" s="6" t="inlineStr">
-        <is>
-          <t>placeholder 200 t·km (in-site přesuny, default)</t>
-        </is>
-      </c>
-      <c r="J198" s="6" t="inlineStr"/>
+      <c r="A198" s="7" t="n">
+        <v>125</v>
+      </c>
+      <c r="B198" s="8" t="inlineStr"/>
+      <c r="C198" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="D198" s="8" t="inlineStr">
+        <is>
+          <t>PSV-77x</t>
+        </is>
+      </c>
+      <c r="E198" s="8" t="inlineStr">
+        <is>
+          <t>PSV-77x-004</t>
+        </is>
+      </c>
+      <c r="F198" s="9" t="inlineStr">
+        <is>
+          <t>Dilatační lišty podlahy — kovové, řezané spáry á 6 m</t>
+        </is>
+      </c>
+      <c r="G198" s="7" t="inlineStr">
+        <is>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="H198" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="I198" s="9" t="inlineStr">
+        <is>
+          <t>placeholder ~60 bm (pole dilatace á 6 m na 495 m² ploše)</t>
+        </is>
+      </c>
+      <c r="J198" s="9" t="inlineStr"/>
     </row>
     <row r="199">
-      <c r="A199" s="3" t="inlineStr">
-        <is>
-          <t>→ Doprava materiálu na stavbu — paušál</t>
-        </is>
-      </c>
+      <c r="A199" s="7" t="n">
+        <v>126</v>
+      </c>
+      <c r="B199" s="8" t="inlineStr"/>
+      <c r="C199" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="D199" s="8" t="inlineStr">
+        <is>
+          <t>PSV-77x</t>
+        </is>
+      </c>
+      <c r="E199" s="8" t="inlineStr">
+        <is>
+          <t>PSV-77x-005</t>
+        </is>
+      </c>
+      <c r="F199" s="9" t="inlineStr">
+        <is>
+          <t>Lemovací úhelníky podlahy — pozink po obvodu stěrky</t>
+        </is>
+      </c>
+      <c r="G199" s="7" t="inlineStr">
+        <is>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="H199" s="7" t="n">
+        <v>95</v>
+      </c>
+      <c r="I199" s="9" t="inlineStr">
+        <is>
+          <t>obvod desky 95 bm</t>
+        </is>
+      </c>
+      <c r="J199" s="9" t="inlineStr"/>
     </row>
     <row r="200">
-      <c r="A200" s="4" t="n">
-        <v>124</v>
-      </c>
-      <c r="B200" s="5" t="inlineStr"/>
-      <c r="C200" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D200" s="5" t="inlineStr">
-        <is>
-          <t>VRN</t>
-        </is>
-      </c>
-      <c r="E200" s="5" t="inlineStr">
-        <is>
-          <t>VRN-013</t>
-        </is>
-      </c>
-      <c r="F200" s="6" t="inlineStr">
-        <is>
-          <t>Doprava materiálu na stavbu vodorovně — paušál pro veškerou montáž</t>
-        </is>
-      </c>
-      <c r="G200" s="4" t="inlineStr">
-        <is>
-          <t>t·km</t>
-        </is>
-      </c>
-      <c r="H200" s="4" t="n">
-        <v>1500</v>
-      </c>
-      <c r="I200" s="6" t="inlineStr">
-        <is>
-          <t>placeholder ~1500 t·km (30 t materiálů × 50 km)</t>
-        </is>
-      </c>
-      <c r="J200" s="6" t="inlineStr"/>
+      <c r="A200" s="7" t="n">
+        <v>127</v>
+      </c>
+      <c r="B200" s="8" t="inlineStr"/>
+      <c r="C200" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="D200" s="8" t="inlineStr">
+        <is>
+          <t>PSV-77x</t>
+        </is>
+      </c>
+      <c r="E200" s="8" t="inlineStr">
+        <is>
+          <t>PSV-77x-006</t>
+        </is>
+      </c>
+      <c r="F200" s="9" t="inlineStr">
+        <is>
+          <t>Protiskluzový posyp křemičitým pískem — pro PU variantu</t>
+        </is>
+      </c>
+      <c r="G200" s="7" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="H200" s="7" t="n">
+        <v>495</v>
+      </c>
+      <c r="I200" s="9" t="inlineStr">
+        <is>
+          <t>495.0 m² (pokud zvolena PU varianta)</t>
+        </is>
+      </c>
+      <c r="J200" s="9" t="inlineStr">
+        <is>
+          <t>ABMV:ABMV_10</t>
+        </is>
+      </c>
     </row>
     <row r="201" ht="22" customHeight="1">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>═══ FÁZE 11: DOKONČENÍ + REVIZE + ODEVZDÁNÍ ═══</t>
+          <t>═══ FÁZE 10: OSTATNÍ + PŘESUN HMOT ═══</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="3" t="inlineStr">
         <is>
+          <t>→ Přesun hmot HSV vodorovně</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="4" t="n">
+        <v>128</v>
+      </c>
+      <c r="B203" s="5" t="inlineStr"/>
+      <c r="C203" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D203" s="5" t="inlineStr">
+        <is>
+          <t>HSV-9</t>
+        </is>
+      </c>
+      <c r="E203" s="5" t="inlineStr">
+        <is>
+          <t>HSV-9-001</t>
+        </is>
+      </c>
+      <c r="F203" s="6" t="inlineStr">
+        <is>
+          <t>Přesun hmot HSV vodorovně — beton, výztuž, ocel, klempířina</t>
+        </is>
+      </c>
+      <c r="G203" s="4" t="inlineStr">
+        <is>
+          <t>t·km</t>
+        </is>
+      </c>
+      <c r="H203" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="I203" s="6" t="inlineStr">
+        <is>
+          <t>placeholder 200 t·km (in-site přesuny, default)</t>
+        </is>
+      </c>
+      <c r="J203" s="6" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="3" t="inlineStr">
+        <is>
+          <t>→ Doprava materiálu na stavbu — paušál</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="4" t="n">
+        <v>129</v>
+      </c>
+      <c r="B205" s="5" t="inlineStr"/>
+      <c r="C205" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D205" s="5" t="inlineStr">
+        <is>
+          <t>VRN</t>
+        </is>
+      </c>
+      <c r="E205" s="5" t="inlineStr">
+        <is>
+          <t>VRN-013</t>
+        </is>
+      </c>
+      <c r="F205" s="6" t="inlineStr">
+        <is>
+          <t>Doprava materiálu na stavbu vodorovně — paušál pro veškerou montáž</t>
+        </is>
+      </c>
+      <c r="G205" s="4" t="inlineStr">
+        <is>
+          <t>t·km</t>
+        </is>
+      </c>
+      <c r="H205" s="4" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I205" s="6" t="inlineStr">
+        <is>
+          <t>placeholder ~1500 t·km (30 t materiálů × 50 km)</t>
+        </is>
+      </c>
+      <c r="J205" s="6" t="inlineStr"/>
+    </row>
+    <row r="206" ht="22" customHeight="1">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>═══ FÁZE 11: DOKONČENÍ + REVIZE + ODEVZDÁNÍ ═══</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="3" t="inlineStr">
+        <is>
           <t>→ Revize TZB (elektro, hydrant, hromosvod)</t>
         </is>
       </c>
-    </row>
-    <row r="203">
-      <c r="A203" s="7" t="n">
-        <v>125</v>
-      </c>
-      <c r="B203" s="8" t="inlineStr"/>
-      <c r="C203" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="D203" s="8" t="inlineStr">
-        <is>
-          <t>VRN</t>
-        </is>
-      </c>
-      <c r="E203" s="8" t="inlineStr">
-        <is>
-          <t>VRN-020</t>
-        </is>
-      </c>
-      <c r="F203" s="9" t="inlineStr">
-        <is>
-          <t>Revize elektroinstalace + protokol</t>
-        </is>
-      </c>
-      <c r="G203" s="7" t="inlineStr">
-        <is>
-          <t>paušál</t>
-        </is>
-      </c>
-      <c r="H203" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I203" s="9" t="inlineStr">
-        <is>
-          <t>paušál (Rožmitál 00523 R precedent)  [csn]</t>
-        </is>
-      </c>
-      <c r="J203" s="9" t="inlineStr"/>
-    </row>
-    <row r="204">
-      <c r="A204" s="7" t="n">
-        <v>126</v>
-      </c>
-      <c r="B204" s="8" t="inlineStr"/>
-      <c r="C204" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="D204" s="8" t="inlineStr">
-        <is>
-          <t>VRN</t>
-        </is>
-      </c>
-      <c r="E204" s="8" t="inlineStr">
-        <is>
-          <t>VRN-021</t>
-        </is>
-      </c>
-      <c r="F204" s="9" t="inlineStr">
-        <is>
-          <t>Revize hydrantového systému + tlaková zkouška</t>
-        </is>
-      </c>
-      <c r="G204" s="7" t="inlineStr">
-        <is>
-          <t>paušál</t>
-        </is>
-      </c>
-      <c r="H204" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I204" s="9" t="inlineStr">
-        <is>
-          <t>paušál  [csn]</t>
-        </is>
-      </c>
-      <c r="J204" s="9" t="inlineStr"/>
-    </row>
-    <row r="205">
-      <c r="A205" s="7" t="n">
-        <v>127</v>
-      </c>
-      <c r="B205" s="8" t="inlineStr"/>
-      <c r="C205" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="D205" s="8" t="inlineStr">
-        <is>
-          <t>VRN</t>
-        </is>
-      </c>
-      <c r="E205" s="8" t="inlineStr">
-        <is>
-          <t>VRN-022</t>
-        </is>
-      </c>
-      <c r="F205" s="9" t="inlineStr">
-        <is>
-          <t>Revize hromosvodu / LPS — měření ekvipotenciality, zemniče, svody</t>
-        </is>
-      </c>
-      <c r="G205" s="7" t="inlineStr">
-        <is>
-          <t>paušál</t>
-        </is>
-      </c>
-      <c r="H205" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I205" s="9" t="inlineStr">
-        <is>
-          <t>paušál  [csn]</t>
-        </is>
-      </c>
-      <c r="J205" s="9" t="inlineStr"/>
-    </row>
-    <row r="206">
-      <c r="A206" s="3" t="inlineStr">
-        <is>
-          <t>→ Likvidace odpadů O + N</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" s="4" t="n">
-        <v>128</v>
-      </c>
-      <c r="B207" s="5" t="inlineStr"/>
-      <c r="C207" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="D207" s="5" t="inlineStr">
-        <is>
-          <t>VRN</t>
-        </is>
-      </c>
-      <c r="E207" s="5" t="inlineStr">
-        <is>
-          <t>VRN-011</t>
-        </is>
-      </c>
-      <c r="F207" s="6" t="inlineStr">
-        <is>
-          <t>Likvidace odpadů kategorie O (běžný) — kontejner + odvoz + skládkovné</t>
-        </is>
-      </c>
-      <c r="G207" s="4" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="H207" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="I207" s="6" t="inlineStr">
-        <is>
-          <t>placeholder ~30 m³ stavebního odpadu kat. O</t>
-        </is>
-      </c>
-      <c r="J207" s="6" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" s="7" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B208" s="8" t="inlineStr"/>
       <c r="C208" s="7" t="n">
@@ -6116,122 +6143,153 @@
       </c>
       <c r="E208" s="8" t="inlineStr">
         <is>
-          <t>VRN-012</t>
+          <t>VRN-020</t>
         </is>
       </c>
       <c r="F208" s="9" t="inlineStr">
         <is>
-          <t>Likvidace odpadů kategorie N (nebezpečné — barvy, oleje, tmely)</t>
+          <t>Revize elektroinstalace + protokol</t>
         </is>
       </c>
       <c r="G208" s="7" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>paušál</t>
         </is>
       </c>
       <c r="H208" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I208" s="9" t="inlineStr">
         <is>
-          <t>placeholder ~2 m³ kat. N</t>
+          <t>paušál (Rožmitál 00523 R precedent)  [csn]</t>
         </is>
       </c>
       <c r="J208" s="9" t="inlineStr"/>
     </row>
     <row r="209">
-      <c r="A209" s="3" t="inlineStr">
-        <is>
-          <t>→ Geodetické zaměření DSPS</t>
-        </is>
-      </c>
+      <c r="A209" s="7" t="n">
+        <v>131</v>
+      </c>
+      <c r="B209" s="8" t="inlineStr"/>
+      <c r="C209" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="D209" s="8" t="inlineStr">
+        <is>
+          <t>VRN</t>
+        </is>
+      </c>
+      <c r="E209" s="8" t="inlineStr">
+        <is>
+          <t>VRN-021</t>
+        </is>
+      </c>
+      <c r="F209" s="9" t="inlineStr">
+        <is>
+          <t>Revize hydrantového systému + tlaková zkouška</t>
+        </is>
+      </c>
+      <c r="G209" s="7" t="inlineStr">
+        <is>
+          <t>paušál</t>
+        </is>
+      </c>
+      <c r="H209" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I209" s="9" t="inlineStr">
+        <is>
+          <t>paušál  [csn]</t>
+        </is>
+      </c>
+      <c r="J209" s="9" t="inlineStr"/>
     </row>
     <row r="210">
-      <c r="A210" s="4" t="n">
-        <v>130</v>
-      </c>
-      <c r="B210" s="5" t="inlineStr"/>
-      <c r="C210" s="4" t="n">
+      <c r="A210" s="7" t="n">
+        <v>132</v>
+      </c>
+      <c r="B210" s="8" t="inlineStr"/>
+      <c r="C210" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="D210" s="5" t="inlineStr">
+      <c r="D210" s="8" t="inlineStr">
         <is>
           <t>VRN</t>
         </is>
       </c>
-      <c r="E210" s="5" t="inlineStr">
-        <is>
-          <t>VRN-015</t>
-        </is>
-      </c>
-      <c r="F210" s="6" t="inlineStr">
-        <is>
-          <t>Geodetické zaměření skutečného provedení (DSPS) — po dokončení stavby</t>
-        </is>
-      </c>
-      <c r="G210" s="4" t="inlineStr">
+      <c r="E210" s="8" t="inlineStr">
+        <is>
+          <t>VRN-022</t>
+        </is>
+      </c>
+      <c r="F210" s="9" t="inlineStr">
+        <is>
+          <t>Revize hromosvodu / LPS — měření ekvipotenciality, zemniče, svody</t>
+        </is>
+      </c>
+      <c r="G210" s="7" t="inlineStr">
         <is>
           <t>paušál</t>
         </is>
       </c>
-      <c r="H210" s="4" t="n">
+      <c r="H210" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="I210" s="6" t="inlineStr">
-        <is>
-          <t>paušál</t>
-        </is>
-      </c>
-      <c r="J210" s="6" t="inlineStr"/>
+      <c r="I210" s="9" t="inlineStr">
+        <is>
+          <t>paušál  [csn]</t>
+        </is>
+      </c>
+      <c r="J210" s="9" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" s="3" t="inlineStr">
         <is>
-          <t>→ Předávací protokoly + kolaudace</t>
+          <t>→ Likvidace odpadů O + N</t>
         </is>
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="7" t="n">
-        <v>131</v>
-      </c>
-      <c r="B212" s="8" t="inlineStr"/>
-      <c r="C212" s="7" t="n">
+      <c r="A212" s="4" t="n">
+        <v>133</v>
+      </c>
+      <c r="B212" s="5" t="inlineStr"/>
+      <c r="C212" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="D212" s="8" t="inlineStr">
+      <c r="D212" s="5" t="inlineStr">
         <is>
           <t>VRN</t>
         </is>
       </c>
-      <c r="E212" s="8" t="inlineStr">
-        <is>
-          <t>VRN-018</t>
-        </is>
-      </c>
-      <c r="F212" s="9" t="inlineStr">
-        <is>
-          <t>Předávací protokoly + dokumentace skutečného provedení (DSPS)</t>
-        </is>
-      </c>
-      <c r="G212" s="7" t="inlineStr">
-        <is>
-          <t>paušál</t>
-        </is>
-      </c>
-      <c r="H212" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I212" s="9" t="inlineStr">
-        <is>
-          <t>paušál</t>
-        </is>
-      </c>
-      <c r="J212" s="9" t="inlineStr"/>
+      <c r="E212" s="5" t="inlineStr">
+        <is>
+          <t>VRN-011</t>
+        </is>
+      </c>
+      <c r="F212" s="6" t="inlineStr">
+        <is>
+          <t>Likvidace odpadů kategorie O (běžný) — kontejner + odvoz + skládkovné</t>
+        </is>
+      </c>
+      <c r="G212" s="4" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="H212" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="I212" s="6" t="inlineStr">
+        <is>
+          <t>placeholder ~30 m³ stavebního odpadu kat. O</t>
+        </is>
+      </c>
+      <c r="J212" s="6" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" s="7" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B213" s="8" t="inlineStr"/>
       <c r="C213" s="7" t="n">
@@ -6244,25 +6302,25 @@
       </c>
       <c r="E213" s="8" t="inlineStr">
         <is>
-          <t>VRN-019</t>
+          <t>VRN-012</t>
         </is>
       </c>
       <c r="F213" s="9" t="inlineStr">
         <is>
-          <t>Kolaudační řízení — příprava + účast na jednání + revize dokumentace</t>
+          <t>Likvidace odpadů kategorie N (nebezpečné — barvy, oleje, tmely)</t>
         </is>
       </c>
       <c r="G213" s="7" t="inlineStr">
         <is>
-          <t>paušál</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="H213" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I213" s="9" t="inlineStr">
         <is>
-          <t>paušál</t>
+          <t>placeholder ~2 m³ kat. N</t>
         </is>
       </c>
       <c r="J213" s="9" t="inlineStr"/>
@@ -6270,13 +6328,13 @@
     <row r="214">
       <c r="A214" s="3" t="inlineStr">
         <is>
-          <t>→ Náhradní výsadba dřevin (po dokončení)</t>
+          <t>→ Geodetické zaměření DSPS</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="4" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B215" s="5" t="inlineStr"/>
       <c r="C215" s="4" t="n">
@@ -6284,117 +6342,245 @@
       </c>
       <c r="D215" s="5" t="inlineStr">
         <is>
+          <t>VRN</t>
+        </is>
+      </c>
+      <c r="E215" s="5" t="inlineStr">
+        <is>
+          <t>VRN-015</t>
+        </is>
+      </c>
+      <c r="F215" s="6" t="inlineStr">
+        <is>
+          <t>Geodetické zaměření skutečného provedení (DSPS) — po dokončení stavby</t>
+        </is>
+      </c>
+      <c r="G215" s="4" t="inlineStr">
+        <is>
+          <t>paušál</t>
+        </is>
+      </c>
+      <c r="H215" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I215" s="6" t="inlineStr">
+        <is>
+          <t>paušál</t>
+        </is>
+      </c>
+      <c r="J215" s="6" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="3" t="inlineStr">
+        <is>
+          <t>→ Předávací protokoly + kolaudace</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="7" t="n">
+        <v>136</v>
+      </c>
+      <c r="B217" s="8" t="inlineStr"/>
+      <c r="C217" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="D217" s="8" t="inlineStr">
+        <is>
+          <t>VRN</t>
+        </is>
+      </c>
+      <c r="E217" s="8" t="inlineStr">
+        <is>
+          <t>VRN-018</t>
+        </is>
+      </c>
+      <c r="F217" s="9" t="inlineStr">
+        <is>
+          <t>Předávací protokoly + dokumentace skutečného provedení (DSPS)</t>
+        </is>
+      </c>
+      <c r="G217" s="7" t="inlineStr">
+        <is>
+          <t>paušál</t>
+        </is>
+      </c>
+      <c r="H217" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I217" s="9" t="inlineStr">
+        <is>
+          <t>paušál</t>
+        </is>
+      </c>
+      <c r="J217" s="9" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="7" t="n">
+        <v>137</v>
+      </c>
+      <c r="B218" s="8" t="inlineStr"/>
+      <c r="C218" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="D218" s="8" t="inlineStr">
+        <is>
+          <t>VRN</t>
+        </is>
+      </c>
+      <c r="E218" s="8" t="inlineStr">
+        <is>
+          <t>VRN-019</t>
+        </is>
+      </c>
+      <c r="F218" s="9" t="inlineStr">
+        <is>
+          <t>Kolaudační řízení — příprava + účast na jednání + revize dokumentace</t>
+        </is>
+      </c>
+      <c r="G218" s="7" t="inlineStr">
+        <is>
+          <t>paušál</t>
+        </is>
+      </c>
+      <c r="H218" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I218" s="9" t="inlineStr">
+        <is>
+          <t>paušál</t>
+        </is>
+      </c>
+      <c r="J218" s="9" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="3" t="inlineStr">
+        <is>
+          <t>→ Náhradní výsadba dřevin (po dokončení)</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="4" t="n">
+        <v>138</v>
+      </c>
+      <c r="B220" s="5" t="inlineStr"/>
+      <c r="C220" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="D220" s="5" t="inlineStr">
+        <is>
           <t>HSV-1</t>
         </is>
       </c>
-      <c r="E215" s="5" t="inlineStr">
+      <c r="E220" s="5" t="inlineStr">
         <is>
           <t>HSV-1-024</t>
         </is>
       </c>
-      <c r="F215" s="6" t="inlineStr">
+      <c r="F220" s="6" t="inlineStr">
         <is>
           <t>Náhradní výsadba dřevin per rozhodnutí orgánu životního prostředí</t>
         </is>
       </c>
-      <c r="G215" s="4" t="inlineStr">
+      <c r="G220" s="4" t="inlineStr">
         <is>
           <t>ks</t>
         </is>
       </c>
-      <c r="H215" s="4" t="n">
+      <c r="H220" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="I215" s="6" t="inlineStr">
+      <c r="I220" s="6" t="inlineStr">
         <is>
           <t>2 ks (per TZ B m.7.b náhradní výsadba)  [TZ:7.b]</t>
         </is>
       </c>
-      <c r="J215" s="6" t="inlineStr"/>
+      <c r="J220" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="81">
     <mergeCell ref="A181:J181"/>
-    <mergeCell ref="A91:J91"/>
+    <mergeCell ref="A184:J184"/>
+    <mergeCell ref="A156:J156"/>
     <mergeCell ref="A171:J171"/>
     <mergeCell ref="A52:J52"/>
-    <mergeCell ref="A63:J63"/>
-    <mergeCell ref="A93:J93"/>
-    <mergeCell ref="A130:J130"/>
+    <mergeCell ref="A165:J165"/>
     <mergeCell ref="A34:J34"/>
-    <mergeCell ref="A148:J148"/>
-    <mergeCell ref="A157:J157"/>
+    <mergeCell ref="A83:J83"/>
     <mergeCell ref="A49:J49"/>
+    <mergeCell ref="A138:J138"/>
+    <mergeCell ref="A132:J132"/>
     <mergeCell ref="A36:J36"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="A119:J119"/>
-    <mergeCell ref="A196:J196"/>
-    <mergeCell ref="A183:J183"/>
-    <mergeCell ref="A75:J75"/>
-    <mergeCell ref="A133:J133"/>
     <mergeCell ref="A3:J3"/>
     <mergeCell ref="A95:J95"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A159:J159"/>
-    <mergeCell ref="A97:J97"/>
+    <mergeCell ref="A219:J219"/>
     <mergeCell ref="A29:J29"/>
-    <mergeCell ref="A209:J209"/>
+    <mergeCell ref="A96:J96"/>
+    <mergeCell ref="A147:J147"/>
     <mergeCell ref="A121:J121"/>
     <mergeCell ref="A202:J202"/>
     <mergeCell ref="A58:J58"/>
     <mergeCell ref="A211:J211"/>
-    <mergeCell ref="A67:J67"/>
     <mergeCell ref="A186:J186"/>
     <mergeCell ref="A24:J24"/>
     <mergeCell ref="A201:J201"/>
-    <mergeCell ref="A60:J60"/>
     <mergeCell ref="A197:J197"/>
-    <mergeCell ref="A146:J146"/>
+    <mergeCell ref="A110:J110"/>
     <mergeCell ref="A124:J124"/>
     <mergeCell ref="A16:J16"/>
-    <mergeCell ref="A84:J84"/>
     <mergeCell ref="A214:J214"/>
+    <mergeCell ref="A204:J204"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A42:J42"/>
     <mergeCell ref="A151:J151"/>
-    <mergeCell ref="A160:J160"/>
     <mergeCell ref="A22:J22"/>
     <mergeCell ref="A135:J135"/>
     <mergeCell ref="A206:J206"/>
+    <mergeCell ref="A144:J144"/>
+    <mergeCell ref="A122:J122"/>
     <mergeCell ref="A190:J190"/>
-    <mergeCell ref="A199:J199"/>
-    <mergeCell ref="A127:J127"/>
+    <mergeCell ref="A72:J72"/>
+    <mergeCell ref="A112:J112"/>
     <mergeCell ref="A176:J176"/>
     <mergeCell ref="A114:J114"/>
-    <mergeCell ref="A107:J107"/>
-    <mergeCell ref="A137:J137"/>
-    <mergeCell ref="A177:J177"/>
-    <mergeCell ref="A90:J90"/>
-    <mergeCell ref="A139:J139"/>
-    <mergeCell ref="A154:J154"/>
+    <mergeCell ref="A182:J182"/>
+    <mergeCell ref="A98:J98"/>
+    <mergeCell ref="A191:J191"/>
+    <mergeCell ref="A70:J70"/>
+    <mergeCell ref="A153:J153"/>
+    <mergeCell ref="A162:J162"/>
+    <mergeCell ref="A164:J164"/>
+    <mergeCell ref="A145:J145"/>
+    <mergeCell ref="A195:J195"/>
+    <mergeCell ref="A76:J76"/>
     <mergeCell ref="A33:J33"/>
+    <mergeCell ref="A85:J85"/>
     <mergeCell ref="A116:J116"/>
     <mergeCell ref="A8:J8"/>
     <mergeCell ref="A188:J188"/>
+    <mergeCell ref="A126:J126"/>
+    <mergeCell ref="A100:J100"/>
     <mergeCell ref="A140:J140"/>
-    <mergeCell ref="A109:J109"/>
     <mergeCell ref="A10:J10"/>
     <mergeCell ref="A19:J19"/>
-    <mergeCell ref="A117:J117"/>
-    <mergeCell ref="A111:J111"/>
+    <mergeCell ref="A68:J68"/>
+    <mergeCell ref="A102:J102"/>
     <mergeCell ref="A39:J39"/>
-    <mergeCell ref="A166:J166"/>
     <mergeCell ref="A142:J142"/>
-    <mergeCell ref="A78:J78"/>
+    <mergeCell ref="A207:J207"/>
+    <mergeCell ref="A216:J216"/>
     <mergeCell ref="A65:J65"/>
+    <mergeCell ref="A193:J193"/>
     <mergeCell ref="A80:J80"/>
     <mergeCell ref="A46:J46"/>
-    <mergeCell ref="A192:J192"/>
-    <mergeCell ref="A105:J105"/>
+    <mergeCell ref="A89:J89"/>
     <mergeCell ref="A57:J57"/>
-    <mergeCell ref="A179:J179"/>
-    <mergeCell ref="A71:J71"/>
-    <mergeCell ref="A185:J185"/>
+    <mergeCell ref="A129:J129"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/test-data/hk212_hala/outputs/sequential_list/hk212_sequential_list.xlsx
+++ b/test-data/hk212_hala/outputs/sequential_list/hk212_sequential_list.xlsx
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J220"/>
+  <dimension ref="A1:J241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6020,14 +6020,14 @@
     <row r="201" ht="22" customHeight="1">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>═══ FÁZE 10: OSTATNÍ + PŘESUN HMOT ═══</t>
+          <t>═══ FÁZE 9.5: TZB INSTALACE — VYTÁPĚNÍ ═══</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="3" t="inlineStr">
         <is>
-          <t>→ Přesun hmot HSV vodorovně</t>
+          <t>→ Doprava topidel + přesun hmot ÚT</t>
         </is>
       </c>
     </row>
@@ -6037,34 +6037,34 @@
       </c>
       <c r="B203" s="5" t="inlineStr"/>
       <c r="C203" s="4" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="D203" s="5" t="inlineStr">
         <is>
-          <t>HSV-9</t>
+          <t>M-UT</t>
         </is>
       </c>
       <c r="E203" s="5" t="inlineStr">
         <is>
-          <t>HSV-9-001</t>
+          <t>M-UT-012</t>
         </is>
       </c>
       <c r="F203" s="6" t="inlineStr">
         <is>
-          <t>Přesun hmot HSV vodorovně — beton, výztuž, ocel, klempířina</t>
+          <t>Doprava zařízení + přesun hmot pro M-UT kapitolu</t>
         </is>
       </c>
       <c r="G203" s="4" t="inlineStr">
         <is>
-          <t>t·km</t>
+          <t>soubor</t>
         </is>
       </c>
       <c r="H203" s="4" t="n">
-        <v>200</v>
+        <v>1</v>
       </c>
       <c r="I203" s="6" t="inlineStr">
         <is>
-          <t>placeholder 200 t·km (in-site přesuny, default)</t>
+          <t>1 soubor  [TZ:8, document:UT_HalaHK_TZ_DPS.doc, document:UT_HalaHK_TZ_VM_DPS_E.pdf]</t>
         </is>
       </c>
       <c r="J203" s="6" t="inlineStr"/>
@@ -6072,7 +6072,7 @@
     <row r="204">
       <c r="A204" s="3" t="inlineStr">
         <is>
-          <t>→ Doprava materiálu na stavbu — paušál</t>
+          <t>→ Montážní plošina pro práci ve výšce 5 m (ECOSUN)</t>
         </is>
       </c>
     </row>
@@ -6082,432 +6082,953 @@
       </c>
       <c r="B205" s="5" t="inlineStr"/>
       <c r="C205" s="4" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="D205" s="5" t="inlineStr">
         <is>
-          <t>VRN</t>
+          <t>M-UT</t>
         </is>
       </c>
       <c r="E205" s="5" t="inlineStr">
         <is>
-          <t>VRN-013</t>
+          <t>M-UT-009</t>
         </is>
       </c>
       <c r="F205" s="6" t="inlineStr">
         <is>
-          <t>Doprava materiálu na stavbu vodorovně — paušál pro veškerou montáž</t>
+          <t>Montážní plošina / práce ve výšce pro montáž topidel ve výšce 5 m</t>
         </is>
       </c>
       <c r="G205" s="4" t="inlineStr">
         <is>
-          <t>t·km</t>
+          <t>soubor</t>
         </is>
       </c>
       <c r="H205" s="4" t="n">
-        <v>1500</v>
+        <v>1</v>
       </c>
       <c r="I205" s="6" t="inlineStr">
         <is>
-          <t>placeholder ~1500 t·km (30 t materiálů × 50 km)</t>
+          <t>1 soubor  [TZ:8, document:UT_HalaHK_TZ_DPS.doc, document:UT_HalaHK_TZ_VM_DPS_E.pdf]</t>
         </is>
       </c>
       <c r="J205" s="6" t="inlineStr"/>
     </row>
-    <row r="206" ht="22" customHeight="1">
-      <c r="A206" s="2" t="inlineStr">
-        <is>
-          <t>═══ FÁZE 11: DOKONČENÍ + REVIZE + ODEVZDÁNÍ ═══</t>
+    <row r="206">
+      <c r="A206" s="3" t="inlineStr">
+        <is>
+          <t>→ ECOSUN S+ 12 — dodávka + závěs + montáž na strop haly</t>
         </is>
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="3" t="inlineStr">
-        <is>
-          <t>→ Revize TZB (elektro, hydrant, hromosvod)</t>
-        </is>
-      </c>
+      <c r="A207" s="4" t="n">
+        <v>130</v>
+      </c>
+      <c r="B207" s="5" t="inlineStr"/>
+      <c r="C207" s="4" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="D207" s="5" t="inlineStr">
+        <is>
+          <t>M-UT</t>
+        </is>
+      </c>
+      <c r="E207" s="5" t="inlineStr">
+        <is>
+          <t>M-UT-001</t>
+        </is>
+      </c>
+      <c r="F207" s="6" t="inlineStr">
+        <is>
+          <t>Dodávka el. sálavý panel Fénix ECOSUN S+ 12, 1200 W, č.kat. 5401542</t>
+        </is>
+      </c>
+      <c r="G207" s="4" t="inlineStr">
+        <is>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="H207" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="I207" s="6" t="inlineStr">
+        <is>
+          <t>20 ks  [TZ:8, document:UT_HalaHK_TZ_DPS.doc, document:UT_HalaHK_TZ_VM_DPS_E.pdf]</t>
+        </is>
+      </c>
+      <c r="J207" s="6" t="inlineStr"/>
     </row>
     <row r="208">
-      <c r="A208" s="7" t="n">
-        <v>130</v>
-      </c>
-      <c r="B208" s="8" t="inlineStr"/>
-      <c r="C208" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="D208" s="8" t="inlineStr">
-        <is>
-          <t>VRN</t>
-        </is>
-      </c>
-      <c r="E208" s="8" t="inlineStr">
-        <is>
-          <t>VRN-020</t>
-        </is>
-      </c>
-      <c r="F208" s="9" t="inlineStr">
-        <is>
-          <t>Revize elektroinstalace + protokol</t>
-        </is>
-      </c>
-      <c r="G208" s="7" t="inlineStr">
-        <is>
-          <t>paušál</t>
-        </is>
-      </c>
-      <c r="H208" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I208" s="9" t="inlineStr">
-        <is>
-          <t>paušál (Rožmitál 00523 R precedent)  [csn]</t>
-        </is>
-      </c>
-      <c r="J208" s="9" t="inlineStr"/>
+      <c r="A208" s="10" t="n">
+        <v>131</v>
+      </c>
+      <c r="B208" s="11" t="inlineStr"/>
+      <c r="C208" s="10" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="D208" s="11" t="inlineStr">
+        <is>
+          <t>M-UT</t>
+        </is>
+      </c>
+      <c r="E208" s="11" t="inlineStr">
+        <is>
+          <t>M-UT-003</t>
+        </is>
+      </c>
+      <c r="F208" s="12" t="inlineStr">
+        <is>
+          <t>Závěsný materiál pro panely ECOSUN — řetízky prům. délka 5 m/ks</t>
+        </is>
+      </c>
+      <c r="G208" s="10" t="inlineStr">
+        <is>
+          <t>sada</t>
+        </is>
+      </c>
+      <c r="H208" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="I208" s="12" t="inlineStr">
+        <is>
+          <t>20 sad  [TZ:8, document:UT_HalaHK_TZ_DPS.doc, document:UT_HalaHK_TZ_VM_DPS_E.pdf]</t>
+        </is>
+      </c>
+      <c r="J208" s="12" t="inlineStr"/>
     </row>
     <row r="209">
-      <c r="A209" s="7" t="n">
-        <v>131</v>
-      </c>
-      <c r="B209" s="8" t="inlineStr"/>
-      <c r="C209" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="D209" s="8" t="inlineStr">
-        <is>
-          <t>VRN</t>
-        </is>
-      </c>
-      <c r="E209" s="8" t="inlineStr">
-        <is>
-          <t>VRN-021</t>
-        </is>
-      </c>
-      <c r="F209" s="9" t="inlineStr">
-        <is>
-          <t>Revize hydrantového systému + tlaková zkouška</t>
-        </is>
-      </c>
-      <c r="G209" s="7" t="inlineStr">
-        <is>
-          <t>paušál</t>
-        </is>
-      </c>
-      <c r="H209" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I209" s="9" t="inlineStr">
-        <is>
-          <t>paušál  [csn]</t>
-        </is>
-      </c>
-      <c r="J209" s="9" t="inlineStr"/>
+      <c r="A209" s="4" t="n">
+        <v>132</v>
+      </c>
+      <c r="B209" s="5" t="inlineStr"/>
+      <c r="C209" s="4" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="D209" s="5" t="inlineStr">
+        <is>
+          <t>M-UT</t>
+        </is>
+      </c>
+      <c r="E209" s="5" t="inlineStr">
+        <is>
+          <t>M-UT-002</t>
+        </is>
+      </c>
+      <c r="F209" s="6" t="inlineStr">
+        <is>
+          <t>Montáž el. sálavý panel ECOSUN S+ 12 ve výšce 5 m na stropní konstrukci</t>
+        </is>
+      </c>
+      <c r="G209" s="4" t="inlineStr">
+        <is>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="H209" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="I209" s="6" t="inlineStr">
+        <is>
+          <t>20 ks  [TZ:8, document:UT_HalaHK_TZ_DPS.doc, document:UT_HalaHK_TZ_VM_DPS_E.pdf]</t>
+        </is>
+      </c>
+      <c r="J209" s="6" t="inlineStr"/>
     </row>
     <row r="210">
-      <c r="A210" s="7" t="n">
-        <v>132</v>
-      </c>
-      <c r="B210" s="8" t="inlineStr"/>
-      <c r="C210" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="D210" s="8" t="inlineStr">
-        <is>
-          <t>VRN</t>
-        </is>
-      </c>
-      <c r="E210" s="8" t="inlineStr">
-        <is>
-          <t>VRN-022</t>
-        </is>
-      </c>
-      <c r="F210" s="9" t="inlineStr">
-        <is>
-          <t>Revize hromosvodu / LPS — měření ekvipotenciality, zemniče, svody</t>
-        </is>
-      </c>
-      <c r="G210" s="7" t="inlineStr">
-        <is>
-          <t>paušál</t>
-        </is>
-      </c>
-      <c r="H210" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I210" s="9" t="inlineStr">
-        <is>
-          <t>paušál  [csn]</t>
-        </is>
-      </c>
-      <c r="J210" s="9" t="inlineStr"/>
+      <c r="A210" s="3" t="inlineStr">
+        <is>
+          <t>→ Dalap E-HP 9 kW — dodávka + montáž v rozích haly</t>
+        </is>
+      </c>
     </row>
     <row r="211">
-      <c r="A211" s="3" t="inlineStr">
-        <is>
-          <t>→ Likvidace odpadů O + N</t>
-        </is>
-      </c>
+      <c r="A211" s="4" t="n">
+        <v>133</v>
+      </c>
+      <c r="B211" s="5" t="inlineStr"/>
+      <c r="C211" s="4" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="D211" s="5" t="inlineStr">
+        <is>
+          <t>M-UT</t>
+        </is>
+      </c>
+      <c r="E211" s="5" t="inlineStr">
+        <is>
+          <t>M-UT-004</t>
+        </is>
+      </c>
+      <c r="F211" s="6" t="inlineStr">
+        <is>
+          <t>Dodávka nástěnný el. ohřívač s ventilátorem Dalap E-HP 9 kW</t>
+        </is>
+      </c>
+      <c r="G211" s="4" t="inlineStr">
+        <is>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="H211" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I211" s="6" t="inlineStr">
+        <is>
+          <t>4 ks  [TZ:8, document:UT_HalaHK_TZ_DPS.doc, document:UT_HalaHK_TZ_VM_DPS_E.pdf]</t>
+        </is>
+      </c>
+      <c r="J211" s="6" t="inlineStr"/>
     </row>
     <row r="212">
-      <c r="A212" s="4" t="n">
-        <v>133</v>
-      </c>
-      <c r="B212" s="5" t="inlineStr"/>
-      <c r="C212" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="D212" s="5" t="inlineStr">
-        <is>
-          <t>VRN</t>
-        </is>
-      </c>
-      <c r="E212" s="5" t="inlineStr">
-        <is>
-          <t>VRN-011</t>
-        </is>
-      </c>
-      <c r="F212" s="6" t="inlineStr">
-        <is>
-          <t>Likvidace odpadů kategorie O (běžný) — kontejner + odvoz + skládkovné</t>
-        </is>
-      </c>
-      <c r="G212" s="4" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="H212" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="I212" s="6" t="inlineStr">
-        <is>
-          <t>placeholder ~30 m³ stavebního odpadu kat. O</t>
-        </is>
-      </c>
-      <c r="J212" s="6" t="inlineStr"/>
+      <c r="A212" s="10" t="n">
+        <v>134</v>
+      </c>
+      <c r="B212" s="11" t="inlineStr"/>
+      <c r="C212" s="10" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="D212" s="11" t="inlineStr">
+        <is>
+          <t>M-UT</t>
+        </is>
+      </c>
+      <c r="E212" s="11" t="inlineStr">
+        <is>
+          <t>M-UT-005</t>
+        </is>
+      </c>
+      <c r="F212" s="12" t="inlineStr">
+        <is>
+          <t>Montáž nástěnný el. ohřívač Dalap E-HP 9 kW v rozích haly</t>
+        </is>
+      </c>
+      <c r="G212" s="10" t="inlineStr">
+        <is>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="H212" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="I212" s="12" t="inlineStr">
+        <is>
+          <t>4 ks  [TZ:8, document:UT_HalaHK_TZ_DPS.doc, document:UT_HalaHK_TZ_VM_DPS_E.pdf]</t>
+        </is>
+      </c>
+      <c r="J212" s="12" t="inlineStr"/>
     </row>
     <row r="213">
-      <c r="A213" s="7" t="n">
-        <v>134</v>
-      </c>
-      <c r="B213" s="8" t="inlineStr"/>
-      <c r="C213" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="D213" s="8" t="inlineStr">
-        <is>
-          <t>VRN</t>
-        </is>
-      </c>
-      <c r="E213" s="8" t="inlineStr">
-        <is>
-          <t>VRN-012</t>
-        </is>
-      </c>
-      <c r="F213" s="9" t="inlineStr">
-        <is>
-          <t>Likvidace odpadů kategorie N (nebezpečné — barvy, oleje, tmely)</t>
-        </is>
-      </c>
-      <c r="G213" s="7" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="H213" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I213" s="9" t="inlineStr">
-        <is>
-          <t>placeholder ~2 m³ kat. N</t>
-        </is>
-      </c>
-      <c r="J213" s="9" t="inlineStr"/>
+      <c r="A213" s="3" t="inlineStr">
+        <is>
+          <t>→ Regulace — UET 15D + prostorové termostaty</t>
+        </is>
+      </c>
     </row>
     <row r="214">
-      <c r="A214" s="3" t="inlineStr">
-        <is>
-          <t>→ Geodetické zaměření DSPS</t>
-        </is>
-      </c>
+      <c r="A214" s="4" t="n">
+        <v>135</v>
+      </c>
+      <c r="B214" s="5" t="inlineStr"/>
+      <c r="C214" s="4" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="D214" s="5" t="inlineStr">
+        <is>
+          <t>M-UT</t>
+        </is>
+      </c>
+      <c r="E214" s="5" t="inlineStr">
+        <is>
+          <t>M-UT-006</t>
+        </is>
+      </c>
+      <c r="F214" s="6" t="inlineStr">
+        <is>
+          <t>Dodávka + osazení řídicí jednotka UET 15D pro Dalap</t>
+        </is>
+      </c>
+      <c r="G214" s="4" t="inlineStr">
+        <is>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="H214" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I214" s="6" t="inlineStr">
+        <is>
+          <t>4 ks  [TZ:8, document:UT_HalaHK_TZ_DPS.doc, document:UT_HalaHK_TZ_VM_DPS_E.pdf]</t>
+        </is>
+      </c>
+      <c r="J214" s="6" t="inlineStr"/>
     </row>
     <row r="215">
-      <c r="A215" s="4" t="n">
-        <v>135</v>
-      </c>
-      <c r="B215" s="5" t="inlineStr"/>
-      <c r="C215" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="D215" s="5" t="inlineStr">
-        <is>
-          <t>VRN</t>
-        </is>
-      </c>
-      <c r="E215" s="5" t="inlineStr">
-        <is>
-          <t>VRN-015</t>
-        </is>
-      </c>
-      <c r="F215" s="6" t="inlineStr">
-        <is>
-          <t>Geodetické zaměření skutečného provedení (DSPS) — po dokončení stavby</t>
-        </is>
-      </c>
-      <c r="G215" s="4" t="inlineStr">
-        <is>
-          <t>paušál</t>
-        </is>
-      </c>
-      <c r="H215" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I215" s="6" t="inlineStr">
-        <is>
-          <t>paušál</t>
-        </is>
-      </c>
-      <c r="J215" s="6" t="inlineStr"/>
+      <c r="A215" s="10" t="n">
+        <v>136</v>
+      </c>
+      <c r="B215" s="11" t="inlineStr"/>
+      <c r="C215" s="10" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="D215" s="11" t="inlineStr">
+        <is>
+          <t>M-UT</t>
+        </is>
+      </c>
+      <c r="E215" s="11" t="inlineStr">
+        <is>
+          <t>M-UT-007</t>
+        </is>
+      </c>
+      <c r="F215" s="12" t="inlineStr">
+        <is>
+          <t>Dodávka + osazení prostorový termostat</t>
+        </is>
+      </c>
+      <c r="G215" s="10" t="inlineStr">
+        <is>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="H215" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="I215" s="12" t="inlineStr">
+        <is>
+          <t>4 + 4 = 8 ks  [TZ:8, document:UT_HalaHK_TZ_DPS.doc, document:UT_HalaHK_TZ_VM_DPS_E.pdf]</t>
+        </is>
+      </c>
+      <c r="J215" s="12" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" s="3" t="inlineStr">
         <is>
+          <t>→ Pomocný montážní + kotevní materiál ÚT</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="4" t="n">
+        <v>137</v>
+      </c>
+      <c r="B217" s="5" t="inlineStr"/>
+      <c r="C217" s="4" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="D217" s="5" t="inlineStr">
+        <is>
+          <t>M-UT</t>
+        </is>
+      </c>
+      <c r="E217" s="5" t="inlineStr">
+        <is>
+          <t>M-UT-008</t>
+        </is>
+      </c>
+      <c r="F217" s="6" t="inlineStr">
+        <is>
+          <t>Pomocný montážní + kotevní materiál ÚT</t>
+        </is>
+      </c>
+      <c r="G217" s="4" t="inlineStr">
+        <is>
+          <t>soubor</t>
+        </is>
+      </c>
+      <c r="H217" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I217" s="6" t="inlineStr">
+        <is>
+          <t>1 soubor  [TZ:8, document:UT_HalaHK_TZ_DPS.doc, document:UT_HalaHK_TZ_VM_DPS_E.pdf]</t>
+        </is>
+      </c>
+      <c r="J217" s="6" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="3" t="inlineStr">
+        <is>
+          <t>→ Funkční zkouška + nastavení systému vytápění</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="4" t="n">
+        <v>138</v>
+      </c>
+      <c r="B219" s="5" t="inlineStr"/>
+      <c r="C219" s="4" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="D219" s="5" t="inlineStr">
+        <is>
+          <t>M-UT</t>
+        </is>
+      </c>
+      <c r="E219" s="5" t="inlineStr">
+        <is>
+          <t>M-UT-010</t>
+        </is>
+      </c>
+      <c r="F219" s="6" t="inlineStr">
+        <is>
+          <t>Funkční zkouška + nastavení systému vytápění</t>
+        </is>
+      </c>
+      <c r="G219" s="4" t="inlineStr">
+        <is>
+          <t>soubor</t>
+        </is>
+      </c>
+      <c r="H219" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I219" s="6" t="inlineStr">
+        <is>
+          <t>1 soubor  [TZ:8, document:UT_HalaHK_TZ_DPS.doc, document:UT_HalaHK_TZ_VM_DPS_E.pdf]</t>
+        </is>
+      </c>
+      <c r="J219" s="6" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="3" t="inlineStr">
+        <is>
+          <t>→ Předání dokumentace + zaškolení obsluhy ÚT</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="4" t="n">
+        <v>139</v>
+      </c>
+      <c r="B221" s="5" t="inlineStr"/>
+      <c r="C221" s="4" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="D221" s="5" t="inlineStr">
+        <is>
+          <t>M-UT</t>
+        </is>
+      </c>
+      <c r="E221" s="5" t="inlineStr">
+        <is>
+          <t>M-UT-011</t>
+        </is>
+      </c>
+      <c r="F221" s="6" t="inlineStr">
+        <is>
+          <t>Předání dokumentace + zaškolení obsluhy</t>
+        </is>
+      </c>
+      <c r="G221" s="4" t="inlineStr">
+        <is>
+          <t>soubor</t>
+        </is>
+      </c>
+      <c r="H221" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I221" s="6" t="inlineStr">
+        <is>
+          <t>1 soubor  [TZ:8, document:UT_HalaHK_TZ_DPS.doc, document:UT_HalaHK_TZ_VM_DPS_E.pdf]</t>
+        </is>
+      </c>
+      <c r="J221" s="6" t="inlineStr"/>
+    </row>
+    <row r="222" ht="22" customHeight="1">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>═══ FÁZE 10: OSTATNÍ + PŘESUN HMOT ═══</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="3" t="inlineStr">
+        <is>
+          <t>→ Přesun hmot HSV vodorovně</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="4" t="n">
+        <v>140</v>
+      </c>
+      <c r="B224" s="5" t="inlineStr"/>
+      <c r="C224" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D224" s="5" t="inlineStr">
+        <is>
+          <t>HSV-9</t>
+        </is>
+      </c>
+      <c r="E224" s="5" t="inlineStr">
+        <is>
+          <t>HSV-9-001</t>
+        </is>
+      </c>
+      <c r="F224" s="6" t="inlineStr">
+        <is>
+          <t>Přesun hmot HSV vodorovně — beton, výztuž, ocel, klempířina</t>
+        </is>
+      </c>
+      <c r="G224" s="4" t="inlineStr">
+        <is>
+          <t>t·km</t>
+        </is>
+      </c>
+      <c r="H224" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="I224" s="6" t="inlineStr">
+        <is>
+          <t>placeholder 200 t·km (in-site přesuny, default)</t>
+        </is>
+      </c>
+      <c r="J224" s="6" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="3" t="inlineStr">
+        <is>
+          <t>→ Doprava materiálu na stavbu — paušál</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="4" t="n">
+        <v>141</v>
+      </c>
+      <c r="B226" s="5" t="inlineStr"/>
+      <c r="C226" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D226" s="5" t="inlineStr">
+        <is>
+          <t>VRN</t>
+        </is>
+      </c>
+      <c r="E226" s="5" t="inlineStr">
+        <is>
+          <t>VRN-013</t>
+        </is>
+      </c>
+      <c r="F226" s="6" t="inlineStr">
+        <is>
+          <t>Doprava materiálu na stavbu vodorovně — paušál pro veškerou montáž</t>
+        </is>
+      </c>
+      <c r="G226" s="4" t="inlineStr">
+        <is>
+          <t>t·km</t>
+        </is>
+      </c>
+      <c r="H226" s="4" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I226" s="6" t="inlineStr">
+        <is>
+          <t>placeholder ~1500 t·km (30 t materiálů × 50 km)</t>
+        </is>
+      </c>
+      <c r="J226" s="6" t="inlineStr"/>
+    </row>
+    <row r="227" ht="22" customHeight="1">
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>═══ FÁZE 11: DOKONČENÍ + REVIZE + ODEVZDÁNÍ ═══</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="3" t="inlineStr">
+        <is>
+          <t>→ Revize TZB (elektro, hydrant, hromosvod)</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="7" t="n">
+        <v>142</v>
+      </c>
+      <c r="B229" s="8" t="inlineStr"/>
+      <c r="C229" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="D229" s="8" t="inlineStr">
+        <is>
+          <t>VRN</t>
+        </is>
+      </c>
+      <c r="E229" s="8" t="inlineStr">
+        <is>
+          <t>VRN-020</t>
+        </is>
+      </c>
+      <c r="F229" s="9" t="inlineStr">
+        <is>
+          <t>Revize elektroinstalace + protokol</t>
+        </is>
+      </c>
+      <c r="G229" s="7" t="inlineStr">
+        <is>
+          <t>paušál</t>
+        </is>
+      </c>
+      <c r="H229" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I229" s="9" t="inlineStr">
+        <is>
+          <t>paušál (Rožmitál 00523 R precedent)  [csn]</t>
+        </is>
+      </c>
+      <c r="J229" s="9" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="7" t="n">
+        <v>143</v>
+      </c>
+      <c r="B230" s="8" t="inlineStr"/>
+      <c r="C230" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="D230" s="8" t="inlineStr">
+        <is>
+          <t>VRN</t>
+        </is>
+      </c>
+      <c r="E230" s="8" t="inlineStr">
+        <is>
+          <t>VRN-021</t>
+        </is>
+      </c>
+      <c r="F230" s="9" t="inlineStr">
+        <is>
+          <t>Revize hydrantového systému + tlaková zkouška</t>
+        </is>
+      </c>
+      <c r="G230" s="7" t="inlineStr">
+        <is>
+          <t>paušál</t>
+        </is>
+      </c>
+      <c r="H230" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I230" s="9" t="inlineStr">
+        <is>
+          <t>paušál  [csn]</t>
+        </is>
+      </c>
+      <c r="J230" s="9" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="7" t="n">
+        <v>144</v>
+      </c>
+      <c r="B231" s="8" t="inlineStr"/>
+      <c r="C231" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="D231" s="8" t="inlineStr">
+        <is>
+          <t>VRN</t>
+        </is>
+      </c>
+      <c r="E231" s="8" t="inlineStr">
+        <is>
+          <t>VRN-022</t>
+        </is>
+      </c>
+      <c r="F231" s="9" t="inlineStr">
+        <is>
+          <t>Revize hromosvodu / LPS — měření ekvipotenciality, zemniče, svody</t>
+        </is>
+      </c>
+      <c r="G231" s="7" t="inlineStr">
+        <is>
+          <t>paušál</t>
+        </is>
+      </c>
+      <c r="H231" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I231" s="9" t="inlineStr">
+        <is>
+          <t>paušál  [csn]</t>
+        </is>
+      </c>
+      <c r="J231" s="9" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="3" t="inlineStr">
+        <is>
+          <t>→ Likvidace odpadů O + N</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="4" t="n">
+        <v>145</v>
+      </c>
+      <c r="B233" s="5" t="inlineStr"/>
+      <c r="C233" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="D233" s="5" t="inlineStr">
+        <is>
+          <t>VRN</t>
+        </is>
+      </c>
+      <c r="E233" s="5" t="inlineStr">
+        <is>
+          <t>VRN-011</t>
+        </is>
+      </c>
+      <c r="F233" s="6" t="inlineStr">
+        <is>
+          <t>Likvidace odpadů kategorie O (běžný) — kontejner + odvoz + skládkovné</t>
+        </is>
+      </c>
+      <c r="G233" s="4" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="H233" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="I233" s="6" t="inlineStr">
+        <is>
+          <t>placeholder ~30 m³ stavebního odpadu kat. O</t>
+        </is>
+      </c>
+      <c r="J233" s="6" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="7" t="n">
+        <v>146</v>
+      </c>
+      <c r="B234" s="8" t="inlineStr"/>
+      <c r="C234" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="D234" s="8" t="inlineStr">
+        <is>
+          <t>VRN</t>
+        </is>
+      </c>
+      <c r="E234" s="8" t="inlineStr">
+        <is>
+          <t>VRN-012</t>
+        </is>
+      </c>
+      <c r="F234" s="9" t="inlineStr">
+        <is>
+          <t>Likvidace odpadů kategorie N (nebezpečné — barvy, oleje, tmely)</t>
+        </is>
+      </c>
+      <c r="G234" s="7" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="H234" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I234" s="9" t="inlineStr">
+        <is>
+          <t>placeholder ~2 m³ kat. N</t>
+        </is>
+      </c>
+      <c r="J234" s="9" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="3" t="inlineStr">
+        <is>
+          <t>→ Geodetické zaměření DSPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="4" t="n">
+        <v>147</v>
+      </c>
+      <c r="B236" s="5" t="inlineStr"/>
+      <c r="C236" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="D236" s="5" t="inlineStr">
+        <is>
+          <t>VRN</t>
+        </is>
+      </c>
+      <c r="E236" s="5" t="inlineStr">
+        <is>
+          <t>VRN-015</t>
+        </is>
+      </c>
+      <c r="F236" s="6" t="inlineStr">
+        <is>
+          <t>Geodetické zaměření skutečného provedení (DSPS) — po dokončení stavby</t>
+        </is>
+      </c>
+      <c r="G236" s="4" t="inlineStr">
+        <is>
+          <t>paušál</t>
+        </is>
+      </c>
+      <c r="H236" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I236" s="6" t="inlineStr">
+        <is>
+          <t>paušál</t>
+        </is>
+      </c>
+      <c r="J236" s="6" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="3" t="inlineStr">
+        <is>
           <t>→ Předávací protokoly + kolaudace</t>
         </is>
       </c>
     </row>
-    <row r="217">
-      <c r="A217" s="7" t="n">
-        <v>136</v>
-      </c>
-      <c r="B217" s="8" t="inlineStr"/>
-      <c r="C217" s="7" t="n">
+    <row r="238">
+      <c r="A238" s="7" t="n">
+        <v>148</v>
+      </c>
+      <c r="B238" s="8" t="inlineStr"/>
+      <c r="C238" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="D217" s="8" t="inlineStr">
+      <c r="D238" s="8" t="inlineStr">
         <is>
           <t>VRN</t>
         </is>
       </c>
-      <c r="E217" s="8" t="inlineStr">
+      <c r="E238" s="8" t="inlineStr">
         <is>
           <t>VRN-018</t>
         </is>
       </c>
-      <c r="F217" s="9" t="inlineStr">
+      <c r="F238" s="9" t="inlineStr">
         <is>
           <t>Předávací protokoly + dokumentace skutečného provedení (DSPS)</t>
         </is>
       </c>
-      <c r="G217" s="7" t="inlineStr">
+      <c r="G238" s="7" t="inlineStr">
         <is>
           <t>paušál</t>
         </is>
       </c>
-      <c r="H217" s="7" t="n">
+      <c r="H238" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="I217" s="9" t="inlineStr">
+      <c r="I238" s="9" t="inlineStr">
         <is>
           <t>paušál</t>
         </is>
       </c>
-      <c r="J217" s="9" t="inlineStr"/>
-    </row>
-    <row r="218">
-      <c r="A218" s="7" t="n">
-        <v>137</v>
-      </c>
-      <c r="B218" s="8" t="inlineStr"/>
-      <c r="C218" s="7" t="n">
+      <c r="J238" s="9" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="7" t="n">
+        <v>149</v>
+      </c>
+      <c r="B239" s="8" t="inlineStr"/>
+      <c r="C239" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="D218" s="8" t="inlineStr">
+      <c r="D239" s="8" t="inlineStr">
         <is>
           <t>VRN</t>
         </is>
       </c>
-      <c r="E218" s="8" t="inlineStr">
+      <c r="E239" s="8" t="inlineStr">
         <is>
           <t>VRN-019</t>
         </is>
       </c>
-      <c r="F218" s="9" t="inlineStr">
+      <c r="F239" s="9" t="inlineStr">
         <is>
           <t>Kolaudační řízení — příprava + účast na jednání + revize dokumentace</t>
         </is>
       </c>
-      <c r="G218" s="7" t="inlineStr">
+      <c r="G239" s="7" t="inlineStr">
         <is>
           <t>paušál</t>
         </is>
       </c>
-      <c r="H218" s="7" t="n">
+      <c r="H239" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="I218" s="9" t="inlineStr">
+      <c r="I239" s="9" t="inlineStr">
         <is>
           <t>paušál</t>
         </is>
       </c>
-      <c r="J218" s="9" t="inlineStr"/>
-    </row>
-    <row r="219">
-      <c r="A219" s="3" t="inlineStr">
+      <c r="J239" s="9" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="3" t="inlineStr">
         <is>
           <t>→ Náhradní výsadba dřevin (po dokončení)</t>
         </is>
       </c>
     </row>
-    <row r="220">
-      <c r="A220" s="4" t="n">
-        <v>138</v>
-      </c>
-      <c r="B220" s="5" t="inlineStr"/>
-      <c r="C220" s="4" t="n">
+    <row r="241">
+      <c r="A241" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="B241" s="5" t="inlineStr"/>
+      <c r="C241" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="D220" s="5" t="inlineStr">
+      <c r="D241" s="5" t="inlineStr">
         <is>
           <t>HSV-1</t>
         </is>
       </c>
-      <c r="E220" s="5" t="inlineStr">
+      <c r="E241" s="5" t="inlineStr">
         <is>
           <t>HSV-1-024</t>
         </is>
       </c>
-      <c r="F220" s="6" t="inlineStr">
+      <c r="F241" s="6" t="inlineStr">
         <is>
           <t>Náhradní výsadba dřevin per rozhodnutí orgánu životního prostředí</t>
         </is>
       </c>
-      <c r="G220" s="4" t="inlineStr">
+      <c r="G241" s="4" t="inlineStr">
         <is>
           <t>ks</t>
         </is>
       </c>
-      <c r="H220" s="4" t="n">
+      <c r="H241" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="I220" s="6" t="inlineStr">
+      <c r="I241" s="6" t="inlineStr">
         <is>
           <t>2 ks (per TZ B m.7.b náhradní výsadba)  [TZ:7.b]</t>
         </is>
       </c>
-      <c r="J220" s="6" t="inlineStr"/>
+      <c r="J241" s="6" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="81">
+  <mergeCells count="90">
     <mergeCell ref="A181:J181"/>
     <mergeCell ref="A184:J184"/>
     <mergeCell ref="A156:J156"/>
     <mergeCell ref="A171:J171"/>
     <mergeCell ref="A52:J52"/>
     <mergeCell ref="A165:J165"/>
+    <mergeCell ref="A220:J220"/>
     <mergeCell ref="A34:J34"/>
     <mergeCell ref="A83:J83"/>
+    <mergeCell ref="A222:J222"/>
     <mergeCell ref="A49:J49"/>
     <mergeCell ref="A138:J138"/>
     <mergeCell ref="A132:J132"/>
@@ -6518,25 +7039,26 @@
     <mergeCell ref="A95:J95"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A159:J159"/>
-    <mergeCell ref="A219:J219"/>
     <mergeCell ref="A29:J29"/>
     <mergeCell ref="A96:J96"/>
     <mergeCell ref="A147:J147"/>
     <mergeCell ref="A121:J121"/>
     <mergeCell ref="A202:J202"/>
     <mergeCell ref="A58:J58"/>
-    <mergeCell ref="A211:J211"/>
     <mergeCell ref="A186:J186"/>
     <mergeCell ref="A24:J24"/>
     <mergeCell ref="A201:J201"/>
     <mergeCell ref="A197:J197"/>
     <mergeCell ref="A110:J110"/>
+    <mergeCell ref="A228:J228"/>
     <mergeCell ref="A124:J124"/>
+    <mergeCell ref="A237:J237"/>
     <mergeCell ref="A16:J16"/>
-    <mergeCell ref="A214:J214"/>
+    <mergeCell ref="A223:J223"/>
     <mergeCell ref="A204:J204"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A42:J42"/>
+    <mergeCell ref="A213:J213"/>
     <mergeCell ref="A151:J151"/>
     <mergeCell ref="A22:J22"/>
     <mergeCell ref="A135:J135"/>
@@ -6551,9 +7073,11 @@
     <mergeCell ref="A182:J182"/>
     <mergeCell ref="A98:J98"/>
     <mergeCell ref="A191:J191"/>
+    <mergeCell ref="A225:J225"/>
     <mergeCell ref="A70:J70"/>
     <mergeCell ref="A153:J153"/>
     <mergeCell ref="A162:J162"/>
+    <mergeCell ref="A227:J227"/>
     <mergeCell ref="A164:J164"/>
     <mergeCell ref="A145:J145"/>
     <mergeCell ref="A195:J195"/>
@@ -6566,20 +7090,24 @@
     <mergeCell ref="A126:J126"/>
     <mergeCell ref="A100:J100"/>
     <mergeCell ref="A140:J140"/>
+    <mergeCell ref="A240:J240"/>
     <mergeCell ref="A10:J10"/>
     <mergeCell ref="A19:J19"/>
     <mergeCell ref="A68:J68"/>
     <mergeCell ref="A102:J102"/>
     <mergeCell ref="A39:J39"/>
+    <mergeCell ref="A232:J232"/>
     <mergeCell ref="A142:J142"/>
-    <mergeCell ref="A207:J207"/>
     <mergeCell ref="A216:J216"/>
     <mergeCell ref="A65:J65"/>
+    <mergeCell ref="A218:J218"/>
     <mergeCell ref="A193:J193"/>
     <mergeCell ref="A80:J80"/>
     <mergeCell ref="A46:J46"/>
     <mergeCell ref="A89:J89"/>
     <mergeCell ref="A57:J57"/>
+    <mergeCell ref="A235:J235"/>
+    <mergeCell ref="A210:J210"/>
     <mergeCell ref="A129:J129"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/test-data/hk212_hala/outputs/sequential_list/hk212_sequential_list.xlsx
+++ b/test-data/hk212_hala/outputs/sequential_list/hk212_sequential_list.xlsx
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J241"/>
+  <dimension ref="A1:J271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7017,8 +7017,815 @@
       </c>
       <c r="J241" s="6" t="inlineStr"/>
     </row>
+    <row r="242" ht="22" customHeight="1">
+      <c r="A242" s="2" t="inlineStr">
+        <is>
+          <t>═══ FÁZE 12: VENKOVNÍ ÚPRAVY (SO-13) ═══</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="3" t="inlineStr">
+        <is>
+          <t>→ Externí přípojky — výkop + potrubí (paralelně se ZS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="4" t="n">
+        <v>151</v>
+      </c>
+      <c r="B244" s="5" t="inlineStr"/>
+      <c r="C244" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D244" s="5" t="inlineStr">
+        <is>
+          <t>M-VK</t>
+        </is>
+      </c>
+      <c r="E244" s="5" t="inlineStr">
+        <is>
+          <t>M-VK-005</t>
+        </is>
+      </c>
+      <c r="F244" s="6" t="inlineStr">
+        <is>
+          <t>Přípojka kanalizace dešťové KG PVC SN8 DN200 — potrubí + uložení v pískovém loži + zásyp + napojení</t>
+        </is>
+      </c>
+      <c r="G244" s="4" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="H244" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="I244" s="6" t="inlineStr">
+        <is>
+          <t>40 m  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
+        </is>
+      </c>
+      <c r="J244" s="6" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="10" t="n">
+        <v>152</v>
+      </c>
+      <c r="B245" s="11" t="inlineStr"/>
+      <c r="C245" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D245" s="11" t="inlineStr">
+        <is>
+          <t>M-VK</t>
+        </is>
+      </c>
+      <c r="E245" s="11" t="inlineStr">
+        <is>
+          <t>M-VK-006</t>
+        </is>
+      </c>
+      <c r="F245" s="12" t="inlineStr">
+        <is>
+          <t>Přípojka kanalizace splaškové KG PVC SN8 DN150 — potrubí + uložení + zásyp + napojení</t>
+        </is>
+      </c>
+      <c r="G245" s="10" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="H245" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="I245" s="12" t="inlineStr">
+        <is>
+          <t>30 m  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
+        </is>
+      </c>
+      <c r="J245" s="12" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="4" t="n">
+        <v>153</v>
+      </c>
+      <c r="B246" s="5" t="inlineStr"/>
+      <c r="C246" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D246" s="5" t="inlineStr">
+        <is>
+          <t>M-VK</t>
+        </is>
+      </c>
+      <c r="E246" s="5" t="inlineStr">
+        <is>
+          <t>M-VK-008</t>
+        </is>
+      </c>
+      <c r="F246" s="6" t="inlineStr">
+        <is>
+          <t>Přípojka NN — chránička HDPE Ø110 mm + pomocné výkopy + pískové lože + zásyp + výstražná páska</t>
+        </is>
+      </c>
+      <c r="G246" s="4" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="H246" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="I246" s="6" t="inlineStr">
+        <is>
+          <t>40 m  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
+        </is>
+      </c>
+      <c r="J246" s="6" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="10" t="n">
+        <v>154</v>
+      </c>
+      <c r="B247" s="11" t="inlineStr"/>
+      <c r="C247" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D247" s="11" t="inlineStr">
+        <is>
+          <t>M-VK</t>
+        </is>
+      </c>
+      <c r="E247" s="11" t="inlineStr">
+        <is>
+          <t>M-VK-007</t>
+        </is>
+      </c>
+      <c r="F247" s="12" t="inlineStr">
+        <is>
+          <t>Revizní šachta betonová Ø1000 mm, h ~1.5-2.0 m, vč. poklopu litinového B125 a vnitřních stupadel</t>
+        </is>
+      </c>
+      <c r="G247" s="10" t="inlineStr">
+        <is>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="H247" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I247" s="12" t="inlineStr">
+        <is>
+          <t>3 ks  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
+        </is>
+      </c>
+      <c r="J247" s="12" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="3" t="inlineStr">
+        <is>
+          <t>→ Přeložka vodovodního řadu (PODMÍNĚNÁ — pending ABMV_23)</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="7" t="n">
+        <v>155</v>
+      </c>
+      <c r="B249" s="8" t="inlineStr"/>
+      <c r="C249" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="D249" s="8" t="inlineStr">
+        <is>
+          <t>M-VK</t>
+        </is>
+      </c>
+      <c r="E249" s="8" t="inlineStr">
+        <is>
+          <t>M-VK-009</t>
+        </is>
+      </c>
+      <c r="F249" s="9" t="inlineStr">
+        <is>
+          <t>Přeložka stávajícího vodovodního řadu (rerouting) — kompletní práce vč. potrubí, výkop, napojení, tlakové zkoušky</t>
+        </is>
+      </c>
+      <c r="G249" s="7" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="H249" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I249" s="9" t="inlineStr">
+        <is>
+          <t>1 kpl  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
+        </is>
+      </c>
+      <c r="J249" s="9" t="inlineStr">
+        <is>
+          <t>ABMV:ABMV_23</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="3" t="inlineStr">
+        <is>
+          <t>→ Retenční nádrž 30 m³ prefab betonová (pending ABMV_24)</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="4" t="n">
+        <v>156</v>
+      </c>
+      <c r="B251" s="5" t="inlineStr"/>
+      <c r="C251" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D251" s="5" t="inlineStr">
+        <is>
+          <t>M-VK</t>
+        </is>
+      </c>
+      <c r="E251" s="5" t="inlineStr">
+        <is>
+          <t>M-VK-011</t>
+        </is>
+      </c>
+      <c r="F251" s="6" t="inlineStr">
+        <is>
+          <t>Retenční nádrž 30 m³ — prefabrikovaná betonová, rozměry 6.15×2.75×2.0 m, vč. usazení do připraveného výkopu a napojení na dešťovou kanalizaci</t>
+        </is>
+      </c>
+      <c r="G251" s="4" t="inlineStr">
+        <is>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="H251" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I251" s="6" t="inlineStr">
+        <is>
+          <t>1 ks prefab  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
+        </is>
+      </c>
+      <c r="J251" s="6" t="inlineStr">
+        <is>
+          <t>ABMV:ABMV_24</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="3" t="inlineStr">
+        <is>
+          <t>→ Hydrant podzemní DN80 + napojení</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="4" t="n">
+        <v>157</v>
+      </c>
+      <c r="B253" s="5" t="inlineStr"/>
+      <c r="C253" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D253" s="5" t="inlineStr">
+        <is>
+          <t>M-VK</t>
+        </is>
+      </c>
+      <c r="E253" s="5" t="inlineStr">
+        <is>
+          <t>M-VK-010</t>
+        </is>
+      </c>
+      <c r="F253" s="6" t="inlineStr">
+        <is>
+          <t>Hydrant podzemní DN80 vč. uzávěru, šoupátka, zemní soupravy, poklopu litinového a napojení na vodovodní řad</t>
+        </is>
+      </c>
+      <c r="G253" s="4" t="inlineStr">
+        <is>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="H253" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I253" s="6" t="inlineStr">
+        <is>
+          <t>1 ks  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
+        </is>
+      </c>
+      <c r="J253" s="6" t="inlineStr"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="3" t="inlineStr">
+        <is>
+          <t>→ Rampy 4× (R1-R4) — podklad ŠD + výztuž + bednění + beton + obrubník</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="4" t="n">
+        <v>158</v>
+      </c>
+      <c r="B255" s="5" t="inlineStr"/>
+      <c r="C255" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D255" s="5" t="inlineStr">
+        <is>
+          <t>M-VK</t>
+        </is>
+      </c>
+      <c r="E255" s="5" t="inlineStr">
+        <is>
+          <t>M-VK-003</t>
+        </is>
+      </c>
+      <c r="F255" s="6" t="inlineStr">
+        <is>
+          <t>Drcený štěrk ŠD 32/63 podklad rampy + okapní pas tl 200 mm</t>
+        </is>
+      </c>
+      <c r="G255" s="4" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="H255" s="4" t="n">
+        <v>8.66</v>
+      </c>
+      <c r="I255" s="6" t="inlineStr">
+        <is>
+          <t>43.32 × 0.20 = 8.66 m³  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
+        </is>
+      </c>
+      <c r="J255" s="6" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="A256" s="10" t="n">
+        <v>159</v>
+      </c>
+      <c r="B256" s="11" t="inlineStr"/>
+      <c r="C256" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D256" s="11" t="inlineStr">
+        <is>
+          <t>M-VK</t>
+        </is>
+      </c>
+      <c r="E256" s="11" t="inlineStr">
+        <is>
+          <t>M-VK-002</t>
+        </is>
+      </c>
+      <c r="F256" s="12" t="inlineStr">
+        <is>
+          <t>Výztuž KARI síť Q188 + bednění boční rampy 4 lokality</t>
+        </is>
+      </c>
+      <c r="G256" s="10" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="H256" s="10" t="n">
+        <v>43.32</v>
+      </c>
+      <c r="I256" s="12" t="inlineStr">
+        <is>
+          <t>4 lokality rampy = 43.32 m²  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
+        </is>
+      </c>
+      <c r="J256" s="12" t="inlineStr"/>
+    </row>
+    <row r="257">
+      <c r="A257" s="4" t="n">
+        <v>160</v>
+      </c>
+      <c r="B257" s="5" t="inlineStr"/>
+      <c r="C257" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D257" s="5" t="inlineStr">
+        <is>
+          <t>M-VK</t>
+        </is>
+      </c>
+      <c r="E257" s="5" t="inlineStr">
+        <is>
+          <t>M-VK-001</t>
+        </is>
+      </c>
+      <c r="F257" s="6" t="inlineStr">
+        <is>
+          <t>Beton C25/30 XF3 — vstupní/nájezdové rampy tl 150 mm, 4 lokality (R1 sever, R2+R3 jih, R4 západ bezbariérová)</t>
+        </is>
+      </c>
+      <c r="G257" s="4" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="H257" s="4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I257" s="6" t="inlineStr">
+        <is>
+          <t>(9.2+11.5+9.2+13.42) × 0.15 = 6.50 m³  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
+        </is>
+      </c>
+      <c r="J257" s="6" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="10" t="n">
+        <v>161</v>
+      </c>
+      <c r="B258" s="11" t="inlineStr"/>
+      <c r="C258" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D258" s="11" t="inlineStr">
+        <is>
+          <t>M-VK</t>
+        </is>
+      </c>
+      <c r="E258" s="11" t="inlineStr">
+        <is>
+          <t>M-VK-004</t>
+        </is>
+      </c>
+      <c r="F258" s="12" t="inlineStr">
+        <is>
+          <t>Obrubník betonový ABO 100×250×1000 kolem ramp + lůžko z betonu C16/20</t>
+        </is>
+      </c>
+      <c r="G258" s="10" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="H258" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="I258" s="12" t="inlineStr">
+        <is>
+          <t>~30.0 m  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
+        </is>
+      </c>
+      <c r="J258" s="12" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="3" t="inlineStr">
+        <is>
+          <t>→ Zpevněné plochy — podklad ŠD + asfalt + obrubník + napojení</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="4" t="n">
+        <v>162</v>
+      </c>
+      <c r="B260" s="5" t="inlineStr"/>
+      <c r="C260" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D260" s="5" t="inlineStr">
+        <is>
+          <t>M-VK</t>
+        </is>
+      </c>
+      <c r="E260" s="5" t="inlineStr">
+        <is>
+          <t>M-VK-013</t>
+        </is>
+      </c>
+      <c r="F260" s="6" t="inlineStr">
+        <is>
+          <t>Drcené kamenivo ŠD 32/63 podklad zpevněných ploch tl 200 mm</t>
+        </is>
+      </c>
+      <c r="G260" s="4" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="H260" s="4" t="n">
+        <v>65</v>
+      </c>
+      <c r="I260" s="6" t="inlineStr">
+        <is>
+          <t>325.0 × 0.20 = 65.0 m³  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
+        </is>
+      </c>
+      <c r="J260" s="6" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" s="10" t="n">
+        <v>163</v>
+      </c>
+      <c r="B261" s="11" t="inlineStr"/>
+      <c r="C261" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D261" s="11" t="inlineStr">
+        <is>
+          <t>M-VK</t>
+        </is>
+      </c>
+      <c r="E261" s="11" t="inlineStr">
+        <is>
+          <t>M-VK-014</t>
+        </is>
+      </c>
+      <c r="F261" s="12" t="inlineStr">
+        <is>
+          <t>Asfaltový beton ACO 11+ tl 50 mm obrusná vrstva — parkoviště + manipulace</t>
+        </is>
+      </c>
+      <c r="G261" s="10" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="H261" s="10" t="n">
+        <v>325</v>
+      </c>
+      <c r="I261" s="12" t="inlineStr">
+        <is>
+          <t>125.0+150.0+50.0 = 325.0 m²  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
+        </is>
+      </c>
+      <c r="J261" s="12" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="A262" s="4" t="n">
+        <v>164</v>
+      </c>
+      <c r="B262" s="5" t="inlineStr"/>
+      <c r="C262" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D262" s="5" t="inlineStr">
+        <is>
+          <t>M-VK</t>
+        </is>
+      </c>
+      <c r="E262" s="5" t="inlineStr">
+        <is>
+          <t>M-VK-015</t>
+        </is>
+      </c>
+      <c r="F262" s="6" t="inlineStr">
+        <is>
+          <t>Obrubník betonový silniční ABO 100×250×1000 mm + lůžko z betonu C16/20</t>
+        </is>
+      </c>
+      <c r="G262" s="4" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="H262" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="I262" s="6" t="inlineStr">
+        <is>
+          <t>~90.0 m  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
+        </is>
+      </c>
+      <c r="J262" s="6" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="10" t="n">
+        <v>165</v>
+      </c>
+      <c r="B263" s="11" t="inlineStr"/>
+      <c r="C263" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D263" s="11" t="inlineStr">
+        <is>
+          <t>M-VK</t>
+        </is>
+      </c>
+      <c r="E263" s="11" t="inlineStr">
+        <is>
+          <t>M-VK-017</t>
+        </is>
+      </c>
+      <c r="F263" s="12" t="inlineStr">
+        <is>
+          <t>Komunikační napojení na stávající vozovku — vč. úpravy navazujícího pásu asfaltu, frézování styčné spáry, zalévací zálivka</t>
+        </is>
+      </c>
+      <c r="G263" s="10" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="H263" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="I263" s="12" t="inlineStr">
+        <is>
+          <t>50.0 m²  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
+        </is>
+      </c>
+      <c r="J263" s="12" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="3" t="inlineStr">
+        <is>
+          <t>→ Liniový žlab pojízdný B125 — venkovní plochy</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="4" t="n">
+        <v>166</v>
+      </c>
+      <c r="B265" s="5" t="inlineStr"/>
+      <c r="C265" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D265" s="5" t="inlineStr">
+        <is>
+          <t>M-VK</t>
+        </is>
+      </c>
+      <c r="E265" s="5" t="inlineStr">
+        <is>
+          <t>M-VK-012</t>
+        </is>
+      </c>
+      <c r="F265" s="6" t="inlineStr">
+        <is>
+          <t>Liniový žlab POJÍZDNÝ tř. zatížení B125 — odvodnění zpevněných ploch parkoviště + manipulace, vč. mřížky</t>
+        </is>
+      </c>
+      <c r="G265" s="4" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="H265" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="I265" s="6" t="inlineStr">
+        <is>
+          <t>40 m  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
+        </is>
+      </c>
+      <c r="J265" s="6" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="3" t="inlineStr">
+        <is>
+          <t>→ Vodorovné značení 10× parkovacích stání</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="4" t="n">
+        <v>167</v>
+      </c>
+      <c r="B267" s="5" t="inlineStr"/>
+      <c r="C267" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D267" s="5" t="inlineStr">
+        <is>
+          <t>M-VK</t>
+        </is>
+      </c>
+      <c r="E267" s="5" t="inlineStr">
+        <is>
+          <t>M-VK-016</t>
+        </is>
+      </c>
+      <c r="F267" s="6" t="inlineStr">
+        <is>
+          <t>Vodorovné značení parkovacích stání — symbol P + krajní čáry, barva bílá nestripovaná retroflexní</t>
+        </is>
+      </c>
+      <c r="G267" s="4" t="inlineStr">
+        <is>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="H267" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="I267" s="6" t="inlineStr">
+        <is>
+          <t>10 ks  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
+        </is>
+      </c>
+      <c r="J267" s="6" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" s="3" t="inlineStr">
+        <is>
+          <t>→ Vyspádování okolního terénu k odvodnění</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="4" t="n">
+        <v>168</v>
+      </c>
+      <c r="B269" s="5" t="inlineStr"/>
+      <c r="C269" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D269" s="5" t="inlineStr">
+        <is>
+          <t>M-VK</t>
+        </is>
+      </c>
+      <c r="E269" s="5" t="inlineStr">
+        <is>
+          <t>M-VK-019</t>
+        </is>
+      </c>
+      <c r="F269" s="6" t="inlineStr">
+        <is>
+          <t>Vyspádování okolního terénu k odvodňovacím prvkům (žlabům, retenční nádrži) — hutněná zemina, finální úprava</t>
+        </is>
+      </c>
+      <c r="G269" s="4" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="H269" s="4" t="n">
+        <v>300</v>
+      </c>
+      <c r="I269" s="6" t="inlineStr">
+        <is>
+          <t>300 m²  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
+        </is>
+      </c>
+      <c r="J269" s="6" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="3" t="inlineStr">
+        <is>
+          <t>→ Ohumusování + osetí travou zbytkových ploch</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="4" t="n">
+        <v>169</v>
+      </c>
+      <c r="B271" s="5" t="inlineStr"/>
+      <c r="C271" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D271" s="5" t="inlineStr">
+        <is>
+          <t>M-VK</t>
+        </is>
+      </c>
+      <c r="E271" s="5" t="inlineStr">
+        <is>
+          <t>M-VK-018</t>
+        </is>
+      </c>
+      <c r="F271" s="6" t="inlineStr">
+        <is>
+          <t>Ohumusování tl 100 mm + osetí trávou parkové směsi — rekultivace zbytkových ploch okolo haly</t>
+        </is>
+      </c>
+      <c r="G271" s="4" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="H271" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="I271" s="6" t="inlineStr">
+        <is>
+          <t>500 m²  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
+        </is>
+      </c>
+      <c r="J271" s="6" t="inlineStr"/>
+    </row>
   </sheetData>
-  <mergeCells count="90">
+  <mergeCells count="101">
     <mergeCell ref="A181:J181"/>
     <mergeCell ref="A184:J184"/>
     <mergeCell ref="A156:J156"/>
@@ -7028,6 +7835,7 @@
     <mergeCell ref="A220:J220"/>
     <mergeCell ref="A34:J34"/>
     <mergeCell ref="A83:J83"/>
+    <mergeCell ref="A270:J270"/>
     <mergeCell ref="A222:J222"/>
     <mergeCell ref="A49:J49"/>
     <mergeCell ref="A138:J138"/>
@@ -7035,8 +7843,10 @@
     <mergeCell ref="A36:J36"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="A119:J119"/>
+    <mergeCell ref="A264:J264"/>
     <mergeCell ref="A3:J3"/>
     <mergeCell ref="A95:J95"/>
+    <mergeCell ref="A248:J248"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A159:J159"/>
     <mergeCell ref="A29:J29"/>
@@ -7048,18 +7858,23 @@
     <mergeCell ref="A186:J186"/>
     <mergeCell ref="A24:J24"/>
     <mergeCell ref="A201:J201"/>
+    <mergeCell ref="A266:J266"/>
+    <mergeCell ref="A250:J250"/>
     <mergeCell ref="A197:J197"/>
     <mergeCell ref="A110:J110"/>
     <mergeCell ref="A228:J228"/>
     <mergeCell ref="A124:J124"/>
     <mergeCell ref="A237:J237"/>
     <mergeCell ref="A16:J16"/>
+    <mergeCell ref="A243:J243"/>
+    <mergeCell ref="A252:J252"/>
     <mergeCell ref="A223:J223"/>
     <mergeCell ref="A204:J204"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A42:J42"/>
     <mergeCell ref="A213:J213"/>
     <mergeCell ref="A151:J151"/>
+    <mergeCell ref="A254:J254"/>
     <mergeCell ref="A22:J22"/>
     <mergeCell ref="A135:J135"/>
     <mergeCell ref="A206:J206"/>
@@ -7078,8 +7893,10 @@
     <mergeCell ref="A153:J153"/>
     <mergeCell ref="A162:J162"/>
     <mergeCell ref="A227:J227"/>
+    <mergeCell ref="A268:J268"/>
     <mergeCell ref="A164:J164"/>
     <mergeCell ref="A145:J145"/>
+    <mergeCell ref="A242:J242"/>
     <mergeCell ref="A195:J195"/>
     <mergeCell ref="A76:J76"/>
     <mergeCell ref="A33:J33"/>
@@ -7089,6 +7906,7 @@
     <mergeCell ref="A188:J188"/>
     <mergeCell ref="A126:J126"/>
     <mergeCell ref="A100:J100"/>
+    <mergeCell ref="A259:J259"/>
     <mergeCell ref="A140:J140"/>
     <mergeCell ref="A240:J240"/>
     <mergeCell ref="A10:J10"/>

--- a/test-data/hk212_hala/outputs/sequential_list/hk212_sequential_list.xlsx
+++ b/test-data/hk212_hala/outputs/sequential_list/hk212_sequential_list.xlsx
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J271"/>
+  <dimension ref="A1:J270"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7020,7 +7020,7 @@
     <row r="242" ht="22" customHeight="1">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>═══ FÁZE 12: VENKOVNÍ ÚPRAVY (SO-13) ═══</t>
+          <t>═══ FÁZE 12: VENKOVNÍ ÚPRAVY (SO-13) — minimal scope per user decision 2026-05-27 ═══</t>
         </is>
       </c>
     </row>
@@ -7329,7 +7329,7 @@
     <row r="254">
       <c r="A254" s="3" t="inlineStr">
         <is>
-          <t>→ Rampy 4× (R1-R4) — podklad ŠD + výztuž + bednění + beton + obrubník</t>
+          <t>→ Drcený štěrk podklady (rampy + okapní chodník)</t>
         </is>
       </c>
     </row>
@@ -7386,109 +7386,121 @@
       </c>
       <c r="E256" s="11" t="inlineStr">
         <is>
-          <t>M-VK-002</t>
+          <t>M-VK-022</t>
         </is>
       </c>
       <c r="F256" s="12" t="inlineStr">
         <is>
-          <t>Výztuž KARI síť Q188 + bednění boční rampy 4 lokality</t>
+          <t>Drcený štěrk ŠD 32/63 podklad okapního chodníku tl 150 mm</t>
         </is>
       </c>
       <c r="G256" s="10" t="inlineStr">
         <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="H256" s="10" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="I256" s="12" t="inlineStr">
+        <is>
+          <t>80.0 × 0.7 × 0.15 = 8.40 m³  [document:A103 řezy A-B detail, document:A101 půdorys 1NP, document:C.3 KOO situace]</t>
+        </is>
+      </c>
+      <c r="J256" s="12" t="inlineStr">
+        <is>
+          <t>ABMV:ABMV_31</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="3" t="inlineStr">
+        <is>
+          <t>→ Okapní chodník — sokl 0.7 m × 80 m po obvodu haly (beton + výztuž + dilatace, pending ABMV_31)</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="4" t="n">
+        <v>160</v>
+      </c>
+      <c r="B258" s="5" t="inlineStr"/>
+      <c r="C258" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D258" s="5" t="inlineStr">
+        <is>
+          <t>M-VK</t>
+        </is>
+      </c>
+      <c r="E258" s="5" t="inlineStr">
+        <is>
+          <t>M-VK-020</t>
+        </is>
+      </c>
+      <c r="F258" s="6" t="inlineStr">
+        <is>
+          <t>Beton C25/30 XF3 — okapní chodník po obvodu haly (sokl 0.7 m × ~80 m mimo 4 vstupy), tl 200 mm</t>
+        </is>
+      </c>
+      <c r="G258" s="4" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="H258" s="4" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="I258" s="6" t="inlineStr">
+        <is>
+          <t>80.0 × 0.7 × 0.2 = 11.20 m³  [document:A103 řezy A-B detail, document:A101 půdorys 1NP, document:C.3 KOO situace]</t>
+        </is>
+      </c>
+      <c r="J258" s="6" t="inlineStr">
+        <is>
+          <t>ABMV:ABMV_31</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="10" t="n">
+        <v>161</v>
+      </c>
+      <c r="B259" s="11" t="inlineStr"/>
+      <c r="C259" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D259" s="11" t="inlineStr">
+        <is>
+          <t>M-VK</t>
+        </is>
+      </c>
+      <c r="E259" s="11" t="inlineStr">
+        <is>
+          <t>M-VK-021</t>
+        </is>
+      </c>
+      <c r="F259" s="12" t="inlineStr">
+        <is>
+          <t>Výztuž KARI síť Q188 + boční bednění + dilatační lišty — okapní chodník</t>
+        </is>
+      </c>
+      <c r="G259" s="10" t="inlineStr">
+        <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="H256" s="10" t="n">
-        <v>43.32</v>
-      </c>
-      <c r="I256" s="12" t="inlineStr">
-        <is>
-          <t>4 lokality rampy = 43.32 m²  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
-        </is>
-      </c>
-      <c r="J256" s="12" t="inlineStr"/>
-    </row>
-    <row r="257">
-      <c r="A257" s="4" t="n">
-        <v>160</v>
-      </c>
-      <c r="B257" s="5" t="inlineStr"/>
-      <c r="C257" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="D257" s="5" t="inlineStr">
-        <is>
-          <t>M-VK</t>
-        </is>
-      </c>
-      <c r="E257" s="5" t="inlineStr">
-        <is>
-          <t>M-VK-001</t>
-        </is>
-      </c>
-      <c r="F257" s="6" t="inlineStr">
-        <is>
-          <t>Beton C25/30 XF3 — vstupní/nájezdové rampy tl 150 mm, 4 lokality (R1 sever, R2+R3 jih, R4 západ bezbariérová)</t>
-        </is>
-      </c>
-      <c r="G257" s="4" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="H257" s="4" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I257" s="6" t="inlineStr">
-        <is>
-          <t>(9.2+11.5+9.2+13.42) × 0.15 = 6.50 m³  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
-        </is>
-      </c>
-      <c r="J257" s="6" t="inlineStr"/>
-    </row>
-    <row r="258">
-      <c r="A258" s="10" t="n">
-        <v>161</v>
-      </c>
-      <c r="B258" s="11" t="inlineStr"/>
-      <c r="C258" s="10" t="n">
-        <v>12</v>
-      </c>
-      <c r="D258" s="11" t="inlineStr">
-        <is>
-          <t>M-VK</t>
-        </is>
-      </c>
-      <c r="E258" s="11" t="inlineStr">
-        <is>
-          <t>M-VK-004</t>
-        </is>
-      </c>
-      <c r="F258" s="12" t="inlineStr">
-        <is>
-          <t>Obrubník betonový ABO 100×250×1000 kolem ramp + lůžko z betonu C16/20</t>
-        </is>
-      </c>
-      <c r="G258" s="10" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="H258" s="10" t="n">
-        <v>30</v>
-      </c>
-      <c r="I258" s="12" t="inlineStr">
-        <is>
-          <t>~30.0 m  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
-        </is>
-      </c>
-      <c r="J258" s="12" t="inlineStr"/>
-    </row>
-    <row r="259">
-      <c r="A259" s="3" t="inlineStr">
-        <is>
-          <t>→ Zpevněné plochy — podklad ŠD + asfalt + obrubník + napojení</t>
+      <c r="H259" s="10" t="n">
+        <v>56</v>
+      </c>
+      <c r="I259" s="12" t="inlineStr">
+        <is>
+          <t>80.0 × 0.7 = 56.00 m²  [document:A103 řezy A-B detail, document:A101 půdorys 1NP, document:C.3 KOO situace]</t>
+        </is>
+      </c>
+      <c r="J259" s="12" t="inlineStr">
+        <is>
+          <t>ABMV:ABMV_31</t>
         </is>
       </c>
     </row>
@@ -7507,70 +7519,43 @@
       </c>
       <c r="E260" s="5" t="inlineStr">
         <is>
-          <t>M-VK-013</t>
+          <t>M-VK-023</t>
         </is>
       </c>
       <c r="F260" s="6" t="inlineStr">
         <is>
-          <t>Drcené kamenivo ŠD 32/63 podklad zpevněných ploch tl 200 mm</t>
+          <t>Dilatační lišty + těsnění spár mezi segmenty okapního chodníku (à ~4 m)</t>
         </is>
       </c>
       <c r="G260" s="4" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>m</t>
         </is>
       </c>
       <c r="H260" s="4" t="n">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="I260" s="6" t="inlineStr">
         <is>
-          <t>325.0 × 0.20 = 65.0 m³  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
-        </is>
-      </c>
-      <c r="J260" s="6" t="inlineStr"/>
+          <t>80.0 / 4 = 20 ks dilatací  [document:A103 řezy A-B detail, document:A101 půdorys 1NP, document:C.3 KOO situace]</t>
+        </is>
+      </c>
+      <c r="J260" s="6" t="inlineStr">
+        <is>
+          <t>ABMV:ABMV_31</t>
+        </is>
+      </c>
     </row>
     <row r="261">
-      <c r="A261" s="10" t="n">
-        <v>163</v>
-      </c>
-      <c r="B261" s="11" t="inlineStr"/>
-      <c r="C261" s="10" t="n">
-        <v>12</v>
-      </c>
-      <c r="D261" s="11" t="inlineStr">
-        <is>
-          <t>M-VK</t>
-        </is>
-      </c>
-      <c r="E261" s="11" t="inlineStr">
-        <is>
-          <t>M-VK-014</t>
-        </is>
-      </c>
-      <c r="F261" s="12" t="inlineStr">
-        <is>
-          <t>Asfaltový beton ACO 11+ tl 50 mm obrusná vrstva — parkoviště + manipulace</t>
-        </is>
-      </c>
-      <c r="G261" s="10" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="H261" s="10" t="n">
-        <v>325</v>
-      </c>
-      <c r="I261" s="12" t="inlineStr">
-        <is>
-          <t>125.0+150.0+50.0 = 325.0 m²  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
-        </is>
-      </c>
-      <c r="J261" s="12" t="inlineStr"/>
+      <c r="A261" s="3" t="inlineStr">
+        <is>
+          <t>→ Rampy 4× (R1-R4) — výztuž + bednění + beton + obrubník (per A101)</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="4" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B262" s="5" t="inlineStr"/>
       <c r="C262" s="4" t="n">
@@ -7583,32 +7568,32 @@
       </c>
       <c r="E262" s="5" t="inlineStr">
         <is>
-          <t>M-VK-015</t>
+          <t>M-VK-002</t>
         </is>
       </c>
       <c r="F262" s="6" t="inlineStr">
         <is>
-          <t>Obrubník betonový silniční ABO 100×250×1000 mm + lůžko z betonu C16/20</t>
+          <t>Výztuž KARI síť Q188 + bednění boční rampy 4 lokality</t>
         </is>
       </c>
       <c r="G262" s="4" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="H262" s="4" t="n">
-        <v>90</v>
+        <v>43.32</v>
       </c>
       <c r="I262" s="6" t="inlineStr">
         <is>
-          <t>~90.0 m  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
+          <t>4 lokality rampy = 43.32 m²  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
         </is>
       </c>
       <c r="J262" s="6" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" s="10" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B263" s="11" t="inlineStr"/>
       <c r="C263" s="10" t="n">
@@ -7621,208 +7606,201 @@
       </c>
       <c r="E263" s="11" t="inlineStr">
         <is>
-          <t>M-VK-017</t>
+          <t>M-VK-001</t>
         </is>
       </c>
       <c r="F263" s="12" t="inlineStr">
         <is>
-          <t>Komunikační napojení na stávající vozovku — vč. úpravy navazujícího pásu asfaltu, frézování styčné spáry, zalévací zálivka</t>
+          <t>Beton C25/30 XF3 — vstupní/nájezdové rampy tl 150 mm, 4 lokality (R1 sever, R2+R3 jih, R4 západ bezbariérová)</t>
         </is>
       </c>
       <c r="G263" s="10" t="inlineStr">
         <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="H263" s="10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I263" s="12" t="inlineStr">
+        <is>
+          <t>(9.2+11.5+9.2+13.42) × 0.15 = 6.50 m³  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
+        </is>
+      </c>
+      <c r="J263" s="12" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="4" t="n">
+        <v>165</v>
+      </c>
+      <c r="B264" s="5" t="inlineStr"/>
+      <c r="C264" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D264" s="5" t="inlineStr">
+        <is>
+          <t>M-VK</t>
+        </is>
+      </c>
+      <c r="E264" s="5" t="inlineStr">
+        <is>
+          <t>M-VK-004</t>
+        </is>
+      </c>
+      <c r="F264" s="6" t="inlineStr">
+        <is>
+          <t>Obrubník betonový ABO 100×250×1000 kolem ramp + lůžko z betonu C16/20</t>
+        </is>
+      </c>
+      <c r="G264" s="4" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="H264" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="I264" s="6" t="inlineStr">
+        <is>
+          <t>~30.0 m  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
+        </is>
+      </c>
+      <c r="J264" s="6" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="3" t="inlineStr">
+        <is>
+          <t>→ Liniový žlab pojízdný B125 — SZ + JZ fasáda (40 m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="4" t="n">
+        <v>166</v>
+      </c>
+      <c r="B266" s="5" t="inlineStr"/>
+      <c r="C266" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D266" s="5" t="inlineStr">
+        <is>
+          <t>M-VK</t>
+        </is>
+      </c>
+      <c r="E266" s="5" t="inlineStr">
+        <is>
+          <t>M-VK-012</t>
+        </is>
+      </c>
+      <c r="F266" s="6" t="inlineStr">
+        <is>
+          <t>Liniový žlab POJÍZDNÝ tř. zatížení B125 — odvodnění zpevněných ploch parkoviště + manipulace, vč. mřížky</t>
+        </is>
+      </c>
+      <c r="G266" s="4" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="H266" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="I266" s="6" t="inlineStr">
+        <is>
+          <t>40 m  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
+        </is>
+      </c>
+      <c r="J266" s="6" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="3" t="inlineStr">
+        <is>
+          <t>→ Vyspádování okolního terénu k odvodnění</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="4" t="n">
+        <v>167</v>
+      </c>
+      <c r="B268" s="5" t="inlineStr"/>
+      <c r="C268" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D268" s="5" t="inlineStr">
+        <is>
+          <t>M-VK</t>
+        </is>
+      </c>
+      <c r="E268" s="5" t="inlineStr">
+        <is>
+          <t>M-VK-019</t>
+        </is>
+      </c>
+      <c r="F268" s="6" t="inlineStr">
+        <is>
+          <t>Vyspádování okolního terénu k odvodňovacím prvkům (žlabům, retenční nádrži) — hutněná zemina, finální úprava</t>
+        </is>
+      </c>
+      <c r="G268" s="4" t="inlineStr">
+        <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="H263" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="I263" s="12" t="inlineStr">
-        <is>
-          <t>50.0 m²  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
-        </is>
-      </c>
-      <c r="J263" s="12" t="inlineStr"/>
-    </row>
-    <row r="264">
-      <c r="A264" s="3" t="inlineStr">
-        <is>
-          <t>→ Liniový žlab pojízdný B125 — venkovní plochy</t>
-        </is>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" s="4" t="n">
-        <v>166</v>
-      </c>
-      <c r="B265" s="5" t="inlineStr"/>
-      <c r="C265" s="4" t="n">
+      <c r="H268" s="4" t="n">
+        <v>300</v>
+      </c>
+      <c r="I268" s="6" t="inlineStr">
+        <is>
+          <t>300 m²  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
+        </is>
+      </c>
+      <c r="J268" s="6" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" s="3" t="inlineStr">
+        <is>
+          <t>→ Ohumusování + osetí travou zbytkových ploch</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="4" t="n">
+        <v>168</v>
+      </c>
+      <c r="B270" s="5" t="inlineStr"/>
+      <c r="C270" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="D265" s="5" t="inlineStr">
+      <c r="D270" s="5" t="inlineStr">
         <is>
           <t>M-VK</t>
         </is>
       </c>
-      <c r="E265" s="5" t="inlineStr">
-        <is>
-          <t>M-VK-012</t>
-        </is>
-      </c>
-      <c r="F265" s="6" t="inlineStr">
-        <is>
-          <t>Liniový žlab POJÍZDNÝ tř. zatížení B125 — odvodnění zpevněných ploch parkoviště + manipulace, vč. mřížky</t>
-        </is>
-      </c>
-      <c r="G265" s="4" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="H265" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="I265" s="6" t="inlineStr">
-        <is>
-          <t>40 m  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
-        </is>
-      </c>
-      <c r="J265" s="6" t="inlineStr"/>
-    </row>
-    <row r="266">
-      <c r="A266" s="3" t="inlineStr">
-        <is>
-          <t>→ Vodorovné značení 10× parkovacích stání</t>
-        </is>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" s="4" t="n">
-        <v>167</v>
-      </c>
-      <c r="B267" s="5" t="inlineStr"/>
-      <c r="C267" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="D267" s="5" t="inlineStr">
-        <is>
-          <t>M-VK</t>
-        </is>
-      </c>
-      <c r="E267" s="5" t="inlineStr">
-        <is>
-          <t>M-VK-016</t>
-        </is>
-      </c>
-      <c r="F267" s="6" t="inlineStr">
-        <is>
-          <t>Vodorovné značení parkovacích stání — symbol P + krajní čáry, barva bílá nestripovaná retroflexní</t>
-        </is>
-      </c>
-      <c r="G267" s="4" t="inlineStr">
-        <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="H267" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="I267" s="6" t="inlineStr">
-        <is>
-          <t>10 ks  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
-        </is>
-      </c>
-      <c r="J267" s="6" t="inlineStr"/>
-    </row>
-    <row r="268">
-      <c r="A268" s="3" t="inlineStr">
-        <is>
-          <t>→ Vyspádování okolního terénu k odvodnění</t>
-        </is>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" s="4" t="n">
-        <v>168</v>
-      </c>
-      <c r="B269" s="5" t="inlineStr"/>
-      <c r="C269" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="D269" s="5" t="inlineStr">
-        <is>
-          <t>M-VK</t>
-        </is>
-      </c>
-      <c r="E269" s="5" t="inlineStr">
-        <is>
-          <t>M-VK-019</t>
-        </is>
-      </c>
-      <c r="F269" s="6" t="inlineStr">
-        <is>
-          <t>Vyspádování okolního terénu k odvodňovacím prvkům (žlabům, retenční nádrži) — hutněná zemina, finální úprava</t>
-        </is>
-      </c>
-      <c r="G269" s="4" t="inlineStr">
+      <c r="E270" s="5" t="inlineStr">
+        <is>
+          <t>M-VK-018</t>
+        </is>
+      </c>
+      <c r="F270" s="6" t="inlineStr">
+        <is>
+          <t>Ohumusování tl 100 mm + osetí trávou parkové směsi — rekultivace zbytkových ploch okolo haly</t>
+        </is>
+      </c>
+      <c r="G270" s="4" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="H269" s="4" t="n">
-        <v>300</v>
-      </c>
-      <c r="I269" s="6" t="inlineStr">
-        <is>
-          <t>300 m²  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
-        </is>
-      </c>
-      <c r="J269" s="6" t="inlineStr"/>
-    </row>
-    <row r="270">
-      <c r="A270" s="3" t="inlineStr">
-        <is>
-          <t>→ Ohumusování + osetí travou zbytkových ploch</t>
-        </is>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" s="4" t="n">
-        <v>169</v>
-      </c>
-      <c r="B271" s="5" t="inlineStr"/>
-      <c r="C271" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="D271" s="5" t="inlineStr">
-        <is>
-          <t>M-VK</t>
-        </is>
-      </c>
-      <c r="E271" s="5" t="inlineStr">
-        <is>
-          <t>M-VK-018</t>
-        </is>
-      </c>
-      <c r="F271" s="6" t="inlineStr">
-        <is>
-          <t>Ohumusování tl 100 mm + osetí trávou parkové směsi — rekultivace zbytkových ploch okolo haly</t>
-        </is>
-      </c>
-      <c r="G271" s="4" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="H271" s="4" t="n">
+      <c r="H270" s="4" t="n">
         <v>500</v>
       </c>
-      <c r="I271" s="6" t="inlineStr">
+      <c r="I270" s="6" t="inlineStr">
         <is>
           <t>500 m²  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
         </is>
       </c>
-      <c r="J271" s="6" t="inlineStr"/>
+      <c r="J270" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="101">
@@ -7835,7 +7813,7 @@
     <mergeCell ref="A220:J220"/>
     <mergeCell ref="A34:J34"/>
     <mergeCell ref="A83:J83"/>
-    <mergeCell ref="A270:J270"/>
+    <mergeCell ref="A261:J261"/>
     <mergeCell ref="A222:J222"/>
     <mergeCell ref="A49:J49"/>
     <mergeCell ref="A138:J138"/>
@@ -7843,7 +7821,6 @@
     <mergeCell ref="A36:J36"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="A119:J119"/>
-    <mergeCell ref="A264:J264"/>
     <mergeCell ref="A3:J3"/>
     <mergeCell ref="A95:J95"/>
     <mergeCell ref="A248:J248"/>
@@ -7851,14 +7828,15 @@
     <mergeCell ref="A159:J159"/>
     <mergeCell ref="A29:J29"/>
     <mergeCell ref="A96:J96"/>
+    <mergeCell ref="A265:J265"/>
     <mergeCell ref="A147:J147"/>
     <mergeCell ref="A121:J121"/>
     <mergeCell ref="A202:J202"/>
     <mergeCell ref="A58:J58"/>
     <mergeCell ref="A186:J186"/>
+    <mergeCell ref="A257:J257"/>
     <mergeCell ref="A24:J24"/>
     <mergeCell ref="A201:J201"/>
-    <mergeCell ref="A266:J266"/>
     <mergeCell ref="A250:J250"/>
     <mergeCell ref="A197:J197"/>
     <mergeCell ref="A110:J110"/>
@@ -7893,20 +7871,20 @@
     <mergeCell ref="A153:J153"/>
     <mergeCell ref="A162:J162"/>
     <mergeCell ref="A227:J227"/>
-    <mergeCell ref="A268:J268"/>
     <mergeCell ref="A164:J164"/>
     <mergeCell ref="A145:J145"/>
+    <mergeCell ref="A267:J267"/>
     <mergeCell ref="A242:J242"/>
     <mergeCell ref="A195:J195"/>
     <mergeCell ref="A76:J76"/>
     <mergeCell ref="A33:J33"/>
     <mergeCell ref="A85:J85"/>
     <mergeCell ref="A116:J116"/>
+    <mergeCell ref="A269:J269"/>
     <mergeCell ref="A8:J8"/>
     <mergeCell ref="A188:J188"/>
     <mergeCell ref="A126:J126"/>
     <mergeCell ref="A100:J100"/>
-    <mergeCell ref="A259:J259"/>
     <mergeCell ref="A140:J140"/>
     <mergeCell ref="A240:J240"/>
     <mergeCell ref="A10:J10"/>

--- a/test-data/hk212_hala/outputs/sequential_list/hk212_sequential_list.xlsx
+++ b/test-data/hk212_hala/outputs/sequential_list/hk212_sequential_list.xlsx
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J270"/>
+  <dimension ref="A1:J273"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7329,7 +7329,7 @@
     <row r="254">
       <c r="A254" s="3" t="inlineStr">
         <is>
-          <t>→ Drcený štěrk podklady (rampy + okapní chodník)</t>
+          <t>→ Drcený štěrk podklad ramp</t>
         </is>
       </c>
     </row>
@@ -7372,435 +7372,561 @@
       <c r="J255" s="6" t="inlineStr"/>
     </row>
     <row r="256">
-      <c r="A256" s="10" t="n">
+      <c r="A256" s="3" t="inlineStr">
+        <is>
+          <t>→ Okapní chodník — complete layer stack 0.7 m × 80 m po obvodu haly (zemní pláň → štěrk → hutnění → bednění → výztuž → beton → dilatace, pending ABMV_31 + ABMV_32)</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="4" t="n">
         <v>159</v>
       </c>
-      <c r="B256" s="11" t="inlineStr"/>
-      <c r="C256" s="10" t="n">
+      <c r="B257" s="5" t="inlineStr"/>
+      <c r="C257" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="D256" s="11" t="inlineStr">
+      <c r="D257" s="5" t="inlineStr">
         <is>
           <t>M-VK</t>
         </is>
       </c>
-      <c r="E256" s="11" t="inlineStr">
+      <c r="E257" s="5" t="inlineStr">
+        <is>
+          <t>M-VK-024</t>
+        </is>
+      </c>
+      <c r="F257" s="6" t="inlineStr">
+        <is>
+          <t>Úprava zemní pláně + hutnění pod okapní chodník (Edef2 ≥ 30 MPa)</t>
+        </is>
+      </c>
+      <c r="G257" s="4" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="H257" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="I257" s="6" t="inlineStr">
+        <is>
+          <t>80.0 × 0.7 = 56.0 m²  [document:A103 řez A-B detail, norma:ČSN 73 6126, norma:ČSN EN 13670]</t>
+        </is>
+      </c>
+      <c r="J257" s="6" t="inlineStr">
+        <is>
+          <t>ABMV:ABMV_32</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="10" t="n">
+        <v>160</v>
+      </c>
+      <c r="B258" s="11" t="inlineStr"/>
+      <c r="C258" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D258" s="11" t="inlineStr">
+        <is>
+          <t>M-VK</t>
+        </is>
+      </c>
+      <c r="E258" s="11" t="inlineStr">
         <is>
           <t>M-VK-022</t>
         </is>
       </c>
-      <c r="F256" s="12" t="inlineStr">
+      <c r="F258" s="12" t="inlineStr">
         <is>
           <t>Drcený štěrk ŠD 32/63 podklad okapního chodníku tl 150 mm</t>
         </is>
       </c>
-      <c r="G256" s="10" t="inlineStr">
+      <c r="G258" s="10" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="H256" s="10" t="n">
+      <c r="H258" s="10" t="n">
         <v>8.4</v>
       </c>
-      <c r="I256" s="12" t="inlineStr">
+      <c r="I258" s="12" t="inlineStr">
         <is>
           <t>80.0 × 0.7 × 0.15 = 8.40 m³  [document:A103 řezy A-B detail, document:A101 půdorys 1NP, document:C.3 KOO situace]</t>
         </is>
       </c>
-      <c r="J256" s="12" t="inlineStr">
+      <c r="J258" s="12" t="inlineStr">
         <is>
           <t>ABMV:ABMV_31</t>
         </is>
       </c>
     </row>
-    <row r="257">
-      <c r="A257" s="3" t="inlineStr">
-        <is>
-          <t>→ Okapní chodník — sokl 0.7 m × 80 m po obvodu haly (beton + výztuž + dilatace, pending ABMV_31)</t>
-        </is>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" s="4" t="n">
-        <v>160</v>
-      </c>
-      <c r="B258" s="5" t="inlineStr"/>
-      <c r="C258" s="4" t="n">
+    <row r="259">
+      <c r="A259" s="4" t="n">
+        <v>161</v>
+      </c>
+      <c r="B259" s="5" t="inlineStr"/>
+      <c r="C259" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="D258" s="5" t="inlineStr">
+      <c r="D259" s="5" t="inlineStr">
         <is>
           <t>M-VK</t>
         </is>
       </c>
-      <c r="E258" s="5" t="inlineStr">
+      <c r="E259" s="5" t="inlineStr">
+        <is>
+          <t>M-VK-025</t>
+        </is>
+      </c>
+      <c r="F259" s="6" t="inlineStr">
+        <is>
+          <t>Hutnění štěrkového podkladu okapního chodníku vibrodeskou (Edef2 ≥ 45 MPa)</t>
+        </is>
+      </c>
+      <c r="G259" s="4" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="H259" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="I259" s="6" t="inlineStr">
+        <is>
+          <t>80.0 × 0.7 = 56.0 m²  [document:A103 řez A-B detail, norma:ČSN 73 6126, norma:ČSN EN 13670]</t>
+        </is>
+      </c>
+      <c r="J259" s="6" t="inlineStr">
+        <is>
+          <t>ABMV:ABMV_32</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="10" t="n">
+        <v>162</v>
+      </c>
+      <c r="B260" s="11" t="inlineStr"/>
+      <c r="C260" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D260" s="11" t="inlineStr">
+        <is>
+          <t>M-VK</t>
+        </is>
+      </c>
+      <c r="E260" s="11" t="inlineStr">
+        <is>
+          <t>M-VK-026</t>
+        </is>
+      </c>
+      <c r="F260" s="12" t="inlineStr">
+        <is>
+          <t>Bednění boční vnější hrana okapního chodníku v 200 mm (vnitřní hrana = stěna haly)</t>
+        </is>
+      </c>
+      <c r="G260" s="10" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="H260" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="I260" s="12" t="inlineStr">
+        <is>
+          <t>80.0 × 0.2 = 16.0 m²  [document:A103 řez A-B detail, norma:ČSN 73 6126, norma:ČSN EN 13670]</t>
+        </is>
+      </c>
+      <c r="J260" s="12" t="inlineStr">
+        <is>
+          <t>ABMV:ABMV_32</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="4" t="n">
+        <v>163</v>
+      </c>
+      <c r="B261" s="5" t="inlineStr"/>
+      <c r="C261" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D261" s="5" t="inlineStr">
+        <is>
+          <t>M-VK</t>
+        </is>
+      </c>
+      <c r="E261" s="5" t="inlineStr">
+        <is>
+          <t>M-VK-021</t>
+        </is>
+      </c>
+      <c r="F261" s="6" t="inlineStr">
+        <is>
+          <t>Výztuž KARI síť Q188 (150/150/6 mm) — okapní chodník</t>
+        </is>
+      </c>
+      <c r="G261" s="4" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="H261" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="I261" s="6" t="inlineStr">
+        <is>
+          <t>80.0 × 0.7 = 56.00 m²  [document:A103 řezy A-B detail, document:A101 půdorys 1NP, document:C.3 KOO situace]</t>
+        </is>
+      </c>
+      <c r="J261" s="6" t="inlineStr">
+        <is>
+          <t>ABMV:ABMV_31</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="10" t="n">
+        <v>164</v>
+      </c>
+      <c r="B262" s="11" t="inlineStr"/>
+      <c r="C262" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D262" s="11" t="inlineStr">
+        <is>
+          <t>M-VK</t>
+        </is>
+      </c>
+      <c r="E262" s="11" t="inlineStr">
         <is>
           <t>M-VK-020</t>
         </is>
       </c>
-      <c r="F258" s="6" t="inlineStr">
+      <c r="F262" s="12" t="inlineStr">
         <is>
           <t>Beton C25/30 XF3 — okapní chodník po obvodu haly (sokl 0.7 m × ~80 m mimo 4 vstupy), tl 200 mm</t>
         </is>
       </c>
-      <c r="G258" s="4" t="inlineStr">
+      <c r="G262" s="10" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="H258" s="4" t="n">
+      <c r="H262" s="10" t="n">
         <v>11.2</v>
       </c>
-      <c r="I258" s="6" t="inlineStr">
+      <c r="I262" s="12" t="inlineStr">
         <is>
           <t>80.0 × 0.7 × 0.2 = 11.20 m³  [document:A103 řezy A-B detail, document:A101 půdorys 1NP, document:C.3 KOO situace]</t>
         </is>
       </c>
-      <c r="J258" s="6" t="inlineStr">
+      <c r="J262" s="12" t="inlineStr">
         <is>
           <t>ABMV:ABMV_31</t>
         </is>
       </c>
     </row>
-    <row r="259">
-      <c r="A259" s="10" t="n">
-        <v>161</v>
-      </c>
-      <c r="B259" s="11" t="inlineStr"/>
-      <c r="C259" s="10" t="n">
+    <row r="263">
+      <c r="A263" s="4" t="n">
+        <v>165</v>
+      </c>
+      <c r="B263" s="5" t="inlineStr"/>
+      <c r="C263" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="D259" s="11" t="inlineStr">
+      <c r="D263" s="5" t="inlineStr">
         <is>
           <t>M-VK</t>
         </is>
       </c>
-      <c r="E259" s="11" t="inlineStr">
-        <is>
-          <t>M-VK-021</t>
-        </is>
-      </c>
-      <c r="F259" s="12" t="inlineStr">
-        <is>
-          <t>Výztuž KARI síť Q188 + boční bednění + dilatační lišty — okapní chodník</t>
-        </is>
-      </c>
-      <c r="G259" s="10" t="inlineStr">
+      <c r="E263" s="5" t="inlineStr">
+        <is>
+          <t>M-VK-023</t>
+        </is>
+      </c>
+      <c r="F263" s="6" t="inlineStr">
+        <is>
+          <t>Dilatační lišty + těsnění spár mezi segmenty okapního chodníku (à ~4 m)</t>
+        </is>
+      </c>
+      <c r="G263" s="4" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="H263" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="I263" s="6" t="inlineStr">
+        <is>
+          <t>80.0 / 4 = 20 ks dilatací  [document:A103 řezy A-B detail, document:A101 půdorys 1NP, document:C.3 KOO situace]</t>
+        </is>
+      </c>
+      <c r="J263" s="6" t="inlineStr">
+        <is>
+          <t>ABMV:ABMV_31</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="3" t="inlineStr">
+        <is>
+          <t>→ Rampy 4× (R1-R4) — výztuž + bednění + beton + obrubník (per A101)</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="4" t="n">
+        <v>166</v>
+      </c>
+      <c r="B265" s="5" t="inlineStr"/>
+      <c r="C265" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D265" s="5" t="inlineStr">
+        <is>
+          <t>M-VK</t>
+        </is>
+      </c>
+      <c r="E265" s="5" t="inlineStr">
+        <is>
+          <t>M-VK-002</t>
+        </is>
+      </c>
+      <c r="F265" s="6" t="inlineStr">
+        <is>
+          <t>Výztuž KARI síť Q188 + bednění boční rampy 4 lokality</t>
+        </is>
+      </c>
+      <c r="G265" s="4" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="H259" s="10" t="n">
-        <v>56</v>
-      </c>
-      <c r="I259" s="12" t="inlineStr">
-        <is>
-          <t>80.0 × 0.7 = 56.00 m²  [document:A103 řezy A-B detail, document:A101 půdorys 1NP, document:C.3 KOO situace]</t>
-        </is>
-      </c>
-      <c r="J259" s="12" t="inlineStr">
-        <is>
-          <t>ABMV:ABMV_31</t>
-        </is>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" s="4" t="n">
-        <v>162</v>
-      </c>
-      <c r="B260" s="5" t="inlineStr"/>
-      <c r="C260" s="4" t="n">
+      <c r="H265" s="4" t="n">
+        <v>43.32</v>
+      </c>
+      <c r="I265" s="6" t="inlineStr">
+        <is>
+          <t>4 lokality rampy = 43.32 m²  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
+        </is>
+      </c>
+      <c r="J265" s="6" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="10" t="n">
+        <v>167</v>
+      </c>
+      <c r="B266" s="11" t="inlineStr"/>
+      <c r="C266" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="D260" s="5" t="inlineStr">
+      <c r="D266" s="11" t="inlineStr">
         <is>
           <t>M-VK</t>
         </is>
       </c>
-      <c r="E260" s="5" t="inlineStr">
-        <is>
-          <t>M-VK-023</t>
-        </is>
-      </c>
-      <c r="F260" s="6" t="inlineStr">
-        <is>
-          <t>Dilatační lišty + těsnění spár mezi segmenty okapního chodníku (à ~4 m)</t>
-        </is>
-      </c>
-      <c r="G260" s="4" t="inlineStr">
+      <c r="E266" s="11" t="inlineStr">
+        <is>
+          <t>M-VK-001</t>
+        </is>
+      </c>
+      <c r="F266" s="12" t="inlineStr">
+        <is>
+          <t>Beton C25/30 XF3 — vstupní/nájezdové rampy tl 150 mm, 4 lokality (R1 sever, R2+R3 jih, R4 západ bezbariérová)</t>
+        </is>
+      </c>
+      <c r="G266" s="10" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="H266" s="10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I266" s="12" t="inlineStr">
+        <is>
+          <t>(9.2+11.5+9.2+13.42) × 0.15 = 6.50 m³  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
+        </is>
+      </c>
+      <c r="J266" s="12" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="4" t="n">
+        <v>168</v>
+      </c>
+      <c r="B267" s="5" t="inlineStr"/>
+      <c r="C267" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D267" s="5" t="inlineStr">
+        <is>
+          <t>M-VK</t>
+        </is>
+      </c>
+      <c r="E267" s="5" t="inlineStr">
+        <is>
+          <t>M-VK-004</t>
+        </is>
+      </c>
+      <c r="F267" s="6" t="inlineStr">
+        <is>
+          <t>Obrubník betonový ABO 100×250×1000 kolem ramp + lůžko z betonu C16/20</t>
+        </is>
+      </c>
+      <c r="G267" s="4" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="H260" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="I260" s="6" t="inlineStr">
-        <is>
-          <t>80.0 / 4 = 20 ks dilatací  [document:A103 řezy A-B detail, document:A101 půdorys 1NP, document:C.3 KOO situace]</t>
-        </is>
-      </c>
-      <c r="J260" s="6" t="inlineStr">
-        <is>
-          <t>ABMV:ABMV_31</t>
-        </is>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" s="3" t="inlineStr">
-        <is>
-          <t>→ Rampy 4× (R1-R4) — výztuž + bednění + beton + obrubník (per A101)</t>
-        </is>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" s="4" t="n">
-        <v>163</v>
-      </c>
-      <c r="B262" s="5" t="inlineStr"/>
-      <c r="C262" s="4" t="n">
+      <c r="H267" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="I267" s="6" t="inlineStr">
+        <is>
+          <t>~30.0 m  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
+        </is>
+      </c>
+      <c r="J267" s="6" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" s="3" t="inlineStr">
+        <is>
+          <t>→ Liniový žlab pojízdný B125 — SZ + JZ fasáda (40 m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="4" t="n">
+        <v>169</v>
+      </c>
+      <c r="B269" s="5" t="inlineStr"/>
+      <c r="C269" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="D262" s="5" t="inlineStr">
+      <c r="D269" s="5" t="inlineStr">
         <is>
           <t>M-VK</t>
         </is>
       </c>
-      <c r="E262" s="5" t="inlineStr">
-        <is>
-          <t>M-VK-002</t>
-        </is>
-      </c>
-      <c r="F262" s="6" t="inlineStr">
-        <is>
-          <t>Výztuž KARI síť Q188 + bednění boční rampy 4 lokality</t>
-        </is>
-      </c>
-      <c r="G262" s="4" t="inlineStr">
+      <c r="E269" s="5" t="inlineStr">
+        <is>
+          <t>M-VK-012</t>
+        </is>
+      </c>
+      <c r="F269" s="6" t="inlineStr">
+        <is>
+          <t>Liniový žlab POJÍZDNÝ tř. zatížení B125 — odvodnění zpevněných ploch parkoviště + manipulace, vč. mřížky</t>
+        </is>
+      </c>
+      <c r="G269" s="4" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="H269" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="I269" s="6" t="inlineStr">
+        <is>
+          <t>40 m  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
+        </is>
+      </c>
+      <c r="J269" s="6" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="3" t="inlineStr">
+        <is>
+          <t>→ Vyspádování okolního terénu k odvodnění</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="4" t="n">
+        <v>170</v>
+      </c>
+      <c r="B271" s="5" t="inlineStr"/>
+      <c r="C271" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D271" s="5" t="inlineStr">
+        <is>
+          <t>M-VK</t>
+        </is>
+      </c>
+      <c r="E271" s="5" t="inlineStr">
+        <is>
+          <t>M-VK-019</t>
+        </is>
+      </c>
+      <c r="F271" s="6" t="inlineStr">
+        <is>
+          <t>Vyspádování okolního terénu k odvodňovacím prvkům (žlabům, retenční nádrži) — hutněná zemina, finální úprava</t>
+        </is>
+      </c>
+      <c r="G271" s="4" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="H262" s="4" t="n">
-        <v>43.32</v>
-      </c>
-      <c r="I262" s="6" t="inlineStr">
-        <is>
-          <t>4 lokality rampy = 43.32 m²  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
-        </is>
-      </c>
-      <c r="J262" s="6" t="inlineStr"/>
-    </row>
-    <row r="263">
-      <c r="A263" s="10" t="n">
-        <v>164</v>
-      </c>
-      <c r="B263" s="11" t="inlineStr"/>
-      <c r="C263" s="10" t="n">
+      <c r="H271" s="4" t="n">
+        <v>300</v>
+      </c>
+      <c r="I271" s="6" t="inlineStr">
+        <is>
+          <t>300 m²  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
+        </is>
+      </c>
+      <c r="J271" s="6" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" s="3" t="inlineStr">
+        <is>
+          <t>→ Ohumusování + osetí travou zbytkových ploch</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="4" t="n">
+        <v>171</v>
+      </c>
+      <c r="B273" s="5" t="inlineStr"/>
+      <c r="C273" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="D263" s="11" t="inlineStr">
+      <c r="D273" s="5" t="inlineStr">
         <is>
           <t>M-VK</t>
         </is>
       </c>
-      <c r="E263" s="11" t="inlineStr">
-        <is>
-          <t>M-VK-001</t>
-        </is>
-      </c>
-      <c r="F263" s="12" t="inlineStr">
-        <is>
-          <t>Beton C25/30 XF3 — vstupní/nájezdové rampy tl 150 mm, 4 lokality (R1 sever, R2+R3 jih, R4 západ bezbariérová)</t>
-        </is>
-      </c>
-      <c r="G263" s="10" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="H263" s="10" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I263" s="12" t="inlineStr">
-        <is>
-          <t>(9.2+11.5+9.2+13.42) × 0.15 = 6.50 m³  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
-        </is>
-      </c>
-      <c r="J263" s="12" t="inlineStr"/>
-    </row>
-    <row r="264">
-      <c r="A264" s="4" t="n">
-        <v>165</v>
-      </c>
-      <c r="B264" s="5" t="inlineStr"/>
-      <c r="C264" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="D264" s="5" t="inlineStr">
-        <is>
-          <t>M-VK</t>
-        </is>
-      </c>
-      <c r="E264" s="5" t="inlineStr">
-        <is>
-          <t>M-VK-004</t>
-        </is>
-      </c>
-      <c r="F264" s="6" t="inlineStr">
-        <is>
-          <t>Obrubník betonový ABO 100×250×1000 kolem ramp + lůžko z betonu C16/20</t>
-        </is>
-      </c>
-      <c r="G264" s="4" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="H264" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="I264" s="6" t="inlineStr">
-        <is>
-          <t>~30.0 m  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
-        </is>
-      </c>
-      <c r="J264" s="6" t="inlineStr"/>
-    </row>
-    <row r="265">
-      <c r="A265" s="3" t="inlineStr">
-        <is>
-          <t>→ Liniový žlab pojízdný B125 — SZ + JZ fasáda (40 m)</t>
-        </is>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" s="4" t="n">
-        <v>166</v>
-      </c>
-      <c r="B266" s="5" t="inlineStr"/>
-      <c r="C266" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="D266" s="5" t="inlineStr">
-        <is>
-          <t>M-VK</t>
-        </is>
-      </c>
-      <c r="E266" s="5" t="inlineStr">
-        <is>
-          <t>M-VK-012</t>
-        </is>
-      </c>
-      <c r="F266" s="6" t="inlineStr">
-        <is>
-          <t>Liniový žlab POJÍZDNÝ tř. zatížení B125 — odvodnění zpevněných ploch parkoviště + manipulace, vč. mřížky</t>
-        </is>
-      </c>
-      <c r="G266" s="4" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="H266" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="I266" s="6" t="inlineStr">
-        <is>
-          <t>40 m  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
-        </is>
-      </c>
-      <c r="J266" s="6" t="inlineStr"/>
-    </row>
-    <row r="267">
-      <c r="A267" s="3" t="inlineStr">
-        <is>
-          <t>→ Vyspádování okolního terénu k odvodnění</t>
-        </is>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" s="4" t="n">
-        <v>167</v>
-      </c>
-      <c r="B268" s="5" t="inlineStr"/>
-      <c r="C268" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="D268" s="5" t="inlineStr">
-        <is>
-          <t>M-VK</t>
-        </is>
-      </c>
-      <c r="E268" s="5" t="inlineStr">
-        <is>
-          <t>M-VK-019</t>
-        </is>
-      </c>
-      <c r="F268" s="6" t="inlineStr">
-        <is>
-          <t>Vyspádování okolního terénu k odvodňovacím prvkům (žlabům, retenční nádrži) — hutněná zemina, finální úprava</t>
-        </is>
-      </c>
-      <c r="G268" s="4" t="inlineStr">
+      <c r="E273" s="5" t="inlineStr">
+        <is>
+          <t>M-VK-018</t>
+        </is>
+      </c>
+      <c r="F273" s="6" t="inlineStr">
+        <is>
+          <t>Ohumusování tl 100 mm + osetí trávou parkové směsi — rekultivace zbytkových ploch okolo haly</t>
+        </is>
+      </c>
+      <c r="G273" s="4" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="H268" s="4" t="n">
-        <v>300</v>
-      </c>
-      <c r="I268" s="6" t="inlineStr">
-        <is>
-          <t>300 m²  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
-        </is>
-      </c>
-      <c r="J268" s="6" t="inlineStr"/>
-    </row>
-    <row r="269">
-      <c r="A269" s="3" t="inlineStr">
-        <is>
-          <t>→ Ohumusování + osetí travou zbytkových ploch</t>
-        </is>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" s="4" t="n">
-        <v>168</v>
-      </c>
-      <c r="B270" s="5" t="inlineStr"/>
-      <c r="C270" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="D270" s="5" t="inlineStr">
-        <is>
-          <t>M-VK</t>
-        </is>
-      </c>
-      <c r="E270" s="5" t="inlineStr">
-        <is>
-          <t>M-VK-018</t>
-        </is>
-      </c>
-      <c r="F270" s="6" t="inlineStr">
-        <is>
-          <t>Ohumusování tl 100 mm + osetí trávou parkové směsi — rekultivace zbytkových ploch okolo haly</t>
-        </is>
-      </c>
-      <c r="G270" s="4" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="H270" s="4" t="n">
+      <c r="H273" s="4" t="n">
         <v>500</v>
       </c>
-      <c r="I270" s="6" t="inlineStr">
+      <c r="I273" s="6" t="inlineStr">
         <is>
           <t>500 m²  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
         </is>
       </c>
-      <c r="J270" s="6" t="inlineStr"/>
+      <c r="J273" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="101">
@@ -7813,7 +7939,7 @@
     <mergeCell ref="A220:J220"/>
     <mergeCell ref="A34:J34"/>
     <mergeCell ref="A83:J83"/>
-    <mergeCell ref="A261:J261"/>
+    <mergeCell ref="A270:J270"/>
     <mergeCell ref="A222:J222"/>
     <mergeCell ref="A49:J49"/>
     <mergeCell ref="A138:J138"/>
@@ -7821,6 +7947,8 @@
     <mergeCell ref="A36:J36"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="A119:J119"/>
+    <mergeCell ref="A256:J256"/>
+    <mergeCell ref="A264:J264"/>
     <mergeCell ref="A3:J3"/>
     <mergeCell ref="A95:J95"/>
     <mergeCell ref="A248:J248"/>
@@ -7828,13 +7956,11 @@
     <mergeCell ref="A159:J159"/>
     <mergeCell ref="A29:J29"/>
     <mergeCell ref="A96:J96"/>
-    <mergeCell ref="A265:J265"/>
     <mergeCell ref="A147:J147"/>
     <mergeCell ref="A121:J121"/>
     <mergeCell ref="A202:J202"/>
     <mergeCell ref="A58:J58"/>
     <mergeCell ref="A186:J186"/>
-    <mergeCell ref="A257:J257"/>
     <mergeCell ref="A24:J24"/>
     <mergeCell ref="A201:J201"/>
     <mergeCell ref="A250:J250"/>
@@ -7871,16 +7997,15 @@
     <mergeCell ref="A153:J153"/>
     <mergeCell ref="A162:J162"/>
     <mergeCell ref="A227:J227"/>
+    <mergeCell ref="A268:J268"/>
     <mergeCell ref="A164:J164"/>
     <mergeCell ref="A145:J145"/>
-    <mergeCell ref="A267:J267"/>
     <mergeCell ref="A242:J242"/>
     <mergeCell ref="A195:J195"/>
     <mergeCell ref="A76:J76"/>
     <mergeCell ref="A33:J33"/>
     <mergeCell ref="A85:J85"/>
     <mergeCell ref="A116:J116"/>
-    <mergeCell ref="A269:J269"/>
     <mergeCell ref="A8:J8"/>
     <mergeCell ref="A188:J188"/>
     <mergeCell ref="A126:J126"/>
@@ -7904,6 +8029,7 @@
     <mergeCell ref="A57:J57"/>
     <mergeCell ref="A235:J235"/>
     <mergeCell ref="A210:J210"/>
+    <mergeCell ref="A272:J272"/>
     <mergeCell ref="A129:J129"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/test-data/hk212_hala/outputs/sequential_list/hk212_sequential_list.xlsx
+++ b/test-data/hk212_hala/outputs/sequential_list/hk212_sequential_list.xlsx
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J273"/>
+  <dimension ref="A1:J276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7374,7 +7374,7 @@
     <row r="256">
       <c r="A256" s="3" t="inlineStr">
         <is>
-          <t>→ Okapní chodník — complete layer stack 0.7 m × 80 m po obvodu haly (zemní pláň → štěrk → hutnění → bednění → výztuž → beton → dilatace, pending ABMV_31 + ABMV_32)</t>
+          <t>→ Okapní chodník — complete 10-layer stack 0.7 m × 80 m po obvodu haly (výkop → odvoz → pláň → geotextilie → štěrk → hutnění → bednění → výztuž → beton → dilatace, pending ABMV_31 + ABMV_32)</t>
         </is>
       </c>
     </row>
@@ -7393,25 +7393,25 @@
       </c>
       <c r="E257" s="5" t="inlineStr">
         <is>
-          <t>M-VK-024</t>
+          <t>M-VK-027</t>
         </is>
       </c>
       <c r="F257" s="6" t="inlineStr">
         <is>
-          <t>Úprava zemní pláně + hutnění pod okapní chodník (Edef2 ≥ 30 MPa)</t>
+          <t>Výkop rýhy pro okapní chodník hl. 400 mm (na hloubku všech vrstev)</t>
         </is>
       </c>
       <c r="G257" s="4" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="H257" s="4" t="n">
-        <v>56</v>
+        <v>22.4</v>
       </c>
       <c r="I257" s="6" t="inlineStr">
         <is>
-          <t>80.0 × 0.7 = 56.0 m²  [document:A103 řez A-B detail, norma:ČSN 73 6126, norma:ČSN EN 13670]</t>
+          <t>80.0 × 0.7 × 0.4 = 22.4 m³  [document:A103 řez A-B detail, norma:ČSN 73 6126, norma:ČSN okapový chodník]</t>
         </is>
       </c>
       <c r="J257" s="6" t="inlineStr">
@@ -7435,12 +7435,12 @@
       </c>
       <c r="E258" s="11" t="inlineStr">
         <is>
-          <t>M-VK-022</t>
+          <t>M-VK-028</t>
         </is>
       </c>
       <c r="F258" s="12" t="inlineStr">
         <is>
-          <t>Drcený štěrk ŠD 32/63 podklad okapního chodníku tl 150 mm</t>
+          <t>Odvoz vykopané zeminy z rýhy okapního chodníku na skládku</t>
         </is>
       </c>
       <c r="G258" s="10" t="inlineStr">
@@ -7449,16 +7449,15 @@
         </is>
       </c>
       <c r="H258" s="10" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="I258" s="12" t="inlineStr">
-        <is>
-          <t>80.0 × 0.7 × 0.15 = 8.40 m³  [document:A103 řezy A-B detail, document:A101 půdorys 1NP, document:C.3 KOO situace]</t>
-        </is>
+        <v>22.4</v>
+      </c>
+      <c r="I258" s="12">
+        <f> 22.4 m³ (1:1 s výkopem)  [document:A103 řez A-B detail, norma:ČSN 73 6126, norma:ČSN okapový chodník]</f>
+        <v/>
       </c>
       <c r="J258" s="12" t="inlineStr">
         <is>
-          <t>ABMV:ABMV_31</t>
+          <t>ABMV:ABMV_32</t>
         </is>
       </c>
     </row>
@@ -7477,12 +7476,12 @@
       </c>
       <c r="E259" s="5" t="inlineStr">
         <is>
-          <t>M-VK-025</t>
+          <t>M-VK-024</t>
         </is>
       </c>
       <c r="F259" s="6" t="inlineStr">
         <is>
-          <t>Hutnění štěrkového podkladu okapního chodníku vibrodeskou (Edef2 ≥ 45 MPa)</t>
+          <t>Úprava zemní pláně + hutnění pod okapní chodník (Edef2 ≥ 30 MPa)</t>
         </is>
       </c>
       <c r="G259" s="4" t="inlineStr">
@@ -7519,12 +7518,12 @@
       </c>
       <c r="E260" s="11" t="inlineStr">
         <is>
-          <t>M-VK-026</t>
+          <t>M-VK-029</t>
         </is>
       </c>
       <c r="F260" s="12" t="inlineStr">
         <is>
-          <t>Bednění boční vnější hrana okapního chodníku v 200 mm (vnitřní hrana = stěna haly)</t>
+          <t>Geotextilie 300 g/m² separační — mezi hutněnou zemní pláň a štěrkový podklad okapního chodníku</t>
         </is>
       </c>
       <c r="G260" s="10" t="inlineStr">
@@ -7533,11 +7532,11 @@
         </is>
       </c>
       <c r="H260" s="10" t="n">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="I260" s="12" t="inlineStr">
         <is>
-          <t>80.0 × 0.2 = 16.0 m²  [document:A103 řez A-B detail, norma:ČSN 73 6126, norma:ČSN EN 13670]</t>
+          <t>80.0 × 0.7 = 56.0 m²  [document:A103 řez A-B detail, norma:ČSN 73 6126, norma:ČSN okapový chodník]</t>
         </is>
       </c>
       <c r="J260" s="12" t="inlineStr">
@@ -7561,25 +7560,25 @@
       </c>
       <c r="E261" s="5" t="inlineStr">
         <is>
-          <t>M-VK-021</t>
+          <t>M-VK-022</t>
         </is>
       </c>
       <c r="F261" s="6" t="inlineStr">
         <is>
-          <t>Výztuž KARI síť Q188 (150/150/6 mm) — okapní chodník</t>
+          <t>Drcený štěrk ŠD 32/63 podklad okapního chodníku tl 150 mm</t>
         </is>
       </c>
       <c r="G261" s="4" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="H261" s="4" t="n">
-        <v>56</v>
+        <v>8.4</v>
       </c>
       <c r="I261" s="6" t="inlineStr">
         <is>
-          <t>80.0 × 0.7 = 56.00 m²  [document:A103 řezy A-B detail, document:A101 půdorys 1NP, document:C.3 KOO situace]</t>
+          <t>80.0 × 0.7 × 0.15 = 8.40 m³  [document:A103 řezy A-B detail, document:A101 půdorys 1NP, document:C.3 KOO situace]</t>
         </is>
       </c>
       <c r="J261" s="6" t="inlineStr">
@@ -7603,30 +7602,30 @@
       </c>
       <c r="E262" s="11" t="inlineStr">
         <is>
-          <t>M-VK-020</t>
+          <t>M-VK-025</t>
         </is>
       </c>
       <c r="F262" s="12" t="inlineStr">
         <is>
-          <t>Beton C25/30 XF3 — okapní chodník po obvodu haly (sokl 0.7 m × ~80 m mimo 4 vstupy), tl 200 mm</t>
+          <t>Hutnění štěrkového podkladu okapního chodníku vibrodeskou (Edef2 ≥ 45 MPa)</t>
         </is>
       </c>
       <c r="G262" s="10" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="H262" s="10" t="n">
-        <v>11.2</v>
+        <v>56</v>
       </c>
       <c r="I262" s="12" t="inlineStr">
         <is>
-          <t>80.0 × 0.7 × 0.2 = 11.20 m³  [document:A103 řezy A-B detail, document:A101 půdorys 1NP, document:C.3 KOO situace]</t>
+          <t>80.0 × 0.7 = 56.0 m²  [document:A103 řez A-B detail, norma:ČSN 73 6126, norma:ČSN EN 13670]</t>
         </is>
       </c>
       <c r="J262" s="12" t="inlineStr">
         <is>
-          <t>ABMV:ABMV_31</t>
+          <t>ABMV:ABMV_32</t>
         </is>
       </c>
     </row>
@@ -7645,43 +7644,78 @@
       </c>
       <c r="E263" s="5" t="inlineStr">
         <is>
-          <t>M-VK-023</t>
+          <t>M-VK-026</t>
         </is>
       </c>
       <c r="F263" s="6" t="inlineStr">
         <is>
-          <t>Dilatační lišty + těsnění spár mezi segmenty okapního chodníku (à ~4 m)</t>
+          <t>Bednění boční vnější hrana okapního chodníku v 200 mm (vnitřní hrana = stěna haly)</t>
         </is>
       </c>
       <c r="G263" s="4" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="H263" s="4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I263" s="6" t="inlineStr">
         <is>
-          <t>80.0 / 4 = 20 ks dilatací  [document:A103 řezy A-B detail, document:A101 půdorys 1NP, document:C.3 KOO situace]</t>
+          <t>80.0 × 0.2 = 16.0 m²  [document:A103 řez A-B detail, norma:ČSN 73 6126, norma:ČSN EN 13670]</t>
         </is>
       </c>
       <c r="J263" s="6" t="inlineStr">
         <is>
+          <t>ABMV:ABMV_32</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="10" t="n">
+        <v>166</v>
+      </c>
+      <c r="B264" s="11" t="inlineStr"/>
+      <c r="C264" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D264" s="11" t="inlineStr">
+        <is>
+          <t>M-VK</t>
+        </is>
+      </c>
+      <c r="E264" s="11" t="inlineStr">
+        <is>
+          <t>M-VK-021</t>
+        </is>
+      </c>
+      <c r="F264" s="12" t="inlineStr">
+        <is>
+          <t>Výztuž KARI síť Q188 (150/150/6 mm) — okapní chodník</t>
+        </is>
+      </c>
+      <c r="G264" s="10" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="H264" s="10" t="n">
+        <v>56</v>
+      </c>
+      <c r="I264" s="12" t="inlineStr">
+        <is>
+          <t>80.0 × 0.7 = 56.00 m²  [document:A103 řezy A-B detail, document:A101 půdorys 1NP, document:C.3 KOO situace]</t>
+        </is>
+      </c>
+      <c r="J264" s="12" t="inlineStr">
+        <is>
           <t>ABMV:ABMV_31</t>
-        </is>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" s="3" t="inlineStr">
-        <is>
-          <t>→ Rampy 4× (R1-R4) — výztuž + bednění + beton + obrubník (per A101)</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="4" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B265" s="5" t="inlineStr"/>
       <c r="C265" s="4" t="n">
@@ -7694,32 +7728,36 @@
       </c>
       <c r="E265" s="5" t="inlineStr">
         <is>
-          <t>M-VK-002</t>
+          <t>M-VK-020</t>
         </is>
       </c>
       <c r="F265" s="6" t="inlineStr">
         <is>
-          <t>Výztuž KARI síť Q188 + bednění boční rampy 4 lokality</t>
+          <t>Beton C25/30 XF3 — okapní chodník po obvodu haly (sokl 0.7 m × ~80 m mimo 4 vstupy), tl 200 mm</t>
         </is>
       </c>
       <c r="G265" s="4" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="H265" s="4" t="n">
-        <v>43.32</v>
+        <v>11.2</v>
       </c>
       <c r="I265" s="6" t="inlineStr">
         <is>
-          <t>4 lokality rampy = 43.32 m²  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
-        </is>
-      </c>
-      <c r="J265" s="6" t="inlineStr"/>
+          <t>80.0 × 0.7 × 0.2 = 11.20 m³  [document:A103 řezy A-B detail, document:A101 půdorys 1NP, document:C.3 KOO situace]</t>
+        </is>
+      </c>
+      <c r="J265" s="6" t="inlineStr">
+        <is>
+          <t>ABMV:ABMV_31</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" s="10" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B266" s="11" t="inlineStr"/>
       <c r="C266" s="10" t="n">
@@ -7732,201 +7770,288 @@
       </c>
       <c r="E266" s="11" t="inlineStr">
         <is>
+          <t>M-VK-023</t>
+        </is>
+      </c>
+      <c r="F266" s="12" t="inlineStr">
+        <is>
+          <t>Dilatační lišty + těsnění spár mezi segmenty okapního chodníku (à ~4 m)</t>
+        </is>
+      </c>
+      <c r="G266" s="10" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="H266" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="I266" s="12" t="inlineStr">
+        <is>
+          <t>80.0 / 4 = 20 ks dilatací  [document:A103 řezy A-B detail, document:A101 půdorys 1NP, document:C.3 KOO situace]</t>
+        </is>
+      </c>
+      <c r="J266" s="12" t="inlineStr">
+        <is>
+          <t>ABMV:ABMV_31</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="3" t="inlineStr">
+        <is>
+          <t>→ Rampy 4× (R1-R4) — výztuž + bednění + beton + obrubník (per A101)</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="4" t="n">
+        <v>169</v>
+      </c>
+      <c r="B268" s="5" t="inlineStr"/>
+      <c r="C268" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D268" s="5" t="inlineStr">
+        <is>
+          <t>M-VK</t>
+        </is>
+      </c>
+      <c r="E268" s="5" t="inlineStr">
+        <is>
+          <t>M-VK-002</t>
+        </is>
+      </c>
+      <c r="F268" s="6" t="inlineStr">
+        <is>
+          <t>Výztuž KARI síť Q188 + bednění boční rampy 4 lokality</t>
+        </is>
+      </c>
+      <c r="G268" s="4" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="H268" s="4" t="n">
+        <v>43.32</v>
+      </c>
+      <c r="I268" s="6" t="inlineStr">
+        <is>
+          <t>4 lokality rampy = 43.32 m²  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
+        </is>
+      </c>
+      <c r="J268" s="6" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" s="10" t="n">
+        <v>170</v>
+      </c>
+      <c r="B269" s="11" t="inlineStr"/>
+      <c r="C269" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D269" s="11" t="inlineStr">
+        <is>
+          <t>M-VK</t>
+        </is>
+      </c>
+      <c r="E269" s="11" t="inlineStr">
+        <is>
           <t>M-VK-001</t>
         </is>
       </c>
-      <c r="F266" s="12" t="inlineStr">
+      <c r="F269" s="12" t="inlineStr">
         <is>
           <t>Beton C25/30 XF3 — vstupní/nájezdové rampy tl 150 mm, 4 lokality (R1 sever, R2+R3 jih, R4 západ bezbariérová)</t>
         </is>
       </c>
-      <c r="G266" s="10" t="inlineStr">
+      <c r="G269" s="10" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="H266" s="10" t="n">
+      <c r="H269" s="10" t="n">
         <v>6.5</v>
       </c>
-      <c r="I266" s="12" t="inlineStr">
+      <c r="I269" s="12" t="inlineStr">
         <is>
           <t>(9.2+11.5+9.2+13.42) × 0.15 = 6.50 m³  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
         </is>
       </c>
-      <c r="J266" s="12" t="inlineStr"/>
-    </row>
-    <row r="267">
-      <c r="A267" s="4" t="n">
-        <v>168</v>
-      </c>
-      <c r="B267" s="5" t="inlineStr"/>
-      <c r="C267" s="4" t="n">
+      <c r="J269" s="12" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="4" t="n">
+        <v>171</v>
+      </c>
+      <c r="B270" s="5" t="inlineStr"/>
+      <c r="C270" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="D267" s="5" t="inlineStr">
+      <c r="D270" s="5" t="inlineStr">
         <is>
           <t>M-VK</t>
         </is>
       </c>
-      <c r="E267" s="5" t="inlineStr">
+      <c r="E270" s="5" t="inlineStr">
         <is>
           <t>M-VK-004</t>
         </is>
       </c>
-      <c r="F267" s="6" t="inlineStr">
+      <c r="F270" s="6" t="inlineStr">
         <is>
           <t>Obrubník betonový ABO 100×250×1000 kolem ramp + lůžko z betonu C16/20</t>
         </is>
       </c>
-      <c r="G267" s="4" t="inlineStr">
+      <c r="G270" s="4" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="H267" s="4" t="n">
+      <c r="H270" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="I267" s="6" t="inlineStr">
+      <c r="I270" s="6" t="inlineStr">
         <is>
           <t>~30.0 m  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
         </is>
       </c>
-      <c r="J267" s="6" t="inlineStr"/>
-    </row>
-    <row r="268">
-      <c r="A268" s="3" t="inlineStr">
+      <c r="J270" s="6" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" s="3" t="inlineStr">
         <is>
           <t>→ Liniový žlab pojízdný B125 — SZ + JZ fasáda (40 m)</t>
         </is>
       </c>
     </row>
-    <row r="269">
-      <c r="A269" s="4" t="n">
-        <v>169</v>
-      </c>
-      <c r="B269" s="5" t="inlineStr"/>
-      <c r="C269" s="4" t="n">
+    <row r="272">
+      <c r="A272" s="4" t="n">
+        <v>172</v>
+      </c>
+      <c r="B272" s="5" t="inlineStr"/>
+      <c r="C272" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="D269" s="5" t="inlineStr">
+      <c r="D272" s="5" t="inlineStr">
         <is>
           <t>M-VK</t>
         </is>
       </c>
-      <c r="E269" s="5" t="inlineStr">
+      <c r="E272" s="5" t="inlineStr">
         <is>
           <t>M-VK-012</t>
         </is>
       </c>
-      <c r="F269" s="6" t="inlineStr">
+      <c r="F272" s="6" t="inlineStr">
         <is>
           <t>Liniový žlab POJÍZDNÝ tř. zatížení B125 — odvodnění zpevněných ploch parkoviště + manipulace, vč. mřížky</t>
         </is>
       </c>
-      <c r="G269" s="4" t="inlineStr">
+      <c r="G272" s="4" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="H269" s="4" t="n">
+      <c r="H272" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="I269" s="6" t="inlineStr">
+      <c r="I272" s="6" t="inlineStr">
         <is>
           <t>40 m  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
         </is>
       </c>
-      <c r="J269" s="6" t="inlineStr"/>
-    </row>
-    <row r="270">
-      <c r="A270" s="3" t="inlineStr">
+      <c r="J272" s="6" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="3" t="inlineStr">
         <is>
           <t>→ Vyspádování okolního terénu k odvodnění</t>
         </is>
       </c>
     </row>
-    <row r="271">
-      <c r="A271" s="4" t="n">
-        <v>170</v>
-      </c>
-      <c r="B271" s="5" t="inlineStr"/>
-      <c r="C271" s="4" t="n">
+    <row r="274">
+      <c r="A274" s="4" t="n">
+        <v>173</v>
+      </c>
+      <c r="B274" s="5" t="inlineStr"/>
+      <c r="C274" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="D271" s="5" t="inlineStr">
+      <c r="D274" s="5" t="inlineStr">
         <is>
           <t>M-VK</t>
         </is>
       </c>
-      <c r="E271" s="5" t="inlineStr">
+      <c r="E274" s="5" t="inlineStr">
         <is>
           <t>M-VK-019</t>
         </is>
       </c>
-      <c r="F271" s="6" t="inlineStr">
+      <c r="F274" s="6" t="inlineStr">
         <is>
           <t>Vyspádování okolního terénu k odvodňovacím prvkům (žlabům, retenční nádrži) — hutněná zemina, finální úprava</t>
         </is>
       </c>
-      <c r="G271" s="4" t="inlineStr">
+      <c r="G274" s="4" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="H271" s="4" t="n">
+      <c r="H274" s="4" t="n">
         <v>300</v>
       </c>
-      <c r="I271" s="6" t="inlineStr">
+      <c r="I274" s="6" t="inlineStr">
         <is>
           <t>300 m²  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
         </is>
       </c>
-      <c r="J271" s="6" t="inlineStr"/>
-    </row>
-    <row r="272">
-      <c r="A272" s="3" t="inlineStr">
+      <c r="J274" s="6" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="3" t="inlineStr">
         <is>
           <t>→ Ohumusování + osetí travou zbytkových ploch</t>
         </is>
       </c>
     </row>
-    <row r="273">
-      <c r="A273" s="4" t="n">
-        <v>171</v>
-      </c>
-      <c r="B273" s="5" t="inlineStr"/>
-      <c r="C273" s="4" t="n">
+    <row r="276">
+      <c r="A276" s="4" t="n">
+        <v>174</v>
+      </c>
+      <c r="B276" s="5" t="inlineStr"/>
+      <c r="C276" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="D273" s="5" t="inlineStr">
+      <c r="D276" s="5" t="inlineStr">
         <is>
           <t>M-VK</t>
         </is>
       </c>
-      <c r="E273" s="5" t="inlineStr">
+      <c r="E276" s="5" t="inlineStr">
         <is>
           <t>M-VK-018</t>
         </is>
       </c>
-      <c r="F273" s="6" t="inlineStr">
+      <c r="F276" s="6" t="inlineStr">
         <is>
           <t>Ohumusování tl 100 mm + osetí trávou parkové směsi — rekultivace zbytkových ploch okolo haly</t>
         </is>
       </c>
-      <c r="G273" s="4" t="inlineStr">
+      <c r="G276" s="4" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="H273" s="4" t="n">
+      <c r="H276" s="4" t="n">
         <v>500</v>
       </c>
-      <c r="I273" s="6" t="inlineStr">
+      <c r="I276" s="6" t="inlineStr">
         <is>
           <t>500 m²  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
         </is>
       </c>
-      <c r="J273" s="6" t="inlineStr"/>
+      <c r="J276" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="101">
@@ -7939,7 +8064,6 @@
     <mergeCell ref="A220:J220"/>
     <mergeCell ref="A34:J34"/>
     <mergeCell ref="A83:J83"/>
-    <mergeCell ref="A270:J270"/>
     <mergeCell ref="A222:J222"/>
     <mergeCell ref="A49:J49"/>
     <mergeCell ref="A138:J138"/>
@@ -7948,7 +8072,6 @@
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="A119:J119"/>
     <mergeCell ref="A256:J256"/>
-    <mergeCell ref="A264:J264"/>
     <mergeCell ref="A3:J3"/>
     <mergeCell ref="A95:J95"/>
     <mergeCell ref="A248:J248"/>
@@ -7963,6 +8086,7 @@
     <mergeCell ref="A186:J186"/>
     <mergeCell ref="A24:J24"/>
     <mergeCell ref="A201:J201"/>
+    <mergeCell ref="A275:J275"/>
     <mergeCell ref="A250:J250"/>
     <mergeCell ref="A197:J197"/>
     <mergeCell ref="A110:J110"/>
@@ -7997,9 +8121,9 @@
     <mergeCell ref="A153:J153"/>
     <mergeCell ref="A162:J162"/>
     <mergeCell ref="A227:J227"/>
-    <mergeCell ref="A268:J268"/>
     <mergeCell ref="A164:J164"/>
     <mergeCell ref="A145:J145"/>
+    <mergeCell ref="A267:J267"/>
     <mergeCell ref="A242:J242"/>
     <mergeCell ref="A195:J195"/>
     <mergeCell ref="A76:J76"/>
@@ -8020,16 +8144,17 @@
     <mergeCell ref="A232:J232"/>
     <mergeCell ref="A142:J142"/>
     <mergeCell ref="A216:J216"/>
+    <mergeCell ref="A271:J271"/>
     <mergeCell ref="A65:J65"/>
     <mergeCell ref="A218:J218"/>
     <mergeCell ref="A193:J193"/>
     <mergeCell ref="A80:J80"/>
     <mergeCell ref="A46:J46"/>
+    <mergeCell ref="A273:J273"/>
     <mergeCell ref="A89:J89"/>
     <mergeCell ref="A57:J57"/>
     <mergeCell ref="A235:J235"/>
     <mergeCell ref="A210:J210"/>
-    <mergeCell ref="A272:J272"/>
     <mergeCell ref="A129:J129"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/test-data/hk212_hala/outputs/sequential_list/hk212_sequential_list.xlsx
+++ b/test-data/hk212_hala/outputs/sequential_list/hk212_sequential_list.xlsx
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J270"/>
+  <dimension ref="A1:J276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7329,7 +7329,7 @@
     <row r="254">
       <c r="A254" s="3" t="inlineStr">
         <is>
-          <t>→ Drcený štěrk podklady (rampy + okapní chodník)</t>
+          <t>→ Drcený štěrk podklad ramp</t>
         </is>
       </c>
     </row>
@@ -7372,356 +7372,441 @@
       <c r="J255" s="6" t="inlineStr"/>
     </row>
     <row r="256">
-      <c r="A256" s="10" t="n">
+      <c r="A256" s="3" t="inlineStr">
+        <is>
+          <t>→ Okapní chodník — complete 10-layer stack 0.7 m × 80 m po obvodu haly (výkop → odvoz → pláň → geotextilie → štěrk → hutnění → bednění → výztuž → beton → dilatace, pending ABMV_31 + ABMV_32)</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="4" t="n">
         <v>159</v>
       </c>
-      <c r="B256" s="11" t="inlineStr"/>
-      <c r="C256" s="10" t="n">
+      <c r="B257" s="5" t="inlineStr"/>
+      <c r="C257" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="D256" s="11" t="inlineStr">
+      <c r="D257" s="5" t="inlineStr">
         <is>
           <t>M-VK</t>
         </is>
       </c>
-      <c r="E256" s="11" t="inlineStr">
+      <c r="E257" s="5" t="inlineStr">
+        <is>
+          <t>M-VK-027</t>
+        </is>
+      </c>
+      <c r="F257" s="6" t="inlineStr">
+        <is>
+          <t>Výkop rýhy pro okapní chodník hl. 400 mm (na hloubku všech vrstev)</t>
+        </is>
+      </c>
+      <c r="G257" s="4" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="H257" s="4" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="I257" s="6" t="inlineStr">
+        <is>
+          <t>80.0 × 0.7 × 0.4 = 22.4 m³  [document:A103 řez A-B detail, norma:ČSN 73 6126, norma:ČSN okapový chodník]</t>
+        </is>
+      </c>
+      <c r="J257" s="6" t="inlineStr">
+        <is>
+          <t>ABMV:ABMV_32</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="10" t="n">
+        <v>160</v>
+      </c>
+      <c r="B258" s="11" t="inlineStr"/>
+      <c r="C258" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D258" s="11" t="inlineStr">
+        <is>
+          <t>M-VK</t>
+        </is>
+      </c>
+      <c r="E258" s="11" t="inlineStr">
+        <is>
+          <t>M-VK-028</t>
+        </is>
+      </c>
+      <c r="F258" s="12" t="inlineStr">
+        <is>
+          <t>Odvoz vykopané zeminy z rýhy okapního chodníku na skládku</t>
+        </is>
+      </c>
+      <c r="G258" s="10" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="H258" s="10" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="I258" s="12">
+        <f> 22.4 m³ (1:1 s výkopem)  [document:A103 řez A-B detail, norma:ČSN 73 6126, norma:ČSN okapový chodník]</f>
+        <v/>
+      </c>
+      <c r="J258" s="12" t="inlineStr">
+        <is>
+          <t>ABMV:ABMV_32</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="4" t="n">
+        <v>161</v>
+      </c>
+      <c r="B259" s="5" t="inlineStr"/>
+      <c r="C259" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D259" s="5" t="inlineStr">
+        <is>
+          <t>M-VK</t>
+        </is>
+      </c>
+      <c r="E259" s="5" t="inlineStr">
+        <is>
+          <t>M-VK-024</t>
+        </is>
+      </c>
+      <c r="F259" s="6" t="inlineStr">
+        <is>
+          <t>Úprava zemní pláně + hutnění pod okapní chodník (Edef2 ≥ 30 MPa)</t>
+        </is>
+      </c>
+      <c r="G259" s="4" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="H259" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="I259" s="6" t="inlineStr">
+        <is>
+          <t>80.0 × 0.7 = 56.0 m²  [document:A103 řez A-B detail, norma:ČSN 73 6126, norma:ČSN EN 13670]</t>
+        </is>
+      </c>
+      <c r="J259" s="6" t="inlineStr">
+        <is>
+          <t>ABMV:ABMV_32</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="10" t="n">
+        <v>162</v>
+      </c>
+      <c r="B260" s="11" t="inlineStr"/>
+      <c r="C260" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D260" s="11" t="inlineStr">
+        <is>
+          <t>M-VK</t>
+        </is>
+      </c>
+      <c r="E260" s="11" t="inlineStr">
+        <is>
+          <t>M-VK-029</t>
+        </is>
+      </c>
+      <c r="F260" s="12" t="inlineStr">
+        <is>
+          <t>Geotextilie 300 g/m² separační — mezi hutněnou zemní pláň a štěrkový podklad okapního chodníku</t>
+        </is>
+      </c>
+      <c r="G260" s="10" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="H260" s="10" t="n">
+        <v>56</v>
+      </c>
+      <c r="I260" s="12" t="inlineStr">
+        <is>
+          <t>80.0 × 0.7 = 56.0 m²  [document:A103 řez A-B detail, norma:ČSN 73 6126, norma:ČSN okapový chodník]</t>
+        </is>
+      </c>
+      <c r="J260" s="12" t="inlineStr">
+        <is>
+          <t>ABMV:ABMV_32</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="4" t="n">
+        <v>163</v>
+      </c>
+      <c r="B261" s="5" t="inlineStr"/>
+      <c r="C261" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D261" s="5" t="inlineStr">
+        <is>
+          <t>M-VK</t>
+        </is>
+      </c>
+      <c r="E261" s="5" t="inlineStr">
         <is>
           <t>M-VK-022</t>
         </is>
       </c>
-      <c r="F256" s="12" t="inlineStr">
+      <c r="F261" s="6" t="inlineStr">
         <is>
           <t>Drcený štěrk ŠD 32/63 podklad okapního chodníku tl 150 mm</t>
         </is>
       </c>
-      <c r="G256" s="10" t="inlineStr">
+      <c r="G261" s="4" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="H256" s="10" t="n">
+      <c r="H261" s="4" t="n">
         <v>8.4</v>
       </c>
-      <c r="I256" s="12" t="inlineStr">
+      <c r="I261" s="6" t="inlineStr">
         <is>
           <t>80.0 × 0.7 × 0.15 = 8.40 m³  [document:A103 řezy A-B detail, document:A101 půdorys 1NP, document:C.3 KOO situace]</t>
         </is>
       </c>
-      <c r="J256" s="12" t="inlineStr">
+      <c r="J261" s="6" t="inlineStr">
         <is>
           <t>ABMV:ABMV_31</t>
         </is>
       </c>
     </row>
-    <row r="257">
-      <c r="A257" s="3" t="inlineStr">
-        <is>
-          <t>→ Okapní chodník — sokl 0.7 m × 80 m po obvodu haly (beton + výztuž + dilatace, pending ABMV_31)</t>
-        </is>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" s="4" t="n">
-        <v>160</v>
-      </c>
-      <c r="B258" s="5" t="inlineStr"/>
-      <c r="C258" s="4" t="n">
+    <row r="262">
+      <c r="A262" s="10" t="n">
+        <v>164</v>
+      </c>
+      <c r="B262" s="11" t="inlineStr"/>
+      <c r="C262" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="D258" s="5" t="inlineStr">
+      <c r="D262" s="11" t="inlineStr">
         <is>
           <t>M-VK</t>
         </is>
       </c>
-      <c r="E258" s="5" t="inlineStr">
+      <c r="E262" s="11" t="inlineStr">
+        <is>
+          <t>M-VK-025</t>
+        </is>
+      </c>
+      <c r="F262" s="12" t="inlineStr">
+        <is>
+          <t>Hutnění štěrkového podkladu okapního chodníku vibrodeskou (Edef2 ≥ 45 MPa)</t>
+        </is>
+      </c>
+      <c r="G262" s="10" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="H262" s="10" t="n">
+        <v>56</v>
+      </c>
+      <c r="I262" s="12" t="inlineStr">
+        <is>
+          <t>80.0 × 0.7 = 56.0 m²  [document:A103 řez A-B detail, norma:ČSN 73 6126, norma:ČSN EN 13670]</t>
+        </is>
+      </c>
+      <c r="J262" s="12" t="inlineStr">
+        <is>
+          <t>ABMV:ABMV_32</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="4" t="n">
+        <v>165</v>
+      </c>
+      <c r="B263" s="5" t="inlineStr"/>
+      <c r="C263" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D263" s="5" t="inlineStr">
+        <is>
+          <t>M-VK</t>
+        </is>
+      </c>
+      <c r="E263" s="5" t="inlineStr">
+        <is>
+          <t>M-VK-026</t>
+        </is>
+      </c>
+      <c r="F263" s="6" t="inlineStr">
+        <is>
+          <t>Bednění boční vnější hrana okapního chodníku v 200 mm (vnitřní hrana = stěna haly)</t>
+        </is>
+      </c>
+      <c r="G263" s="4" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="H263" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="I263" s="6" t="inlineStr">
+        <is>
+          <t>80.0 × 0.2 = 16.0 m²  [document:A103 řez A-B detail, norma:ČSN 73 6126, norma:ČSN EN 13670]</t>
+        </is>
+      </c>
+      <c r="J263" s="6" t="inlineStr">
+        <is>
+          <t>ABMV:ABMV_32</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="10" t="n">
+        <v>166</v>
+      </c>
+      <c r="B264" s="11" t="inlineStr"/>
+      <c r="C264" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D264" s="11" t="inlineStr">
+        <is>
+          <t>M-VK</t>
+        </is>
+      </c>
+      <c r="E264" s="11" t="inlineStr">
+        <is>
+          <t>M-VK-021</t>
+        </is>
+      </c>
+      <c r="F264" s="12" t="inlineStr">
+        <is>
+          <t>Výztuž KARI síť Q188 (150/150/6 mm) — okapní chodník</t>
+        </is>
+      </c>
+      <c r="G264" s="10" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="H264" s="10" t="n">
+        <v>56</v>
+      </c>
+      <c r="I264" s="12" t="inlineStr">
+        <is>
+          <t>80.0 × 0.7 = 56.00 m²  [document:A103 řezy A-B detail, document:A101 půdorys 1NP, document:C.3 KOO situace]</t>
+        </is>
+      </c>
+      <c r="J264" s="12" t="inlineStr">
+        <is>
+          <t>ABMV:ABMV_31</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="4" t="n">
+        <v>167</v>
+      </c>
+      <c r="B265" s="5" t="inlineStr"/>
+      <c r="C265" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D265" s="5" t="inlineStr">
+        <is>
+          <t>M-VK</t>
+        </is>
+      </c>
+      <c r="E265" s="5" t="inlineStr">
         <is>
           <t>M-VK-020</t>
         </is>
       </c>
-      <c r="F258" s="6" t="inlineStr">
+      <c r="F265" s="6" t="inlineStr">
         <is>
           <t>Beton C25/30 XF3 — okapní chodník po obvodu haly (sokl 0.7 m × ~80 m mimo 4 vstupy), tl 200 mm</t>
         </is>
       </c>
-      <c r="G258" s="4" t="inlineStr">
+      <c r="G265" s="4" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="H258" s="4" t="n">
+      <c r="H265" s="4" t="n">
         <v>11.2</v>
       </c>
-      <c r="I258" s="6" t="inlineStr">
+      <c r="I265" s="6" t="inlineStr">
         <is>
           <t>80.0 × 0.7 × 0.2 = 11.20 m³  [document:A103 řezy A-B detail, document:A101 půdorys 1NP, document:C.3 KOO situace]</t>
         </is>
       </c>
-      <c r="J258" s="6" t="inlineStr">
+      <c r="J265" s="6" t="inlineStr">
         <is>
           <t>ABMV:ABMV_31</t>
         </is>
       </c>
     </row>
-    <row r="259">
-      <c r="A259" s="10" t="n">
-        <v>161</v>
-      </c>
-      <c r="B259" s="11" t="inlineStr"/>
-      <c r="C259" s="10" t="n">
+    <row r="266">
+      <c r="A266" s="10" t="n">
+        <v>168</v>
+      </c>
+      <c r="B266" s="11" t="inlineStr"/>
+      <c r="C266" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="D259" s="11" t="inlineStr">
+      <c r="D266" s="11" t="inlineStr">
         <is>
           <t>M-VK</t>
         </is>
       </c>
-      <c r="E259" s="11" t="inlineStr">
-        <is>
-          <t>M-VK-021</t>
-        </is>
-      </c>
-      <c r="F259" s="12" t="inlineStr">
-        <is>
-          <t>Výztuž KARI síť Q188 + boční bednění + dilatační lišty — okapní chodník</t>
-        </is>
-      </c>
-      <c r="G259" s="10" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="H259" s="10" t="n">
-        <v>56</v>
-      </c>
-      <c r="I259" s="12" t="inlineStr">
-        <is>
-          <t>80.0 × 0.7 = 56.00 m²  [document:A103 řezy A-B detail, document:A101 půdorys 1NP, document:C.3 KOO situace]</t>
-        </is>
-      </c>
-      <c r="J259" s="12" t="inlineStr">
+      <c r="E266" s="11" t="inlineStr">
+        <is>
+          <t>M-VK-023</t>
+        </is>
+      </c>
+      <c r="F266" s="12" t="inlineStr">
+        <is>
+          <t>Dilatační lišty + těsnění spár mezi segmenty okapního chodníku (à ~4 m)</t>
+        </is>
+      </c>
+      <c r="G266" s="10" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="H266" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="I266" s="12" t="inlineStr">
+        <is>
+          <t>80.0 / 4 = 20 ks dilatací  [document:A103 řezy A-B detail, document:A101 půdorys 1NP, document:C.3 KOO situace]</t>
+        </is>
+      </c>
+      <c r="J266" s="12" t="inlineStr">
         <is>
           <t>ABMV:ABMV_31</t>
         </is>
       </c>
-    </row>
-    <row r="260">
-      <c r="A260" s="4" t="n">
-        <v>162</v>
-      </c>
-      <c r="B260" s="5" t="inlineStr"/>
-      <c r="C260" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="D260" s="5" t="inlineStr">
-        <is>
-          <t>M-VK</t>
-        </is>
-      </c>
-      <c r="E260" s="5" t="inlineStr">
-        <is>
-          <t>M-VK-023</t>
-        </is>
-      </c>
-      <c r="F260" s="6" t="inlineStr">
-        <is>
-          <t>Dilatační lišty + těsnění spár mezi segmenty okapního chodníku (à ~4 m)</t>
-        </is>
-      </c>
-      <c r="G260" s="4" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="H260" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="I260" s="6" t="inlineStr">
-        <is>
-          <t>80.0 / 4 = 20 ks dilatací  [document:A103 řezy A-B detail, document:A101 půdorys 1NP, document:C.3 KOO situace]</t>
-        </is>
-      </c>
-      <c r="J260" s="6" t="inlineStr">
-        <is>
-          <t>ABMV:ABMV_31</t>
-        </is>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" s="3" t="inlineStr">
-        <is>
-          <t>→ Rampy 4× (R1-R4) — výztuž + bednění + beton + obrubník (per A101)</t>
-        </is>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" s="4" t="n">
-        <v>163</v>
-      </c>
-      <c r="B262" s="5" t="inlineStr"/>
-      <c r="C262" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="D262" s="5" t="inlineStr">
-        <is>
-          <t>M-VK</t>
-        </is>
-      </c>
-      <c r="E262" s="5" t="inlineStr">
-        <is>
-          <t>M-VK-002</t>
-        </is>
-      </c>
-      <c r="F262" s="6" t="inlineStr">
-        <is>
-          <t>Výztuž KARI síť Q188 + bednění boční rampy 4 lokality</t>
-        </is>
-      </c>
-      <c r="G262" s="4" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="H262" s="4" t="n">
-        <v>43.32</v>
-      </c>
-      <c r="I262" s="6" t="inlineStr">
-        <is>
-          <t>4 lokality rampy = 43.32 m²  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
-        </is>
-      </c>
-      <c r="J262" s="6" t="inlineStr"/>
-    </row>
-    <row r="263">
-      <c r="A263" s="10" t="n">
-        <v>164</v>
-      </c>
-      <c r="B263" s="11" t="inlineStr"/>
-      <c r="C263" s="10" t="n">
-        <v>12</v>
-      </c>
-      <c r="D263" s="11" t="inlineStr">
-        <is>
-          <t>M-VK</t>
-        </is>
-      </c>
-      <c r="E263" s="11" t="inlineStr">
-        <is>
-          <t>M-VK-001</t>
-        </is>
-      </c>
-      <c r="F263" s="12" t="inlineStr">
-        <is>
-          <t>Beton C25/30 XF3 — vstupní/nájezdové rampy tl 150 mm, 4 lokality (R1 sever, R2+R3 jih, R4 západ bezbariérová)</t>
-        </is>
-      </c>
-      <c r="G263" s="10" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="H263" s="10" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I263" s="12" t="inlineStr">
-        <is>
-          <t>(9.2+11.5+9.2+13.42) × 0.15 = 6.50 m³  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
-        </is>
-      </c>
-      <c r="J263" s="12" t="inlineStr"/>
-    </row>
-    <row r="264">
-      <c r="A264" s="4" t="n">
-        <v>165</v>
-      </c>
-      <c r="B264" s="5" t="inlineStr"/>
-      <c r="C264" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="D264" s="5" t="inlineStr">
-        <is>
-          <t>M-VK</t>
-        </is>
-      </c>
-      <c r="E264" s="5" t="inlineStr">
-        <is>
-          <t>M-VK-004</t>
-        </is>
-      </c>
-      <c r="F264" s="6" t="inlineStr">
-        <is>
-          <t>Obrubník betonový ABO 100×250×1000 kolem ramp + lůžko z betonu C16/20</t>
-        </is>
-      </c>
-      <c r="G264" s="4" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="H264" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="I264" s="6" t="inlineStr">
-        <is>
-          <t>~30.0 m  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
-        </is>
-      </c>
-      <c r="J264" s="6" t="inlineStr"/>
-    </row>
-    <row r="265">
-      <c r="A265" s="3" t="inlineStr">
-        <is>
-          <t>→ Liniový žlab pojízdný B125 — SZ + JZ fasáda (40 m)</t>
-        </is>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" s="4" t="n">
-        <v>166</v>
-      </c>
-      <c r="B266" s="5" t="inlineStr"/>
-      <c r="C266" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="D266" s="5" t="inlineStr">
-        <is>
-          <t>M-VK</t>
-        </is>
-      </c>
-      <c r="E266" s="5" t="inlineStr">
-        <is>
-          <t>M-VK-012</t>
-        </is>
-      </c>
-      <c r="F266" s="6" t="inlineStr">
-        <is>
-          <t>Liniový žlab POJÍZDNÝ tř. zatížení B125 — odvodnění zpevněných ploch parkoviště + manipulace, vč. mřížky</t>
-        </is>
-      </c>
-      <c r="G266" s="4" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="H266" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="I266" s="6" t="inlineStr">
-        <is>
-          <t>40 m  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
-        </is>
-      </c>
-      <c r="J266" s="6" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" s="3" t="inlineStr">
         <is>
-          <t>→ Vyspádování okolního terénu k odvodnění</t>
+          <t>→ Rampy 4× (R1-R4) — výztuž + bednění + beton + obrubník (per A101)</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="4" t="n">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B268" s="5" t="inlineStr"/>
       <c r="C268" s="4" t="n">
@@ -7734,12 +7819,12 @@
       </c>
       <c r="E268" s="5" t="inlineStr">
         <is>
-          <t>M-VK-019</t>
+          <t>M-VK-002</t>
         </is>
       </c>
       <c r="F268" s="6" t="inlineStr">
         <is>
-          <t>Vyspádování okolního terénu k odvodňovacím prvkům (žlabům, retenční nádrži) — hutněná zemina, finální úprava</t>
+          <t>Výztuž KARI síť Q188 + bednění boční rampy 4 lokality</t>
         </is>
       </c>
       <c r="G268" s="4" t="inlineStr">
@@ -7748,25 +7833,56 @@
         </is>
       </c>
       <c r="H268" s="4" t="n">
-        <v>300</v>
+        <v>43.32</v>
       </c>
       <c r="I268" s="6" t="inlineStr">
         <is>
-          <t>300 m²  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
+          <t>4 lokality rampy = 43.32 m²  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
         </is>
       </c>
       <c r="J268" s="6" t="inlineStr"/>
     </row>
     <row r="269">
-      <c r="A269" s="3" t="inlineStr">
-        <is>
-          <t>→ Ohumusování + osetí travou zbytkových ploch</t>
-        </is>
-      </c>
+      <c r="A269" s="10" t="n">
+        <v>170</v>
+      </c>
+      <c r="B269" s="11" t="inlineStr"/>
+      <c r="C269" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D269" s="11" t="inlineStr">
+        <is>
+          <t>M-VK</t>
+        </is>
+      </c>
+      <c r="E269" s="11" t="inlineStr">
+        <is>
+          <t>M-VK-001</t>
+        </is>
+      </c>
+      <c r="F269" s="12" t="inlineStr">
+        <is>
+          <t>Beton C25/30 XF3 — vstupní/nájezdové rampy tl 150 mm, 4 lokality (R1 sever, R2+R3 jih, R4 západ bezbariérová)</t>
+        </is>
+      </c>
+      <c r="G269" s="10" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="H269" s="10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I269" s="12" t="inlineStr">
+        <is>
+          <t>(9.2+11.5+9.2+13.42) × 0.15 = 6.50 m³  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
+        </is>
+      </c>
+      <c r="J269" s="12" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" s="4" t="n">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B270" s="5" t="inlineStr"/>
       <c r="C270" s="4" t="n">
@@ -7779,28 +7895,163 @@
       </c>
       <c r="E270" s="5" t="inlineStr">
         <is>
+          <t>M-VK-004</t>
+        </is>
+      </c>
+      <c r="F270" s="6" t="inlineStr">
+        <is>
+          <t>Obrubník betonový ABO 100×250×1000 kolem ramp + lůžko z betonu C16/20</t>
+        </is>
+      </c>
+      <c r="G270" s="4" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="H270" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="I270" s="6" t="inlineStr">
+        <is>
+          <t>~30.0 m  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
+        </is>
+      </c>
+      <c r="J270" s="6" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" s="3" t="inlineStr">
+        <is>
+          <t>→ Liniový žlab pojízdný B125 — SZ + JZ fasáda (40 m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="4" t="n">
+        <v>172</v>
+      </c>
+      <c r="B272" s="5" t="inlineStr"/>
+      <c r="C272" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D272" s="5" t="inlineStr">
+        <is>
+          <t>M-VK</t>
+        </is>
+      </c>
+      <c r="E272" s="5" t="inlineStr">
+        <is>
+          <t>M-VK-012</t>
+        </is>
+      </c>
+      <c r="F272" s="6" t="inlineStr">
+        <is>
+          <t>Liniový žlab POJÍZDNÝ tř. zatížení B125 — odvodnění zpevněných ploch parkoviště + manipulace, vč. mřížky</t>
+        </is>
+      </c>
+      <c r="G272" s="4" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="H272" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="I272" s="6" t="inlineStr">
+        <is>
+          <t>40 m  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
+        </is>
+      </c>
+      <c r="J272" s="6" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="3" t="inlineStr">
+        <is>
+          <t>→ Vyspádování okolního terénu k odvodnění</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="4" t="n">
+        <v>173</v>
+      </c>
+      <c r="B274" s="5" t="inlineStr"/>
+      <c r="C274" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D274" s="5" t="inlineStr">
+        <is>
+          <t>M-VK</t>
+        </is>
+      </c>
+      <c r="E274" s="5" t="inlineStr">
+        <is>
+          <t>M-VK-019</t>
+        </is>
+      </c>
+      <c r="F274" s="6" t="inlineStr">
+        <is>
+          <t>Vyspádování okolního terénu k odvodňovacím prvkům (žlabům, retenční nádrži) — hutněná zemina, finální úprava</t>
+        </is>
+      </c>
+      <c r="G274" s="4" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="H274" s="4" t="n">
+        <v>300</v>
+      </c>
+      <c r="I274" s="6" t="inlineStr">
+        <is>
+          <t>300 m²  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
+        </is>
+      </c>
+      <c r="J274" s="6" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="3" t="inlineStr">
+        <is>
+          <t>→ Ohumusování + osetí travou zbytkových ploch</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="4" t="n">
+        <v>174</v>
+      </c>
+      <c r="B276" s="5" t="inlineStr"/>
+      <c r="C276" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D276" s="5" t="inlineStr">
+        <is>
+          <t>M-VK</t>
+        </is>
+      </c>
+      <c r="E276" s="5" t="inlineStr">
+        <is>
           <t>M-VK-018</t>
         </is>
       </c>
-      <c r="F270" s="6" t="inlineStr">
+      <c r="F276" s="6" t="inlineStr">
         <is>
           <t>Ohumusování tl 100 mm + osetí trávou parkové směsi — rekultivace zbytkových ploch okolo haly</t>
         </is>
       </c>
-      <c r="G270" s="4" t="inlineStr">
+      <c r="G276" s="4" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="H270" s="4" t="n">
+      <c r="H276" s="4" t="n">
         <v>500</v>
       </c>
-      <c r="I270" s="6" t="inlineStr">
+      <c r="I276" s="6" t="inlineStr">
         <is>
           <t>500 m²  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
         </is>
       </c>
-      <c r="J270" s="6" t="inlineStr"/>
+      <c r="J276" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="101">
@@ -7813,7 +8064,6 @@
     <mergeCell ref="A220:J220"/>
     <mergeCell ref="A34:J34"/>
     <mergeCell ref="A83:J83"/>
-    <mergeCell ref="A261:J261"/>
     <mergeCell ref="A222:J222"/>
     <mergeCell ref="A49:J49"/>
     <mergeCell ref="A138:J138"/>
@@ -7821,6 +8071,7 @@
     <mergeCell ref="A36:J36"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="A119:J119"/>
+    <mergeCell ref="A256:J256"/>
     <mergeCell ref="A3:J3"/>
     <mergeCell ref="A95:J95"/>
     <mergeCell ref="A248:J248"/>
@@ -7828,15 +8079,14 @@
     <mergeCell ref="A159:J159"/>
     <mergeCell ref="A29:J29"/>
     <mergeCell ref="A96:J96"/>
-    <mergeCell ref="A265:J265"/>
     <mergeCell ref="A147:J147"/>
     <mergeCell ref="A121:J121"/>
     <mergeCell ref="A202:J202"/>
     <mergeCell ref="A58:J58"/>
     <mergeCell ref="A186:J186"/>
-    <mergeCell ref="A257:J257"/>
     <mergeCell ref="A24:J24"/>
     <mergeCell ref="A201:J201"/>
+    <mergeCell ref="A275:J275"/>
     <mergeCell ref="A250:J250"/>
     <mergeCell ref="A197:J197"/>
     <mergeCell ref="A110:J110"/>
@@ -7880,7 +8130,6 @@
     <mergeCell ref="A33:J33"/>
     <mergeCell ref="A85:J85"/>
     <mergeCell ref="A116:J116"/>
-    <mergeCell ref="A269:J269"/>
     <mergeCell ref="A8:J8"/>
     <mergeCell ref="A188:J188"/>
     <mergeCell ref="A126:J126"/>
@@ -7895,11 +8144,13 @@
     <mergeCell ref="A232:J232"/>
     <mergeCell ref="A142:J142"/>
     <mergeCell ref="A216:J216"/>
+    <mergeCell ref="A271:J271"/>
     <mergeCell ref="A65:J65"/>
     <mergeCell ref="A218:J218"/>
     <mergeCell ref="A193:J193"/>
     <mergeCell ref="A80:J80"/>
     <mergeCell ref="A46:J46"/>
+    <mergeCell ref="A273:J273"/>
     <mergeCell ref="A89:J89"/>
     <mergeCell ref="A57:J57"/>
     <mergeCell ref="A235:J235"/>

--- a/test-data/hk212_hala/outputs/sequential_list/hk212_sequential_list.xlsx
+++ b/test-data/hk212_hala/outputs/sequential_list/hk212_sequential_list.xlsx
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J276"/>
+  <dimension ref="A1:J340"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7020,14 +7020,14 @@
     <row r="242" ht="22" customHeight="1">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>═══ FÁZE 12: VENKOVNÍ ÚPRAVY (SO-13) — minimal scope per user decision 2026-05-27 ═══</t>
+          <t>═══ FÁZE 12: VENKOVNÍ ÚPRAVY + ZTI (SO-13 + SO-14) — VV authoritative + norm-verified ═══</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="3" t="inlineStr">
         <is>
-          <t>→ Externí přípojky — výkop + potrubí (paralelně se ZS)</t>
+          <t>→ ZTI vnější — kanalizace čerpaná (potrubí + přečerpávací stanice + zemní práce)</t>
         </is>
       </c>
     </row>
@@ -7041,30 +7041,30 @@
       </c>
       <c r="D244" s="5" t="inlineStr">
         <is>
-          <t>M-VK</t>
+          <t>M-ZTI</t>
         </is>
       </c>
       <c r="E244" s="5" t="inlineStr">
         <is>
-          <t>M-VK-005</t>
+          <t>M-ZTI-032</t>
         </is>
       </c>
       <c r="F244" s="6" t="inlineStr">
         <is>
-          <t>Přípojka kanalizace dešťové KG PVC SN8 DN200 — potrubí + uložení v pískovém loži + zásyp + napojení</t>
+          <t>Plastové potrubí PE100 SDR11 d50 (50×4,5 mm) vč. montáže a tvarovek</t>
         </is>
       </c>
       <c r="G244" s="4" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="H244" s="4" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="I244" s="6" t="inlineStr">
         <is>
-          <t>40 m  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
+          <t>VV P1.2c = 8.0 bm  [document:VV výkaz výměr]</t>
         </is>
       </c>
       <c r="J244" s="6" t="inlineStr"/>
@@ -7079,30 +7079,30 @@
       </c>
       <c r="D245" s="11" t="inlineStr">
         <is>
-          <t>M-VK</t>
+          <t>M-ZTI</t>
         </is>
       </c>
       <c r="E245" s="11" t="inlineStr">
         <is>
-          <t>M-VK-006</t>
+          <t>M-ZTI-033</t>
         </is>
       </c>
       <c r="F245" s="12" t="inlineStr">
         <is>
-          <t>Přípojka kanalizace splaškové KG PVC SN8 DN150 — potrubí + uložení + zásyp + napojení</t>
+          <t>Navrtávací pas 75/40</t>
         </is>
       </c>
       <c r="G245" s="10" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="H245" s="10" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="I245" s="12" t="inlineStr">
         <is>
-          <t>30 m  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
+          <t>VV P1.3c = 1.0 ks  [document:VV výkaz výměr]</t>
         </is>
       </c>
       <c r="J245" s="12" t="inlineStr"/>
@@ -7117,30 +7117,30 @@
       </c>
       <c r="D246" s="5" t="inlineStr">
         <is>
-          <t>M-VK</t>
+          <t>M-ZTI</t>
         </is>
       </c>
       <c r="E246" s="5" t="inlineStr">
         <is>
-          <t>M-VK-008</t>
+          <t>M-ZTI-034</t>
         </is>
       </c>
       <c r="F246" s="6" t="inlineStr">
         <is>
-          <t>Přípojka NN — chránička HDPE Ø110 mm + pomocné výkopy + pískové lože + zásyp + výstražná páska</t>
+          <t>Automatická přečerpávací stanice tlakové kanalizace vč. jímky, vystrojení a řídící jednotky (např. Tlakan P2 smart, kpl)</t>
         </is>
       </c>
       <c r="G246" s="4" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="H246" s="4" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="I246" s="6" t="inlineStr">
         <is>
-          <t>40 m  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
+          <t>VV P1.4c = 1.0 kpl  [document:VV výkaz výměr]</t>
         </is>
       </c>
       <c r="J246" s="6" t="inlineStr"/>
@@ -7155,658 +7155,766 @@
       </c>
       <c r="D247" s="11" t="inlineStr">
         <is>
-          <t>M-VK</t>
+          <t>M-ZTI</t>
         </is>
       </c>
       <c r="E247" s="11" t="inlineStr">
         <is>
-          <t>M-VK-007</t>
+          <t>M-ZTI-035</t>
         </is>
       </c>
       <c r="F247" s="12" t="inlineStr">
         <is>
-          <t>Revizní šachta betonová Ø1000 mm, h ~1.5-2.0 m, vč. poklopu litinového B125 a vnitřních stupadel</t>
+          <t>Výkop pro pokládku potrubí šířky 1 m, pažený</t>
         </is>
       </c>
       <c r="G247" s="10" t="inlineStr">
         <is>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="H247" s="10" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="I247" s="12" t="inlineStr">
+        <is>
+          <t>VV P1.5c = 12.8 bm  [document:VV výkaz výměr]</t>
+        </is>
+      </c>
+      <c r="J247" s="12" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="4" t="n">
+        <v>155</v>
+      </c>
+      <c r="B248" s="5" t="inlineStr"/>
+      <c r="C248" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D248" s="5" t="inlineStr">
+        <is>
+          <t>M-ZTI</t>
+        </is>
+      </c>
+      <c r="E248" s="5" t="inlineStr">
+        <is>
+          <t>M-ZTI-036</t>
+        </is>
+      </c>
+      <c r="F248" s="6" t="inlineStr">
+        <is>
+          <t>Pískový podsyp frakce 0–16 mm, výška 0,1 m, zhutnění</t>
+        </is>
+      </c>
+      <c r="G248" s="4" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="H248" s="4" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="I248" s="6" t="inlineStr">
+        <is>
+          <t>VV P1.6c = 1.28 m³  [document:VV výkaz výměr]</t>
+        </is>
+      </c>
+      <c r="J248" s="6" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="10" t="n">
+        <v>156</v>
+      </c>
+      <c r="B249" s="11" t="inlineStr"/>
+      <c r="C249" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D249" s="11" t="inlineStr">
+        <is>
+          <t>M-ZTI</t>
+        </is>
+      </c>
+      <c r="E249" s="11" t="inlineStr">
+        <is>
+          <t>M-ZTI-037</t>
+        </is>
+      </c>
+      <c r="F249" s="12" t="inlineStr">
+        <is>
+          <t>Pískový obsyp frakce 0–16 mm bez ostrých zrn, výška 0,2 m, zhutnění</t>
+        </is>
+      </c>
+      <c r="G249" s="10" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="H249" s="10" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="I249" s="12" t="inlineStr">
+        <is>
+          <t>VV P1.7c = 3.84 m³  [document:VV výkaz výměr]</t>
+        </is>
+      </c>
+      <c r="J249" s="12" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="4" t="n">
+        <v>157</v>
+      </c>
+      <c r="B250" s="5" t="inlineStr"/>
+      <c r="C250" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D250" s="5" t="inlineStr">
+        <is>
+          <t>M-ZTI</t>
+        </is>
+      </c>
+      <c r="E250" s="5" t="inlineStr">
+        <is>
+          <t>M-ZTI-038</t>
+        </is>
+      </c>
+      <c r="F250" s="6" t="inlineStr">
+        <is>
+          <t>Konečný zához výkopu zeminou</t>
+        </is>
+      </c>
+      <c r="G250" s="4" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="H250" s="4" t="n">
+        <v>7.68</v>
+      </c>
+      <c r="I250" s="6" t="inlineStr">
+        <is>
+          <t>VV P1.8c = 7.68 kpl  [document:VV výkaz výměr]</t>
+        </is>
+      </c>
+      <c r="J250" s="6" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="10" t="n">
+        <v>158</v>
+      </c>
+      <c r="B251" s="11" t="inlineStr"/>
+      <c r="C251" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D251" s="11" t="inlineStr">
+        <is>
+          <t>M-ZTI</t>
+        </is>
+      </c>
+      <c r="E251" s="11" t="inlineStr">
+        <is>
+          <t>M-ZTI-039</t>
+        </is>
+      </c>
+      <c r="F251" s="12" t="inlineStr">
+        <is>
+          <t>Odvoz a uskladnění přebytečného výkopového materiálu</t>
+        </is>
+      </c>
+      <c r="G251" s="10" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="H251" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I251" s="12" t="inlineStr">
+        <is>
+          <t>VV P1.10c = 1.0 kpl  [document:VV výkaz výměr]</t>
+        </is>
+      </c>
+      <c r="J251" s="12" t="inlineStr"/>
+    </row>
+    <row r="252">
+      <c r="A252" s="4" t="n">
+        <v>159</v>
+      </c>
+      <c r="B252" s="5" t="inlineStr"/>
+      <c r="C252" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D252" s="5" t="inlineStr">
+        <is>
+          <t>M-ZTI</t>
+        </is>
+      </c>
+      <c r="E252" s="5" t="inlineStr">
+        <is>
+          <t>M-ZTI-040</t>
+        </is>
+      </c>
+      <c r="F252" s="6" t="inlineStr">
+        <is>
+          <t>Montážní a pomocný materiál (součást zemních a pomocných prací)</t>
+        </is>
+      </c>
+      <c r="G252" s="4" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="H252" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I252" s="6" t="inlineStr">
+        <is>
+          <t>VV P1.11c = 1.0 kpl  [document:VV výkaz výměr]</t>
+        </is>
+      </c>
+      <c r="J252" s="6" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="A253" s="10" t="n">
+        <v>160</v>
+      </c>
+      <c r="B253" s="11" t="inlineStr"/>
+      <c r="C253" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D253" s="11" t="inlineStr">
+        <is>
+          <t>M-ZTI</t>
+        </is>
+      </c>
+      <c r="E253" s="11" t="inlineStr">
+        <is>
+          <t>M-ZTI-041</t>
+        </is>
+      </c>
+      <c r="F253" s="12" t="inlineStr">
+        <is>
+          <t>Ostatní práce</t>
+        </is>
+      </c>
+      <c r="G253" s="10" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="H253" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I253" s="12" t="inlineStr">
+        <is>
+          <t>VV P.2.2 = 1.0 kpl  [document:VV výkaz výměr]</t>
+        </is>
+      </c>
+      <c r="J253" s="12" t="inlineStr"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="4" t="n">
+        <v>161</v>
+      </c>
+      <c r="B254" s="5" t="inlineStr"/>
+      <c r="C254" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D254" s="5" t="inlineStr">
+        <is>
+          <t>M-ZTI</t>
+        </is>
+      </c>
+      <c r="E254" s="5" t="inlineStr">
+        <is>
+          <t>M-ZTI-042</t>
+        </is>
+      </c>
+      <c r="F254" s="6" t="inlineStr">
+        <is>
+          <t>Identifikace, vytyčení a průkaz stávajících sítí ve výkopem dotčeném území vč. příp. projektové činnosti</t>
+        </is>
+      </c>
+      <c r="G254" s="4" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="H254" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I254" s="6" t="inlineStr">
+        <is>
+          <t>VV P.2.3 = 1.0 kpl  [document:VV výkaz výměr]</t>
+        </is>
+      </c>
+      <c r="J254" s="6" t="inlineStr"/>
+    </row>
+    <row r="255">
+      <c r="A255" s="10" t="n">
+        <v>162</v>
+      </c>
+      <c r="B255" s="11" t="inlineStr"/>
+      <c r="C255" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D255" s="11" t="inlineStr">
+        <is>
+          <t>M-ZTI</t>
+        </is>
+      </c>
+      <c r="E255" s="11" t="inlineStr">
+        <is>
+          <t>M-ZTI-043</t>
+        </is>
+      </c>
+      <c r="F255" s="12" t="inlineStr">
+        <is>
+          <t>Inženýrská činnost vč. mapových podkladů, správních poplatků atd.</t>
+        </is>
+      </c>
+      <c r="G255" s="10" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="H255" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I255" s="12" t="inlineStr">
+        <is>
+          <t>VV P.2.4 = 1.0 kpl  [document:VV výkaz výměr]</t>
+        </is>
+      </c>
+      <c r="J255" s="12" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="A256" s="4" t="n">
+        <v>163</v>
+      </c>
+      <c r="B256" s="5" t="inlineStr"/>
+      <c r="C256" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D256" s="5" t="inlineStr">
+        <is>
+          <t>M-ZTI</t>
+        </is>
+      </c>
+      <c r="E256" s="5" t="inlineStr">
+        <is>
+          <t>M-ZTI-044</t>
+        </is>
+      </c>
+      <c r="F256" s="6" t="inlineStr">
+        <is>
+          <t>Dílenská dokumentace</t>
+        </is>
+      </c>
+      <c r="G256" s="4" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="H256" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I256" s="6" t="inlineStr">
+        <is>
+          <t>VV P.2.5 = 1.0 kpl  [document:VV výkaz výměr]</t>
+        </is>
+      </c>
+      <c r="J256" s="6" t="inlineStr"/>
+    </row>
+    <row r="257">
+      <c r="A257" s="10" t="n">
+        <v>164</v>
+      </c>
+      <c r="B257" s="11" t="inlineStr"/>
+      <c r="C257" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D257" s="11" t="inlineStr">
+        <is>
+          <t>M-ZTI</t>
+        </is>
+      </c>
+      <c r="E257" s="11" t="inlineStr">
+        <is>
+          <t>M-ZTI-045</t>
+        </is>
+      </c>
+      <c r="F257" s="12" t="inlineStr">
+        <is>
+          <t>Dokumentace skutečného provedení</t>
+        </is>
+      </c>
+      <c r="G257" s="10" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="H257" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I257" s="12" t="inlineStr">
+        <is>
+          <t>VV P.2.6 = 1.0 kpl  [document:VV výkaz výměr]</t>
+        </is>
+      </c>
+      <c r="J257" s="12" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="4" t="n">
+        <v>165</v>
+      </c>
+      <c r="B258" s="5" t="inlineStr"/>
+      <c r="C258" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D258" s="5" t="inlineStr">
+        <is>
+          <t>M-ZTI</t>
+        </is>
+      </c>
+      <c r="E258" s="5" t="inlineStr">
+        <is>
+          <t>M-ZTI-046</t>
+        </is>
+      </c>
+      <c r="F258" s="6" t="inlineStr">
+        <is>
+          <t>Zkouška těsnosti kanalizace</t>
+        </is>
+      </c>
+      <c r="G258" s="4" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="H258" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I258" s="6" t="inlineStr">
+        <is>
+          <t>VV P.2.7 = 1.0 kpl  [document:VV výkaz výměr]</t>
+        </is>
+      </c>
+      <c r="J258" s="6" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="3" t="inlineStr">
+        <is>
+          <t>→ ZTI vnější — vodovod (PE100 + armatury + zemní práce)</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="4" t="n">
+        <v>166</v>
+      </c>
+      <c r="B260" s="5" t="inlineStr"/>
+      <c r="C260" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D260" s="5" t="inlineStr">
+        <is>
+          <t>M-ZTI</t>
+        </is>
+      </c>
+      <c r="E260" s="5" t="inlineStr">
+        <is>
+          <t>M-ZTI-047</t>
+        </is>
+      </c>
+      <c r="F260" s="6" t="inlineStr">
+        <is>
+          <t>Plastové potrubí PE100 SDR11 d50 (50×4,6 mm) vč. montáže a tvarovek</t>
+        </is>
+      </c>
+      <c r="G260" s="4" t="inlineStr">
+        <is>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="H260" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="I260" s="6" t="inlineStr">
+        <is>
+          <t>VV P1.2d = 10.0 bm  [document:VV výkaz výměr]</t>
+        </is>
+      </c>
+      <c r="J260" s="6" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" s="10" t="n">
+        <v>167</v>
+      </c>
+      <c r="B261" s="11" t="inlineStr"/>
+      <c r="C261" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D261" s="11" t="inlineStr">
+        <is>
+          <t>M-ZTI</t>
+        </is>
+      </c>
+      <c r="E261" s="11" t="inlineStr">
+        <is>
+          <t>M-ZTI-048</t>
+        </is>
+      </c>
+      <c r="F261" s="12" t="inlineStr">
+        <is>
+          <t>Navrtávací pas 110/50</t>
+        </is>
+      </c>
+      <c r="G261" s="10" t="inlineStr">
+        <is>
           <t>ks</t>
         </is>
       </c>
-      <c r="H247" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="I247" s="12" t="inlineStr">
-        <is>
-          <t>3 ks  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
-        </is>
-      </c>
-      <c r="J247" s="12" t="inlineStr"/>
-    </row>
-    <row r="248">
-      <c r="A248" s="3" t="inlineStr">
-        <is>
-          <t>→ Přeložka vodovodního řadu (PODMÍNĚNÁ — pending ABMV_23)</t>
-        </is>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" s="7" t="n">
-        <v>155</v>
-      </c>
-      <c r="B249" s="8" t="inlineStr"/>
-      <c r="C249" s="7" t="n">
+      <c r="H261" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I261" s="12" t="inlineStr">
+        <is>
+          <t>VV P1.3d = 1.0 ks  [document:VV výkaz výměr]</t>
+        </is>
+      </c>
+      <c r="J261" s="12" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="A262" s="4" t="n">
+        <v>168</v>
+      </c>
+      <c r="B262" s="5" t="inlineStr"/>
+      <c r="C262" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="D249" s="8" t="inlineStr">
-        <is>
-          <t>M-VK</t>
-        </is>
-      </c>
-      <c r="E249" s="8" t="inlineStr">
-        <is>
-          <t>M-VK-009</t>
-        </is>
-      </c>
-      <c r="F249" s="9" t="inlineStr">
-        <is>
-          <t>Přeložka stávajícího vodovodního řadu (rerouting) — kompletní práce vč. potrubí, výkop, napojení, tlakové zkoušky</t>
-        </is>
-      </c>
-      <c r="G249" s="7" t="inlineStr">
+      <c r="D262" s="5" t="inlineStr">
+        <is>
+          <t>M-ZTI</t>
+        </is>
+      </c>
+      <c r="E262" s="5" t="inlineStr">
+        <is>
+          <t>M-ZTI-049</t>
+        </is>
+      </c>
+      <c r="F262" s="6" t="inlineStr">
+        <is>
+          <t>Uzavírací šoupě vč. zemní soupravy DN40</t>
+        </is>
+      </c>
+      <c r="G262" s="4" t="inlineStr">
         <is>
           <t>kpl</t>
         </is>
       </c>
-      <c r="H249" s="7" t="n">
+      <c r="H262" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="I249" s="9" t="inlineStr">
-        <is>
-          <t>1 kpl  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
-        </is>
-      </c>
-      <c r="J249" s="9" t="inlineStr">
-        <is>
-          <t>ABMV:ABMV_23</t>
-        </is>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" s="3" t="inlineStr">
-        <is>
-          <t>→ Retenční nádrž 30 m³ prefab betonová (pending ABMV_24)</t>
-        </is>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" s="4" t="n">
-        <v>156</v>
-      </c>
-      <c r="B251" s="5" t="inlineStr"/>
-      <c r="C251" s="4" t="n">
+      <c r="I262" s="6" t="inlineStr">
+        <is>
+          <t>VV P1.4d = 1.0 kpl  [document:VV výkaz výměr]</t>
+        </is>
+      </c>
+      <c r="J262" s="6" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="10" t="n">
+        <v>169</v>
+      </c>
+      <c r="B263" s="11" t="inlineStr"/>
+      <c r="C263" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="D251" s="5" t="inlineStr">
-        <is>
-          <t>M-VK</t>
-        </is>
-      </c>
-      <c r="E251" s="5" t="inlineStr">
-        <is>
-          <t>M-VK-011</t>
-        </is>
-      </c>
-      <c r="F251" s="6" t="inlineStr">
-        <is>
-          <t>Retenční nádrž 30 m³ — prefabrikovaná betonová, rozměry 6.15×2.75×2.0 m, vč. usazení do připraveného výkopu a napojení na dešťovou kanalizaci</t>
-        </is>
-      </c>
-      <c r="G251" s="4" t="inlineStr">
-        <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="H251" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I251" s="6" t="inlineStr">
-        <is>
-          <t>1 ks prefab  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
-        </is>
-      </c>
-      <c r="J251" s="6" t="inlineStr">
-        <is>
-          <t>ABMV:ABMV_24</t>
-        </is>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" s="3" t="inlineStr">
-        <is>
-          <t>→ Hydrant podzemní DN80 + napojení</t>
-        </is>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" s="4" t="n">
-        <v>157</v>
-      </c>
-      <c r="B253" s="5" t="inlineStr"/>
-      <c r="C253" s="4" t="n">
+      <c r="D263" s="11" t="inlineStr">
+        <is>
+          <t>M-ZTI</t>
+        </is>
+      </c>
+      <c r="E263" s="11" t="inlineStr">
+        <is>
+          <t>M-ZTI-050</t>
+        </is>
+      </c>
+      <c r="F263" s="12" t="inlineStr">
+        <is>
+          <t>Výkop pro pokládku potrubí šířky 1 m, pažený</t>
+        </is>
+      </c>
+      <c r="G263" s="10" t="inlineStr">
+        <is>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="H263" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="I263" s="12" t="inlineStr">
+        <is>
+          <t>VV P1.5d = 16.0 bm  [document:VV výkaz výměr]</t>
+        </is>
+      </c>
+      <c r="J263" s="12" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="4" t="n">
+        <v>170</v>
+      </c>
+      <c r="B264" s="5" t="inlineStr"/>
+      <c r="C264" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="D253" s="5" t="inlineStr">
-        <is>
-          <t>M-VK</t>
-        </is>
-      </c>
-      <c r="E253" s="5" t="inlineStr">
-        <is>
-          <t>M-VK-010</t>
-        </is>
-      </c>
-      <c r="F253" s="6" t="inlineStr">
-        <is>
-          <t>Hydrant podzemní DN80 vč. uzávěru, šoupátka, zemní soupravy, poklopu litinového a napojení na vodovodní řad</t>
-        </is>
-      </c>
-      <c r="G253" s="4" t="inlineStr">
-        <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="H253" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I253" s="6" t="inlineStr">
-        <is>
-          <t>1 ks  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
-        </is>
-      </c>
-      <c r="J253" s="6" t="inlineStr"/>
-    </row>
-    <row r="254">
-      <c r="A254" s="3" t="inlineStr">
-        <is>
-          <t>→ Drcený štěrk podklad ramp</t>
-        </is>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" s="4" t="n">
-        <v>158</v>
-      </c>
-      <c r="B255" s="5" t="inlineStr"/>
-      <c r="C255" s="4" t="n">
+      <c r="D264" s="5" t="inlineStr">
+        <is>
+          <t>M-ZTI</t>
+        </is>
+      </c>
+      <c r="E264" s="5" t="inlineStr">
+        <is>
+          <t>M-ZTI-051</t>
+        </is>
+      </c>
+      <c r="F264" s="6" t="inlineStr">
+        <is>
+          <t>Pískový podsyp frakce 0–16 mm, výška 0,1 m, zhutnění</t>
+        </is>
+      </c>
+      <c r="G264" s="4" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="H264" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I264" s="6" t="inlineStr">
+        <is>
+          <t>VV P1.6d = 1.6 m³  [document:VV výkaz výměr]</t>
+        </is>
+      </c>
+      <c r="J264" s="6" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="10" t="n">
+        <v>171</v>
+      </c>
+      <c r="B265" s="11" t="inlineStr"/>
+      <c r="C265" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="D255" s="5" t="inlineStr">
-        <is>
-          <t>M-VK</t>
-        </is>
-      </c>
-      <c r="E255" s="5" t="inlineStr">
-        <is>
-          <t>M-VK-003</t>
-        </is>
-      </c>
-      <c r="F255" s="6" t="inlineStr">
-        <is>
-          <t>Drcený štěrk ŠD 32/63 podklad rampy + okapní pas tl 200 mm</t>
-        </is>
-      </c>
-      <c r="G255" s="4" t="inlineStr">
+      <c r="D265" s="11" t="inlineStr">
+        <is>
+          <t>M-ZTI</t>
+        </is>
+      </c>
+      <c r="E265" s="11" t="inlineStr">
+        <is>
+          <t>M-ZTI-052</t>
+        </is>
+      </c>
+      <c r="F265" s="12" t="inlineStr">
+        <is>
+          <t>Pískový obsyp frakce 0–16 mm bez ostrých zrn, výška 0,2 m, zhutnění</t>
+        </is>
+      </c>
+      <c r="G265" s="10" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="H255" s="4" t="n">
-        <v>8.66</v>
-      </c>
-      <c r="I255" s="6" t="inlineStr">
-        <is>
-          <t>43.32 × 0.20 = 8.66 m³  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
-        </is>
-      </c>
-      <c r="J255" s="6" t="inlineStr"/>
-    </row>
-    <row r="256">
-      <c r="A256" s="3" t="inlineStr">
-        <is>
-          <t>→ Okapní chodník — complete 10-layer stack 0.7 m × 80 m po obvodu haly (výkop → odvoz → pláň → geotextilie → štěrk → hutnění → bednění → výztuž → beton → dilatace, pending ABMV_31 + ABMV_32)</t>
-        </is>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" s="4" t="n">
-        <v>159</v>
-      </c>
-      <c r="B257" s="5" t="inlineStr"/>
-      <c r="C257" s="4" t="n">
+      <c r="H265" s="10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I265" s="12" t="inlineStr">
+        <is>
+          <t>VV P1.7d = 4.8 m³  [document:VV výkaz výměr]</t>
+        </is>
+      </c>
+      <c r="J265" s="12" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="4" t="n">
+        <v>172</v>
+      </c>
+      <c r="B266" s="5" t="inlineStr"/>
+      <c r="C266" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="D257" s="5" t="inlineStr">
-        <is>
-          <t>M-VK</t>
-        </is>
-      </c>
-      <c r="E257" s="5" t="inlineStr">
-        <is>
-          <t>M-VK-027</t>
-        </is>
-      </c>
-      <c r="F257" s="6" t="inlineStr">
-        <is>
-          <t>Výkop rýhy pro okapní chodník hl. 400 mm (na hloubku všech vrstev)</t>
-        </is>
-      </c>
-      <c r="G257" s="4" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="H257" s="4" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="I257" s="6" t="inlineStr">
-        <is>
-          <t>80.0 × 0.7 × 0.4 = 22.4 m³  [document:A103 řez A-B detail, norma:ČSN 73 6126, norma:ČSN okapový chodník]</t>
-        </is>
-      </c>
-      <c r="J257" s="6" t="inlineStr">
-        <is>
-          <t>ABMV:ABMV_32</t>
-        </is>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" s="10" t="n">
-        <v>160</v>
-      </c>
-      <c r="B258" s="11" t="inlineStr"/>
-      <c r="C258" s="10" t="n">
+      <c r="D266" s="5" t="inlineStr">
+        <is>
+          <t>M-ZTI</t>
+        </is>
+      </c>
+      <c r="E266" s="5" t="inlineStr">
+        <is>
+          <t>M-ZTI-053</t>
+        </is>
+      </c>
+      <c r="F266" s="6" t="inlineStr">
+        <is>
+          <t>Konečný zához výkopu zeminou</t>
+        </is>
+      </c>
+      <c r="G266" s="4" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="H266" s="4" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="I266" s="6" t="inlineStr">
+        <is>
+          <t>VV P1.8d = 9.6 kpl  [document:VV výkaz výměr]</t>
+        </is>
+      </c>
+      <c r="J266" s="6" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="10" t="n">
+        <v>173</v>
+      </c>
+      <c r="B267" s="11" t="inlineStr"/>
+      <c r="C267" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="D258" s="11" t="inlineStr">
-        <is>
-          <t>M-VK</t>
-        </is>
-      </c>
-      <c r="E258" s="11" t="inlineStr">
-        <is>
-          <t>M-VK-028</t>
-        </is>
-      </c>
-      <c r="F258" s="12" t="inlineStr">
-        <is>
-          <t>Odvoz vykopané zeminy z rýhy okapního chodníku na skládku</t>
-        </is>
-      </c>
-      <c r="G258" s="10" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="H258" s="10" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="I258" s="12">
-        <f> 22.4 m³ (1:1 s výkopem)  [document:A103 řez A-B detail, norma:ČSN 73 6126, norma:ČSN okapový chodník]</f>
-        <v/>
-      </c>
-      <c r="J258" s="12" t="inlineStr">
-        <is>
-          <t>ABMV:ABMV_32</t>
-        </is>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" s="4" t="n">
-        <v>161</v>
-      </c>
-      <c r="B259" s="5" t="inlineStr"/>
-      <c r="C259" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="D259" s="5" t="inlineStr">
-        <is>
-          <t>M-VK</t>
-        </is>
-      </c>
-      <c r="E259" s="5" t="inlineStr">
-        <is>
-          <t>M-VK-024</t>
-        </is>
-      </c>
-      <c r="F259" s="6" t="inlineStr">
-        <is>
-          <t>Úprava zemní pláně + hutnění pod okapní chodník (Edef2 ≥ 30 MPa)</t>
-        </is>
-      </c>
-      <c r="G259" s="4" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="H259" s="4" t="n">
-        <v>56</v>
-      </c>
-      <c r="I259" s="6" t="inlineStr">
-        <is>
-          <t>80.0 × 0.7 = 56.0 m²  [document:A103 řez A-B detail, norma:ČSN 73 6126, norma:ČSN EN 13670]</t>
-        </is>
-      </c>
-      <c r="J259" s="6" t="inlineStr">
-        <is>
-          <t>ABMV:ABMV_32</t>
-        </is>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" s="10" t="n">
-        <v>162</v>
-      </c>
-      <c r="B260" s="11" t="inlineStr"/>
-      <c r="C260" s="10" t="n">
-        <v>12</v>
-      </c>
-      <c r="D260" s="11" t="inlineStr">
-        <is>
-          <t>M-VK</t>
-        </is>
-      </c>
-      <c r="E260" s="11" t="inlineStr">
-        <is>
-          <t>M-VK-029</t>
-        </is>
-      </c>
-      <c r="F260" s="12" t="inlineStr">
-        <is>
-          <t>Geotextilie 300 g/m² separační — mezi hutněnou zemní pláň a štěrkový podklad okapního chodníku</t>
-        </is>
-      </c>
-      <c r="G260" s="10" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="H260" s="10" t="n">
-        <v>56</v>
-      </c>
-      <c r="I260" s="12" t="inlineStr">
-        <is>
-          <t>80.0 × 0.7 = 56.0 m²  [document:A103 řez A-B detail, norma:ČSN 73 6126, norma:ČSN okapový chodník]</t>
-        </is>
-      </c>
-      <c r="J260" s="12" t="inlineStr">
-        <is>
-          <t>ABMV:ABMV_32</t>
-        </is>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" s="4" t="n">
-        <v>163</v>
-      </c>
-      <c r="B261" s="5" t="inlineStr"/>
-      <c r="C261" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="D261" s="5" t="inlineStr">
-        <is>
-          <t>M-VK</t>
-        </is>
-      </c>
-      <c r="E261" s="5" t="inlineStr">
-        <is>
-          <t>M-VK-022</t>
-        </is>
-      </c>
-      <c r="F261" s="6" t="inlineStr">
-        <is>
-          <t>Drcený štěrk ŠD 32/63 podklad okapního chodníku tl 150 mm</t>
-        </is>
-      </c>
-      <c r="G261" s="4" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="H261" s="4" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="I261" s="6" t="inlineStr">
-        <is>
-          <t>80.0 × 0.7 × 0.15 = 8.40 m³  [document:A103 řezy A-B detail, document:A101 půdorys 1NP, document:C.3 KOO situace]</t>
-        </is>
-      </c>
-      <c r="J261" s="6" t="inlineStr">
-        <is>
-          <t>ABMV:ABMV_31</t>
-        </is>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" s="10" t="n">
-        <v>164</v>
-      </c>
-      <c r="B262" s="11" t="inlineStr"/>
-      <c r="C262" s="10" t="n">
-        <v>12</v>
-      </c>
-      <c r="D262" s="11" t="inlineStr">
-        <is>
-          <t>M-VK</t>
-        </is>
-      </c>
-      <c r="E262" s="11" t="inlineStr">
-        <is>
-          <t>M-VK-025</t>
-        </is>
-      </c>
-      <c r="F262" s="12" t="inlineStr">
-        <is>
-          <t>Hutnění štěrkového podkladu okapního chodníku vibrodeskou (Edef2 ≥ 45 MPa)</t>
-        </is>
-      </c>
-      <c r="G262" s="10" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="H262" s="10" t="n">
-        <v>56</v>
-      </c>
-      <c r="I262" s="12" t="inlineStr">
-        <is>
-          <t>80.0 × 0.7 = 56.0 m²  [document:A103 řez A-B detail, norma:ČSN 73 6126, norma:ČSN EN 13670]</t>
-        </is>
-      </c>
-      <c r="J262" s="12" t="inlineStr">
-        <is>
-          <t>ABMV:ABMV_32</t>
-        </is>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" s="4" t="n">
-        <v>165</v>
-      </c>
-      <c r="B263" s="5" t="inlineStr"/>
-      <c r="C263" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="D263" s="5" t="inlineStr">
-        <is>
-          <t>M-VK</t>
-        </is>
-      </c>
-      <c r="E263" s="5" t="inlineStr">
-        <is>
-          <t>M-VK-026</t>
-        </is>
-      </c>
-      <c r="F263" s="6" t="inlineStr">
-        <is>
-          <t>Bednění boční vnější hrana okapního chodníku v 200 mm (vnitřní hrana = stěna haly)</t>
-        </is>
-      </c>
-      <c r="G263" s="4" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="H263" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="I263" s="6" t="inlineStr">
-        <is>
-          <t>80.0 × 0.2 = 16.0 m²  [document:A103 řez A-B detail, norma:ČSN 73 6126, norma:ČSN EN 13670]</t>
-        </is>
-      </c>
-      <c r="J263" s="6" t="inlineStr">
-        <is>
-          <t>ABMV:ABMV_32</t>
-        </is>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" s="10" t="n">
-        <v>166</v>
-      </c>
-      <c r="B264" s="11" t="inlineStr"/>
-      <c r="C264" s="10" t="n">
-        <v>12</v>
-      </c>
-      <c r="D264" s="11" t="inlineStr">
-        <is>
-          <t>M-VK</t>
-        </is>
-      </c>
-      <c r="E264" s="11" t="inlineStr">
-        <is>
-          <t>M-VK-021</t>
-        </is>
-      </c>
-      <c r="F264" s="12" t="inlineStr">
-        <is>
-          <t>Výztuž KARI síť Q188 (150/150/6 mm) — okapní chodník</t>
-        </is>
-      </c>
-      <c r="G264" s="10" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="H264" s="10" t="n">
-        <v>56</v>
-      </c>
-      <c r="I264" s="12" t="inlineStr">
-        <is>
-          <t>80.0 × 0.7 = 56.00 m²  [document:A103 řezy A-B detail, document:A101 půdorys 1NP, document:C.3 KOO situace]</t>
-        </is>
-      </c>
-      <c r="J264" s="12" t="inlineStr">
-        <is>
-          <t>ABMV:ABMV_31</t>
-        </is>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" s="4" t="n">
-        <v>167</v>
-      </c>
-      <c r="B265" s="5" t="inlineStr"/>
-      <c r="C265" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="D265" s="5" t="inlineStr">
-        <is>
-          <t>M-VK</t>
-        </is>
-      </c>
-      <c r="E265" s="5" t="inlineStr">
-        <is>
-          <t>M-VK-020</t>
-        </is>
-      </c>
-      <c r="F265" s="6" t="inlineStr">
-        <is>
-          <t>Beton C25/30 XF3 — okapní chodník po obvodu haly (sokl 0.7 m × ~80 m mimo 4 vstupy), tl 200 mm</t>
-        </is>
-      </c>
-      <c r="G265" s="4" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="H265" s="4" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="I265" s="6" t="inlineStr">
-        <is>
-          <t>80.0 × 0.7 × 0.2 = 11.20 m³  [document:A103 řezy A-B detail, document:A101 půdorys 1NP, document:C.3 KOO situace]</t>
-        </is>
-      </c>
-      <c r="J265" s="6" t="inlineStr">
-        <is>
-          <t>ABMV:ABMV_31</t>
-        </is>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" s="10" t="n">
-        <v>168</v>
-      </c>
-      <c r="B266" s="11" t="inlineStr"/>
-      <c r="C266" s="10" t="n">
-        <v>12</v>
-      </c>
-      <c r="D266" s="11" t="inlineStr">
-        <is>
-          <t>M-VK</t>
-        </is>
-      </c>
-      <c r="E266" s="11" t="inlineStr">
-        <is>
-          <t>M-VK-023</t>
-        </is>
-      </c>
-      <c r="F266" s="12" t="inlineStr">
-        <is>
-          <t>Dilatační lišty + těsnění spár mezi segmenty okapního chodníku (à ~4 m)</t>
-        </is>
-      </c>
-      <c r="G266" s="10" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="H266" s="10" t="n">
-        <v>20</v>
-      </c>
-      <c r="I266" s="12" t="inlineStr">
-        <is>
-          <t>80.0 / 4 = 20 ks dilatací  [document:A103 řezy A-B detail, document:A101 půdorys 1NP, document:C.3 KOO situace]</t>
-        </is>
-      </c>
-      <c r="J266" s="12" t="inlineStr">
-        <is>
-          <t>ABMV:ABMV_31</t>
-        </is>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" s="3" t="inlineStr">
-        <is>
-          <t>→ Rampy 4× (R1-R4) — výztuž + bednění + beton + obrubník (per A101)</t>
-        </is>
-      </c>
+      <c r="D267" s="11" t="inlineStr">
+        <is>
+          <t>M-ZTI</t>
+        </is>
+      </c>
+      <c r="E267" s="11" t="inlineStr">
+        <is>
+          <t>M-ZTI-054</t>
+        </is>
+      </c>
+      <c r="F267" s="12" t="inlineStr">
+        <is>
+          <t>Výstražná folie</t>
+        </is>
+      </c>
+      <c r="G267" s="10" t="inlineStr">
+        <is>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="H267" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="I267" s="12" t="inlineStr">
+        <is>
+          <t>VV P1.9d = 10.0 bm  [document:VV výkaz výměr]</t>
+        </is>
+      </c>
+      <c r="J267" s="12" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" s="4" t="n">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="B268" s="5" t="inlineStr"/>
       <c r="C268" s="4" t="n">
@@ -7814,37 +7922,37 @@
       </c>
       <c r="D268" s="5" t="inlineStr">
         <is>
-          <t>M-VK</t>
+          <t>M-ZTI</t>
         </is>
       </c>
       <c r="E268" s="5" t="inlineStr">
         <is>
-          <t>M-VK-002</t>
+          <t>M-ZTI-055</t>
         </is>
       </c>
       <c r="F268" s="6" t="inlineStr">
         <is>
-          <t>Výztuž KARI síť Q188 + bednění boční rampy 4 lokality</t>
+          <t>Odvoz a uskladnění přebytečného výkopového materiálu</t>
         </is>
       </c>
       <c r="G268" s="4" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="H268" s="4" t="n">
-        <v>43.32</v>
+        <v>1</v>
       </c>
       <c r="I268" s="6" t="inlineStr">
         <is>
-          <t>4 lokality rampy = 43.32 m²  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
+          <t>VV P1.10d = 1.0 kpl  [document:VV výkaz výměr]</t>
         </is>
       </c>
       <c r="J268" s="6" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" s="10" t="n">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="B269" s="11" t="inlineStr"/>
       <c r="C269" s="10" t="n">
@@ -7852,209 +7960,2476 @@
       </c>
       <c r="D269" s="11" t="inlineStr">
         <is>
+          <t>M-ZTI</t>
+        </is>
+      </c>
+      <c r="E269" s="11" t="inlineStr">
+        <is>
+          <t>M-ZTI-056</t>
+        </is>
+      </c>
+      <c r="F269" s="12" t="inlineStr">
+        <is>
+          <t>Montážní a pomocný materiál (součást zemních a pomocných prací)</t>
+        </is>
+      </c>
+      <c r="G269" s="10" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="H269" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I269" s="12" t="inlineStr">
+        <is>
+          <t>VV P1.11d = 1.0 kpl  [document:VV výkaz výměr]</t>
+        </is>
+      </c>
+      <c r="J269" s="12" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="3" t="inlineStr">
+        <is>
+          <t>→ ZTI domovní kanalizace — potrubí PP-KG/HT + revizní šachty + retenční nádoba 15 m³ + zasakovací těleso (VV K1, pending ABMV_33)</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="4" t="n">
+        <v>176</v>
+      </c>
+      <c r="B271" s="5" t="inlineStr"/>
+      <c r="C271" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D271" s="5" t="inlineStr">
+        <is>
+          <t>M-ZTI</t>
+        </is>
+      </c>
+      <c r="E271" s="5" t="inlineStr">
+        <is>
+          <t>M-ZTI-016</t>
+        </is>
+      </c>
+      <c r="F271" s="6" t="inlineStr">
+        <is>
+          <t>Potrubí PP-HT DN50</t>
+        </is>
+      </c>
+      <c r="G271" s="4" t="inlineStr">
+        <is>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="H271" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I271" s="6" t="inlineStr">
+        <is>
+          <t>VV K1.2 = 2.0 bm  [document:VV výkaz výměr]</t>
+        </is>
+      </c>
+      <c r="J271" s="6" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" s="10" t="n">
+        <v>177</v>
+      </c>
+      <c r="B272" s="11" t="inlineStr"/>
+      <c r="C272" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D272" s="11" t="inlineStr">
+        <is>
+          <t>M-ZTI</t>
+        </is>
+      </c>
+      <c r="E272" s="11" t="inlineStr">
+        <is>
+          <t>M-ZTI-017</t>
+        </is>
+      </c>
+      <c r="F272" s="12" t="inlineStr">
+        <is>
+          <t>Potrubí PP-HT DN110</t>
+        </is>
+      </c>
+      <c r="G272" s="10" t="inlineStr">
+        <is>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="H272" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="I272" s="12" t="inlineStr">
+        <is>
+          <t>VV K1.3 = 5.0 bm  [document:VV výkaz výměr]</t>
+        </is>
+      </c>
+      <c r="J272" s="12" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="4" t="n">
+        <v>178</v>
+      </c>
+      <c r="B273" s="5" t="inlineStr"/>
+      <c r="C273" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D273" s="5" t="inlineStr">
+        <is>
+          <t>M-ZTI</t>
+        </is>
+      </c>
+      <c r="E273" s="5" t="inlineStr">
+        <is>
+          <t>M-ZTI-018</t>
+        </is>
+      </c>
+      <c r="F273" s="6" t="inlineStr">
+        <is>
+          <t>Kanalizační potrubí PP-KG DN110 vč. tvarovek</t>
+        </is>
+      </c>
+      <c r="G273" s="4" t="inlineStr">
+        <is>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="H273" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I273" s="6" t="inlineStr">
+        <is>
+          <t>VV K1.5 = 1.0 bm  [document:VV výkaz výměr]</t>
+        </is>
+      </c>
+      <c r="J273" s="6" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" s="10" t="n">
+        <v>179</v>
+      </c>
+      <c r="B274" s="11" t="inlineStr"/>
+      <c r="C274" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D274" s="11" t="inlineStr">
+        <is>
+          <t>M-ZTI</t>
+        </is>
+      </c>
+      <c r="E274" s="11" t="inlineStr">
+        <is>
+          <t>M-ZTI-019</t>
+        </is>
+      </c>
+      <c r="F274" s="12" t="inlineStr">
+        <is>
+          <t>Kanalizační potrubí PP-KG DN125 vč. tvarovek</t>
+        </is>
+      </c>
+      <c r="G274" s="10" t="inlineStr">
+        <is>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="H274" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="I274" s="12" t="inlineStr">
+        <is>
+          <t>VV K1.6 = 55.0 bm  [document:VV výkaz výměr]</t>
+        </is>
+      </c>
+      <c r="J274" s="12" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="4" t="n">
+        <v>180</v>
+      </c>
+      <c r="B275" s="5" t="inlineStr"/>
+      <c r="C275" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D275" s="5" t="inlineStr">
+        <is>
+          <t>M-ZTI</t>
+        </is>
+      </c>
+      <c r="E275" s="5" t="inlineStr">
+        <is>
+          <t>M-ZTI-020</t>
+        </is>
+      </c>
+      <c r="F275" s="6" t="inlineStr">
+        <is>
+          <t>Kanalizační potrubí PP-KG DN160 vč. tvarovek</t>
+        </is>
+      </c>
+      <c r="G275" s="4" t="inlineStr">
+        <is>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="H275" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="I275" s="6" t="inlineStr">
+        <is>
+          <t>VV K1.7 = 30.0 bm  [document:VV výkaz výměr]</t>
+        </is>
+      </c>
+      <c r="J275" s="6" t="inlineStr"/>
+    </row>
+    <row r="276">
+      <c r="A276" s="10" t="n">
+        <v>181</v>
+      </c>
+      <c r="B276" s="11" t="inlineStr"/>
+      <c r="C276" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D276" s="11" t="inlineStr">
+        <is>
+          <t>M-ZTI</t>
+        </is>
+      </c>
+      <c r="E276" s="11" t="inlineStr">
+        <is>
+          <t>M-ZTI-021</t>
+        </is>
+      </c>
+      <c r="F276" s="12" t="inlineStr">
+        <is>
+          <t>Kanalizační potrubí PP-KG DN200 vč. tvarovek</t>
+        </is>
+      </c>
+      <c r="G276" s="10" t="inlineStr">
+        <is>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="H276" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="I276" s="12" t="inlineStr">
+        <is>
+          <t>VV K1.8 = 9.0 bm  [document:VV výkaz výměr]</t>
+        </is>
+      </c>
+      <c r="J276" s="12" t="inlineStr"/>
+    </row>
+    <row r="277">
+      <c r="A277" s="4" t="n">
+        <v>182</v>
+      </c>
+      <c r="B277" s="5" t="inlineStr"/>
+      <c r="C277" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D277" s="5" t="inlineStr">
+        <is>
+          <t>M-ZTI</t>
+        </is>
+      </c>
+      <c r="E277" s="5" t="inlineStr">
+        <is>
+          <t>M-ZTI-022</t>
+        </is>
+      </c>
+      <c r="F277" s="6" t="inlineStr">
+        <is>
+          <t>Revizní šachta Dš — bet. skruže DN1000, pojezdný poklop, šachetní dno, regulační prvek max 0,55 l/s + havarijní přepad DN200, hl do 2,5 m (kpl)</t>
+        </is>
+      </c>
+      <c r="G277" s="4" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="H277" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I277" s="6" t="inlineStr">
+        <is>
+          <t>VV K1.9 = 1.0 kpl  [document:VV výkaz výměr]</t>
+        </is>
+      </c>
+      <c r="J277" s="6" t="inlineStr"/>
+    </row>
+    <row r="278">
+      <c r="A278" s="10" t="n">
+        <v>183</v>
+      </c>
+      <c r="B278" s="11" t="inlineStr"/>
+      <c r="C278" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D278" s="11" t="inlineStr">
+        <is>
+          <t>M-ZTI</t>
+        </is>
+      </c>
+      <c r="E278" s="11" t="inlineStr">
+        <is>
+          <t>M-ZTI-023</t>
+        </is>
+      </c>
+      <c r="F278" s="12" t="inlineStr">
+        <is>
+          <t>Revizní betonová šachta dešťová Dš1 — DN1000, rovné dno, hl do 2,0 m, nátok DN160 (-90°/180°), výtok DN200, pojezdový poklop (kpl)</t>
+        </is>
+      </c>
+      <c r="G278" s="10" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="H278" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I278" s="12" t="inlineStr">
+        <is>
+          <t>VV K1.10 = 1.0 kpl  [document:VV výkaz výměr]</t>
+        </is>
+      </c>
+      <c r="J278" s="12" t="inlineStr"/>
+    </row>
+    <row r="279">
+      <c r="A279" s="4" t="n">
+        <v>184</v>
+      </c>
+      <c r="B279" s="5" t="inlineStr"/>
+      <c r="C279" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D279" s="5" t="inlineStr">
+        <is>
+          <t>M-ZTI</t>
+        </is>
+      </c>
+      <c r="E279" s="5" t="inlineStr">
+        <is>
+          <t>M-ZTI-024</t>
+        </is>
+      </c>
+      <c r="F279" s="6" t="inlineStr">
+        <is>
+          <t>Revizní filtrační šachta Dš2 — bet. skruže DN1000, pojezdný poklop, dno, hl do 1,6 m, nátok DN160 -90°, výtok DN160 (kpl)</t>
+        </is>
+      </c>
+      <c r="G279" s="4" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="H279" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I279" s="6" t="inlineStr">
+        <is>
+          <t>VV K1.11 = 1.0 kpl  [document:VV výkaz výměr]</t>
+        </is>
+      </c>
+      <c r="J279" s="6" t="inlineStr"/>
+    </row>
+    <row r="280">
+      <c r="A280" s="10" t="n">
+        <v>185</v>
+      </c>
+      <c r="B280" s="11" t="inlineStr"/>
+      <c r="C280" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D280" s="11" t="inlineStr">
+        <is>
+          <t>M-ZTI</t>
+        </is>
+      </c>
+      <c r="E280" s="11" t="inlineStr">
+        <is>
+          <t>M-ZTI-025</t>
+        </is>
+      </c>
+      <c r="F280" s="12" t="inlineStr">
+        <is>
+          <t>Revizní šachty Rš2 + Rš3 — bet. skruže DN1000, pojezdný poklop, dno, hl dle stáv. kanalizace (kpl)</t>
+        </is>
+      </c>
+      <c r="G280" s="10" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="H280" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I280" s="12" t="inlineStr">
+        <is>
+          <t>VV K1.12 = 2.0 kpl  [document:VV výkaz výměr]</t>
+        </is>
+      </c>
+      <c r="J280" s="12" t="inlineStr"/>
+    </row>
+    <row r="281">
+      <c r="A281" s="4" t="n">
+        <v>186</v>
+      </c>
+      <c r="B281" s="5" t="inlineStr"/>
+      <c r="C281" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D281" s="5" t="inlineStr">
+        <is>
+          <t>M-ZTI</t>
+        </is>
+      </c>
+      <c r="E281" s="5" t="inlineStr">
+        <is>
+          <t>M-ZTI-026</t>
+        </is>
+      </c>
+      <c r="F281" s="6" t="inlineStr">
+        <is>
+          <t>Zasakovací těleso 1,5×3,0×0,39 m — min. využitelný objem 2 m³, zasakovací plocha min 4,5 m², kamenivo/voštinové těleso</t>
+        </is>
+      </c>
+      <c r="G281" s="4" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="H281" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I281" s="6" t="inlineStr">
+        <is>
+          <t>VV K1.13 = 1.0 kpl  [document:VV výkaz výměr]</t>
+        </is>
+      </c>
+      <c r="J281" s="6" t="inlineStr"/>
+    </row>
+    <row r="282">
+      <c r="A282" s="10" t="n">
+        <v>187</v>
+      </c>
+      <c r="B282" s="11" t="inlineStr"/>
+      <c r="C282" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D282" s="11" t="inlineStr">
+        <is>
+          <t>M-ZTI</t>
+        </is>
+      </c>
+      <c r="E282" s="11" t="inlineStr">
+        <is>
+          <t>M-ZTI-027</t>
+        </is>
+      </c>
+      <c r="F282" s="12" t="inlineStr">
+        <is>
+          <t>Akumulačně retenční nádoba na dešťovou vodu 15 m³ — ⌀3,1 m × v=2,0 m, dodávka + montáž (kpl)</t>
+        </is>
+      </c>
+      <c r="G282" s="10" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="H282" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I282" s="12" t="inlineStr">
+        <is>
+          <t>VV K1.14 = 1.0 kpl  [document:VV výkaz výměr]</t>
+        </is>
+      </c>
+      <c r="J282" s="12" t="inlineStr"/>
+    </row>
+    <row r="283">
+      <c r="A283" s="4" t="n">
+        <v>188</v>
+      </c>
+      <c r="B283" s="5" t="inlineStr"/>
+      <c r="C283" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D283" s="5" t="inlineStr">
+        <is>
+          <t>M-ZTI</t>
+        </is>
+      </c>
+      <c r="E283" s="5" t="inlineStr">
+        <is>
+          <t>M-ZTI-028</t>
+        </is>
+      </c>
+      <c r="F283" s="6" t="inlineStr">
+        <is>
+          <t>Revizní šachta Dš2 — bet. skruže DN1000, pojezdný poklop, dno, hl do 2,2 m (kpl)</t>
+        </is>
+      </c>
+      <c r="G283" s="4" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="H283" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I283" s="6" t="inlineStr">
+        <is>
+          <t>VV K1.15 = 1.0 kpl  [document:VV výkaz výměr]</t>
+        </is>
+      </c>
+      <c r="J283" s="6" t="inlineStr"/>
+    </row>
+    <row r="284">
+      <c r="A284" s="10" t="n">
+        <v>189</v>
+      </c>
+      <c r="B284" s="11" t="inlineStr"/>
+      <c r="C284" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D284" s="11" t="inlineStr">
+        <is>
+          <t>M-ZTI</t>
+        </is>
+      </c>
+      <c r="E284" s="11" t="inlineStr">
+        <is>
+          <t>M-ZTI-029</t>
+        </is>
+      </c>
+      <c r="F284" s="12" t="inlineStr">
+        <is>
+          <t>Zápachová uzávěrka pro umyvadla — sifon trubkový chrom designový 5/4" 32 mm (komplet)</t>
+        </is>
+      </c>
+      <c r="G284" s="10" t="inlineStr">
+        <is>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="H284" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I284" s="12" t="inlineStr">
+        <is>
+          <t>VV K2.2 = 1.0 ks  [document:VV výkaz výměr]</t>
+        </is>
+      </c>
+      <c r="J284" s="12" t="inlineStr"/>
+    </row>
+    <row r="285">
+      <c r="A285" s="4" t="n">
+        <v>190</v>
+      </c>
+      <c r="B285" s="5" t="inlineStr"/>
+      <c r="C285" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D285" s="5" t="inlineStr">
+        <is>
+          <t>M-ZTI</t>
+        </is>
+      </c>
+      <c r="E285" s="5" t="inlineStr">
+        <is>
+          <t>M-ZTI-030</t>
+        </is>
+      </c>
+      <c r="F285" s="6" t="inlineStr">
+        <is>
+          <t>Sifon pro odvod kondenzátu z kondenzačního kotle, VZT a boileru (ref. HL 136)</t>
+        </is>
+      </c>
+      <c r="G285" s="4" t="inlineStr">
+        <is>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="H285" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I285" s="6" t="inlineStr">
+        <is>
+          <t>VV K2.3 = 1.0 ks  [document:VV výkaz výměr]</t>
+        </is>
+      </c>
+      <c r="J285" s="6" t="inlineStr"/>
+    </row>
+    <row r="286">
+      <c r="A286" s="10" t="n">
+        <v>191</v>
+      </c>
+      <c r="B286" s="11" t="inlineStr"/>
+      <c r="C286" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D286" s="11" t="inlineStr">
+        <is>
+          <t>M-ZTI</t>
+        </is>
+      </c>
+      <c r="E286" s="11" t="inlineStr">
+        <is>
+          <t>M-ZTI-031</t>
+        </is>
+      </c>
+      <c r="F286" s="12" t="inlineStr">
+        <is>
+          <t>Lapač splavenin a nečistot — litinový</t>
+        </is>
+      </c>
+      <c r="G286" s="10" t="inlineStr">
+        <is>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="H286" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="I286" s="12" t="inlineStr">
+        <is>
+          <t>VV K2.4 = 5.0 ks  [document:VV výkaz výměr]</t>
+        </is>
+      </c>
+      <c r="J286" s="12" t="inlineStr"/>
+    </row>
+    <row r="287">
+      <c r="A287" s="3" t="inlineStr">
+        <is>
+          <t>→ ZTI domovní vodovod — potrubí + armatury + TUV + požární vodovod + hydrant D19/30 (VV DV)</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="4" t="n">
+        <v>192</v>
+      </c>
+      <c r="B288" s="5" t="inlineStr"/>
+      <c r="C288" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D288" s="5" t="inlineStr">
+        <is>
+          <t>M-ZTI</t>
+        </is>
+      </c>
+      <c r="E288" s="5" t="inlineStr">
+        <is>
+          <t>M-ZTI-001</t>
+        </is>
+      </c>
+      <c r="F288" s="6" t="inlineStr">
+        <is>
+          <t>EVO PP-RCT 16×2,2 + izolace mirelon 9 mm</t>
+        </is>
+      </c>
+      <c r="G288" s="4" t="inlineStr">
+        <is>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="H288" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I288" s="6" t="inlineStr">
+        <is>
+          <t>VV DV1.1 = 2.0 bm  [document:VV výkaz výměr]</t>
+        </is>
+      </c>
+      <c r="J288" s="6" t="inlineStr"/>
+    </row>
+    <row r="289">
+      <c r="A289" s="10" t="n">
+        <v>193</v>
+      </c>
+      <c r="B289" s="11" t="inlineStr"/>
+      <c r="C289" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D289" s="11" t="inlineStr">
+        <is>
+          <t>M-ZTI</t>
+        </is>
+      </c>
+      <c r="E289" s="11" t="inlineStr">
+        <is>
+          <t>M-ZTI-002</t>
+        </is>
+      </c>
+      <c r="F289" s="12" t="inlineStr">
+        <is>
+          <t>EVO PP-RCT 16×2,2 + izolace mirelon 13 mm</t>
+        </is>
+      </c>
+      <c r="G289" s="10" t="inlineStr">
+        <is>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="H289" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I289" s="12" t="inlineStr">
+        <is>
+          <t>VV DV1.2 = 2.0 bm  [document:VV výkaz výměr]</t>
+        </is>
+      </c>
+      <c r="J289" s="12" t="inlineStr"/>
+    </row>
+    <row r="290">
+      <c r="A290" s="4" t="n">
+        <v>194</v>
+      </c>
+      <c r="B290" s="5" t="inlineStr"/>
+      <c r="C290" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D290" s="5" t="inlineStr">
+        <is>
+          <t>M-ZTI</t>
+        </is>
+      </c>
+      <c r="E290" s="5" t="inlineStr">
+        <is>
+          <t>M-ZTI-003</t>
+        </is>
+      </c>
+      <c r="F290" s="6" t="inlineStr">
+        <is>
+          <t>EVO PP-RCT 20×2,3–50×4,6 + izolace mirelon 9–30 mm</t>
+        </is>
+      </c>
+      <c r="G290" s="4" t="inlineStr">
+        <is>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="H290" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="I290" s="6" t="inlineStr">
+        <is>
+          <t>VV DV1.3 = 8.0 bm  [document:VV výkaz výměr]</t>
+        </is>
+      </c>
+      <c r="J290" s="6" t="inlineStr"/>
+    </row>
+    <row r="291">
+      <c r="A291" s="10" t="n">
+        <v>195</v>
+      </c>
+      <c r="B291" s="11" t="inlineStr"/>
+      <c r="C291" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D291" s="11" t="inlineStr">
+        <is>
+          <t>M-ZTI</t>
+        </is>
+      </c>
+      <c r="E291" s="11" t="inlineStr">
+        <is>
+          <t>M-ZTI-004</t>
+        </is>
+      </c>
+      <c r="F291" s="12" t="inlineStr">
+        <is>
+          <t>Rohový ventil 1/2" + flexi hadička, připojení zařizovacích předmětů — komplet</t>
+        </is>
+      </c>
+      <c r="G291" s="10" t="inlineStr">
+        <is>
+          <t>kus</t>
+        </is>
+      </c>
+      <c r="H291" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I291" s="12" t="inlineStr">
+        <is>
+          <t>VV DV3.1 = 2.0 kus  [document:VV výkaz výměr]</t>
+        </is>
+      </c>
+      <c r="J291" s="12" t="inlineStr"/>
+    </row>
+    <row r="292">
+      <c r="A292" s="4" t="n">
+        <v>196</v>
+      </c>
+      <c r="B292" s="5" t="inlineStr"/>
+      <c r="C292" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D292" s="5" t="inlineStr">
+        <is>
+          <t>M-ZTI</t>
+        </is>
+      </c>
+      <c r="E292" s="5" t="inlineStr">
+        <is>
+          <t>M-ZTI-005</t>
+        </is>
+      </c>
+      <c r="F292" s="6" t="inlineStr">
+        <is>
+          <t>Kulový kohout DN40 s vypouštěním</t>
+        </is>
+      </c>
+      <c r="G292" s="4" t="inlineStr">
+        <is>
+          <t>kus</t>
+        </is>
+      </c>
+      <c r="H292" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I292" s="6" t="inlineStr">
+        <is>
+          <t>VV DV3.2 = 1.0 kus  [document:VV výkaz výměr]</t>
+        </is>
+      </c>
+      <c r="J292" s="6" t="inlineStr"/>
+    </row>
+    <row r="293">
+      <c r="A293" s="10" t="n">
+        <v>197</v>
+      </c>
+      <c r="B293" s="11" t="inlineStr"/>
+      <c r="C293" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D293" s="11" t="inlineStr">
+        <is>
+          <t>M-ZTI</t>
+        </is>
+      </c>
+      <c r="E293" s="11" t="inlineStr">
+        <is>
+          <t>M-ZTI-006</t>
+        </is>
+      </c>
+      <c r="F293" s="12" t="inlineStr">
+        <is>
+          <t>Podružná vodoměrná sestava dle požadavku provozovatele areálové sítě</t>
+        </is>
+      </c>
+      <c r="G293" s="10" t="inlineStr">
+        <is>
+          <t>kus</t>
+        </is>
+      </c>
+      <c r="H293" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I293" s="12" t="inlineStr">
+        <is>
+          <t>VV DV3.3 = 1.0 kus  [document:VV výkaz výměr]</t>
+        </is>
+      </c>
+      <c r="J293" s="12" t="inlineStr"/>
+    </row>
+    <row r="294">
+      <c r="A294" s="4" t="n">
+        <v>198</v>
+      </c>
+      <c r="B294" s="5" t="inlineStr"/>
+      <c r="C294" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D294" s="5" t="inlineStr">
+        <is>
+          <t>M-ZTI</t>
+        </is>
+      </c>
+      <c r="E294" s="5" t="inlineStr">
+        <is>
+          <t>M-ZTI-007</t>
+        </is>
+      </c>
+      <c r="F294" s="6" t="inlineStr">
+        <is>
+          <t>Stojánková páková umyvadlová směšovací baterie s ramínkem</t>
+        </is>
+      </c>
+      <c r="G294" s="4" t="inlineStr">
+        <is>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="H294" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I294" s="6" t="inlineStr">
+        <is>
+          <t>VV DV4.1 = 1.0 ks  [document:VV výkaz výměr]</t>
+        </is>
+      </c>
+      <c r="J294" s="6" t="inlineStr"/>
+    </row>
+    <row r="295">
+      <c r="A295" s="10" t="n">
+        <v>199</v>
+      </c>
+      <c r="B295" s="11" t="inlineStr"/>
+      <c r="C295" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D295" s="11" t="inlineStr">
+        <is>
+          <t>M-ZTI</t>
+        </is>
+      </c>
+      <c r="E295" s="11" t="inlineStr">
+        <is>
+          <t>M-ZTI-008</t>
+        </is>
+      </c>
+      <c r="F295" s="12" t="inlineStr">
+        <is>
+          <t>Automatická stanice přípravy TUV vč. jistící armatury — el. tlakově nezávislý zásobník (dodávka VYT, komplet)</t>
+        </is>
+      </c>
+      <c r="G295" s="10" t="inlineStr">
+        <is>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="H295" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I295" s="12" t="inlineStr">
+        <is>
+          <t>VV DV5.1 = 1.0 ks  [document:VV výkaz výměr]</t>
+        </is>
+      </c>
+      <c r="J295" s="12" t="inlineStr"/>
+    </row>
+    <row r="296">
+      <c r="A296" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="B296" s="5" t="inlineStr"/>
+      <c r="C296" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D296" s="5" t="inlineStr">
+        <is>
+          <t>M-ZTI</t>
+        </is>
+      </c>
+      <c r="E296" s="5" t="inlineStr">
+        <is>
+          <t>M-ZTI-009</t>
+        </is>
+      </c>
+      <c r="F296" s="6" t="inlineStr">
+        <is>
+          <t>Uzavírací ventil DN20</t>
+        </is>
+      </c>
+      <c r="G296" s="4" t="inlineStr">
+        <is>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="H296" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I296" s="6" t="inlineStr">
+        <is>
+          <t>VV DV5.2 = 2.0 ks  [document:VV výkaz výměr]</t>
+        </is>
+      </c>
+      <c r="J296" s="6" t="inlineStr"/>
+    </row>
+    <row r="297">
+      <c r="A297" s="10" t="n">
+        <v>201</v>
+      </c>
+      <c r="B297" s="11" t="inlineStr"/>
+      <c r="C297" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D297" s="11" t="inlineStr">
+        <is>
+          <t>M-ZTI</t>
+        </is>
+      </c>
+      <c r="E297" s="11" t="inlineStr">
+        <is>
+          <t>M-ZTI-010</t>
+        </is>
+      </c>
+      <c r="F297" s="12" t="inlineStr">
+        <is>
+          <t>Umyvadlo dle výběru investora vč. kotvících prvků (komplet)</t>
+        </is>
+      </c>
+      <c r="G297" s="10" t="inlineStr">
+        <is>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="H297" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I297" s="12" t="inlineStr">
+        <is>
+          <t>VV DV6.1 = 1.0 ks  [document:VV výkaz výměr]</t>
+        </is>
+      </c>
+      <c r="J297" s="12" t="inlineStr"/>
+    </row>
+    <row r="298">
+      <c r="A298" s="4" t="n">
+        <v>202</v>
+      </c>
+      <c r="B298" s="5" t="inlineStr"/>
+      <c r="C298" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D298" s="5" t="inlineStr">
+        <is>
+          <t>M-ZTI</t>
+        </is>
+      </c>
+      <c r="E298" s="5" t="inlineStr">
+        <is>
+          <t>M-ZTI-011</t>
+        </is>
+      </c>
+      <c r="F298" s="6" t="inlineStr">
+        <is>
+          <t>Ocelové pozinkové potrubí DN20 (požární vodovod)</t>
+        </is>
+      </c>
+      <c r="G298" s="4" t="inlineStr">
+        <is>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="H298" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I298" s="6" t="inlineStr">
+        <is>
+          <t>VV DV7.1 = 1.0 bm  [document:VV výkaz výměr]</t>
+        </is>
+      </c>
+      <c r="J298" s="6" t="inlineStr"/>
+    </row>
+    <row r="299">
+      <c r="A299" s="10" t="n">
+        <v>203</v>
+      </c>
+      <c r="B299" s="11" t="inlineStr"/>
+      <c r="C299" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D299" s="11" t="inlineStr">
+        <is>
+          <t>M-ZTI</t>
+        </is>
+      </c>
+      <c r="E299" s="11" t="inlineStr">
+        <is>
+          <t>M-ZTI-012</t>
+        </is>
+      </c>
+      <c r="F299" s="12" t="inlineStr">
+        <is>
+          <t>Ocelové pozinkové potrubí DN25 (požární vodovod)</t>
+        </is>
+      </c>
+      <c r="G299" s="10" t="inlineStr">
+        <is>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="H299" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="I299" s="12" t="inlineStr">
+        <is>
+          <t>VV DV7.2 = 5.0 bm  [document:VV výkaz výměr]</t>
+        </is>
+      </c>
+      <c r="J299" s="12" t="inlineStr"/>
+    </row>
+    <row r="300">
+      <c r="A300" s="4" t="n">
+        <v>204</v>
+      </c>
+      <c r="B300" s="5" t="inlineStr"/>
+      <c r="C300" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D300" s="5" t="inlineStr">
+        <is>
+          <t>M-ZTI</t>
+        </is>
+      </c>
+      <c r="E300" s="5" t="inlineStr">
+        <is>
+          <t>M-ZTI-013</t>
+        </is>
+      </c>
+      <c r="F300" s="6" t="inlineStr">
+        <is>
+          <t>Ocelové pozinkové potrubí DN32 (požární vodovod)</t>
+        </is>
+      </c>
+      <c r="G300" s="4" t="inlineStr">
+        <is>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="H300" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="I300" s="6" t="inlineStr">
+        <is>
+          <t>VV DV7.3 = 40.0 bm  [document:VV výkaz výměr]</t>
+        </is>
+      </c>
+      <c r="J300" s="6" t="inlineStr"/>
+    </row>
+    <row r="301">
+      <c r="A301" s="10" t="n">
+        <v>205</v>
+      </c>
+      <c r="B301" s="11" t="inlineStr"/>
+      <c r="C301" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D301" s="11" t="inlineStr">
+        <is>
+          <t>M-ZTI</t>
+        </is>
+      </c>
+      <c r="E301" s="11" t="inlineStr">
+        <is>
+          <t>M-ZTI-014</t>
+        </is>
+      </c>
+      <c r="F301" s="12" t="inlineStr">
+        <is>
+          <t>Hydrant typu D19/30 dle PBŘ — do výklenku vč. uzavíracího kohoutu + tvarově stálá hadice</t>
+        </is>
+      </c>
+      <c r="G301" s="10" t="inlineStr">
+        <is>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="H301" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I301" s="12" t="inlineStr">
+        <is>
+          <t>VV DV7.4 = 1.0 ks  [document:VV výkaz výměr]</t>
+        </is>
+      </c>
+      <c r="J301" s="12" t="inlineStr"/>
+    </row>
+    <row r="302">
+      <c r="A302" s="4" t="n">
+        <v>206</v>
+      </c>
+      <c r="B302" s="5" t="inlineStr"/>
+      <c r="C302" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D302" s="5" t="inlineStr">
+        <is>
+          <t>M-ZTI</t>
+        </is>
+      </c>
+      <c r="E302" s="5" t="inlineStr">
+        <is>
+          <t>M-ZTI-015</t>
+        </is>
+      </c>
+      <c r="F302" s="6" t="inlineStr">
+        <is>
+          <t>Zpětná klapka DN32 EA — oddělovač požárního a spotřebního vodovodu</t>
+        </is>
+      </c>
+      <c r="G302" s="4" t="inlineStr">
+        <is>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="H302" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I302" s="6" t="inlineStr">
+        <is>
+          <t>VV DV7.5 = 1.0 ks  [document:VV výkaz výměr]</t>
+        </is>
+      </c>
+      <c r="J302" s="6" t="inlineStr"/>
+    </row>
+    <row r="303">
+      <c r="A303" s="3" t="inlineStr">
+        <is>
+          <t>→ Přeložka vodovodního řadu (PODMÍNĚNÁ — pending ABMV_23)</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="7" t="n">
+        <v>207</v>
+      </c>
+      <c r="B304" s="8" t="inlineStr"/>
+      <c r="C304" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="D304" s="8" t="inlineStr">
+        <is>
           <t>M-VK</t>
         </is>
       </c>
-      <c r="E269" s="11" t="inlineStr">
+      <c r="E304" s="8" t="inlineStr">
+        <is>
+          <t>M-VK-009</t>
+        </is>
+      </c>
+      <c r="F304" s="9" t="inlineStr">
+        <is>
+          <t>Přeložka stávajícího vodovodního řadu (rerouting) — kompletní práce vč. potrubí, výkop, napojení, tlakové zkoušky</t>
+        </is>
+      </c>
+      <c r="G304" s="7" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="H304" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I304" s="9" t="inlineStr">
+        <is>
+          <t>1 kpl  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
+        </is>
+      </c>
+      <c r="J304" s="9" t="inlineStr">
+        <is>
+          <t>ABMV:ABMV_23</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="3" t="inlineStr">
+        <is>
+          <t>→ NN chránička HDPE — stavební příprava (silové v elektro VV)</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="4" t="n">
+        <v>208</v>
+      </c>
+      <c r="B306" s="5" t="inlineStr"/>
+      <c r="C306" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D306" s="5" t="inlineStr">
+        <is>
+          <t>M-VK</t>
+        </is>
+      </c>
+      <c r="E306" s="5" t="inlineStr">
+        <is>
+          <t>M-VK-008</t>
+        </is>
+      </c>
+      <c r="F306" s="6" t="inlineStr">
+        <is>
+          <t>Přípojka NN — chránička HDPE Ø110 mm + pomocné výkopy + pískové lože + zásyp + výstražná páska</t>
+        </is>
+      </c>
+      <c r="G306" s="4" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="H306" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="I306" s="6" t="inlineStr">
+        <is>
+          <t>40 m  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
+        </is>
+      </c>
+      <c r="J306" s="6" t="inlineStr"/>
+    </row>
+    <row r="307">
+      <c r="A307" s="3" t="inlineStr">
+        <is>
+          <t>→ Okapní chodník beton — 10-layer stack 0.7 m × 80 m (výkop → odvoz → pláň → geotextilie → štěrk → hutnění → bednění → výztuž → beton → dilatace, pending ABMV_31/32/34)</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="4" t="n">
+        <v>209</v>
+      </c>
+      <c r="B308" s="5" t="inlineStr"/>
+      <c r="C308" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D308" s="5" t="inlineStr">
+        <is>
+          <t>M-VK</t>
+        </is>
+      </c>
+      <c r="E308" s="5" t="inlineStr">
+        <is>
+          <t>M-VK-027</t>
+        </is>
+      </c>
+      <c r="F308" s="6" t="inlineStr">
+        <is>
+          <t>Výkop rýhy pro okapní chodník hl. 400 mm (na hloubku všech vrstev)</t>
+        </is>
+      </c>
+      <c r="G308" s="4" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="H308" s="4" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="I308" s="6" t="inlineStr">
+        <is>
+          <t>80.0 × 0.7 × 0.4 = 22.4 m³  [document:A103 řez A-B detail, norma:ČSN 73 6126, norma:ČSN okapový chodník]</t>
+        </is>
+      </c>
+      <c r="J308" s="6" t="inlineStr">
+        <is>
+          <t>ABMV:ABMV_32</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="10" t="n">
+        <v>210</v>
+      </c>
+      <c r="B309" s="11" t="inlineStr"/>
+      <c r="C309" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D309" s="11" t="inlineStr">
+        <is>
+          <t>M-VK</t>
+        </is>
+      </c>
+      <c r="E309" s="11" t="inlineStr">
+        <is>
+          <t>M-VK-028</t>
+        </is>
+      </c>
+      <c r="F309" s="12" t="inlineStr">
+        <is>
+          <t>Odvoz vykopané zeminy z rýhy okapního chodníku na skládku</t>
+        </is>
+      </c>
+      <c r="G309" s="10" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="H309" s="10" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="I309" s="12">
+        <f> 22.4 m³ (1:1 s výkopem)  [document:A103 řez A-B detail, norma:ČSN 73 6126, norma:ČSN okapový chodník]</f>
+        <v/>
+      </c>
+      <c r="J309" s="12" t="inlineStr">
+        <is>
+          <t>ABMV:ABMV_32</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="4" t="n">
+        <v>211</v>
+      </c>
+      <c r="B310" s="5" t="inlineStr"/>
+      <c r="C310" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D310" s="5" t="inlineStr">
+        <is>
+          <t>M-VK</t>
+        </is>
+      </c>
+      <c r="E310" s="5" t="inlineStr">
+        <is>
+          <t>M-VK-024</t>
+        </is>
+      </c>
+      <c r="F310" s="6" t="inlineStr">
+        <is>
+          <t>Úprava zemní pláně + hutnění pod okapní chodník (Edef2 ≥ 30 MPa)</t>
+        </is>
+      </c>
+      <c r="G310" s="4" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="H310" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="I310" s="6" t="inlineStr">
+        <is>
+          <t>80.0 × 0.7 = 56.0 m²  [document:A103 řez A-B detail, norma:ČSN 73 6126, norma:ČSN EN 13670]</t>
+        </is>
+      </c>
+      <c r="J310" s="6" t="inlineStr">
+        <is>
+          <t>ABMV:ABMV_32</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="10" t="n">
+        <v>212</v>
+      </c>
+      <c r="B311" s="11" t="inlineStr"/>
+      <c r="C311" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D311" s="11" t="inlineStr">
+        <is>
+          <t>M-VK</t>
+        </is>
+      </c>
+      <c r="E311" s="11" t="inlineStr">
+        <is>
+          <t>M-VK-029</t>
+        </is>
+      </c>
+      <c r="F311" s="12" t="inlineStr">
+        <is>
+          <t>Geotextilie 300 g/m² separační — mezi hutněnou zemní pláň a štěrkový podklad okapního chodníku</t>
+        </is>
+      </c>
+      <c r="G311" s="10" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="H311" s="10" t="n">
+        <v>56</v>
+      </c>
+      <c r="I311" s="12" t="inlineStr">
+        <is>
+          <t>80.0 × 0.7 = 56.0 m²  [document:A103 řez A-B detail, norma:ČSN 73 6126, norma:ČSN okapový chodník]</t>
+        </is>
+      </c>
+      <c r="J311" s="12" t="inlineStr">
+        <is>
+          <t>ABMV:ABMV_32</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="4" t="n">
+        <v>213</v>
+      </c>
+      <c r="B312" s="5" t="inlineStr"/>
+      <c r="C312" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D312" s="5" t="inlineStr">
+        <is>
+          <t>M-VK</t>
+        </is>
+      </c>
+      <c r="E312" s="5" t="inlineStr">
+        <is>
+          <t>M-VK-022</t>
+        </is>
+      </c>
+      <c r="F312" s="6" t="inlineStr">
+        <is>
+          <t>Drcený štěrk ŠD 32/63 podklad okapního chodníku tl 150 mm</t>
+        </is>
+      </c>
+      <c r="G312" s="4" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="H312" s="4" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="I312" s="6" t="inlineStr">
+        <is>
+          <t>80.0 × 0.7 × 0.15 = 8.40 m³  [document:A103 řezy A-B detail, document:A101 půdorys 1NP, document:C.3 KOO situace]</t>
+        </is>
+      </c>
+      <c r="J312" s="6" t="inlineStr">
+        <is>
+          <t>ABMV:ABMV_31</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="10" t="n">
+        <v>214</v>
+      </c>
+      <c r="B313" s="11" t="inlineStr"/>
+      <c r="C313" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D313" s="11" t="inlineStr">
+        <is>
+          <t>M-VK</t>
+        </is>
+      </c>
+      <c r="E313" s="11" t="inlineStr">
+        <is>
+          <t>M-VK-025</t>
+        </is>
+      </c>
+      <c r="F313" s="12" t="inlineStr">
+        <is>
+          <t>Hutnění štěrkového podkladu okapního chodníku vibrodeskou (Edef2 ≥ 45 MPa)</t>
+        </is>
+      </c>
+      <c r="G313" s="10" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="H313" s="10" t="n">
+        <v>56</v>
+      </c>
+      <c r="I313" s="12" t="inlineStr">
+        <is>
+          <t>80.0 × 0.7 = 56.0 m²  [document:A103 řez A-B detail, norma:ČSN 73 6126, norma:ČSN EN 13670]</t>
+        </is>
+      </c>
+      <c r="J313" s="12" t="inlineStr">
+        <is>
+          <t>ABMV:ABMV_32</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="4" t="n">
+        <v>215</v>
+      </c>
+      <c r="B314" s="5" t="inlineStr"/>
+      <c r="C314" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D314" s="5" t="inlineStr">
+        <is>
+          <t>M-VK</t>
+        </is>
+      </c>
+      <c r="E314" s="5" t="inlineStr">
+        <is>
+          <t>M-VK-026</t>
+        </is>
+      </c>
+      <c r="F314" s="6" t="inlineStr">
+        <is>
+          <t>Bednění boční vnější hrana okapního chodníku v 200 mm (vnitřní hrana = stěna haly)</t>
+        </is>
+      </c>
+      <c r="G314" s="4" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="H314" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="I314" s="6" t="inlineStr">
+        <is>
+          <t>80.0 × 0.2 = 16.0 m²  [document:A103 řez A-B detail, norma:ČSN 73 6126, norma:ČSN EN 13670]</t>
+        </is>
+      </c>
+      <c r="J314" s="6" t="inlineStr">
+        <is>
+          <t>ABMV:ABMV_32</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="10" t="n">
+        <v>216</v>
+      </c>
+      <c r="B315" s="11" t="inlineStr"/>
+      <c r="C315" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D315" s="11" t="inlineStr">
+        <is>
+          <t>M-VK</t>
+        </is>
+      </c>
+      <c r="E315" s="11" t="inlineStr">
+        <is>
+          <t>M-VK-021</t>
+        </is>
+      </c>
+      <c r="F315" s="12" t="inlineStr">
+        <is>
+          <t>Výztuž KARI síť Q188 (150/150/6 mm) — okapní chodník</t>
+        </is>
+      </c>
+      <c r="G315" s="10" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="H315" s="10" t="n">
+        <v>56</v>
+      </c>
+      <c r="I315" s="12" t="inlineStr">
+        <is>
+          <t>80.0 × 0.7 = 56.00 m²  [document:A103 řezy A-B detail, document:A101 půdorys 1NP, document:C.3 KOO situace]</t>
+        </is>
+      </c>
+      <c r="J315" s="12" t="inlineStr">
+        <is>
+          <t>ABMV:ABMV_31</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="4" t="n">
+        <v>217</v>
+      </c>
+      <c r="B316" s="5" t="inlineStr"/>
+      <c r="C316" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D316" s="5" t="inlineStr">
+        <is>
+          <t>M-VK</t>
+        </is>
+      </c>
+      <c r="E316" s="5" t="inlineStr">
+        <is>
+          <t>M-VK-020</t>
+        </is>
+      </c>
+      <c r="F316" s="6" t="inlineStr">
+        <is>
+          <t>Beton C25/30 XF3 — okapní chodník po obvodu haly (sokl 0.7 m × ~80 m mimo 4 vstupy), tl 200 mm</t>
+        </is>
+      </c>
+      <c r="G316" s="4" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="H316" s="4" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="I316" s="6" t="inlineStr">
+        <is>
+          <t>80.0 × 0.7 × 0.2 = 11.20 m³  [document:A103 řezy A-B detail, document:A101 půdorys 1NP, document:C.3 KOO situace]</t>
+        </is>
+      </c>
+      <c r="J316" s="6" t="inlineStr">
+        <is>
+          <t>ABMV:ABMV_31</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="10" t="n">
+        <v>218</v>
+      </c>
+      <c r="B317" s="11" t="inlineStr"/>
+      <c r="C317" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D317" s="11" t="inlineStr">
+        <is>
+          <t>M-VK</t>
+        </is>
+      </c>
+      <c r="E317" s="11" t="inlineStr">
+        <is>
+          <t>M-VK-023</t>
+        </is>
+      </c>
+      <c r="F317" s="12" t="inlineStr">
+        <is>
+          <t>Dilatační lišty + těsnění spár mezi segmenty okapního chodníku (à ~4 m)</t>
+        </is>
+      </c>
+      <c r="G317" s="10" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="H317" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="I317" s="12" t="inlineStr">
+        <is>
+          <t>80.0 / 4 = 20 ks dilatací  [document:A103 řezy A-B detail, document:A101 půdorys 1NP, document:C.3 KOO situace]</t>
+        </is>
+      </c>
+      <c r="J317" s="12" t="inlineStr">
+        <is>
+          <t>ABMV:ABMV_31</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="3" t="inlineStr">
+        <is>
+          <t>→ Zámková dlažba chodník 1.5 m — ČSN 73 6131 stack (výkop → odvoz → pláň → geotextilie → štěrk → drť 4/8 → obrubník → lože → dlažba → spáry; TZ ARS B p09, pending ABMV_34)</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="4" t="n">
+        <v>219</v>
+      </c>
+      <c r="B319" s="5" t="inlineStr"/>
+      <c r="C319" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D319" s="5" t="inlineStr">
+        <is>
+          <t>M-VK</t>
+        </is>
+      </c>
+      <c r="E319" s="5" t="inlineStr">
+        <is>
+          <t>M-VK-030</t>
+        </is>
+      </c>
+      <c r="F319" s="6" t="inlineStr">
+        <is>
+          <t>Výkop rýhy pro zámkovou dlažbu chodníku hl. ~300 mm</t>
+        </is>
+      </c>
+      <c r="G319" s="4" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="H319" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="I319" s="6" t="inlineStr">
+        <is>
+          <t>80.0 × 1.5 × 0.30 = 36.0 m³  [TZ:ARS B p09, norma:ČSN 73 6131-1, user_decision:2026-05-27]</t>
+        </is>
+      </c>
+      <c r="J319" s="6" t="inlineStr">
+        <is>
+          <t>ABMV:ABMV_34</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="10" t="n">
+        <v>220</v>
+      </c>
+      <c r="B320" s="11" t="inlineStr"/>
+      <c r="C320" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D320" s="11" t="inlineStr">
+        <is>
+          <t>M-VK</t>
+        </is>
+      </c>
+      <c r="E320" s="11" t="inlineStr">
+        <is>
+          <t>M-VK-031</t>
+        </is>
+      </c>
+      <c r="F320" s="12" t="inlineStr">
+        <is>
+          <t>Odvoz vykopané zeminy z rýhy chodníku na skládku</t>
+        </is>
+      </c>
+      <c r="G320" s="10" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="H320" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="I320" s="12">
+        <f> objem výkopu M-VK-030 = 36.0 m³  [TZ:ARS B p09, norma:ČSN 73 6131-1, user_decision:2026-05-27]</f>
+        <v/>
+      </c>
+      <c r="J320" s="12" t="inlineStr">
+        <is>
+          <t>ABMV:ABMV_34</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="4" t="n">
+        <v>221</v>
+      </c>
+      <c r="B321" s="5" t="inlineStr"/>
+      <c r="C321" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D321" s="5" t="inlineStr">
+        <is>
+          <t>M-VK</t>
+        </is>
+      </c>
+      <c r="E321" s="5" t="inlineStr">
+        <is>
+          <t>M-VK-032</t>
+        </is>
+      </c>
+      <c r="F321" s="6" t="inlineStr">
+        <is>
+          <t>Úprava + hutnění zemní pláně pod dlažbu chodníku (Edef2 ≥ 30 MPa)</t>
+        </is>
+      </c>
+      <c r="G321" s="4" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="H321" s="4" t="n">
+        <v>120</v>
+      </c>
+      <c r="I321" s="6" t="inlineStr">
+        <is>
+          <t>80.0 × 1.5 = 120.0 m²  [TZ:ARS B p09, norma:ČSN 73 6131-1, user_decision:2026-05-27]</t>
+        </is>
+      </c>
+      <c r="J321" s="6" t="inlineStr">
+        <is>
+          <t>ABMV:ABMV_34</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="10" t="n">
+        <v>222</v>
+      </c>
+      <c r="B322" s="11" t="inlineStr"/>
+      <c r="C322" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D322" s="11" t="inlineStr">
+        <is>
+          <t>M-VK</t>
+        </is>
+      </c>
+      <c r="E322" s="11" t="inlineStr">
+        <is>
+          <t>M-VK-033</t>
+        </is>
+      </c>
+      <c r="F322" s="12" t="inlineStr">
+        <is>
+          <t>Geotextilie 300 g/m² separační pod dlažbu chodníku</t>
+        </is>
+      </c>
+      <c r="G322" s="10" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="H322" s="10" t="n">
+        <v>120</v>
+      </c>
+      <c r="I322" s="12" t="inlineStr">
+        <is>
+          <t>80.0 × 1.5 = 120.0 m²  [TZ:ARS B p09, norma:ČSN 73 6131-1, user_decision:2026-05-27]</t>
+        </is>
+      </c>
+      <c r="J322" s="12" t="inlineStr">
+        <is>
+          <t>ABMV:ABMV_34</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="4" t="n">
+        <v>223</v>
+      </c>
+      <c r="B323" s="5" t="inlineStr"/>
+      <c r="C323" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D323" s="5" t="inlineStr">
+        <is>
+          <t>M-VK</t>
+        </is>
+      </c>
+      <c r="E323" s="5" t="inlineStr">
+        <is>
+          <t>M-VK-034</t>
+        </is>
+      </c>
+      <c r="F323" s="6" t="inlineStr">
+        <is>
+          <t>Štěrk ŠD 32/63 nosná podkladní vrstva tl 150 mm + hutnění (chodník dlažba)</t>
+        </is>
+      </c>
+      <c r="G323" s="4" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="H323" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="I323" s="6" t="inlineStr">
+        <is>
+          <t>120.0 × 0.15 = 18.0 m³  [TZ:ARS B p09, norma:ČSN 73 6131-1, user_decision:2026-05-27]</t>
+        </is>
+      </c>
+      <c r="J323" s="6" t="inlineStr">
+        <is>
+          <t>ABMV:ABMV_34</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="10" t="n">
+        <v>224</v>
+      </c>
+      <c r="B324" s="11" t="inlineStr"/>
+      <c r="C324" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D324" s="11" t="inlineStr">
+        <is>
+          <t>M-VK</t>
+        </is>
+      </c>
+      <c r="E324" s="11" t="inlineStr">
+        <is>
+          <t>M-VK-035</t>
+        </is>
+      </c>
+      <c r="F324" s="12" t="inlineStr">
+        <is>
+          <t>Jemný štěrk / drť frakce 4/8 mm — ložná vrstva dlažby tl 40 mm</t>
+        </is>
+      </c>
+      <c r="G324" s="10" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="H324" s="10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I324" s="12" t="inlineStr">
+        <is>
+          <t>120.0 × 0.04 = 4.8 m³  [TZ:ARS B p09, norma:ČSN 73 6131-1, user_decision:2026-05-27]</t>
+        </is>
+      </c>
+      <c r="J324" s="12" t="inlineStr">
+        <is>
+          <t>ABMV:ABMV_34</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="4" t="n">
+        <v>225</v>
+      </c>
+      <c r="B325" s="5" t="inlineStr"/>
+      <c r="C325" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D325" s="5" t="inlineStr">
+        <is>
+          <t>M-VK</t>
+        </is>
+      </c>
+      <c r="E325" s="5" t="inlineStr">
+        <is>
+          <t>M-VK-036</t>
+        </is>
+      </c>
+      <c r="F325" s="6" t="inlineStr">
+        <is>
+          <t>Obrubníky betonové ABO 100×250 do betonového lože C16/20 (lemování chodníku)</t>
+        </is>
+      </c>
+      <c r="G325" s="4" t="inlineStr">
+        <is>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="H325" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="I325" s="6" t="inlineStr">
+        <is>
+          <t>~80.0 bm (vnější hrana chodníku)  [TZ:ARS B p09, norma:ČSN 73 6131-1, user_decision:2026-05-27]</t>
+        </is>
+      </c>
+      <c r="J325" s="6" t="inlineStr">
+        <is>
+          <t>ABMV:ABMV_34</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="10" t="n">
+        <v>226</v>
+      </c>
+      <c r="B326" s="11" t="inlineStr"/>
+      <c r="C326" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D326" s="11" t="inlineStr">
+        <is>
+          <t>M-VK</t>
+        </is>
+      </c>
+      <c r="E326" s="11" t="inlineStr">
+        <is>
+          <t>M-VK-037</t>
+        </is>
+      </c>
+      <c r="F326" s="12" t="inlineStr">
+        <is>
+          <t>Beton lože C16/20 pod obrubníky chodníku + boční opěra</t>
+        </is>
+      </c>
+      <c r="G326" s="10" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="H326" s="10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="I326" s="12" t="inlineStr">
+        <is>
+          <t>80 bm × ~0.03 m³/bm (lože + opěra) = ~2.4 m³  [TZ:ARS B p09, norma:ČSN 73 6131-1, user_decision:2026-05-27]</t>
+        </is>
+      </c>
+      <c r="J326" s="12" t="inlineStr">
+        <is>
+          <t>ABMV:ABMV_34</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="4" t="n">
+        <v>227</v>
+      </c>
+      <c r="B327" s="5" t="inlineStr"/>
+      <c r="C327" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D327" s="5" t="inlineStr">
+        <is>
+          <t>M-VK</t>
+        </is>
+      </c>
+      <c r="E327" s="5" t="inlineStr">
+        <is>
+          <t>M-VK-038</t>
+        </is>
+      </c>
+      <c r="F327" s="6" t="inlineStr">
+        <is>
+          <t>Zámková dlažba BEST tl 80 mm — kladení, sklon 2 % od fasády</t>
+        </is>
+      </c>
+      <c r="G327" s="4" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="H327" s="4" t="n">
+        <v>120</v>
+      </c>
+      <c r="I327" s="6" t="inlineStr">
+        <is>
+          <t>80.0 × 1.5 = 120.0 m²  [TZ:ARS B p09, norma:ČSN 73 6131-1, user_decision:2026-05-27]</t>
+        </is>
+      </c>
+      <c r="J327" s="6" t="inlineStr">
+        <is>
+          <t>ABMV:ABMV_34</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="10" t="n">
+        <v>228</v>
+      </c>
+      <c r="B328" s="11" t="inlineStr"/>
+      <c r="C328" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D328" s="11" t="inlineStr">
+        <is>
+          <t>M-VK</t>
+        </is>
+      </c>
+      <c r="E328" s="11" t="inlineStr">
+        <is>
+          <t>M-VK-039</t>
+        </is>
+      </c>
+      <c r="F328" s="12" t="inlineStr">
+        <is>
+          <t>Zásyp spár křemičitým pískem frakce 0,2 mm + hutnění vibrodeskou</t>
+        </is>
+      </c>
+      <c r="G328" s="10" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="H328" s="10" t="n">
+        <v>120</v>
+      </c>
+      <c r="I328" s="12" t="inlineStr">
+        <is>
+          <t>80.0 × 1.5 = 120.0 m²  [TZ:ARS B p09, norma:ČSN 73 6131-1, user_decision:2026-05-27]</t>
+        </is>
+      </c>
+      <c r="J328" s="12" t="inlineStr">
+        <is>
+          <t>ABMV:ABMV_34</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="3" t="inlineStr">
+        <is>
+          <t>→ Drcený štěrk podklad ramp</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="4" t="n">
+        <v>229</v>
+      </c>
+      <c r="B330" s="5" t="inlineStr"/>
+      <c r="C330" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D330" s="5" t="inlineStr">
+        <is>
+          <t>M-VK</t>
+        </is>
+      </c>
+      <c r="E330" s="5" t="inlineStr">
+        <is>
+          <t>M-VK-003</t>
+        </is>
+      </c>
+      <c r="F330" s="6" t="inlineStr">
+        <is>
+          <t>Drcený štěrk ŠD 32/63 podklad rampy + okapní pas tl 200 mm</t>
+        </is>
+      </c>
+      <c r="G330" s="4" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="H330" s="4" t="n">
+        <v>8.66</v>
+      </c>
+      <c r="I330" s="6" t="inlineStr">
+        <is>
+          <t>43.32 × 0.20 = 8.66 m³  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
+        </is>
+      </c>
+      <c r="J330" s="6" t="inlineStr"/>
+    </row>
+    <row r="331">
+      <c r="A331" s="3" t="inlineStr">
+        <is>
+          <t>→ Rampy 4× (R1-R4) — výztuž + bednění + beton + obrubník (per A101)</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="4" t="n">
+        <v>230</v>
+      </c>
+      <c r="B332" s="5" t="inlineStr"/>
+      <c r="C332" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D332" s="5" t="inlineStr">
+        <is>
+          <t>M-VK</t>
+        </is>
+      </c>
+      <c r="E332" s="5" t="inlineStr">
+        <is>
+          <t>M-VK-002</t>
+        </is>
+      </c>
+      <c r="F332" s="6" t="inlineStr">
+        <is>
+          <t>Výztuž KARI síť Q188 + bednění boční rampy 4 lokality</t>
+        </is>
+      </c>
+      <c r="G332" s="4" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="H332" s="4" t="n">
+        <v>43.32</v>
+      </c>
+      <c r="I332" s="6" t="inlineStr">
+        <is>
+          <t>4 lokality rampy = 43.32 m²  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
+        </is>
+      </c>
+      <c r="J332" s="6" t="inlineStr"/>
+    </row>
+    <row r="333">
+      <c r="A333" s="10" t="n">
+        <v>231</v>
+      </c>
+      <c r="B333" s="11" t="inlineStr"/>
+      <c r="C333" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D333" s="11" t="inlineStr">
+        <is>
+          <t>M-VK</t>
+        </is>
+      </c>
+      <c r="E333" s="11" t="inlineStr">
         <is>
           <t>M-VK-001</t>
         </is>
       </c>
-      <c r="F269" s="12" t="inlineStr">
+      <c r="F333" s="12" t="inlineStr">
         <is>
           <t>Beton C25/30 XF3 — vstupní/nájezdové rampy tl 150 mm, 4 lokality (R1 sever, R2+R3 jih, R4 západ bezbariérová)</t>
         </is>
       </c>
-      <c r="G269" s="10" t="inlineStr">
+      <c r="G333" s="10" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="H269" s="10" t="n">
+      <c r="H333" s="10" t="n">
         <v>6.5</v>
       </c>
-      <c r="I269" s="12" t="inlineStr">
+      <c r="I333" s="12" t="inlineStr">
         <is>
           <t>(9.2+11.5+9.2+13.42) × 0.15 = 6.50 m³  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
         </is>
       </c>
-      <c r="J269" s="12" t="inlineStr"/>
-    </row>
-    <row r="270">
-      <c r="A270" s="4" t="n">
-        <v>171</v>
-      </c>
-      <c r="B270" s="5" t="inlineStr"/>
-      <c r="C270" s="4" t="n">
+      <c r="J333" s="12" t="inlineStr"/>
+    </row>
+    <row r="334">
+      <c r="A334" s="4" t="n">
+        <v>232</v>
+      </c>
+      <c r="B334" s="5" t="inlineStr"/>
+      <c r="C334" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="D270" s="5" t="inlineStr">
+      <c r="D334" s="5" t="inlineStr">
         <is>
           <t>M-VK</t>
         </is>
       </c>
-      <c r="E270" s="5" t="inlineStr">
+      <c r="E334" s="5" t="inlineStr">
         <is>
           <t>M-VK-004</t>
         </is>
       </c>
-      <c r="F270" s="6" t="inlineStr">
+      <c r="F334" s="6" t="inlineStr">
         <is>
           <t>Obrubník betonový ABO 100×250×1000 kolem ramp + lůžko z betonu C16/20</t>
         </is>
       </c>
-      <c r="G270" s="4" t="inlineStr">
+      <c r="G334" s="4" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="H270" s="4" t="n">
+      <c r="H334" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="I270" s="6" t="inlineStr">
+      <c r="I334" s="6" t="inlineStr">
         <is>
           <t>~30.0 m  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
         </is>
       </c>
-      <c r="J270" s="6" t="inlineStr"/>
-    </row>
-    <row r="271">
-      <c r="A271" s="3" t="inlineStr">
+      <c r="J334" s="6" t="inlineStr"/>
+    </row>
+    <row r="335">
+      <c r="A335" s="3" t="inlineStr">
         <is>
           <t>→ Liniový žlab pojízdný B125 — SZ + JZ fasáda (40 m)</t>
         </is>
       </c>
     </row>
-    <row r="272">
-      <c r="A272" s="4" t="n">
-        <v>172</v>
-      </c>
-      <c r="B272" s="5" t="inlineStr"/>
-      <c r="C272" s="4" t="n">
+    <row r="336">
+      <c r="A336" s="4" t="n">
+        <v>233</v>
+      </c>
+      <c r="B336" s="5" t="inlineStr"/>
+      <c r="C336" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="D272" s="5" t="inlineStr">
+      <c r="D336" s="5" t="inlineStr">
         <is>
           <t>M-VK</t>
         </is>
       </c>
-      <c r="E272" s="5" t="inlineStr">
+      <c r="E336" s="5" t="inlineStr">
         <is>
           <t>M-VK-012</t>
         </is>
       </c>
-      <c r="F272" s="6" t="inlineStr">
+      <c r="F336" s="6" t="inlineStr">
         <is>
           <t>Liniový žlab POJÍZDNÝ tř. zatížení B125 — odvodnění zpevněných ploch parkoviště + manipulace, vč. mřížky</t>
         </is>
       </c>
-      <c r="G272" s="4" t="inlineStr">
+      <c r="G336" s="4" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="H272" s="4" t="n">
+      <c r="H336" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="I272" s="6" t="inlineStr">
+      <c r="I336" s="6" t="inlineStr">
         <is>
           <t>40 m  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
         </is>
       </c>
-      <c r="J272" s="6" t="inlineStr"/>
-    </row>
-    <row r="273">
-      <c r="A273" s="3" t="inlineStr">
+      <c r="J336" s="6" t="inlineStr"/>
+    </row>
+    <row r="337">
+      <c r="A337" s="3" t="inlineStr">
         <is>
           <t>→ Vyspádování okolního terénu k odvodnění</t>
         </is>
       </c>
     </row>
-    <row r="274">
-      <c r="A274" s="4" t="n">
-        <v>173</v>
-      </c>
-      <c r="B274" s="5" t="inlineStr"/>
-      <c r="C274" s="4" t="n">
+    <row r="338">
+      <c r="A338" s="4" t="n">
+        <v>234</v>
+      </c>
+      <c r="B338" s="5" t="inlineStr"/>
+      <c r="C338" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="D274" s="5" t="inlineStr">
+      <c r="D338" s="5" t="inlineStr">
         <is>
           <t>M-VK</t>
         </is>
       </c>
-      <c r="E274" s="5" t="inlineStr">
+      <c r="E338" s="5" t="inlineStr">
         <is>
           <t>M-VK-019</t>
         </is>
       </c>
-      <c r="F274" s="6" t="inlineStr">
+      <c r="F338" s="6" t="inlineStr">
         <is>
           <t>Vyspádování okolního terénu k odvodňovacím prvkům (žlabům, retenční nádrži) — hutněná zemina, finální úprava</t>
         </is>
       </c>
-      <c r="G274" s="4" t="inlineStr">
+      <c r="G338" s="4" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="H274" s="4" t="n">
+      <c r="H338" s="4" t="n">
         <v>300</v>
       </c>
-      <c r="I274" s="6" t="inlineStr">
+      <c r="I338" s="6" t="inlineStr">
         <is>
           <t>300 m²  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
         </is>
       </c>
-      <c r="J274" s="6" t="inlineStr"/>
-    </row>
-    <row r="275">
-      <c r="A275" s="3" t="inlineStr">
+      <c r="J338" s="6" t="inlineStr"/>
+    </row>
+    <row r="339">
+      <c r="A339" s="3" t="inlineStr">
         <is>
           <t>→ Ohumusování + osetí travou zbytkových ploch</t>
         </is>
       </c>
     </row>
-    <row r="276">
-      <c r="A276" s="4" t="n">
-        <v>174</v>
-      </c>
-      <c r="B276" s="5" t="inlineStr"/>
-      <c r="C276" s="4" t="n">
+    <row r="340">
+      <c r="A340" s="4" t="n">
+        <v>235</v>
+      </c>
+      <c r="B340" s="5" t="inlineStr"/>
+      <c r="C340" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="D276" s="5" t="inlineStr">
+      <c r="D340" s="5" t="inlineStr">
         <is>
           <t>M-VK</t>
         </is>
       </c>
-      <c r="E276" s="5" t="inlineStr">
+      <c r="E340" s="5" t="inlineStr">
         <is>
           <t>M-VK-018</t>
         </is>
       </c>
-      <c r="F276" s="6" t="inlineStr">
+      <c r="F340" s="6" t="inlineStr">
         <is>
           <t>Ohumusování tl 100 mm + osetí trávou parkové směsi — rekultivace zbytkových ploch okolo haly</t>
         </is>
       </c>
-      <c r="G276" s="4" t="inlineStr">
+      <c r="G340" s="4" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="H276" s="4" t="n">
+      <c r="H340" s="4" t="n">
         <v>500</v>
       </c>
-      <c r="I276" s="6" t="inlineStr">
+      <c r="I340" s="6" t="inlineStr">
         <is>
           <t>500 m²  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
         </is>
       </c>
-      <c r="J276" s="6" t="inlineStr"/>
+      <c r="J340" s="6" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="101">
+  <mergeCells count="104">
+    <mergeCell ref="A307:J307"/>
     <mergeCell ref="A181:J181"/>
     <mergeCell ref="A184:J184"/>
     <mergeCell ref="A156:J156"/>
@@ -8064,6 +10439,7 @@
     <mergeCell ref="A220:J220"/>
     <mergeCell ref="A34:J34"/>
     <mergeCell ref="A83:J83"/>
+    <mergeCell ref="A270:J270"/>
     <mergeCell ref="A222:J222"/>
     <mergeCell ref="A49:J49"/>
     <mergeCell ref="A138:J138"/>
@@ -8071,10 +10447,10 @@
     <mergeCell ref="A36:J36"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="A119:J119"/>
-    <mergeCell ref="A256:J256"/>
     <mergeCell ref="A3:J3"/>
     <mergeCell ref="A95:J95"/>
-    <mergeCell ref="A248:J248"/>
+    <mergeCell ref="A331:J331"/>
+    <mergeCell ref="A303:J303"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A159:J159"/>
     <mergeCell ref="A29:J29"/>
@@ -8083,26 +10459,24 @@
     <mergeCell ref="A121:J121"/>
     <mergeCell ref="A202:J202"/>
     <mergeCell ref="A58:J58"/>
+    <mergeCell ref="A329:J329"/>
     <mergeCell ref="A186:J186"/>
     <mergeCell ref="A24:J24"/>
     <mergeCell ref="A201:J201"/>
-    <mergeCell ref="A275:J275"/>
-    <mergeCell ref="A250:J250"/>
     <mergeCell ref="A197:J197"/>
     <mergeCell ref="A110:J110"/>
     <mergeCell ref="A228:J228"/>
     <mergeCell ref="A124:J124"/>
     <mergeCell ref="A237:J237"/>
+    <mergeCell ref="A305:J305"/>
     <mergeCell ref="A16:J16"/>
     <mergeCell ref="A243:J243"/>
-    <mergeCell ref="A252:J252"/>
     <mergeCell ref="A223:J223"/>
     <mergeCell ref="A204:J204"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A42:J42"/>
     <mergeCell ref="A213:J213"/>
     <mergeCell ref="A151:J151"/>
-    <mergeCell ref="A254:J254"/>
     <mergeCell ref="A22:J22"/>
     <mergeCell ref="A135:J135"/>
     <mergeCell ref="A206:J206"/>
@@ -8110,6 +10484,7 @@
     <mergeCell ref="A122:J122"/>
     <mergeCell ref="A190:J190"/>
     <mergeCell ref="A72:J72"/>
+    <mergeCell ref="A318:J318"/>
     <mergeCell ref="A112:J112"/>
     <mergeCell ref="A176:J176"/>
     <mergeCell ref="A114:J114"/>
@@ -8122,8 +10497,8 @@
     <mergeCell ref="A162:J162"/>
     <mergeCell ref="A227:J227"/>
     <mergeCell ref="A164:J164"/>
+    <mergeCell ref="A335:J335"/>
     <mergeCell ref="A145:J145"/>
-    <mergeCell ref="A267:J267"/>
     <mergeCell ref="A242:J242"/>
     <mergeCell ref="A195:J195"/>
     <mergeCell ref="A76:J76"/>
@@ -8134,6 +10509,7 @@
     <mergeCell ref="A188:J188"/>
     <mergeCell ref="A126:J126"/>
     <mergeCell ref="A100:J100"/>
+    <mergeCell ref="A259:J259"/>
     <mergeCell ref="A140:J140"/>
     <mergeCell ref="A240:J240"/>
     <mergeCell ref="A10:J10"/>
@@ -8141,16 +10517,17 @@
     <mergeCell ref="A68:J68"/>
     <mergeCell ref="A102:J102"/>
     <mergeCell ref="A39:J39"/>
+    <mergeCell ref="A337:J337"/>
     <mergeCell ref="A232:J232"/>
     <mergeCell ref="A142:J142"/>
     <mergeCell ref="A216:J216"/>
-    <mergeCell ref="A271:J271"/>
+    <mergeCell ref="A287:J287"/>
+    <mergeCell ref="A339:J339"/>
     <mergeCell ref="A65:J65"/>
     <mergeCell ref="A218:J218"/>
     <mergeCell ref="A193:J193"/>
     <mergeCell ref="A80:J80"/>
     <mergeCell ref="A46:J46"/>
-    <mergeCell ref="A273:J273"/>
     <mergeCell ref="A89:J89"/>
     <mergeCell ref="A57:J57"/>
     <mergeCell ref="A235:J235"/>

--- a/test-data/hk212_hala/outputs/sequential_list/hk212_sequential_list.xlsx
+++ b/test-data/hk212_hala/outputs/sequential_list/hk212_sequential_list.xlsx
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J340"/>
+  <dimension ref="A1:J349"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -10295,7 +10295,7 @@
     <row r="335">
       <c r="A335" s="3" t="inlineStr">
         <is>
-          <t>→ Liniový žlab pojízdný B125 — SZ + JZ fasáda (40 m)</t>
+          <t>→ Liniový žlab SZ + JZ fasáda 46.5 m — complete (výkop → žlab polymerbeton + osazení → lože + obetonování → rošt D400 + osazení mříže → vpusti DN150 + čela; real ÚRS codes, pending ABMV_35/36)</t>
         </is>
       </c>
     </row>
@@ -10314,39 +10314,77 @@
       </c>
       <c r="E336" s="5" t="inlineStr">
         <is>
-          <t>M-VK-012</t>
+          <t>M-VK-040</t>
         </is>
       </c>
       <c r="F336" s="6" t="inlineStr">
         <is>
-          <t>Liniový žlab POJÍZDNÝ tř. zatížení B125 — odvodnění zpevněných ploch parkoviště + manipulace, vč. mřížky</t>
+          <t>Výkop rýhy pro liniový žlab š 300 mm, hl 350 mm (SZ + JZ fasáda)</t>
         </is>
       </c>
       <c r="G336" s="4" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="H336" s="4" t="n">
-        <v>40</v>
+        <v>4.9</v>
       </c>
       <c r="I336" s="6" t="inlineStr">
         <is>
-          <t>40 m  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
-        </is>
-      </c>
-      <c r="J336" s="6" t="inlineStr"/>
+          <t>46.5 × 0.30 × 0.35 = 4.9 m³  [TZ:ARS D.1.1, user_measurement:2026-05-27, customer_reminder:SOLAR DISPOREC 2026-05-27]</t>
+        </is>
+      </c>
+      <c r="J336" s="6" t="inlineStr">
+        <is>
+          <t>ABMV:ABMV_35</t>
+        </is>
+      </c>
     </row>
     <row r="337">
-      <c r="A337" s="3" t="inlineStr">
-        <is>
-          <t>→ Vyspádování okolního terénu k odvodnění</t>
+      <c r="A337" s="10" t="n">
+        <v>234</v>
+      </c>
+      <c r="B337" s="11" t="inlineStr"/>
+      <c r="C337" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D337" s="11" t="inlineStr">
+        <is>
+          <t>M-VK</t>
+        </is>
+      </c>
+      <c r="E337" s="11" t="inlineStr">
+        <is>
+          <t>M-VK-041</t>
+        </is>
+      </c>
+      <c r="F337" s="12" t="inlineStr">
+        <is>
+          <t>Odvoz vykopané zeminy z rýhy žlabu na skládku</t>
+        </is>
+      </c>
+      <c r="G337" s="10" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="H337" s="10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I337" s="12">
+        <f> 4.9 m³  [TZ:ARS D.1.1, user_measurement:2026-05-27, customer_reminder:SOLAR DISPOREC 2026-05-27]</f>
+        <v/>
+      </c>
+      <c r="J337" s="12" t="inlineStr">
+        <is>
+          <t>ABMV:ABMV_35</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="4" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B338" s="5" t="inlineStr"/>
       <c r="C338" s="4" t="n">
@@ -10359,39 +10397,78 @@
       </c>
       <c r="E338" s="5" t="inlineStr">
         <is>
-          <t>M-VK-019</t>
+          <t>M-VK-042</t>
         </is>
       </c>
       <c r="F338" s="6" t="inlineStr">
         <is>
-          <t>Vyspádování okolního terénu k odvodňovacím prvkům (žlabům, retenční nádrži) — hutněná zemina, finální úprava</t>
+          <t>Žlab odvodňovací polymerbeton spádový š 130 mm (materiál, kaskáda spádu 0,5 %)</t>
         </is>
       </c>
       <c r="G338" s="4" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m</t>
         </is>
       </c>
       <c r="H338" s="4" t="n">
-        <v>300</v>
+        <v>46.5</v>
       </c>
       <c r="I338" s="6" t="inlineStr">
         <is>
-          <t>300 m²  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
-        </is>
-      </c>
-      <c r="J338" s="6" t="inlineStr"/>
+          <t>46.5 m  [TZ:ARS D.1.1, user_measurement:2026-05-27, customer_reminder:SOLAR DISPOREC 2026-05-27]</t>
+        </is>
+      </c>
+      <c r="J338" s="6" t="inlineStr">
+        <is>
+          <t>ABMV:ABMV_35</t>
+        </is>
+      </c>
     </row>
     <row r="339">
-      <c r="A339" s="3" t="inlineStr">
-        <is>
-          <t>→ Ohumusování + osetí travou zbytkových ploch</t>
+      <c r="A339" s="10" t="n">
+        <v>236</v>
+      </c>
+      <c r="B339" s="11" t="inlineStr"/>
+      <c r="C339" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D339" s="11" t="inlineStr">
+        <is>
+          <t>M-VK</t>
+        </is>
+      </c>
+      <c r="E339" s="11" t="inlineStr">
+        <is>
+          <t>M-VK-043</t>
+        </is>
+      </c>
+      <c r="F339" s="12" t="inlineStr">
+        <is>
+          <t>Osazení odvodňovacího polymerbetonového žlabu s krycím roštem š do 210 mm</t>
+        </is>
+      </c>
+      <c r="G339" s="10" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="H339" s="10" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="I339" s="12" t="inlineStr">
+        <is>
+          <t>46.5 m  [TZ:ARS D.1.1, user_measurement:2026-05-27, customer_reminder:SOLAR DISPOREC 2026-05-27]</t>
+        </is>
+      </c>
+      <c r="J339" s="12" t="inlineStr">
+        <is>
+          <t>ABMV:ABMV_35,ABMV_36</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="4" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B340" s="5" t="inlineStr"/>
       <c r="C340" s="4" t="n">
@@ -10404,28 +10481,332 @@
       </c>
       <c r="E340" s="5" t="inlineStr">
         <is>
+          <t>M-VK-046</t>
+        </is>
+      </c>
+      <c r="F340" s="6" t="inlineStr">
+        <is>
+          <t>Betonové lože C25/30 pod žlab min 150 mm ("podklad" per customer)</t>
+        </is>
+      </c>
+      <c r="G340" s="4" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="H340" s="4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="I340" s="6" t="inlineStr">
+        <is>
+          <t>46.5 × 0.30 × 0.15 = 2.1 m³  [TZ:ARS D.1.1, user_measurement:2026-05-27, customer_reminder:SOLAR DISPOREC 2026-05-27]</t>
+        </is>
+      </c>
+      <c r="J340" s="6" t="inlineStr">
+        <is>
+          <t>ABMV:ABMV_35</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="10" t="n">
+        <v>238</v>
+      </c>
+      <c r="B341" s="11" t="inlineStr"/>
+      <c r="C341" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D341" s="11" t="inlineStr">
+        <is>
+          <t>M-VK</t>
+        </is>
+      </c>
+      <c r="E341" s="11" t="inlineStr">
+        <is>
+          <t>M-VK-047</t>
+        </is>
+      </c>
+      <c r="F341" s="12" t="inlineStr">
+        <is>
+          <t>Obetonování žlabu C25/30 po vrchní hranu ("zapravení" boky per customer)</t>
+        </is>
+      </c>
+      <c r="G341" s="10" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="H341" s="10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I341" s="12" t="inlineStr">
+        <is>
+          <t>2 × (0.085 × 0.20) × 46.5 ≈ 1.7 m³  [TZ:ARS D.1.1, user_measurement:2026-05-27, customer_reminder:SOLAR DISPOREC 2026-05-27]</t>
+        </is>
+      </c>
+      <c r="J341" s="12" t="inlineStr">
+        <is>
+          <t>ABMV:ABMV_35</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="4" t="n">
+        <v>239</v>
+      </c>
+      <c r="B342" s="5" t="inlineStr"/>
+      <c r="C342" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D342" s="5" t="inlineStr">
+        <is>
+          <t>M-VK</t>
+        </is>
+      </c>
+      <c r="E342" s="5" t="inlineStr">
+        <is>
+          <t>M-VK-044</t>
+        </is>
+      </c>
+      <c r="F342" s="6" t="inlineStr">
+        <is>
+          <t>Rošt / mříž litinová D400 600/40T (materiál, pojízdný — nákladní doprava)</t>
+        </is>
+      </c>
+      <c r="G342" s="4" t="inlineStr">
+        <is>
+          <t>kus</t>
+        </is>
+      </c>
+      <c r="H342" s="4" t="n">
+        <v>47</v>
+      </c>
+      <c r="I342" s="6" t="inlineStr">
+        <is>
+          <t>46.5 / 1.0 ≈ 47 ks  [TZ:ARS D.1.1, user_measurement:2026-05-27, customer_reminder:SOLAR DISPOREC 2026-05-27]</t>
+        </is>
+      </c>
+      <c r="J342" s="6" t="inlineStr">
+        <is>
+          <t>ABMV:ABMV_35</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="10" t="n">
+        <v>240</v>
+      </c>
+      <c r="B343" s="11" t="inlineStr"/>
+      <c r="C343" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D343" s="11" t="inlineStr">
+        <is>
+          <t>M-VK</t>
+        </is>
+      </c>
+      <c r="E343" s="11" t="inlineStr">
+        <is>
+          <t>M-VK-045</t>
+        </is>
+      </c>
+      <c r="F343" s="12" t="inlineStr">
+        <is>
+          <t>Osazování kovových mříží litinových D400 v rámu (montáž roštu)</t>
+        </is>
+      </c>
+      <c r="G343" s="10" t="inlineStr">
+        <is>
+          <t>kus</t>
+        </is>
+      </c>
+      <c r="H343" s="10" t="n">
+        <v>47</v>
+      </c>
+      <c r="I343" s="12" t="inlineStr">
+        <is>
+          <t>47 ks  [TZ:ARS D.1.1, user_measurement:2026-05-27, customer_reminder:SOLAR DISPOREC 2026-05-27]</t>
+        </is>
+      </c>
+      <c r="J343" s="12" t="inlineStr">
+        <is>
+          <t>ABMV:ABMV_35,ABMV_36</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="4" t="n">
+        <v>241</v>
+      </c>
+      <c r="B344" s="5" t="inlineStr"/>
+      <c r="C344" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D344" s="5" t="inlineStr">
+        <is>
+          <t>M-VK</t>
+        </is>
+      </c>
+      <c r="E344" s="5" t="inlineStr">
+        <is>
+          <t>M-VK-048</t>
+        </is>
+      </c>
+      <c r="F344" s="6" t="inlineStr">
+        <is>
+          <t>Vpust ACO Drain dolní díl, odtok DN150 — napojení na dešťovou kanalizaci (SZ + JZ větev)</t>
+        </is>
+      </c>
+      <c r="G344" s="4" t="inlineStr">
+        <is>
+          <t>kus</t>
+        </is>
+      </c>
+      <c r="H344" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I344" s="6" t="inlineStr">
+        <is>
+          <t>1 + 1 = 2 ks  [TZ:ARS D.1.1, user_measurement:2026-05-27, customer_reminder:SOLAR DISPOREC 2026-05-27]</t>
+        </is>
+      </c>
+      <c r="J344" s="6" t="inlineStr">
+        <is>
+          <t>ABMV:ABMV_35</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="10" t="n">
+        <v>242</v>
+      </c>
+      <c r="B345" s="11" t="inlineStr"/>
+      <c r="C345" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D345" s="11" t="inlineStr">
+        <is>
+          <t>M-VK</t>
+        </is>
+      </c>
+      <c r="E345" s="11" t="inlineStr">
+        <is>
+          <t>M-VK-049</t>
+        </is>
+      </c>
+      <c r="F345" s="12" t="inlineStr">
+        <is>
+          <t>Čela žlabu kombi (začátek/konec) — 2 čela × 2 větve</t>
+        </is>
+      </c>
+      <c r="G345" s="10" t="inlineStr">
+        <is>
+          <t>kus</t>
+        </is>
+      </c>
+      <c r="H345" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="I345" s="12" t="inlineStr">
+        <is>
+          <t>2 × 2 = 4 ks  [TZ:ARS D.1.1, user_measurement:2026-05-27, customer_reminder:SOLAR DISPOREC 2026-05-27]</t>
+        </is>
+      </c>
+      <c r="J345" s="12" t="inlineStr">
+        <is>
+          <t>ABMV:ABMV_35</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="3" t="inlineStr">
+        <is>
+          <t>→ Vyspádování okolního terénu k odvodnění</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="4" t="n">
+        <v>243</v>
+      </c>
+      <c r="B347" s="5" t="inlineStr"/>
+      <c r="C347" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D347" s="5" t="inlineStr">
+        <is>
+          <t>M-VK</t>
+        </is>
+      </c>
+      <c r="E347" s="5" t="inlineStr">
+        <is>
+          <t>M-VK-019</t>
+        </is>
+      </c>
+      <c r="F347" s="6" t="inlineStr">
+        <is>
+          <t>Vyspádování okolního terénu k odvodňovacím prvkům (žlabům, retenční nádrži) — hutněná zemina, finální úprava</t>
+        </is>
+      </c>
+      <c r="G347" s="4" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="H347" s="4" t="n">
+        <v>300</v>
+      </c>
+      <c r="I347" s="6" t="inlineStr">
+        <is>
+          <t>300 m²  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
+        </is>
+      </c>
+      <c r="J347" s="6" t="inlineStr"/>
+    </row>
+    <row r="348">
+      <c r="A348" s="3" t="inlineStr">
+        <is>
+          <t>→ Ohumusování + osetí travou zbytkových ploch</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="4" t="n">
+        <v>244</v>
+      </c>
+      <c r="B349" s="5" t="inlineStr"/>
+      <c r="C349" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D349" s="5" t="inlineStr">
+        <is>
+          <t>M-VK</t>
+        </is>
+      </c>
+      <c r="E349" s="5" t="inlineStr">
+        <is>
           <t>M-VK-018</t>
         </is>
       </c>
-      <c r="F340" s="6" t="inlineStr">
+      <c r="F349" s="6" t="inlineStr">
         <is>
           <t>Ohumusování tl 100 mm + osetí trávou parkové směsi — rekultivace zbytkových ploch okolo haly</t>
         </is>
       </c>
-      <c r="G340" s="4" t="inlineStr">
+      <c r="G349" s="4" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="H340" s="4" t="n">
+      <c r="H349" s="4" t="n">
         <v>500</v>
       </c>
-      <c r="I340" s="6" t="inlineStr">
+      <c r="I349" s="6" t="inlineStr">
         <is>
           <t>500 m²  [document:C.3 KOO situace, document:A101 půdorys 1NP, document:A103 řez A-B]</t>
         </is>
       </c>
-      <c r="J340" s="6" t="inlineStr"/>
+      <c r="J349" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="104">
@@ -10486,6 +10867,7 @@
     <mergeCell ref="A72:J72"/>
     <mergeCell ref="A318:J318"/>
     <mergeCell ref="A112:J112"/>
+    <mergeCell ref="A348:J348"/>
     <mergeCell ref="A176:J176"/>
     <mergeCell ref="A114:J114"/>
     <mergeCell ref="A182:J182"/>
@@ -10495,6 +10877,7 @@
     <mergeCell ref="A70:J70"/>
     <mergeCell ref="A153:J153"/>
     <mergeCell ref="A162:J162"/>
+    <mergeCell ref="A346:J346"/>
     <mergeCell ref="A227:J227"/>
     <mergeCell ref="A164:J164"/>
     <mergeCell ref="A335:J335"/>
@@ -10517,12 +10900,10 @@
     <mergeCell ref="A68:J68"/>
     <mergeCell ref="A102:J102"/>
     <mergeCell ref="A39:J39"/>
-    <mergeCell ref="A337:J337"/>
     <mergeCell ref="A232:J232"/>
     <mergeCell ref="A142:J142"/>
     <mergeCell ref="A216:J216"/>
     <mergeCell ref="A287:J287"/>
-    <mergeCell ref="A339:J339"/>
     <mergeCell ref="A65:J65"/>
     <mergeCell ref="A218:J218"/>
     <mergeCell ref="A193:J193"/>
